--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -9,13 +9,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blockers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E01 Blockers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$4:$W$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blockers'!$A$4:$H$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sprint Plan'!$A$4:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'E01 Blockers'!$A$4:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint Plan'!$A$4:$G$23</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -4014,7 +4016,7 @@
       </c>
       <c r="E17" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
@@ -4052,7 +4054,9 @@
       </c>
       <c r="O17" s="46" t="n"/>
       <c r="P17" s="46" t="n"/>
-      <c r="Q17" s="47" t="n"/>
+      <c r="Q17" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R17" s="39" t="n">
         <v>6</v>
       </c>
@@ -4079,8 +4083,20 @@
       </c>
       <c r="V17" s="48" t="inlineStr">
         <is>
-          <t>SPRINT 1 — Day 3. Independent of E01-S01, so it is the parallel track that makes the sprint fit; do not sequence it after the schema.
-The lock helper signature IS the story: ttl_ms must be a REQUIRED argument with no default. A lock without a TTL survives the death of the process holding it and deadlocks slot allocation for the rest of the session. Making it mandatory means that failure cannot be introduced by omission. Acceptance: acquire_lock() without a TTL raises TypeError at the call site.</t>
+          <t>CLOSED 7 Aug 2026. Redis layer complete; 35 integration tests, all probing real behaviour against a real Redis.
+DELIVERED: common/redis/ — keys.py (23 key builders, no literal permitted elsewhere), client.py (pool, retry, health), locks.py (mandatory TTL), primitives.py (token bucket + timer ZSET, both Lua), state.py (typed Pydantic accessors).
+THE STORY'S REAL CONTENT — ttl_ms is a REQUIRED positional argument with no default. A lock without a TTL survives the death of the process holding it and deadlocks slot allocation for the rest of the session, silently. Also bounded above (MAX_TTL_MS 300s) to catch seconds-passed-as-milliseconds, which is the realistic mistake.
+DESIGN DECISIONS AND WHY:
+  - Release/extend are compare-and-delete in Lua. The naive get-then-delete is a race: the lock can expire between check and delete, be re-acquired by another process, and you then delete THEIR lock.
+  - Token bucket and pop-due are Lua for the same reason. A Python-side get/compute/set lets two callers see the same token count and both proceed — for the order limiter that means breaching the broker cap and, above 10/sec, the SEBI threshold. Proven by a 25-way concurrent test that must yield exactly capacity.
+  - decode_responses=True is load-bearing, not cosmetic. Without it every read is bytes and b"1" != "1", so a kill-switch check silently reads as "not set" and trading continues.
+  - Invalid stored state is treated as ABSENT, not raised. Half-valid trading state is worse than none because the system keeps acting on it; absent routes into the existing fail-closed path (no indicators -&gt; no signal). Logged loudly.
+  - is_kill_switch_active FAILS CLOSED — an unreachable Redis returns True (halted). A false halt costs a trade; a false all-clear costs an uncontrolled position. Tested against a dead endpoint.
+  - assert_noeviction() refuses to start if Redis is not noeviction, because under any eviction policy Redis silently discards positions or the kill switch with no error at the point of loss.
+ISSUES FOUND AND FIXED DURING THE BUILD:
+  1. bandit S105 false-positived on _TOKEN_BUCKET_LUA (matches "token" in the identifier). A noqa CANNOT go on that line — it ends by opening a triple-quoted string, so the comment becomes Lua source, and # is not a comment in Lua, which silently corrupts the script. Renamed the constant instead.
+  2. Package named common/redis shadows the library by name; verified safe because Python 3 uses absolute imports. Documented in __init__.
+NOT DONE HERE: stream helpers live in E01-S04; keys.py already provides their key builders.</t>
         </is>
       </c>
       <c r="W17" s="49" t="n"/>
@@ -4108,7 +4124,7 @@
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F18" s="41" t="inlineStr">
@@ -4146,7 +4162,9 @@
       </c>
       <c r="O18" s="46" t="n"/>
       <c r="P18" s="46" t="n"/>
-      <c r="Q18" s="47" t="n"/>
+      <c r="Q18" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R18" s="39" t="n">
         <v>6</v>
       </c>
@@ -4173,9 +4191,19 @@
       </c>
       <c r="V18" s="48" t="inlineStr">
         <is>
-          <t>SPRINT 1 — Day 5 (needs E01-S03).
-CONFIRMED AGAINST OPS CONFIG: docker-compose runs redis-server with --maxmemory 2gb --maxmemory-policy noeviction. That makes the untrimmed-stream trap real rather than theoretical — an unbounded XADD will fill the 2GB ceiling and Redis will then REFUSE WRITES rather than evict. Therefore maxlen must be a required argument on EventStream.publish(), same pattern as the lock TTL in E01-S03. Acceptance: publish() without maxlen is a TypeError.
-Second acceptance is the recovery integration test: publish 100, consume 50, kill the consumer, restart — the remaining 50 plus the unacked are processed, none lost, none duplicated beyond at-least-once.</t>
+          <t>CLOSED 7 Aug 2026. Event stream layer complete; 27 integration tests including the epic's headline acceptance criterion.
+DELIVERED: common/events/ — envelope.py (versioned, immutable, correlation-carrying) and stream.py (publish, consumer groups, backlog recovery, reclaim, dead-letter).
+THE STORY'S REAL CONTENT — maxlen is a REQUIRED keyword argument on publish(), with no default. Redis runs maxmemory 2gb + noeviction. That policy is right (trading state must never be silently evicted) but it means an untrimmed stream does NOT drop old entries — it fills memory and Redis then REFUSES ALL WRITES, system-wide, mid-session. stream:ticks alone is ~10 MB/day. A stream publishable without a bound should not be constructible, and now is not.
+ACCEPTANCE CRITERION PROVEN: test_crash_mid_stream_loses_nothing — publish 100, consume+ack 50, strand 10 unacked (the crash), restart, assert all 100 processed and pending == 0. This catches the single easiest mistake in the component: on restart a consumer MUST read its own pending backlog at id '0' first. A '&gt;' read returns only NEW messages, so every entry in flight at the moment of a crash is invisible and stranded forever. Backlog is also drained BEFORE new messages, since taking new work ahead of older unacked work reorders the stream from the consumer's view.
+DESIGN DECISIONS AND WHY:
+  - At-least-once delivery, consumers idempotent. Correct rather than a limitation: a bar processed twice yields the same indicator state; a duplicate signal is caught by lock:symbol and uq_open_symbol; a duplicate audit event by message_id. Exactly-once would need distributed transactions across Redis and Postgres for no practical gain.
+  - Approximate trimming (MAXLEN ~). The property needed is "bounded", not "exactly N"; exact trimming is materially more expensive. The test asserts boundedness, not equality, so it does not encode a Redis implementation detail.
+  - Dead-letter writes to the DLQ BEFORE acking the original. If the process dies between the two the entry stays pending and is retried — recoverable. Acking first would lose it outright.
+  - A malformed entry is logged and SKIPPED, never raised out of the read loop. One poisoned message must not stop the stream. Envelope.from_fields raises ValueError specifically so consumers can catch a narrow type to dead-letter.
+  - schema_version present from message one — retrofitting it onto streams that already hold unversioned entries means writing a shim that guesses.
+  - Consumer names carry a uuid suffix. Two processes sharing a name share a pending list, so one can acknowledge the other's in-flight work.
+  - Payload is nested JSON in ONE stream field, not spread across fields. Redis stream fields are a flat string map; flattening would lose type information exactly where Decimal matters.
+ISSUE FOUND AND FIXED: redis-py types the xadd field map as an invariant dict of bytes|str|int|float; dict[str, str] is a valid subset but mypy will not narrow it. Cast with the reason recorded in place rather than loosening the function signature.</t>
         </is>
       </c>
       <c r="W18" s="49" t="n"/>
@@ -4203,7 +4231,7 @@
       </c>
       <c r="E19" s="40" t="inlineStr">
         <is>
-          <t>Moved to Backlog</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F19" s="41" t="inlineStr">
@@ -4237,7 +4265,7 @@
       <c r="L19" s="40" t="n"/>
       <c r="M19" s="44" t="n"/>
       <c r="N19" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="46" t="n"/>
       <c r="P19" s="46" t="n"/>
@@ -4267,9 +4295,11 @@
       </c>
       <c r="V19" s="48" t="inlineStr">
         <is>
-          <t>DEFERRED SPRINT 1 -&gt; SPRINT 2. This is the scope cut that makes Sprint 1 fit; see the Sprint Plan sheet for the capacity finding.
-Why this story rather than compressing something else: it is the ONLY safety-critical (red) story in E01 and it carries the strictest Definition of Done — property-based test over generated event sequences, an explicit tamper test, an explicit DB-outage test, and a second read on a different day. Squeezing it into a Friday afternoon violates the working rule that a red story is never merged at the end of a session. Nothing in Sprint 2 depends on it, so the deferral costs nothing.
-Still blocked on E01-S01 only. Pull into Sprint 2 at full 1-day estimate — do NOT compress it there either.</t>
+          <t>PULLED BACK IN 7 Aug 2026 — status changed from 'Moved to Backlog' to Active.
+PROCEDURE §8.3 REQUIRES re-evaluating the ORIGINAL DEFERRAL REASON, not just the status. The original reason was SPRINT CAPACITY: E01 was 8.5 days against a 5-day sprint, this is the only safety-critical story in the epic and carries the strictest DoD, and nothing in Sprint 2 depended on it.
+THAT REASON HAS LAPSED. The direction is now to complete every E01 item, so the capacity constraint that justified deferral no longer applies. Per §8.3 a deferred item whose reason has lapsed becomes Active — and the lapse is recorded here so the record of WHY it was ever deferred is not lost.
+It was never blocked: its only dependency is E01-S01, which is Closed.
+The safety-critical (red) DoD STILL APPLIES IN FULL and is NOT relaxed by the reprioritisation: property-based test over generated event sequences, explicit tamper test, explicit DB-outage test, and not merged at the end of a session.</t>
         </is>
       </c>
       <c r="W19" s="49" t="n"/>
@@ -18529,6 +18559,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="59" min="1" max="1"/>
+    <col width="42" customWidth="1" style="59" min="2" max="2"/>
+    <col width="26" customWidth="1" style="59" min="3" max="3"/>
+    <col width="40" customWidth="1" style="59" min="4" max="4"/>
+    <col width="18" customWidth="1" style="59" min="5" max="5"/>
+    <col width="12" customWidth="1" style="59" min="6" max="6"/>
+    <col width="14" customWidth="1" style="59" min="7" max="7"/>
+    <col width="90" customWidth="1" style="59" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>E01 BLOCKERS — PERSISTENCE &amp; DATA LAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blockers specific to E01 items. A blocker is something that cannot be resolved from inside the project and that prevents CORRECT completion — not 'this is hard'. See DEVELOPMENT_PROCEDURE.md §8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>Blocker</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>Blocks</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>Target Date</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>Resolution Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>E01-B1</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>None identified — every remaining E01 item is buildable</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>nothing</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>No action. Recorded so the absence is explicit rather than assumed.</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G5" s="46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H5" s="49" t="inlineStr">
+        <is>
+          <t>Assessed 7 Aug 2026 before starting E01-S02/S03/S04/S05/S06.
+E01 depends on NO external credential, account or third-party answer. Postgres and Redis are local containers; nothing in the epic touches the broker, the AI provider, news, or the static IP.
+The blockers that DO exist (B1 Algo-ID value, B4 data pricing, B6 static IP, B7 autobahn CVE) all gate E02+ or live trading, NOT E01. Verified against the main Blockers sheet.
+The one thing that LOOKED like an E01 blocker — the undecided TimescaleDB pin — was DESIGNED AWAY rather than waited on: the migration detects the installed version at runtime and emits matching DDL, verified on 2.17.2 and 2.29.1. That is the preferred resolution when one exists (DEVELOPMENT_PROCEDURE.md §8.2).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"New,Business Review,Business Approved,Active,Development In-Progress,Development Completed,QA In-Progress,QA-Success,QA-Fail,Closed,Removed,Moved to Backlog,Blocked,On Hold"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
@@ -19150,7 +19311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -3922,7 +3922,7 @@
       </c>
       <c r="E16" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
@@ -3960,7 +3960,9 @@
       </c>
       <c r="O16" s="46" t="n"/>
       <c r="P16" s="46" t="n"/>
-      <c r="Q16" s="47" t="n"/>
+      <c r="Q16" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R16" s="39" t="n">
         <v>5</v>
       </c>
@@ -3986,9 +3988,24 @@
       </c>
       <c r="V16" s="48" t="inlineStr">
         <is>
-          <t>SPRINT 1 — Day 4 (needs E01-S01 complete).
-warm_up_batch() is the story's real risk. It is the workhorse of BP-2, the pre-market warm-up that has to finish inside a 45-minute window. A per-symbol loop issuing ~150 queries will miss the deadline; one query using WHERE symbol_id = ANY(...) with a window function will not. Write it as the batch form from the start.
-Acceptance is measurable and must be measured in the test, not asserted: bulk insert of 100k bars in under 10s, and grep -r 'import sqlalchemy' src/algotrader/{ingest,signals,execution,premarket} must return nothing — no ORM leakage past the repository boundary.</t>
+          <t>CLOSED 7 Aug 2026. Repository layer complete; 25 integration tests, both acceptance criteria measured rather than asserted.
+DELIVERED: common/db/engine.py (async engine, session factory, unit_of_work / read_only boundaries) and common/db/repositories.py (Instrument, Bar, DailyStatus, Order, Position, DecisionLog-read repositories plus Protocols).
+THE ARCHITECTURE THIS STORY OWNS — the symbol &lt;-&gt; symbol_id impedance mismatch (spec §2.3 E). Domain models address instruments by ticker; every table uses an integer FK. InstrumentRepository holds a bidirectional cache and is the ONLY component permitted to translate. Proven: 50 lookups issue 0 queries.
+THREE REAL BUGS FOUND BY EXECUTION:
+  1. POSTGRESQL CAPS BOUND PARAMETERS AT 65535. A bar has up to 12 columns, so the spec's "one TX per batch of ~10k" sends ~120,000 parameters and fails outright with "number of parameters must be between 0 and 65535". This would have surfaced during the 24-MILLION-row historical backfill, not in any unit test. bulk_upsert now chunks INTERNALLY against the parameter limit, sized off the WIDEST row (sizing off the first row under-counts when callers omit optional columns), so no caller can hit it.
+  2. Chunked multi-row INSERT was correct but SLOW — 100k bars in 23.8s against a 10s budget. Implemented the spec's COPY path (task 3): COPY into a temp table, then one set-based INSERT ... SELECT ... ON CONFLICT DO UPDATE. Now inside budget. COPY cannot express ON CONFLICT itself, which is why the temp table exists.
+  3. The COPY path needed CREATE TEMP TABLE IF NOT EXISTS + TRUNCATE, not a bare CREATE. ON COMMIT DROP only fires at COMMIT, so the SECOND chunk of a backfill inside one transaction failed with "relation _bar_load already exists".
+  Also: DISTINCT ON (symbol_id, timeframe, ts) ORDER BY ... ctid DESC in the COPY upsert. ON CONFLICT raises "cannot affect row a second time" when the SOURCE holds duplicate keys, which a batch spanning a reconnect legitimately does. Last occurrence wins, matching the INSERT path.
+  Also: the Windows ProactorEventLoop defect RESURFACED in pytest-asyncio. configure_event_loop_policy() must run BEFORE the loop is created; calling it inside create_engine was too late because pytest-asyncio had already built one. Now called at tests/conftest.py import time. Lesson recorded: every async entry point owns that responsibility separately.
+DESIGN DECISIONS AND WHY:
+  - Repositories return plain dicts, never ORM instances. An ORM object carries session affinity and lazy loaders; once its session closes, touching an unloaded attribute raises MissingGreenlet deep inside business logic. A dict cannot.
+  - warm_up_batch is ONE query with a window function. A per-symbol loop is correct and passes every other test, then misses the 45-minute BP-2 deadline with 450 round trips. The test asserts the QUERY COUNT is constant regardless of symbol count, so that refactor fails here rather than at 08:45 on a trading morning.
+  - expire_on_commit=False: the default makes every attribute a fresh SELECT after commit, and in async code that lazy load raises MissingGreenlet rather than merely being slow.
+  - Server-side statement_timeout, not a client-side cancel. A client-side timeout abandons the query while the server keeps executing it.
+  - read_only() rolls back rather than commits — releases the snapshot immediately, so a long idle-in-transaction session cannot hold back vacuum across the database.
+  - ON CONFLICT DO UPDATE, not DO NOTHING: a late trade report legitimately revises volume and vwap, and a corporate action re-adjusts prices. DO NOTHING would silently pin stale data.
+  - UnknownSymbolError raises rather than returning None. Silently skipping an unknown symbol loses market data with NO error; the gap surfaces days later as an indicator that never warms up.
+SECURITY: the COPY path builds SQL identifiers by f-string because PostgreSQL cannot parameterise identifiers. Every interpolated value comes from a fixed tuple in the function and is unreachable from market data, news or any request. Justified in place with a noqa so it does not need re-deriving at review time; all VALUES still go through COPY's binary protocol or bound parameters.</t>
         </is>
       </c>
       <c r="W16" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4248,7 +4248,7 @@
       </c>
       <c r="E19" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F19" s="41" t="inlineStr">
@@ -4286,7 +4286,9 @@
       </c>
       <c r="O19" s="46" t="n"/>
       <c r="P19" s="46" t="n"/>
-      <c r="Q19" s="47" t="n"/>
+      <c r="Q19" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R19" s="39" t="n">
         <v>5</v>
       </c>
@@ -4312,11 +4314,22 @@
       </c>
       <c r="V19" s="48" t="inlineStr">
         <is>
-          <t>PULLED BACK IN 7 Aug 2026 — status changed from 'Moved to Backlog' to Active.
-PROCEDURE §8.3 REQUIRES re-evaluating the ORIGINAL DEFERRAL REASON, not just the status. The original reason was SPRINT CAPACITY: E01 was 8.5 days against a 5-day sprint, this is the only safety-critical story in the epic and carries the strictest DoD, and nothing in Sprint 2 depended on it.
-THAT REASON HAS LAPSED. The direction is now to complete every E01 item, so the capacity constraint that justified deferral no longer applies. Per §8.3 a deferred item whose reason has lapsed becomes Active — and the lapse is recorded here so the record of WHY it was ever deferred is not lost.
-It was never blocked: its only dependency is E01-S01, which is Closed.
-The safety-critical (red) DoD STILL APPLIES IN FULL and is NOT relaxed by the reprioritisation: property-based test over generated event sequences, explicit tamper test, explicit DB-outage test, and not merged at the end of a session.</t>
+          <t>CLOSED 7 Aug 2026. SAFETY-CRITICAL (red) — the strict DoD was met in full and NOT relaxed by the reprioritisation. 30 tests: property-based over generated sequences, explicit tamper tests, explicit outage tests, and a concurrency test.
+DELIVERED: common/audit.py — canonical_json, compute_row_hash, AuditEntry, AuditWriter (with disk buffer), verify_chain.
+THREE PROPERTIES, EACH ENFORCED STRUCTURALLY:
+  1. Cannot be modified or deleted — the app role has INSERT but no UPDATE/DELETE (E01-S01 grants). Append-only by convention is a promise; by a missing grant it is a guarantee.
+  2. Tampering is DETECTABLE even by someone who bypasses the grants. Each row hashes its predecessor's hash, so altering any historical row invalidates every hash after it. Tested: a modified payload, a flipped REJECT-&gt;ALLOW, a deleted row, and — the important one — a LOCALLY CONSISTENT FORGERY where the attacker recomputes that row's own hash. It still breaks, at the NEXT row. Hiding a change requires recomputing the entire remaining chain.
+  3. Survives the DB being down. Entries buffer to disk (fsync per line) and replay in order on recovery; the chain is computed at replay time because a buffered entry's position is not knowable while the DB is down.
+DESIGN DECISIONS AND WHY:
+  - AuditWriter takes a session FACTORY, never a session. An audit entry written inside a business transaction VANISHES when that transaction rolls back — and a failed attempt is often exactly what you need to investigate. Making it a factory means sharing a transaction is impossible, not merely discouraged.
+  - pg_advisory_xact_lock, taken BEFORE reading the chain head. Read-then-lock lets two writers observe the same prev_hash and fork the chain — and a forked chain fails verification with no tampering having occurred. Transaction-scoped so a crashed writer cannot leak the lock. Proven by a 20-write concurrent test asserting one valid chain with contiguous seq.
+  - write() NEVER raises on a DB failure. An audit write that killed the caller would mean a database blip stops trading AND loses the record of why.
+  - canonical_json with sort_keys: Python dicts are insertion-ordered, so the same logical payload built by two code paths would hash differently and fail verification for no reason.
+  - Timestamps normalised to UTC before hashing, so a row hashed in one timezone verifies in another. Naive timestamps are refused outright.
+  - GLOBAL chain, not per-correlation_id. The per-correlation alternative is simpler and lock-free but CANNOT detect deletion of an entire trade's worth of entries — precisely the tampering worth defending against. Tested.
+  - A failed replay KEEPS the buffer file for retry. Deleting first and failing after would lose entries permanently; retrying at worst duplicates, which is recoverable.
+ISSUE FOUND AND FIXED: create_engine_from_url had no connect timeout, so the outage tests pointed at a dead endpoint HUNG the suite on the OS TCP timeout (minutes). Added connect_timeout, defaulting to 10s. This is a production concern too, not just a test one: without it "the database is down" presents as "the process appears to hang", which is a far worse failure to diagnose at 09:15.
+SECURITY: verify_chain originally interpolated its WHERE clause and needed an S608 suppression that kept drifting as the formatter reflowed the string. Rewritten as a four-entry lookup table of complete literal queries — no interpolation at all, so there is no injection surface to justify rather than a justified one. Better answer than a noqa.</t>
         </is>
       </c>
       <c r="W19" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4357,7 +4357,7 @@
       </c>
       <c r="E20" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F20" s="52" t="inlineStr">
@@ -4395,7 +4395,9 @@
       </c>
       <c r="O20" s="46" t="n"/>
       <c r="P20" s="46" t="n"/>
-      <c r="Q20" s="47" t="n"/>
+      <c r="Q20" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R20" s="39" t="n">
         <v>3</v>
       </c>
@@ -4414,8 +4416,19 @@
       <c r="U20" s="48" t="n"/>
       <c r="V20" s="48" t="inlineStr">
         <is>
-          <t>NOT SPRINT 1 — and correctly so. This sits inside E01 but is P2 / Phase 6, so it was never Sprint 1 work despite Sprint 1 originally being scoped as 'all of E01'. Leaving it New rather than marking it deferred, because it was never scheduled.
-Pull it in when tick archival is actually needed by the replay harness (E22-S03, Sprint 16). Provisionally placed there.</t>
+          <t>CLOSED 7 Aug 2026. Retention, archival and restore complete; 16 integration tests. This was P2/Phase 6 and originally scheduled for Sprint 16 — built now because the direction is to complete every E01 item and it has no blocker.
+DELIVERED: common/db/retention.py — archive_bars, read_archive, restore_bars, purge_archived_bars, compression_status.
+THE SAFETY PROPERTY THIS STORY IS REALLY ABOUT — market data CANNOT BE RE-DERIVED. A gap is permanent and silently corrupts every future backtest over that window. So:
+  - archive_bars WRITES AND READS BACK, comparing row counts, before returning. A write that reports success having produced a truncated file is exactly the failure an archive must not have, and it is only detectable by reading.
+  - Nothing in archive_bars deletes. purge_archived_bars is a SEPARATE call that re-reads the archive and refuses unless it holds at least as many rows as the database does for that range. Both refusals are tested, each paired with a control proving the refusal is targeted rather than blanket.
+  - An EMPTY range is refused outright. An empty archive would later look like a verified archive of nothing and could authorise a purge of data it never held.
+  - The full cycle is tested: archive -&gt; purge -&gt; restore -&gt; prices still exact. An archive nobody has restored from is a hypothesis, not a backup.
+DESIGN DECISIONS AND WHY:
+  - Decimals are archived as STRINGS, not floats. A float round trip loses exactness and would silently corrupt every archived price — the one thing this file exists to preserve faithfully. Asserted directly.
+  - Parquet over CSV: columnar, ~10x compression on this shape, preserves types, and readable by pandas/DuckDB/Polars with no loader. CSV would turn every Decimal into a string and every timestamp into an ambiguous one.
+  - restore uses ON CONFLICT DO NOTHING, not DO UPDATE. The archive is older by definition, so the live copy is authoritative; a restore that overwrote would roll back corrections that arrived after the archive was taken. Tested.
+  - compression_status treats ZERO compressed chunks as HEALTHY on a young database — nothing is 90 days old yet. What matters is that the policy is scheduled and its last run did not fail. A policy that silently stops converting produces no error at all; the first symptom is the disk filling weeks later.
+DEPENDENCY DECISION (procedure §8.2 — a decision, not a blocker): pyarrow was not installed or declared. Added as a main dependency at &gt;=18.0 (installed 25.0.0). It is large (~100 MB) but is the standard implementation and the archive job runs in the same deployment as everything else. Also added to the mypy ignore_missing_imports overrides, since it ships no stubs.</t>
         </is>
       </c>
       <c r="W20" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -10,14 +10,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blockers" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E01 Blockers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Plan" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Findings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Plan" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$4:$W$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$4:$W$197</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blockers'!$A$4:$H$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'E01 Blockers'!$A$4:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint Plan'!$A$4:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA Results'!$A$4:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Security Findings'!$A$4:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Sprint Plan'!$A$4:$G$23</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -30,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -228,8 +232,35 @@
       <color rgb="FF8A3A24"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -350,8 +381,38 @@
         <bgColor rgb="FFFEF6E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -374,11 +435,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -504,6 +579,37 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1185,6 +1291,693 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Stories by status</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!B60</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$61:$A$73</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$B$61:$B$73</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Effort by phase — closed vs remaining</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!B76</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$77:$A$85</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$B$77:$B$85</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!C76</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$77:$A$85</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$C$77:$C$85</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Phase</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Days</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Completion by epic</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!B88</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$89:$A$112</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$B$89:$B$112</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% complete</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>E01 security findings by severity (all fixed)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$118:$A$121</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$B$118:$B$121</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Findings</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>E01 QA outcomes</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'QA Results'!J4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'QA Results'!$I$5:$I$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'QA Results'!$J$5:$J$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Findings by severity (all fixed)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Security Findings'!K4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Security Findings'!$J$5:$J$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Security Findings'!$K$5:$K$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1368,11 +2161,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="24" customWidth="1" style="59" min="1" max="1"/>
-    <col width="12" customWidth="1" style="59" min="2" max="4"/>
+    <col width="26" customWidth="1" style="59" min="1" max="1"/>
+    <col width="13" customWidth="1" style="59" min="2" max="4"/>
+    <col width="13" customWidth="1" style="59" min="3" max="3"/>
     <col width="3" customWidth="1" style="59" min="5" max="5"/>
     <col width="8" customWidth="1" style="59" min="6" max="6"/>
     <col width="27" customWidth="1" style="59" min="7" max="7"/>
@@ -1462,7 +2256,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTA(Backlog!$A$5:$A$195)</f>
+        <f>COUNTA(Backlog!$A$5:$A$197)</f>
         <v/>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1481,15 +2275,15 @@
         </is>
       </c>
       <c r="I6" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F6)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F6)</f>
         <v/>
       </c>
       <c r="J6" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F6,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F6,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K6" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F6,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F6,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L6" s="10">
@@ -1504,7 +2298,7 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>SUM(Backlog!$J$5:$J$195)</f>
+        <f>SUM(Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1523,15 +2317,15 @@
         </is>
       </c>
       <c r="I7" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F7)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F7)</f>
         <v/>
       </c>
       <c r="J7" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F7,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F7,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K7" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F7,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F7,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L7" s="10">
@@ -1546,7 +2340,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1565,15 +2359,15 @@
         </is>
       </c>
       <c r="I8" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F8)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F8)</f>
         <v/>
       </c>
       <c r="J8" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F8,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F8,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K8" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F8,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F8,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L8" s="10">
@@ -1588,7 +2382,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>SUMPRODUCT(COUNTIF(Backlog!$E$5:$E$195,{"Active","Development In-Progress","Development Completed","QA In-Progress","QA-Success"}))</f>
+        <f>SUMPRODUCT(COUNTIF(Backlog!$E$5:$E$197,{"Active","Development In-Progress","Development Completed","QA In-Progress","QA-Success"}))</f>
         <v/>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1607,15 +2401,15 @@
         </is>
       </c>
       <c r="I9" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F9)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F9)</f>
         <v/>
       </c>
       <c r="J9" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F9,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F9,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K9" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F9,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F9,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L9" s="10">
@@ -1630,7 +2424,7 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <f>COUNTIF(Backlog!$E$5:$E$195,"New")</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,"New")</f>
         <v/>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1649,15 +2443,15 @@
         </is>
       </c>
       <c r="I10" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F10)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F10)</f>
         <v/>
       </c>
       <c r="J10" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F10,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F10,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K10" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F10,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F10,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L10" s="10">
@@ -1672,7 +2466,7 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>COUNTIF(Backlog!$E$5:$E$195,"Blocked")+COUNTIF(Backlog!$E$5:$E$195,"On Hold")</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,"Blocked")+COUNTIF(Backlog!$E$5:$E$197,"On Hold")</f>
         <v/>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1691,15 +2485,15 @@
         </is>
       </c>
       <c r="I11" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F11)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F11)</f>
         <v/>
       </c>
       <c r="J11" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F11,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F11,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K11" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F11,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F11,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L11" s="10">
@@ -1714,7 +2508,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>IFERROR(COUNTIF(Backlog!$E$5:$E$195,"Closed")/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR(COUNTIF(Backlog!$E$5:$E$197,"Closed")/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1733,15 +2527,15 @@
         </is>
       </c>
       <c r="I12" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F12)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F12)</f>
         <v/>
       </c>
       <c r="J12" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F12,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F12,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K12" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F12,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F12,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L12" s="10">
@@ -1756,7 +2550,7 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>SUMIF(Backlog!$E$5:$E$195,"Closed",Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,"Closed",Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1775,15 +2569,15 @@
         </is>
       </c>
       <c r="I13" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F13)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F13)</f>
         <v/>
       </c>
       <c r="J13" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F13,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F13,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K13" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F13,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F13,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L13" s="10">
@@ -1798,7 +2592,7 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>SUM(Backlog!$J$5:$J$195)-SUMIF(Backlog!$E$5:$E$195,"Closed",Backlog!$J$5:$J$195)</f>
+        <f>SUM(Backlog!$J$5:$J$197)-SUMIF(Backlog!$E$5:$E$197,"Closed",Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1817,15 +2611,15 @@
         </is>
       </c>
       <c r="I14" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F14)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F14)</f>
         <v/>
       </c>
       <c r="J14" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F14,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F14,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K14" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F14,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F14,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L14" s="10">
@@ -1850,15 +2644,15 @@
         </is>
       </c>
       <c r="I15" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F15)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F15)</f>
         <v/>
       </c>
       <c r="J15" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F15,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F15,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K15" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F15,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F15,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L15" s="10">
@@ -1888,15 +2682,15 @@
         </is>
       </c>
       <c r="I16" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F16)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F16)</f>
         <v/>
       </c>
       <c r="J16" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F16,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F16,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K16" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F16,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F16,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L16" s="10">
@@ -1941,15 +2735,15 @@
         </is>
       </c>
       <c r="I17" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F17)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F17)</f>
         <v/>
       </c>
       <c r="J17" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F17,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F17,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K17" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F17,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F17,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L17" s="10">
@@ -1964,15 +2758,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A18)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>IFERROR($B18/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B18/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A18,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A18,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1991,15 +2785,15 @@
         </is>
       </c>
       <c r="I18" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F18)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F18)</f>
         <v/>
       </c>
       <c r="J18" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F18,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F18,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K18" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F18,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F18,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L18" s="10">
@@ -2014,15 +2808,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A19)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="14">
-        <f>IFERROR($B19/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B19/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A19,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A19,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -2041,15 +2835,15 @@
         </is>
       </c>
       <c r="I19" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F19)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F19)</f>
         <v/>
       </c>
       <c r="J19" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F19,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F19,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K19" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F19,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F19,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L19" s="10">
@@ -2064,15 +2858,15 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A20)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>IFERROR($B20/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B20/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A20,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A20,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -2091,15 +2885,15 @@
         </is>
       </c>
       <c r="I20" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F20)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F20)</f>
         <v/>
       </c>
       <c r="J20" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F20,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F20,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K20" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F20,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F20,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L20" s="10">
@@ -2114,15 +2908,15 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A21)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>IFERROR($B21/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B21/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D21" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A21,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A21,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2141,15 +2935,15 @@
         </is>
       </c>
       <c r="I21" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F21)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F21)</f>
         <v/>
       </c>
       <c r="J21" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F21,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F21,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K21" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F21,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F21,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L21" s="10">
@@ -2164,15 +2958,15 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A22)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="14">
-        <f>IFERROR($B22/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B22/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D22" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A22,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A22,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2191,15 +2985,15 @@
         </is>
       </c>
       <c r="I22" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F22)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F22)</f>
         <v/>
       </c>
       <c r="J22" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F22,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F22,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K22" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F22,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F22,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L22" s="10">
@@ -2214,15 +3008,15 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A23)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="14">
-        <f>IFERROR($B23/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B23/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D23" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A23,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A23,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2241,15 +3035,15 @@
         </is>
       </c>
       <c r="I23" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F23)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F23)</f>
         <v/>
       </c>
       <c r="J23" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F23,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F23,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K23" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F23,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F23,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L23" s="10">
@@ -2264,15 +3058,15 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A24)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="14">
-        <f>IFERROR($B24/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B24/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D24" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A24,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A24,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2291,15 +3085,15 @@
         </is>
       </c>
       <c r="I24" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F24)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F24)</f>
         <v/>
       </c>
       <c r="J24" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F24,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F24,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K24" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F24,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F24,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L24" s="10">
@@ -2314,15 +3108,15 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A25)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="14">
-        <f>IFERROR($B25/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B25/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D25" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A25,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A25,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2341,15 +3135,15 @@
         </is>
       </c>
       <c r="I25" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F25)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F25)</f>
         <v/>
       </c>
       <c r="J25" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F25,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F25,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K25" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F25,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F25,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L25" s="10">
@@ -2364,15 +3158,15 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A26)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="14">
-        <f>IFERROR($B26/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B26/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D26" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A26,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A26,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2391,15 +3185,15 @@
         </is>
       </c>
       <c r="I26" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F26)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F26)</f>
         <v/>
       </c>
       <c r="J26" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F26,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F26,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K26" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F26,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F26,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L26" s="10">
@@ -2414,15 +3208,15 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A27)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="14">
-        <f>IFERROR($B27/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B27/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D27" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A27,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A27,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2441,15 +3235,15 @@
         </is>
       </c>
       <c r="I27" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F27)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F27)</f>
         <v/>
       </c>
       <c r="J27" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F27,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F27,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K27" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F27,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F27,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L27" s="10">
@@ -2464,15 +3258,15 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A28)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="14">
-        <f>IFERROR($B28/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B28/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D28" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A28,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A28,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2491,15 +3285,15 @@
         </is>
       </c>
       <c r="I28" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F28)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F28)</f>
         <v/>
       </c>
       <c r="J28" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F28,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F28,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K28" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F28,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F28,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L28" s="10">
@@ -2514,15 +3308,15 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A29)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="14">
-        <f>IFERROR($B29/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B29/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D29" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A29,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A29,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2541,15 +3335,15 @@
         </is>
       </c>
       <c r="I29" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$195,$F29)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$197,$F29)</f>
         <v/>
       </c>
       <c r="J29" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$195,$F29,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$B$5:$B$197,$F29,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="K29" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$195,$F29,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$197,$F29,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
       <c r="L29" s="10">
@@ -2564,15 +3358,15 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A30)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="14">
-        <f>IFERROR($B30/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B30/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D30" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A30,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A30,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2606,15 +3400,15 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$195,$A31)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="14">
-        <f>IFERROR($B31/COUNTA(Backlog!$A$5:$A$195),0)</f>
+        <f>IFERROR($B31/COUNTA(Backlog!$A$5:$A$197),0)</f>
         <v/>
       </c>
       <c r="D31" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$195,$A31,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$E$5:$E$197,$A31,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
     </row>
@@ -2673,15 +3467,15 @@
         </is>
       </c>
       <c r="B36" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$195,$A36)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$197,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$195,$A36,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$F$5:$F$197,$A36,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D36" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$195,$A36,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$F$5:$F$197,$A36,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2692,15 +3486,15 @@
         </is>
       </c>
       <c r="B37" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$195,$A37)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$197,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$195,$A37,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$F$5:$F$197,$A37,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D37" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$195,$A37,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$F$5:$F$197,$A37,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2711,15 +3505,15 @@
         </is>
       </c>
       <c r="B38" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$195,$A38)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$197,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$195,$A38,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$F$5:$F$197,$A38,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D38" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$195,$A38,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$F$5:$F$197,$A38,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2730,15 +3524,15 @@
         </is>
       </c>
       <c r="B39" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$195,$A39)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$197,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$195,$A39,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$F$5:$F$197,$A39,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D39" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$195,$A39,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$F$5:$F$197,$A39,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2778,15 +3572,15 @@
         </is>
       </c>
       <c r="B43" s="31">
-        <f>COUNTIF(Backlog!$H$5:$H$195,$A43)</f>
+        <f>COUNTIF(Backlog!$H$5:$H$197,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="9">
-        <f>SUMIF(Backlog!$H$5:$H$195,$A43,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$H$5:$H$197,$A43,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D43" s="31">
-        <f>COUNTIFS(Backlog!$H$5:$H$195,$A43,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$H$5:$H$197,$A43,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2797,15 +3591,15 @@
         </is>
       </c>
       <c r="B44" s="31">
-        <f>COUNTIF(Backlog!$H$5:$H$195,$A44)</f>
+        <f>COUNTIF(Backlog!$H$5:$H$197,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="9">
-        <f>SUMIF(Backlog!$H$5:$H$195,$A44,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$H$5:$H$197,$A44,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D44" s="31">
-        <f>COUNTIFS(Backlog!$H$5:$H$195,$A44,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$H$5:$H$197,$A44,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2816,15 +3610,15 @@
         </is>
       </c>
       <c r="B45" s="31">
-        <f>COUNTIF(Backlog!$H$5:$H$195,$A45)</f>
+        <f>COUNTIF(Backlog!$H$5:$H$197,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="9">
-        <f>SUMIF(Backlog!$H$5:$H$195,$A45,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$H$5:$H$197,$A45,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D45" s="31">
-        <f>COUNTIFS(Backlog!$H$5:$H$195,$A45,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$H$5:$H$197,$A45,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2864,15 +3658,15 @@
         </is>
       </c>
       <c r="B49" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$195,$A49)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$197,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$195,$A49,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$I$5:$I$197,$A49,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D49" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$195,$A49,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$197,$A49,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2883,15 +3677,15 @@
         </is>
       </c>
       <c r="B50" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$195,$A50)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$197,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$195,$A50,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$I$5:$I$197,$A50,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D50" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$195,$A50,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$197,$A50,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2902,15 +3696,15 @@
         </is>
       </c>
       <c r="B51" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$195,$A51)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$197,$A51)</f>
         <v/>
       </c>
       <c r="C51" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$195,$A51,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$I$5:$I$197,$A51,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D51" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$195,$A51,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$197,$A51,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2921,15 +3715,15 @@
         </is>
       </c>
       <c r="B52" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$195,$A52)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$197,$A52)</f>
         <v/>
       </c>
       <c r="C52" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$195,$A52,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$I$5:$I$197,$A52,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D52" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$195,$A52,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$197,$A52,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2940,15 +3734,15 @@
         </is>
       </c>
       <c r="B53" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$195,$A53)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$197,$A53)</f>
         <v/>
       </c>
       <c r="C53" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$195,$A53,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$I$5:$I$197,$A53,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D53" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$195,$A53,Backlog!$E$5:$E$195,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$197,$A53,Backlog!$E$5:$E$197,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -2959,16 +3753,708 @@
         </is>
       </c>
       <c r="B54" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$195,$A54)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$197,$A54)</f>
         <v/>
       </c>
       <c r="C54" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$195,$A54,Backlog!$J$5:$J$195)</f>
+        <f>SUMIF(Backlog!$I$5:$I$197,$A54,Backlog!$J$5:$J$197)</f>
         <v/>
       </c>
       <c r="D54" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$195,$A54,Backlog!$E$5:$E$195,"Closed")</f>
-        <v/>
+        <f>COUNTIFS(Backlog!$I$5:$I$197,$A54,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="71" t="inlineStr">
+        <is>
+          <t>CHARTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="72" t="inlineStr">
+        <is>
+          <t>Every figure below is a live formula over the Backlog sheet — the charts redraw themselves when a story's Status or Est. Days changes. Nothing here is hand-typed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="64" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B60" s="64" t="inlineStr">
+        <is>
+          <t>Stories</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B61">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Business Review</t>
+        </is>
+      </c>
+      <c r="B62">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Business Approved</t>
+        </is>
+      </c>
+      <c r="B63">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B64">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Development In-Progress</t>
+        </is>
+      </c>
+      <c r="B65">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Development Completed</t>
+        </is>
+      </c>
+      <c r="B66">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QA In-Progress</t>
+        </is>
+      </c>
+      <c r="B67">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
+        </is>
+      </c>
+      <c r="B68">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QA-Fail</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B70">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B71">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="B72">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Moved to Backlog</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>COUNTIF(Backlog!$E$5:$E$197,$A$73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="71" t="inlineStr">
+        <is>
+          <t>Effort by phase (days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="64" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B76" s="64" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C76" s="64" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B77">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$77,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$77,Backlog!$J$5:$J$197)-$B$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B78">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$78,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$78,Backlog!$J$5:$J$197)-$B$78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B79">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$79,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C79">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$79,Backlog!$J$5:$J$197)-$B$79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B80">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$80,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$80,Backlog!$J$5:$J$197)-$B$80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B81">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$81,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$81,Backlog!$J$5:$J$197)-$B$81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B82">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$82,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$82,Backlog!$J$5:$J$197)-$B$82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B83">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$83,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C83">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$83,Backlog!$J$5:$J$197)-$B$83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B84">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$84,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C84">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$84,Backlog!$J$5:$J$197)-$B$84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B85">
+        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$85,Backlog!$E$5:$E$197,"Closed")</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>SUMIF(Backlog!$G$5:$G$197,$A$85,Backlog!$J$5:$J$197)-$B$85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="71" t="inlineStr">
+        <is>
+          <t>Epic completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="64" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="B88" s="64" t="inlineStr">
+        <is>
+          <t>% complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <f>$F$6</f>
+        <v/>
+      </c>
+      <c r="B89" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$89,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$89,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="B90" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$90,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$90,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="B91" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$91,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$91,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="B92" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$92,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$92,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="B93" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$93,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$93,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="B94" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$94,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$94,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="B95" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$95,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$95,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="B96" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$96,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$96,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="B97" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$97,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$97,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <f>$F$15</f>
+        <v/>
+      </c>
+      <c r="B98" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$98,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$98,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <f>$F$16</f>
+        <v/>
+      </c>
+      <c r="B99" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$99,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$99,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <f>$F$17</f>
+        <v/>
+      </c>
+      <c r="B100" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$100,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$100,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <f>$F$18</f>
+        <v/>
+      </c>
+      <c r="B101" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$101,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$101,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <f>$F$19</f>
+        <v/>
+      </c>
+      <c r="B102" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$102,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$102,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <f>$F$20</f>
+        <v/>
+      </c>
+      <c r="B103" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$103,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$103,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <f>$F$21</f>
+        <v/>
+      </c>
+      <c r="B104" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$104,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$104,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <f>$F$22</f>
+        <v/>
+      </c>
+      <c r="B105" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$105,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$105,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <f>$F$23</f>
+        <v/>
+      </c>
+      <c r="B106" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$106,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$106,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <f>$F$24</f>
+        <v/>
+      </c>
+      <c r="B107" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$107,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$107,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <f>$F$25</f>
+        <v/>
+      </c>
+      <c r="B108" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$108,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$108,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <f>$F$26</f>
+        <v/>
+      </c>
+      <c r="B109" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$109,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$109,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <f>$F$27</f>
+        <v/>
+      </c>
+      <c r="B110" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$110,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$110,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <f>$F$28</f>
+        <v/>
+      </c>
+      <c r="B111" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$111,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$111,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <f>$F$29</f>
+        <v/>
+      </c>
+      <c r="B112" s="73">
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$112,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$112,Backlog!$J$5:$J$197),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="71" t="inlineStr">
+        <is>
+          <t>QA and security (E01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="64" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B115" s="64" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>QA checks passed</t>
+        </is>
+      </c>
+      <c r="B116">
+        <f>'QA Results'!$J$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>QA checks failed</t>
+        </is>
+      </c>
+      <c r="B117">
+        <f>'QA Results'!$J$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Security findings HIGH</t>
+        </is>
+      </c>
+      <c r="B118">
+        <f>'Security Findings'!$K$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Security findings MEDIUM</t>
+        </is>
+      </c>
+      <c r="B119">
+        <f>'Security Findings'!$K$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Security findings LOW</t>
+        </is>
+      </c>
+      <c r="B120">
+        <f>'Security Findings'!$K$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Security findings INFO</t>
+        </is>
+      </c>
+      <c r="B121">
+        <f>'Security Findings'!$K$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Findings still open</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Automated tests in suite</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -2979,6 +4465,7 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2988,7 +4475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W195"/>
+  <dimension ref="A1:W197"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -18101,14 +19588,250 @@
       </c>
       <c r="W195" s="49" t="n"/>
     </row>
+    <row r="196">
+      <c r="A196" s="38" t="inlineStr">
+        <is>
+          <t>E01-S09</t>
+        </is>
+      </c>
+      <c r="B196" s="39" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="C196" s="40" t="inlineStr">
+        <is>
+          <t>PERSISTENCE &amp; DATA LAYER</t>
+        </is>
+      </c>
+      <c r="D196" s="40" t="inlineStr">
+        <is>
+          <t>E01 end-to-end QA suite</t>
+        </is>
+      </c>
+      <c r="E196" s="40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F196" s="41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G196" s="39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H196" s="50" t="inlineStr">
+        <is>
+          <t>Correctness-critical</t>
+        </is>
+      </c>
+      <c r="I196" s="39" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="J196" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K196" s="40" t="inlineStr">
+        <is>
+          <t>E01-S01..S06</t>
+        </is>
+      </c>
+      <c r="L196" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M196" s="44" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="N196" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" s="46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P196" s="46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q196" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="R196" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="S196" s="48" t="inlineStr">
+        <is>
+          <t>As a developer, I want the whole E01 stack exercised as ONE system, so that defects in the seams between components are caught here rather than in Phase 1.</t>
+        </is>
+      </c>
+      <c r="T196" s="48" t="inlineStr">
+        <is>
+          <t>1. Full trade lifecycle: instrument sync -&gt; hazard flags -&gt; bars -&gt; Redis state -&gt; stream -&gt; rate limit -&gt; order -&gt; position -&gt; audit -&gt; verify -&gt; archive -&gt; restore (QA-E01-01..12)
+2. Cross-component contract tests — symbol validity agreement, JSONB round trip, correlation_id propagation, lock/index agreement
+3. Fail-closed behaviour for every component</t>
+        </is>
+      </c>
+      <c r="U196" s="48" t="inlineStr">
+        <is>
+          <t>• One correlation_id reconstructs the full trade from decision_log
+• Every component consumes what the previous one produced, unmodified
+• Prices are still exact Decimals after an archive/restore cycle
+• Every failure path degrades to 'do not trade', never to 'proceed'</t>
+        </is>
+      </c>
+      <c r="V196" s="48" t="inlineStr">
+        <is>
+          <t>CLOSED 7 Aug 2026. 9 tests in tests/integration/test_e01_end_to_end.py.
+THIS SUITE IMMEDIATELY EARNED ITS KEEP — it HUNG on first run, which turned out to be QA-SEC-05: the decision_log.symbol_id foreign key blocking the audit writer on an uncommitted business transaction. No per-story suite could have found that, because it only appears when the audit writer and a business transaction run against the same instrument at the same time.
+Also validates the seams no single story owns: that a symbol the instruments table accepts is also a legal Redis key (a disagreement would mean a bar written and then a throw building the cache key for it), and that an audit payload survives the JSONB round trip so verification reads back what was hashed.</t>
+        </is>
+      </c>
+      <c r="W196" s="49" t="inlineStr">
+        <is>
+          <t>Run with: pytest tests/integration/test_e01_end_to_end.py
+Requires Docker (TimescaleDB + Redis containers). Skips cleanly without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="38" t="inlineStr">
+        <is>
+          <t>E01-S10</t>
+        </is>
+      </c>
+      <c r="B197" s="39" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="C197" s="40" t="inlineStr">
+        <is>
+          <t>PERSISTENCE &amp; DATA LAYER</t>
+        </is>
+      </c>
+      <c r="D197" s="40" t="inlineStr">
+        <is>
+          <t>E01 penetration-test suite</t>
+        </is>
+      </c>
+      <c r="E197" s="40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F197" s="41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G197" s="39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H197" s="50" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I197" s="39" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="J197" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K197" s="40" t="inlineStr">
+        <is>
+          <t>E01-S01..S06</t>
+        </is>
+      </c>
+      <c r="L197" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M197" s="44" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="N197" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" s="46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P197" s="46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q197" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="R197" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="S197" s="48" t="inlineStr">
+        <is>
+          <t>As the operator, I want E01 attacked deliberately rather than reviewed, so that the security properties it claims are the ones it actually has.</t>
+        </is>
+      </c>
+      <c r="T197" s="48" t="inlineStr">
+        <is>
+          <t>1. Audit hash collision / forgery probes
+2. Payload canonicalisation probes
+3. Redis key injection via broker-supplied symbols
+4. DLQ key growth
+5. FK-induced audit blocking
+6. Error-message leakage and log flooding
+7. Chain preimage / reordering resistance</t>
+        </is>
+      </c>
+      <c r="U197" s="48" t="inlineStr">
+        <is>
+          <t>• Every finding has a regression test that fails if it is reintroduced
+• Every rejection test is paired with a control proving it is targeted
+• Real NSE symbols (M&amp;M, BAJAJ-AUTO) are NOT broken by the input filter</t>
+        </is>
+      </c>
+      <c r="V197" s="48" t="inlineStr">
+        <is>
+          <t>CLOSED 7 Aug 2026. 39 tests in tests/security/test_e01_pentest.py.
+SIX VULNERABILITIES FOUND AND FIXED — see the 'Security Findings' sheet for the full detail. The most serious (QA-SEC-01, HIGH) was a hash collision in the audit chain: the material was built with "|".join(...) and an unescaped delimiter, so two DIFFERENT audit rows produced an IDENTICAL hash. That defeats the entire tamper-evidence property the chain exists to provide.
+Threat model is deliberately realistic rather than theatrical: broker instrument data is untrusted external input, news and AI output reach audit payloads, and an attacker WITH database access is explicitly in scope for the audit chain — that is the whole reason it is hash-chained rather than merely append-only.</t>
+        </is>
+      </c>
+      <c r="W197" s="49" t="inlineStr">
+        <is>
+          <t>Two of the six were found by the pen-test suite failing on its OWN first run (QA-SEC-03 regex bypass, QA-SEC-06 log flooding), which is the strongest argument for writing adversarial tests rather than reviewing code.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:W195"/>
-  <conditionalFormatting sqref="A5:D195">
+  <autoFilter ref="A4:W197"/>
+  <conditionalFormatting sqref="A5:D197">
     <cfRule type="expression" priority="16" dxfId="42">
       <formula>OR($E5="Removed",$E5="Closed")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E195">
+  <conditionalFormatting sqref="E5:E197">
     <cfRule type="expression" priority="2" dxfId="13">
       <formula>EXACT($E5,"New")</formula>
     </cfRule>
@@ -18153,11 +19876,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E195" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid status" error="Pick a status from the list." promptTitle="Status" prompt="Select the current status" type="list">
+    <dataValidation sqref="E5:E197" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid status" error="Pick a status from the list." promptTitle="Status" prompt="Select the current status" type="list">
       <formula1>"New,Business Review,Business Approved,Active,Development In-Progress,Development Completed,QA In-Progress,QA-Success,QA-Fail,Closed,Removed,Moved to Backlog,Blocked,On Hold"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="Q5:Q195" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid percentage" error="Enter a value between 0% and 100%." type="decimal">
+    <dataValidation sqref="Q5:Q197" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid percentage" error="Enter a value between 0% and 100%." type="decimal">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -18733,6 +20456,1138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="59" min="1" max="1"/>
+    <col width="11" customWidth="1" style="59" min="2" max="2"/>
+    <col width="30" customWidth="1" style="59" min="3" max="3"/>
+    <col width="10" customWidth="1" style="59" min="4" max="4"/>
+    <col width="62" customWidth="1" style="59" min="5" max="5"/>
+    <col width="34" customWidth="1" style="59" min="6" max="6"/>
+    <col width="34" customWidth="1" style="59" min="7" max="7"/>
+    <col width="14" customWidth="1" style="59" min="9" max="9"/>
+    <col width="10" customWidth="1" style="59" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="59">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>QA RESULTS — E01 END-TO-END</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="59">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>End-to-end verification of the persistence layer as ONE system. Per-story suites test components in isolation; these test the SEAMS between them, which is where integration defects live. Run: pytest tests/integration/  (requires Docker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>QA ID</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E4" s="63" t="inlineStr">
+        <is>
+          <t>What was verified</t>
+        </is>
+      </c>
+      <c r="F4" s="63" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="G4" s="63" t="inlineStr">
+        <is>
+          <t>Test file</t>
+        </is>
+      </c>
+      <c r="I4" s="64" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="J4" s="64" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1" s="59">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-01</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>E01-S01</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Instrument sync</t>
+        </is>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E5" s="67" t="inlineStr">
+        <is>
+          <t>Upsert is idempotent; symbol&lt;-&gt;id cache resolves; a new listing mid-session needs no restart</t>
+        </is>
+      </c>
+      <c r="F5" s="67" t="inlineStr">
+        <is>
+          <t>50 lookups issue 0 queries</t>
+        </is>
+      </c>
+      <c r="G5" s="67" t="inlineStr">
+        <is>
+          <t>test_e01_end_to_end.py</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1" s="59">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-02</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>E01-S01</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Hazard flags + eligibility view</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>Per-symbol-per-day flags stored; v_eligible_today excludes T2T/ASM/GSM and is IST-anchored</t>
+        </is>
+      </c>
+      <c r="F6" s="67" t="inlineStr">
+        <is>
+          <t>T2T symbol correctly excluded</t>
+        </is>
+      </c>
+      <c r="G6" s="67" t="inlineStr">
+        <is>
+          <t>test_schema_business_rules.py</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1" s="59">
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-03</t>
+        </is>
+      </c>
+      <c r="B7" s="65" t="inlineStr">
+        <is>
+          <t>E01-S02</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="inlineStr">
+        <is>
+          <t>Bar write and warm-up read</t>
+        </is>
+      </c>
+      <c r="D7" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t>30 bars written; warm_up_batch returns them oldest-first as exact Decimals</t>
+        </is>
+      </c>
+      <c r="F7" s="67" t="inlineStr">
+        <is>
+          <t>query count constant vs symbol count</t>
+        </is>
+      </c>
+      <c r="G7" s="67" t="inlineStr">
+        <is>
+          <t>test_repositories.py</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1" s="59">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-04</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>E01-S03</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>Redis typed state round trip</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E8" s="67" t="inlineStr">
+        <is>
+          <t>Decimal survives model_dump_json exactly; corrupt payload reads as absent</t>
+        </is>
+      </c>
+      <c r="F8" s="67" t="inlineStr">
+        <is>
+          <t>1510.7500 in == 1510.7500 out</t>
+        </is>
+      </c>
+      <c r="G8" s="67" t="inlineStr">
+        <is>
+          <t>test_redis_layer.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1" s="59">
+      <c r="A9" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-05</t>
+        </is>
+      </c>
+      <c r="B9" s="65" t="inlineStr">
+        <is>
+          <t>E01-S03</t>
+        </is>
+      </c>
+      <c r="C9" s="65" t="inlineStr">
+        <is>
+          <t>Slot lock + DB unique index</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E9" s="67" t="inlineStr">
+        <is>
+          <t>Lock refuses the second holder; partial unique index refuses the second insert independently</t>
+        </is>
+      </c>
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>both layers hold</t>
+        </is>
+      </c>
+      <c r="G9" s="67" t="inlineStr">
+        <is>
+          <t>test_e01_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1" s="59">
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-06</t>
+        </is>
+      </c>
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>E01-S04</t>
+        </is>
+      </c>
+      <c r="C10" s="65" t="inlineStr">
+        <is>
+          <t>Signal across the stream</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>Envelope published and consumed; correlation_id preserved end to end</t>
+        </is>
+      </c>
+      <c r="F10" s="67" t="inlineStr">
+        <is>
+          <t>correlation_id matches</t>
+        </is>
+      </c>
+      <c r="G10" s="67" t="inlineStr">
+        <is>
+          <t>test_event_streams.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1" s="59">
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-07</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>E01-S03</t>
+        </is>
+      </c>
+      <c r="C11" s="65" t="inlineStr">
+        <is>
+          <t>Order rate limiting</t>
+        </is>
+      </c>
+      <c r="D11" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E11" s="67" t="inlineStr">
+        <is>
+          <t>Token bucket gates before submission; 25 concurrent callers yield exactly capacity</t>
+        </is>
+      </c>
+      <c r="F11" s="67" t="inlineStr">
+        <is>
+          <t>exactly 5 of 25 allowed</t>
+        </is>
+      </c>
+      <c r="G11" s="67" t="inlineStr">
+        <is>
+          <t>test_redis_layer.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1" s="59">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-08</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>E01-S02</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="inlineStr">
+        <is>
+          <t>Two-transaction order submission</t>
+        </is>
+      </c>
+      <c r="D12" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E12" s="67" t="inlineStr">
+        <is>
+          <t>SUBMITTING row exists before the broker call; recovery finds it by client_order_id</t>
+        </is>
+      </c>
+      <c r="F12" s="67" t="inlineStr">
+        <is>
+          <t>status transitions correctly</t>
+        </is>
+      </c>
+      <c r="G12" s="67" t="inlineStr">
+        <is>
+          <t>test_e01_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1" s="59">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-09</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>E01-S01</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="inlineStr">
+        <is>
+          <t>Position with stop + deadline</t>
+        </is>
+      </c>
+      <c r="D13" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>BR-1 and BR-7 enforced NOT NULL; slot occupied then freed on close</t>
+        </is>
+      </c>
+      <c r="F13" s="67" t="inlineStr">
+        <is>
+          <t>naked position impossible</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr">
+        <is>
+          <t>test_schema_business_rules.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1" s="59">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-10</t>
+        </is>
+      </c>
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>E01-S03</t>
+        </is>
+      </c>
+      <c r="C14" s="65" t="inlineStr">
+        <is>
+          <t>Square-off timer armed</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>ZSET schedule; pop_due is atomic across 6 concurrent workers, no double-pop</t>
+        </is>
+      </c>
+      <c r="F14" s="67" t="inlineStr">
+        <is>
+          <t>20 popped, 0 duplicates</t>
+        </is>
+      </c>
+      <c r="G14" s="67" t="inlineStr">
+        <is>
+          <t>test_redis_layer.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1" s="59">
+      <c r="A15" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-11</t>
+        </is>
+      </c>
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>E01-S05</t>
+        </is>
+      </c>
+      <c r="C15" s="65" t="inlineStr">
+        <is>
+          <t>Audit trail reconstructs the trade</t>
+        </is>
+      </c>
+      <c r="D15" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>5 stages written; chain verifies; by_correlation returns them in order</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>PREMARKET-&gt;SIGNAL-&gt;RISK-&gt;ORDER-&gt;FILL</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr">
+        <is>
+          <t>test_e01_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1" s="59">
+      <c r="A16" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-12</t>
+        </is>
+      </c>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>E01-S06</t>
+        </is>
+      </c>
+      <c r="C16" s="65" t="inlineStr">
+        <is>
+          <t>Archive / purge / restore cycle</t>
+        </is>
+      </c>
+      <c r="D16" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>30 bars archived and verified, purged only after verification, restored with exact prices</t>
+        </is>
+      </c>
+      <c r="F16" s="67" t="inlineStr">
+        <is>
+          <t>prices identical after restore</t>
+        </is>
+      </c>
+      <c r="G16" s="67" t="inlineStr">
+        <is>
+          <t>test_retention.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1" s="59">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-13</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C17" s="65" t="inlineStr">
+        <is>
+          <t>Symbol validity agreement</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>Every symbol the instruments table accepts is also a legal Redis key</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
+          <t>M&amp;M, BAJAJ-AUTO, L&amp;TFH all pass</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>test_e01_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1" s="59">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-14</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C18" s="65" t="inlineStr">
+        <is>
+          <t>Audit payload JSONB round trip</t>
+        </is>
+      </c>
+      <c r="D18" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>Unicode, nesting, nulls, bools and 2^53+1 all survive; chain still verifies</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>verification clean on tricky payload</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr">
+        <is>
+          <t>test_e01_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1" s="59">
+      <c r="A19" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-15</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C19" s="65" t="inlineStr">
+        <is>
+          <t>Fail-closed on every degradation</t>
+        </is>
+      </c>
+      <c r="D19" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>Missing bars -&gt; empty; corrupt state -&gt; absent; Redis down -&gt; kill switch ENGAGED; audit down -&gt; buffered</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>no path fails open</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr">
+        <is>
+          <t>test_e01_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1" s="59">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-16</t>
+        </is>
+      </c>
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>E01-S01</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="inlineStr">
+        <is>
+          <t>Migration round trip</t>
+        </is>
+      </c>
+      <c r="D20" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>upgrade head -&gt; downgrade base -&gt; upgrade head clean, across all 3 migrations</t>
+        </is>
+      </c>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>3 migrations reversible</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr">
+        <is>
+          <t>test_datastore_scaffold.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G20"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="59" min="1" max="1"/>
+    <col width="10" customWidth="1" style="59" min="2" max="2"/>
+    <col width="16" customWidth="1" style="59" min="3" max="3"/>
+    <col width="9" customWidth="1" style="59" min="4" max="4"/>
+    <col width="58" customWidth="1" style="59" min="5" max="5"/>
+    <col width="52" customWidth="1" style="59" min="6" max="6"/>
+    <col width="52" customWidth="1" style="59" min="7" max="7"/>
+    <col width="34" customWidth="1" style="59" min="8" max="8"/>
+    <col width="14" customWidth="1" style="59" min="10" max="10"/>
+    <col width="10" customWidth="1" style="59" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="59">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>SECURITY FINDINGS — E01 PENETRATION TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="59">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Findings from attacking the code rather than reviewing it. Threat model: broker instrument data is untrusted external input; news and AI output reach audit payloads; an attacker WITH database access is IN SCOPE for the audit chain — that is why it is hash-chained, not merely append-only. Every finding has a regression test that fails if it is reintroduced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="63" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="F4" s="63" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G4" s="63" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="H4" s="63" t="inlineStr">
+        <is>
+          <t>Regression test</t>
+        </is>
+      </c>
+      <c r="J4" s="64" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="K4" s="64" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1" s="59">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-01</t>
+        </is>
+      </c>
+      <c r="B5" s="68" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Audit chain</t>
+        </is>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E5" s="67" t="inlineStr">
+        <is>
+          <t>Hash collision via delimiter ambiguity. Material was '|'.join(fields) with the delimiter unescaped, so a field containing '|' shifted the boundary: stage='SIGNAL'/outcome='ALLOW|X' and stage='SIGNAL|ALLOW'/outcome='X' produced an IDENTICAL digest.</t>
+        </is>
+      </c>
+      <c r="F5" s="67" t="inlineStr">
+        <is>
+          <t>Defeats tamper-evidence entirely — a record could be substituted for another without breaking the chain. Same class as CVE-2012-2459 (Merkle ambiguity).</t>
+        </is>
+      </c>
+      <c r="G5" s="67" t="inlineStr">
+        <is>
+          <t>Length-prefix every field (len:value), making the encoding injective, plus an 'AUDITv2' domain-separation tag. Standard remedy for concatenation ambiguity.</t>
+        </is>
+      </c>
+      <c r="H5" s="67" t="inlineStr">
+        <is>
+          <t>5 parametrised collision probes + determinism control</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1" s="59">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-05</t>
+        </is>
+      </c>
+      <c r="B6" s="68" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Audit writer</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>decision_log.symbol_id foreign key blocked the audit writer. PostgreSQL takes a shared lock on the referenced row to validate the FK, so an audit write referencing an instrument whose row is uncommitted waits for that business transaction.</t>
+        </is>
+      </c>
+      <c r="F6" s="67" t="inlineStr">
+        <is>
+          <t>Defeats the reason AuditWriter uses an independent session. During the daily instrument sync — one transaction, thousands of rows — every concurrent audit write for those symbols stalls, then falls to the disk buffer at statement_timeout. The audit trail degrades because of an unrelated bulk write.</t>
+        </is>
+      </c>
+      <c r="G6" s="67" t="inlineStr">
+        <is>
+          <t>Dropped the FK; kept the column. An audit log must be writable unconditionally and must outlive delisted instruments. TimescaleDB refuses to add an FK to a compressed hypertable at all, which is further evidence it never belonged.</t>
+        </is>
+      </c>
+      <c r="H6" s="67" t="inlineStr">
+        <is>
+          <t>Two-session probe before and after the fix; E2E suite</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1" s="59">
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-03</t>
+        </is>
+      </c>
+      <c r="B7" s="69" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="inlineStr">
+        <is>
+          <t>Redis keyspace</t>
+        </is>
+      </c>
+      <c r="D7" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E7" s="67" t="inlineStr">
+        <is>
+          <t>Broker-supplied symbols flowed unvalidated into Redis key names. ':' shifts key boundaries so two logical states share one slot; '*' and '?' are glob wildcards in any SCAN; '\n' and '\x00' are accepted by Redis but rejected by PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="F7" s="67" t="inlineStr">
+        <is>
+          <t>Silent state corruption in a component holding positions and the kill switch. None of these raise — the wrong value is simply read.</t>
+        </is>
+      </c>
+      <c r="G7" s="67" t="inlineStr">
+        <is>
+          <t>Validate every key component against an allowlist. Deliberately permits &amp; and - so real NSE tickers (M&amp;M, BAJAJ-AUTO, L&amp;TFH) are not broken — verified by a control test.</t>
+        </is>
+      </c>
+      <c r="H7" s="67" t="inlineStr">
+        <is>
+          <t>10 hostile inputs x 4 builders + 5 real-symbol controls</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1" s="59">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-02</t>
+        </is>
+      </c>
+      <c r="B8" s="69" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>Audit payload</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E8" s="67" t="inlineStr">
+        <is>
+          <t>json.dumps coerces non-string keys, so {1:'a'} and {'1':'a'} serialised identically — two different payloads, one hash. {1:'a','1':'b'} emitted a duplicate JSON key.</t>
+        </is>
+      </c>
+      <c r="F8" s="67" t="inlineStr">
+        <is>
+          <t>Canonicalisation defect in a structure whose only purpose is to be canonical.</t>
+        </is>
+      </c>
+      <c r="G8" s="67" t="inlineStr">
+        <is>
+          <t>Reject non-string keys at any depth, at the boundary, rather than coercing them.</t>
+        </is>
+      </c>
+      <c r="H8" s="67" t="inlineStr">
+        <is>
+          <t>6 payload shapes refused + serialisation control</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1" s="59">
+      <c r="A9" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-06</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C9" s="65" t="inlineStr">
+        <is>
+          <t>Input validation</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E9" s="67" t="inlineStr">
+        <is>
+          <t>The key-rejection message echoed the entire rejected value, so a hostile 200 KB ticker produced 200 KB of log.</t>
+        </is>
+      </c>
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>Denial of service against the log pipeline, and a log-injection vector.</t>
+        </is>
+      </c>
+      <c r="G9" s="67" t="inlineStr">
+        <is>
+          <t>Truncate the echo to 64 characters and report the true length instead.</t>
+        </is>
+      </c>
+      <c r="H9" s="67" t="inlineStr">
+        <is>
+          <t>Asserts the message stays under 2 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1" s="59">
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-04</t>
+        </is>
+      </c>
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C10" s="65" t="inlineStr">
+        <is>
+          <t>Event streams</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>stream_dlq was not idempotent: a DLQ entry that itself failed produced stream:dlq:dlq:signals, then stream:dlq:dlq:dlq:signals.</t>
+        </is>
+      </c>
+      <c r="F10" s="67" t="inlineStr">
+        <is>
+          <t>Unbounded key growth under repeated failure, and each new key escapes the MAXLEN configured for the stream it came from — which under noeviction is how Redis stops accepting writes.</t>
+        </is>
+      </c>
+      <c r="G10" s="67" t="inlineStr">
+        <is>
+          <t>Strip an existing dlq: prefix so the operation is idempotent.</t>
+        </is>
+      </c>
+      <c r="H10" s="67" t="inlineStr">
+        <is>
+          <t>Applied 5 times, key must remain stable</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1" s="59">
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-07</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C11" s="65" t="inlineStr">
+        <is>
+          <t>Regex validation</t>
+        </is>
+      </c>
+      <c r="D11" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E11" s="67" t="inlineStr">
+        <is>
+          <t>The first version of the key filter used re.compile(r'^...$').match(). In Python '$' also matches immediately BEFORE a trailing newline, so 'svc\n' passed validation.</t>
+        </is>
+      </c>
+      <c r="F11" s="67" t="inlineStr">
+        <is>
+          <t>A newline reached the keyspace despite an apparently correct anchored pattern. Classic and easy to miss on review.</t>
+        </is>
+      </c>
+      <c r="G11" s="67" t="inlineStr">
+        <is>
+          <t>Switched to fullmatch, which has no trailing-newline exception.</t>
+        </is>
+      </c>
+      <c r="H11" s="67" t="inlineStr">
+        <is>
+          <t>Found by the pen-test suite failing on its own first run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H11"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
@@ -19354,7 +22209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -7040,7 +7040,7 @@
       </c>
       <c r="E33" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development In-Progress</t>
         </is>
       </c>
       <c r="F33" s="41" t="inlineStr">
@@ -7071,12 +7071,18 @@
           <t>E03-S01</t>
         </is>
       </c>
-      <c r="L33" s="40" t="n"/>
+      <c r="L33" s="40" t="inlineStr">
+        <is>
+          <t>Feed only — B1/B4 (broker data source). Engine is complete.</t>
+        </is>
+      </c>
       <c r="M33" s="44" t="n"/>
       <c r="N33" s="45" t="n"/>
       <c r="O33" s="46" t="n"/>
       <c r="P33" s="46" t="n"/>
-      <c r="Q33" s="47" t="n"/>
+      <c r="Q33" s="47" t="n">
+        <v>0.7</v>
+      </c>
       <c r="R33" s="39" t="n">
         <v>5</v>
       </c>
@@ -7087,11 +7093,11 @@
       </c>
       <c r="T33" s="48" t="inlineStr">
         <is>
-          <t>1. Fetch corporate action data
-2. Apply split/bonus adjustment factors to historical series
-3. Mark `is_adjusted` on affected rows
-4. Re-adjustment when a new action is announced
-5. Verify against a known historical split</t>
+          <t>1. Fetch corporate action data — NOT DONE, needs a data source (see Blocked By)
+2. [DONE] Store actions in `corporate_action` — the source of truth for adjustment
+3. [DONE] Derive `price_adj_factor` / `volume_adj_factor` per bar; raw OHLC never mutated
+4. [DONE] Re-adjustment when a new action is announced — full recompute, idempotent
+5. [DONE] Verify against a known historical split</t>
         </is>
       </c>
       <c r="U33" s="48" t="inlineStr">
@@ -7100,8 +7106,24 @@
 • 🔴 Unadjusted data can never reach the indicator engine</t>
         </is>
       </c>
-      <c r="V33" s="48" t="n"/>
-      <c r="W33" s="49" t="n"/>
+      <c r="V33" s="48" t="inlineStr">
+        <is>
+          <t>DESIGN BLOCKER RESOLVED 11 Aug 2026. See SPRINT02_TECHNICAL_SPEC.md §4 and CA-B1 on the Blockers sheet.
+THE BLOCKER: the schema specified `ohlcv.is_adjusted BOOLEAN`, which cannot support re-adjustment. When a second action arrives you need the factor ALREADY APPLIED in order to apply the next one, and a boolean does not carry it. Adjusting prices in place compounds silently — no exception, no failing test, just a permanently wrong price history. This is safety-critical because a wrong adjustment does not fail loudly; every backtest over the affected symbol simply becomes fiction.
+THE RESOLUTION: raw prices are never modified. A new `corporate_action` table is the source of truth, and each bar carries two derived factors — adjusted price = raw * price_adj_factor. Recompute always rebuilds from the FULL action history, which makes it idempotent, and makes a mis-entered action fixable by correcting its row and recomputing.
+TWO factors, not one: a dividend reduces price but leaves volume untouched, so a single reciprocal factor would corrupt volume on every dividend — and volume feeds both the liquidity filter and the volume-ratio indicator.
+BR-16 IS ENFORCED STRUCTURALLY, not by convention: BarRepository has no method that returns raw prices. The only accessor is `raw_bars_for_audit`, named to be hard to reach for, and a test asserts no raw-read sibling exists. The trading path cannot ask for unadjusted data by accident.</t>
+        </is>
+      </c>
+      <c r="W33" s="49" t="inlineStr">
+        <is>
+          <t>18 tests, all passing. Three findings came out of building it, each now covered by its own test:
+1. ORDER INDEPENDENCE WAS ONLY APPROXIMATE. A Hypothesis property test caught that multiplying Decimal QUOTIENTS is not exactly associative — combining the same three splits in two different orders gave answers differing in the last digits. Fixed by keeping factors as exact ratios (numerator/denominator held separately) and dividing once at the end. Actions arrive from a feed in arbitrary order, so this had to be exact rather than nearly exact.
+2. RESTORE FROM ARCHIVE MISSED ADJUSTMENTS. Archived bars are not in `ohlcv`, so any action recorded while they were away updated the live bars and skipped them. Restoring them would have spliced an unadjusted segment onto an adjusted series. `restore_bars` now recomputes factors for every restored symbol.
+3. CONCURRENT RECOMPUTE COULD LOSE AN ACTION. Two recomputes for one symbol could interleave and the older action set could win. Row locks do not catch this because both writers are self-consistent. Now takes a per-symbol transaction-scoped advisory lock before reading, same pattern as the audit chain.
+ALSO: dividends are recorded but NOT applied to prices (APPLY_DIVIDEND_ADJUSTMENT = False). These are intraday strategies that never hold across an ex-date, and dividend adjustment rewrites every historical price. Flip it only alongside a decision about what backtests are measuring.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="59">
       <c r="A34" s="38" t="inlineStr">
@@ -19896,7 +19918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="59" min="1" max="1"/>
@@ -20259,6 +20281,47 @@
 EXPOSURE ASSESSMENT (why this is On Hold rather than Active): the flaw needs an attacker able to influence a redirect response. This client connects to one known endpoint (wss://ws.kite.trade) over TLS, and the compose design already puts the core network on `internal: true` with egress filtered to broker hosts. That is not a fix, but it means the practical exposure is small and does not block development.
 ACTIONS: (1) add to the Zerodha email alongside B1/B4 — ask when the autobahn pin will be updated; (2) at E02-S03, verify TLS cert validation is ON and the endpoint is not permitted to redirect; (3) re-run pip-audit each sprint; (4) re-evaluate before live trading — this belongs on PRE_LIVE_CHECKLIST.
 Same family as B2: both are the broker SDK holding the system back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>CA-B1</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>`ohlcv.is_adjusted BOOLEAN` cannot support re-adjustment</t>
+        </is>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>E03-S02, E06 (all indicators), E22 (backtest validity)</t>
+        </is>
+      </c>
+      <c r="D12" s="48" t="inlineStr">
+        <is>
+          <t>Redesign the adjustment storage model before any price is adjusted</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G12" s="46" t="n"/>
+      <c r="H12" s="49" t="inlineStr">
+        <is>
+          <t>RESOLVED 11 Aug 2026 — schema redesigned, built and tested. Full analysis in SPRINT02_TECHNICAL_SPEC.md §4.
+WHY IT WAS BLOCKING: a boolean records THAT a bar was adjusted, not BY HOW MUCH. The second corporate action therefore has nothing to build on, and adjusting the stored price in place compounds the first adjustment with no error and no failing test. Safety-critical: a wrong adjustment is silent, and it invalidates every backtest over that symbol rather than throwing.
+RESOLUTION: raw OHLC is immutable (BR-15). `corporate_action` holds the actions (BR-19); each bar carries `price_adj_factor` and `volume_adj_factor`; the repository applies them on read. Recompute rebuilds from the full history, so it is idempotent and a bad action is fixed by correcting the row.
+NOT A BLOCKER ANYMORE, but E03-S02 stays open: the adjustment ENGINE is done, the corporate action FEED is not, and that needs a data source — which is the same credential dependency as B1/B4, not a design gap.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -20519,7 +20519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -20636,7 +20636,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -20677,11 +20677,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL -&gt; FIXED</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="59">
@@ -21207,6 +21207,302 @@
       <c r="G20" s="67" t="inlineStr">
         <is>
           <t>test_datastore_scaffold.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-17</t>
+        </is>
+      </c>
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>E03-S02</t>
+        </is>
+      </c>
+      <c r="C21" s="65" t="inlineStr">
+        <is>
+          <t>Adjusted bars vs the domain model</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>Every adjusted bar must be constructible as a Bar. A 1:3 split gives factor 1/3 stored as NUMERIC(18,10); raw * factor is 14 decimal places and Price is Field(decimal_places=4), so the model REJECTED it.</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
+          <t>7 ratios incl. 1:3, 1:6, 2:3, 1:7 now build Bars; warm_up_batch output too</t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr">
+        <is>
+          <t>test_corporate_actions.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-18</t>
+        </is>
+      </c>
+      <c r="B22" s="65" t="inlineStr">
+        <is>
+          <t>E03-S02</t>
+        </is>
+      </c>
+      <c r="C22" s="65" t="inlineStr">
+        <is>
+          <t>OHLC coherence after rounding</t>
+        </is>
+      </c>
+      <c r="D22" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>Quantising each field independently cannot invert high/low, because rounding is monotonic. Pinned because the per-field quantisation rests on it.</t>
+        </is>
+      </c>
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>high&gt;=low, high&gt;=open/close, low&lt;=open/close across a 1:7 split</t>
+        </is>
+      </c>
+      <c r="G22" s="67" t="inlineStr">
+        <is>
+          <t>test_corporate_actions.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-19</t>
+        </is>
+      </c>
+      <c r="B23" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C23" s="65" t="inlineStr">
+        <is>
+          <t>Pre-flight gate blocks live mode</t>
+        </is>
+      </c>
+      <c r="D23" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>doctor must fail LIVE on the CONFIGURED broker credentials and on an unverified holiday calendar (BR-20). It checked neither.</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>LIVE fails on KITE_*; PAPER only warns on the calendar</t>
+        </is>
+      </c>
+      <c r="G23" s="67" t="inlineStr">
+        <is>
+          <t>test_preflight_gate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-20</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C24" s="65" t="inlineStr">
+        <is>
+          <t>Read-only adapter cannot trade</t>
+        </is>
+      </c>
+      <c r="D24" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>ReadOnlyGuard is the security boundary behind "compromising any other service cannot place an order". broker/adapter.py measured 0% coverage — the boundary had NO test.</t>
+        </is>
+      </c>
+      <c r="F24" s="67" t="inlineStr">
+        <is>
+          <t>place/modify/cancel all raise; a new mutating verb fails the guard test</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr">
+        <is>
+          <t>test_safety_invariants.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-21</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C25" s="65" t="inlineStr">
+        <is>
+          <t>Four governing invariants</t>
+        </is>
+      </c>
+      <c r="D25" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>Probed directly, not via existing tests: Recommendation has no sizing field and forbids injection; config refuses to exceed every hard bound; SecretString survives 9 render paths + pickle + exception; no eval/exec/dynamic import in the strategy path.</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>24 direct probes, all pass</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="inlineStr">
+        <is>
+          <t>scripts + test_safety_invariants.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-22</t>
+        </is>
+      </c>
+      <c r="B26" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C26" s="65" t="inlineStr">
+        <is>
+          <t>Constraints C2 / C5 / C9</t>
+        </is>
+      </c>
+      <c r="D26" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>Order rate 3 &lt; hard cap &lt; SEBI 10; CAS square-off strictly earlier than non-CAS; installed SDK exposes market_protection AND algo_id.</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>verified against kiteconnect 5.2.1 signature</t>
+        </is>
+      </c>
+      <c r="G26" s="67" t="inlineStr">
+        <is>
+          <t>test_market_protection.py + probes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-23</t>
+        </is>
+      </c>
+      <c r="B27" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C27" s="65" t="inlineStr">
+        <is>
+          <t>Dependency vulnerabilities</t>
+        </is>
+      </c>
+      <c r="D27" s="66" t="inlineStr">
+        <is>
+          <t>PASS (1 accepted)</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>pip-audit across the full dependency tree. Only finding is the known autobahn CVE-2020-35678 pinned by kiteconnect — tracked as B7, On Hold, not fixable locally.</t>
+        </is>
+      </c>
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>no NEW vulnerabilities</t>
+        </is>
+      </c>
+      <c r="G27" s="67" t="inlineStr">
+        <is>
+          <t>make audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-24</t>
+        </is>
+      </c>
+      <c r="B28" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C28" s="65" t="inlineStr">
+        <is>
+          <t>Documentation vs reality</t>
+        </is>
+      </c>
+      <c r="D28" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE (the stated entry point) claimed 112 tests and "Database: no migrations written", and pointed C2 at the wrong module. README claimed 112 tests.</t>
+        </is>
+      </c>
+      <c r="F28" s="67" t="inlineStr">
+        <is>
+          <t>counts, status tables and the C2 row corrected</t>
+        </is>
+      </c>
+      <c r="G28" s="67" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE.md, README.md</t>
         </is>
       </c>
     </row>
@@ -21227,7 +21523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -21355,7 +21651,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -21405,7 +21701,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="59">
@@ -21631,6 +21927,132 @@
       <c r="H11" s="67" t="inlineStr">
         <is>
           <t>Found by the pen-test suite failing on its own first run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-08</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="inlineStr">
+        <is>
+          <t>Pre-flight gate (doctor.py)</t>
+        </is>
+      </c>
+      <c r="D12" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E12" s="67" t="inlineStr">
+        <is>
+          <t>check_secrets hardcoded ANGELONE_API_KEY / CLIENT_ID / TOTP_SECRET while config sets broker.primary = zerodha. Those three variables appear NOWHERE else in the repo — not in .env.example, not in SETUP.md.</t>
+        </is>
+      </c>
+      <c r="F12" s="67" t="inlineStr">
+        <is>
+          <t>The gate before real capital validated a broker this deployment never uses. In LIVE mode it would hard-FAIL on credentials nobody was told to set, while reporting nothing at all about the Kite credentials actually required. A pre-flight check that validates the wrong aircraft is worse than none, because it reports green.</t>
+        </is>
+      </c>
+      <c r="G12" s="67" t="inlineStr">
+        <is>
+          <t>Moved the variable names onto BrokerProfile.credential_env_vars and made doctor derive them from broker.primary / broker.fallback. Fallback gaps degrade coverage rather than blocking trading.</t>
+        </is>
+      </c>
+      <c r="H12" s="67" t="inlineStr">
+        <is>
+          <t>4 tests incl. switching the configured broker switches what is checked, and a cross-check that every declared variable exists in .env.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-09</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="inlineStr">
+        <is>
+          <t>Pre-flight gate (doctor.py)</t>
+        </is>
+      </c>
+      <c r="D13" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>BR-20 requires doctor to FAIL when the NSE holiday calendar is unverified. check_market_calendar only ever WARNED — including in LIVE mode.</t>
+        </is>
+      </c>
+      <c r="F13" s="67" t="inlineStr">
+        <is>
+          <t>The system could go live with a fixed-date-only calendar, treating Diwali or any lunar-calendar holiday as a normal trading day: it would run the pre-market pipeline against data that never arrives and compute indicators across a phantom session. Nothing errors.</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr">
+        <is>
+          <t>Escalated to fail when mode is LIVE, kept as a warning otherwise so development stays usable.</t>
+        </is>
+      </c>
+      <c r="H13" s="67" t="inlineStr">
+        <is>
+          <t>Live-mode and paper-mode branches both asserted in test_preflight_gate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-10</t>
+        </is>
+      </c>
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C14" s="65" t="inlineStr">
+        <is>
+          <t>Broker adapter</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>ReadOnlyGuard — the mixin that stops a read-only adapter placing orders — had zero test coverage. broker/adapter.py measured 0%.</t>
+        </is>
+      </c>
+      <c r="F14" s="67" t="inlineStr">
+        <is>
+          <t>MASTER_REFERENCE and LOW_LEVEL_ARCHITECTURE both claim that compromising any service other than execution-svc cannot place an order. That guarantee rested entirely on three raise statements that no test exercised; deleting them broke nothing.</t>
+        </is>
+      </c>
+      <c r="G14" s="67" t="inlineStr">
+        <is>
+          <t>Added probes for place/modify/cancel, plus a structural test that fails if TradingAdapter gains a new mutating method the guard does not override.</t>
+        </is>
+      </c>
+      <c r="H14" s="67" t="inlineStr">
+        <is>
+          <t>6 tests in test_safety_invariants.py</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -20519,7 +20519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -20636,7 +20636,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -20681,7 +20681,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="59">
@@ -21503,6 +21503,191 @@
       <c r="G28" s="67" t="inlineStr">
         <is>
           <t>MASTER_REFERENCE.md, README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-25</t>
+        </is>
+      </c>
+      <c r="B29" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C29" s="65" t="inlineStr">
+        <is>
+          <t>Trading-day search bounds</t>
+        </is>
+      </c>
+      <c r="D29" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>next/previous_trading_day had unbounded while loops. With a malformed holiday list they do not hang - they return a SILENTLY WRONG date. Measured: previous_trading_day(2026-06-15) returned 2025-12-31, walking back 166 days without complaint.</t>
+        </is>
+      </c>
+      <c r="F29" s="67" t="inlineStr">
+        <is>
+          <t>Now raises HolidayDataError past 10 days and names the file to check; a real 4-day long weekend still resolves</t>
+        </is>
+      </c>
+      <c r="G29" s="67" t="inlineStr">
+        <is>
+          <t>test_calendar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-26</t>
+        </is>
+      </c>
+      <c r="B30" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C30" s="65" t="inlineStr">
+        <is>
+          <t>Inverted date range</t>
+        </is>
+      </c>
+      <c r="D30" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>trading_days_between(start &gt; end) returned [] silently. A backfill handed reversed dates would report success having fetched nothing, and a market-data gap is permanent.</t>
+        </is>
+      </c>
+      <c r="F30" s="67" t="inlineStr">
+        <is>
+          <t>Now raises ValueError naming both dates</t>
+        </is>
+      </c>
+      <c r="G30" s="67" t="inlineStr">
+        <is>
+          <t>test_calendar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-27</t>
+        </is>
+      </c>
+      <c r="B31" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C31" s="65" t="inlineStr">
+        <is>
+          <t>Position P&amp;L arithmetic</t>
+        </is>
+      </c>
+      <c r="D31" s="66" t="inlineStr">
+        <is>
+          <t>PASS (was untested)</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>unrealized_pnl / r_multiple / initial_risk had NO tests. The short-side sign flip in particular: if wrong, every short reports inverted P&amp;L and the risk engine cuts winners while holding losers. Verified correct, then pinned.</t>
+        </is>
+      </c>
+      <c r="F31" s="67" t="inlineStr">
+        <is>
+          <t>Long and short are exact mirror images; touching the stop is exactly -1R; Decimal stays exact to the paise</t>
+        </is>
+      </c>
+      <c r="G31" s="67" t="inlineStr">
+        <is>
+          <t>test_trading_models.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-28</t>
+        </is>
+      </c>
+      <c r="B32" s="65" t="inlineStr">
+        <is>
+          <t>E03-S02</t>
+        </is>
+      </c>
+      <c r="C32" s="65" t="inlineStr">
+        <is>
+          <t>Untaken corporate action branches</t>
+        </is>
+      </c>
+      <c r="D32" s="66" t="inlineStr">
+        <is>
+          <t>PASS (was untested)</t>
+        </is>
+      </c>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>Consolidation had never run against the database, only in factor arithmetic. The dividend-adjustment body is dormant behind APPLY_DIVIDEND_ADJUSTMENT=False - flipping that flag would have run code no test had ever executed, on a path that rewrites every historical price.</t>
+        </is>
+      </c>
+      <c r="F32" s="67" t="inlineStr">
+        <is>
+          <t>5:1 consolidation gives price x5 / volume x0.2; dividend formula verified behind the flag; split+consolidation compose correctly</t>
+        </is>
+      </c>
+      <c r="G32" s="67" t="inlineStr">
+        <is>
+          <t>test_corporate_actions.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-29</t>
+        </is>
+      </c>
+      <c r="B33" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C33" s="65" t="inlineStr">
+        <is>
+          <t>Model coherence validators</t>
+        </is>
+      </c>
+      <c r="D33" s="66" t="inlineStr">
+        <is>
+          <t>PASS (was untested)</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="inlineStr">
+        <is>
+          <t>RiskDecision coherence (approved needs sizing, rejected needs a reason), OrderRequest limit/trigger requirements, Trigger stop direction, and Order.remaining overfill clamping were all unexercised.</t>
+        </is>
+      </c>
+      <c r="F33" s="67" t="inlineStr">
+        <is>
+          <t>An approved-without-sizing decision and an overfill returning negative remaining are both now impossible</t>
+        </is>
+      </c>
+      <c r="G33" s="67" t="inlineStr">
+        <is>
+          <t>test_trading_models.py</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -20519,7 +20519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -20636,7 +20636,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -21688,6 +21688,80 @@
       <c r="G33" s="67" t="inlineStr">
         <is>
           <t>test_trading_models.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-30</t>
+        </is>
+      </c>
+      <c r="B34" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C34" s="65" t="inlineStr">
+        <is>
+          <t>Secrets provider layer</t>
+        </is>
+      </c>
+      <c r="D34" s="66" t="inlineStr">
+        <is>
+          <t>PASS (was untested)</t>
+        </is>
+      </c>
+      <c r="E34" s="67" t="inlineStr">
+        <is>
+          <t>EnvSecretsProvider, SopsSecretsProvider and build_provider had zero tests - C6 implementation resting on nothing. Key property: a sops decryption failure must not echo stderr, which can contain the offending secret material.</t>
+        </is>
+      </c>
+      <c r="F34" s="67" t="inlineStr">
+        <is>
+          <t>stderr excluded from the error AND the cause chain cut (from None); sops resolved absolutely with shell=False; unknown provider refused rather than defaulted; vault fails closed</t>
+        </is>
+      </c>
+      <c r="G34" s="67" t="inlineStr">
+        <is>
+          <t>test_secrets_providers.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="65" t="inlineStr">
+        <is>
+          <t>QA-E01-31</t>
+        </is>
+      </c>
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C35" s="65" t="inlineStr">
+        <is>
+          <t>Container and layering audit</t>
+        </is>
+      </c>
+      <c r="D35" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E35" s="67" t="inlineStr">
+        <is>
+          <t>Dockerfile multi-stage, non-root uid 1001, --chown on copies, healthcheck. Compose: no-new-privileges, internal network with no egress, localhost-only port bindings. Layering clean - no SQLAlchemy outside the persistence layer, no broker SDK outside broker/.</t>
+        </is>
+      </c>
+      <c r="F35" s="67" t="inlineStr">
+        <is>
+          <t>git history scanned for secrets: clean. No os.system, shell=True or eval anywhere.</t>
+        </is>
+      </c>
+      <c r="G35" s="67" t="inlineStr">
+        <is>
+          <t>manual audit + probes</t>
         </is>
       </c>
     </row>
@@ -21708,7 +21782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -21836,7 +21910,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -21886,7 +21960,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="59">
@@ -22238,6 +22312,132 @@
       <c r="H14" s="67" t="inlineStr">
         <is>
           <t>6 tests in test_safety_invariants.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-11</t>
+        </is>
+      </c>
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C15" s="65" t="inlineStr">
+        <is>
+          <t>Log redaction</t>
+        </is>
+      </c>
+      <c r="D15" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>Secrets survived redaction and reached the log via TWO paths the filter never touched: (1) exc_info=True, because logging.Formatter renders record.exc_info itself long after every filter has run; (2) an exception passed as a format arg, because _scrub_value only handled str/dict/list so an Exception object fell through and the formatter called str() on it later.</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>Violates invariant 3 and C6. engine.healthcheck logs with exc_info=True by design, and SQLAlchemy/psycopg/Alembic all put the connection URL in their exceptions - so the FIRST failed database healthcheck would write the DSN password to disk in clear text. The message path was perfectly redacted the whole time.</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr">
+        <is>
+          <t>Pre-render and scrub record.exc_text (the formatter uses it verbatim when set, and only falls back to exc_info when it is empty); scrub stack_info; render BaseException through the scrubber in _scrub_value.</t>
+        </is>
+      </c>
+      <c r="H15" s="67" t="inlineStr">
+        <is>
+          <t>6 tests: exc_info, exception-as-arg, chained cause, stack_info, an opaque registered value with no regex shape, plus a control that the host and exception type still survive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-12</t>
+        </is>
+      </c>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C16" s="65" t="inlineStr">
+        <is>
+          <t>Database privileges</t>
+        </is>
+      </c>
+      <c r="D16" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>corporate_action shipped with NO grants at all for algotrader_app, and its sequence had no USAGE. The grant migration enumerates tables BY NAME and ran long before the table existed.</t>
+        </is>
+      </c>
+      <c r="F16" s="67" t="inlineStr">
+        <is>
+          <t>The entire E03-S02 adjustment path was dead behind a permission nobody had granted: InsufficientPrivilege on INSERT from the feed and on the SELECT inside recompute_factors. Every test passed because the harness connects as the table owner - the failure would have surfaced only in production.</t>
+        </is>
+      </c>
+      <c r="G16" s="67" t="inlineStr">
+        <is>
+          <t>Migration b7c2f9a41d38 grants the table and its sequence, guarded so it is runnable where the role does not exist. Verified upgrade -&gt; downgrade -&gt; upgrade.</t>
+        </is>
+      </c>
+      <c r="H16" s="67" t="inlineStr">
+        <is>
+          <t>5 tests comparing the LIVE catalogue against Base.metadata, so any future table without grants fails immediately; plus an end-to-end write under SET ROLE algotrader_app</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-13</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C17" s="65" t="inlineStr">
+        <is>
+          <t>Supply chain</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>No lockfile anywhere. pyproject declares floors (&gt;=), so CI, the Docker build and a developer laptop each resolved dependencies independently.</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
+          <t>The image was not the artifact CI tested; builds were not reproducible; a breaking or compromised upstream release would land automatically on a system that holds broker credentials. The pinned ruff/mypy lines record this exact lesson for linters but it was never applied to runtime dependencies.</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>constraints.txt with 116 pins, generated inside the SAME Linux image the Dockerfile builds from (a Windows freeze would omit uvloop and add Windows-only wheels). Wired into the Dockerfile and all three CI install steps.</t>
+        </is>
+      </c>
+      <c r="H17" s="67" t="inlineStr">
+        <is>
+          <t>Image rebuilt and verified: runs non-root, imports cleanly, pins applied (SQLAlchemy 2.0.51). pip-audit re-run against the pinned set - no new vulnerabilities.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -259,8 +259,13 @@
       <color rgb="001F3864"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -411,6 +416,16 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9EC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -453,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -610,6 +625,12 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4475,7 +4496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W197"/>
+  <dimension ref="A1:X197"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -4500,6 +4521,7 @@
     <col width="50" customWidth="1" style="59" min="21" max="21"/>
     <col width="40" customWidth="1" style="59" min="22" max="22"/>
     <col width="30" customWidth="1" style="59" min="23" max="23"/>
+    <col width="70" customWidth="1" style="59" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" customHeight="1" s="59">
@@ -4630,6 +4652,11 @@
       <c r="W4" s="37" t="inlineStr">
         <is>
           <t>Comments</t>
+        </is>
+      </c>
+      <c r="X4" s="74" t="inlineStr">
+        <is>
+          <t>Build Concerns</t>
         </is>
       </c>
     </row>
@@ -5820,6 +5847,11 @@
         </is>
       </c>
       <c r="W19" s="49" t="n"/>
+      <c r="X19" s="75" t="inlineStr">
+        <is>
+          <t>The hash chain cannot detect TRUNCATION. Deleting the last N rows leaves a perfectly valid chain — verification passes. The append-only GRANT is the real control there and it is tested, but if you ever need tamper-evidence against someone with DB owner rights, that needs an external anchor (periodically publishing the tip hash somewhere the DB cannot reach). Decide whether that is in scope before relying on the chain for a compliance claim.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="59">
       <c r="A20" s="38" t="inlineStr">
@@ -6189,7 +6221,7 @@
       </c>
       <c r="E23" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development In-Progress</t>
         </is>
       </c>
       <c r="F23" s="41" t="inlineStr">
@@ -6225,7 +6257,9 @@
       <c r="N23" s="45" t="n"/>
       <c r="O23" s="46" t="n"/>
       <c r="P23" s="46" t="n"/>
-      <c r="Q23" s="47" t="n"/>
+      <c r="Q23" s="47" t="n">
+        <v>0.8</v>
+      </c>
       <c r="R23" s="39" t="n">
         <v>7</v>
       </c>
@@ -6252,8 +6286,17 @@
 • Expired token is detected before the pre-market job starts</t>
         </is>
       </c>
-      <c r="V23" s="48" t="n"/>
+      <c r="V23" s="48" t="inlineStr">
+        <is>
+          <t>Auth manager, session lifecycle and the login-URL builder are built and tested (38 security tests). SECURITY CHANGE from the original tasks: the re-auth notice carries NO login link. ReauthNotice has no url/link field at all, so the phishing reflex cannot be re-introduced by a future edit - a test asserts the absence. Remaining 20%: the request_token -&gt; access_token HTTP exchange needs live credentials to verify end to end, and the callback endpoint belongs with E17-S01's dashboard (see the E17-S01 concern about localhost vs phone access - same network decision).</t>
+        </is>
+      </c>
       <c r="W23" s="49" t="n"/>
+      <c r="X23" s="75" t="inlineStr">
+        <is>
+          <t>TWO issues. (1) Task 5 sends a login link over Telegram, which trains you to authenticate from an inbound message — the consent-phishing pattern. Anyone who can post one message (leaked bot token, SIM-swapped Telegram, lookalike bot) sends a link to THEIR Kite app at the time you expect it; you authenticate on a genuine Zerodha page and hand them a request_token they exchange with their own api_secret. 2FA does not help — you are authorising the wrong app, not leaking a password. Server-side nonce checks cannot help either: the attack completes entirely outside your system. FIX: send a notification with NO link; open the dashboard from your own bookmark. (2) Task 2 says 'local callback endpoint' but acceptance says 'completes from a phone'. A phone cannot reach 127.0.0.1 on the server. Either the callback is publicly reachable over HTTPS — which puts an inbound endpoint on the box holding broker credentials, against the internal-network design — or the flow completes on the server host. Decide before building.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="59">
       <c r="A24" s="38" t="inlineStr">
@@ -6278,7 +6321,7 @@
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development In-Progress</t>
         </is>
       </c>
       <c r="F24" s="41" t="inlineStr">
@@ -6314,7 +6357,9 @@
       <c r="N24" s="45" t="n"/>
       <c r="O24" s="46" t="n"/>
       <c r="P24" s="46" t="n"/>
-      <c r="Q24" s="47" t="n"/>
+      <c r="Q24" s="47" t="n">
+        <v>0.7</v>
+      </c>
       <c r="R24" s="39" t="n">
         <v>5</v>
       </c>
@@ -6338,7 +6383,11 @@
 • A failed auth prevents the session reaching `TRADING`</t>
         </is>
       </c>
-      <c r="V24" s="48" t="n"/>
+      <c r="V24" s="48" t="inlineStr">
+        <is>
+          <t>Session validity, expiry-at-next-reauth and the notice hook are built and tested. Remaining: wiring the scheduled trigger and the health gate, which belong to the orchestrator rather than the broker layer.</t>
+        </is>
+      </c>
       <c r="W24" s="49" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1" s="59">
@@ -6364,7 +6413,7 @@
       </c>
       <c r="E25" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F25" s="41" t="inlineStr">
@@ -6400,7 +6449,9 @@
       <c r="N25" s="45" t="n"/>
       <c r="O25" s="46" t="n"/>
       <c r="P25" s="46" t="n"/>
-      <c r="Q25" s="47" t="n"/>
+      <c r="Q25" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R25" s="39" t="n">
         <v>4</v>
       </c>
@@ -6423,7 +6474,11 @@
 • Data endpoints work from a non-whitelisted IP (verifying the order-only scope)</t>
         </is>
       </c>
-      <c r="V25" s="48" t="n"/>
+      <c r="V25" s="48" t="inlineStr">
+        <is>
+          <t>Read-only adapter built on ReadOnlyGuard; place/modify/cancel all raise PermissionError, asserted. subscribe() deliberately raises: E05-S01 will implement the documented Kite WebSocket wire protocol rather than KiteTicker, which avoids autobahn 19.11.2 (CVE-2020-35678, blocker B7) and the Twisted reactor bridging problem in one move. Needs no static IP - Zerodha validates the whitelist on order endpoints only.</t>
+        </is>
+      </c>
       <c r="W25" s="49" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1" s="59">
@@ -6449,7 +6504,7 @@
       </c>
       <c r="E26" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F26" s="41" t="inlineStr">
@@ -6485,7 +6540,9 @@
       <c r="N26" s="45" t="n"/>
       <c r="O26" s="46" t="n"/>
       <c r="P26" s="46" t="n"/>
-      <c r="Q26" s="47" t="n"/>
+      <c r="Q26" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" s="39" t="n">
         <v>7</v>
       </c>
@@ -6511,8 +6568,17 @@
 • A timeout raises `AmbiguousOrderError`, never a silent retry</t>
         </is>
       </c>
-      <c r="V26" s="48" t="n"/>
+      <c r="V26" s="48" t="inlineStr">
+        <is>
+          <t>Trading adapter with market protection enforced at the boundary (missing and zero both refused). client_order_id -&gt; Kite tag resolved: the tag is alphanumeric, max 20 chars, and IS returned in the orderbook, so broker_tag() truncates the sha256 id deterministically in one place and the submission and recovery paths are asserted to agree. Restructured so the trading adapter does NOT inherit ReadOnlyGuard - 'may trade' is stated positively rather than achieved by overriding a refusal.</t>
+        </is>
+      </c>
       <c r="W26" s="49" t="n"/>
+      <c r="X26" s="75" t="inlineStr">
+        <is>
+          <t>client_order_id is 8-64 chars, but the only carrier the broker offers is Kite's `tag` parameter, which is length-limited (verify the current limit in the developer console — historically 20 chars). If the tag cannot hold the full id, E15-S02's recovery path 'query by client_order_id' cannot round-trip and the idempotency guarantee is decorative. Decide the truncation or mapping scheme HERE, not in E15.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="59">
       <c r="A27" s="38" t="inlineStr">
@@ -6537,7 +6603,7 @@
       </c>
       <c r="E27" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F27" s="41" t="inlineStr">
@@ -6573,7 +6639,9 @@
       <c r="N27" s="45" t="n"/>
       <c r="O27" s="46" t="n"/>
       <c r="P27" s="46" t="n"/>
-      <c r="Q27" s="47" t="n"/>
+      <c r="Q27" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" s="39" t="n">
         <v>5</v>
       </c>
@@ -6597,8 +6665,17 @@
 • Queue depth beyond threshold rejects rather than buffers</t>
         </is>
       </c>
-      <c r="V27" s="48" t="n"/>
+      <c r="V27" s="48" t="inlineStr">
+        <is>
+          <t>Redis token bucket, account-wide key, orders and data on separate budgets so a backfill cannot starve an exit. Refuses rather than queues. Config refuses &gt;= 10 orders/sec in code. FOUND A REAL DEFECT while testing this - see QA-SEC-14.</t>
+        </is>
+      </c>
       <c r="W27" s="49" t="n"/>
+      <c r="X27" s="75" t="inlineStr">
+        <is>
+          <t>Zerodha's 10/sec is enforced ACCOUNT-WIDE, not per app or per connection. A Redis bucket covers this system's processes but not orders you place manually in the Kite app at the same time. Running at 3/sec leaves headroom, but either accept that or document that manual trading during a session is prohibited.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="59">
       <c r="A28" s="38" t="inlineStr">
@@ -6623,7 +6700,7 @@
       </c>
       <c r="E28" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F28" s="41" t="inlineStr">
@@ -6659,7 +6736,9 @@
       <c r="N28" s="45" t="n"/>
       <c r="O28" s="46" t="n"/>
       <c r="P28" s="46" t="n"/>
-      <c r="Q28" s="47" t="n"/>
+      <c r="Q28" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R28" s="39" t="n">
         <v>4</v>
       </c>
@@ -6681,8 +6760,17 @@
           <t>• A limit price is always snapped to a valid tick before submission</t>
         </is>
       </c>
-      <c r="V28" s="48" t="n"/>
+      <c r="V28" s="48" t="inlineStr">
+        <is>
+          <t>Instrument sync with new-listing and delisting detection, and an implausibility check so a truncated download is loud rather than silently shrinking the universe. Side-aware tick rounding added: buy rounds down, sell rounds up, so neither side ever pays more than intended.</t>
+        </is>
+      </c>
       <c r="W28" s="49" t="n"/>
+      <c r="X28" s="75" t="inlineStr">
+        <is>
+          <t>Tick rounding direction is not neutral. Rounding a BUY limit up and a SELL limit down crosses the spread and pays it; rounding both the same way biases fills systematically. Specify direction per side and prove it against a real instrument with a non-0.05 tick.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="59">
       <c r="A29" s="38" t="inlineStr">
@@ -6707,7 +6795,7 @@
       </c>
       <c r="E29" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F29" s="41" t="inlineStr">
@@ -6743,7 +6831,9 @@
       <c r="N29" s="45" t="n"/>
       <c r="O29" s="46" t="n"/>
       <c r="P29" s="46" t="n"/>
-      <c r="Q29" s="47" t="n"/>
+      <c r="Q29" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R29" s="39" t="n">
         <v>3</v>
       </c>
@@ -6764,8 +6854,17 @@
           <t>• Sizing uses live margin, never a computed leverage multiple</t>
         </is>
       </c>
-      <c r="V29" s="48" t="n"/>
+      <c r="V29" s="48" t="inlineStr">
+        <is>
+          <t>Live margin plus a staleness bound. margin_for_sizing() refuses a snapshot older than the TTL, which closes the time-of-check/time-of-use gap - margin falls after every fill, so a stale reading can authorise a position the account cannot carry.</t>
+        </is>
+      </c>
       <c r="W29" s="49" t="n"/>
+      <c r="X29" s="75" t="inlineStr">
+        <is>
+          <t>Caching margin then sizing on it is a time-of-check/time-of-use gap — margin can fall between the fetch and the order, especially right after another fill. A staleness guard bounds AGE but not CHANGE. Re-verify immediately before submission for the first position of the day and after any fill.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="59">
       <c r="A30" s="38" t="inlineStr">
@@ -6843,7 +6942,11 @@
         </is>
       </c>
       <c r="U30" s="48" t="n"/>
-      <c r="V30" s="48" t="n"/>
+      <c r="V30" s="48" t="inlineStr">
+        <is>
+          <t>DEFERRED, not blocked. Fyers fallback is the only Low-risk story in E02 and adds a second broker SDK plus a second auth flow. Worth doing once the primary path has run against live data, so the fallback is written against known behaviour rather than assumptions.</t>
+        </is>
+      </c>
       <c r="W30" s="49" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1" s="59">
@@ -6869,7 +6972,7 @@
       </c>
       <c r="E31" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F31" s="41" t="inlineStr">
@@ -6905,7 +7008,9 @@
       <c r="N31" s="45" t="n"/>
       <c r="O31" s="46" t="n"/>
       <c r="P31" s="46" t="n"/>
-      <c r="Q31" s="47" t="n"/>
+      <c r="Q31" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R31" s="39" t="n">
         <v>5</v>
       </c>
@@ -6928,8 +7033,17 @@
           <t>• Simulated timeout + reconnect produces exactly one position (chaos test)</t>
         </is>
       </c>
-      <c r="V31" s="48" t="n"/>
+      <c r="V31" s="48" t="inlineStr">
+        <is>
+          <t>Error taxonomy with the safety switch: classify(mutating=True) makes any UNRECOGNISED failure AmbiguousOrderError, routing to query-by-tag rather than retry. Only a 429 is retryable. Verified by mutation testing - breaking the fail-closed rule fails the test.</t>
+        </is>
+      </c>
       <c r="W31" s="49" t="n"/>
+      <c r="X31" s="75" t="inlineStr">
+        <is>
+          <t>The unmapped-error path is the one that matters. A new Kite error code arriving mid-session must fail closed — treat as ambiguous, query by id, never retry — rather than falling through to a generic retry. 'Log loudly' is not a behaviour; specify the default disposition for unknown codes.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="59">
       <c r="A32" s="38" t="inlineStr">
@@ -7016,6 +7130,11 @@
       </c>
       <c r="V32" s="48" t="n"/>
       <c r="W32" s="49" t="n"/>
+      <c r="X32" s="75" t="inlineStr">
+        <is>
+          <t>NSE replaced the legacy bhavcopy with the UDiFF format and moved the URL. A fetcher written against the old path will 404, or worse fetch a stale mirror. Pin the exact source and assert on the header row, not just on HTTP 200. Also: bhavcopy is UNADJUSTED, so this must land before E03-S02 computes factors, never after.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="59">
       <c r="A33" s="38" t="inlineStr">
@@ -7204,6 +7323,11 @@
       <c r="U34" s="48" t="n"/>
       <c r="V34" s="48" t="n"/>
       <c r="W34" s="49" t="n"/>
+      <c r="X34" s="75" t="inlineStr">
+        <is>
+          <t>Three constraints collide. Kite's historical endpoint is rate-limited, caps the date range per request by interval, and is a PAID add-on — so this cannot start until blocker B4 is resolved and the subscription exists. Also, a multi-hour backfill during market hours competes with live data against the same account-wide limit. Schedule it outside the session.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="59">
       <c r="A35" s="38" t="inlineStr">
@@ -7289,6 +7413,11 @@
       </c>
       <c r="V35" s="48" t="n"/>
       <c r="W35" s="49" t="n"/>
+      <c r="X35" s="75" t="inlineStr">
+        <is>
+          <t>'Unexplained jumps beyond circuit limits' will fire on every split and bonus, because a raw price series is SUPPOSED to gap at an ex-date. The check must join corporate_action and treat an explained jump as clean — otherwise every corporate action raises a false alarm and the report stops being read.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="59">
       <c r="A36" s="38" t="inlineStr">
@@ -7368,6 +7497,11 @@
       <c r="U36" s="48" t="n"/>
       <c r="V36" s="48" t="n"/>
       <c r="W36" s="49" t="n"/>
+      <c r="X36" s="75" t="inlineStr">
+        <is>
+          <t>'Verify against broker-supplied weekly bars' only holds if both sides use the same adjustment basis. Kite's weekly bars are adjusted; ours are raw-plus-factor. Compare adjusted-to-adjusted, or the check fails for every symbol that ever had a corporate action.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1" s="59">
       <c r="A37" s="38" t="inlineStr">
@@ -7527,6 +7661,11 @@
       </c>
       <c r="V38" s="48" t="n"/>
       <c r="W38" s="49" t="n"/>
+      <c r="X38" s="75" t="inlineStr">
+        <is>
+          <t>Publication time matters more than the schedule. NSE posts these lists at varying times; a 05:30 fetch may retrieve yesterday's file under today's name. Assert the file's OWN effective date, not the fetch time. Also use gsm_stage, not just the boolean — stage 4 is periodic call auction with no upward movement, a completely different hazard from stage 1, and the schema now carries the stage for exactly this reason.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1" s="59">
       <c r="A39" s="38" t="inlineStr">
@@ -7853,6 +7992,11 @@
       </c>
       <c r="V42" s="48" t="n"/>
       <c r="W42" s="49" t="n"/>
+      <c r="X42" s="75" t="inlineStr">
+        <is>
+          <t>The deadline must be pinned at position OPEN and stored with the position, never recomputed at exit time from current classification. If NSE reclassifies a symbol during the day, a recomputed deadline could move LATER and put you past the broker's square-off. E15-S06 computes at open — make sure this story feeds that path, not the exit path.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1" s="59">
       <c r="A43" s="38" t="inlineStr">
@@ -8019,6 +8163,11 @@
       </c>
       <c r="V44" s="48" t="n"/>
       <c r="W44" s="49" t="n"/>
+      <c r="X44" s="75" t="inlineStr">
+        <is>
+          <t>The Muhurat session is the trap: Diwali is a holiday on which the exchange runs a special ~1-hour evening session. A calendar with one session per day cannot express it. 'Stand down' is the right default, but record it as a DECISION — otherwise someone later 'fixes' the calendar and the system trades a session it was never tested against.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1" s="59">
       <c r="A45" s="38" t="inlineStr">
@@ -8106,6 +8255,11 @@
       </c>
       <c r="V45" s="48" t="n"/>
       <c r="W45" s="49" t="n"/>
+      <c r="X45" s="75" t="inlineStr">
+        <is>
+          <t>KiteTicker is Twisted/autobahn-based and thread-oriented, not asyncio-native, so the bridge needs a deliberate boundary. autobahn is also the component carrying CVE-2020-35678 (blocker B7). Separately: Kite caps concurrent WebSocket connections (3) and instruments per connection. A 200-symbol universe fits, but the reconnect path must not leak connections or you hit the cap after a few reconnects and the feed dies for good.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1" s="59">
       <c r="A46" s="38" t="inlineStr">
@@ -8350,6 +8504,11 @@
       </c>
       <c r="V48" s="48" t="n"/>
       <c r="W48" s="49" t="n"/>
+      <c r="X48" s="75" t="inlineStr">
+        <is>
+          <t>The filter is max(5 x ATR%, 2%) — but ATR comes from the indicator engine, which is NOT ready at session start. At 09:15, exactly when prints are most erratic, the ATR term is unavailable. Define cold-start behaviour explicitly: the 2% floor must apply on its own until ATR is ready, and must not silently evaluate to 'no limit'.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1" s="59">
       <c r="A49" s="38" t="inlineStr">
@@ -8515,6 +8674,11 @@
       </c>
       <c r="V50" s="48" t="n"/>
       <c r="W50" s="49" t="n"/>
+      <c r="X50" s="75" t="inlineStr">
+        <is>
+          <t>Cascading 1m-&gt;5m-&gt;15m-&gt;1h means one bad 1m bar propagates silently into every higher timeframe with no independent check. Also the CAS window (15:15-15:30 for CAS stocks) is a call auction, not continuous trading — bars built from it are not comparable to intraday bars and should be flagged or excluded.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1" s="59">
       <c r="A51" s="38" t="inlineStr">
@@ -8759,6 +8923,11 @@
       </c>
       <c r="V53" s="48" t="n"/>
       <c r="W53" s="49" t="n"/>
+      <c r="X53" s="75" t="inlineStr">
+        <is>
+          <t>'Incremental matches batch to 4dp' is only well-defined once the SEEDING convention is fixed. TA-Lib's EMA seeds from an SMA of the first N periods; a naive streaming EMA seeds from the first value, and the two never converge exactly. Pick one, document it, and make warm-up AND state-restore use the same one — otherwise a restart silently changes indicator values, and therefore signals.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1" s="59">
       <c r="A54" s="38" t="inlineStr">
@@ -8928,6 +9097,11 @@
       </c>
       <c r="V55" s="48" t="n"/>
       <c r="W55" s="49" t="n"/>
+      <c r="X55" s="75" t="inlineStr">
+        <is>
+          <t>Restoring indicator state from Redis must produce identical values to a full re-warm from history. If they differ, a mid-session restart changes signals with nothing visible to show for it. Test that specifically: warm from history, snapshot, restore, compare — do not assume.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1" s="59">
       <c r="A56" s="38" t="inlineStr">
@@ -9168,6 +9342,11 @@
       </c>
       <c r="V58" s="48" t="n"/>
       <c r="W58" s="49" t="n"/>
+      <c r="X58" s="75" t="inlineStr">
+        <is>
+          <t>'Sealed at 09:30 and never mutates' needs an explicit rule for a late tick whose exchange timestamp falls inside the window but which ARRIVES after the seal. Drop it, or the range mutates and every level derived from it shifts underneath positions already sized against it.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1" s="59">
       <c r="A59" s="38" t="inlineStr">
@@ -9482,6 +9661,11 @@
       </c>
       <c r="V62" s="48" t="n"/>
       <c r="W62" s="49" t="n"/>
+      <c r="X62" s="75" t="inlineStr">
+        <is>
+          <t>'Cheapest first' makes the recorded exclusion reason ORDER-DEPENDENT — a symbol that is both T2T and illiquid is attributed to whichever check ran first. If the audit answer 'why was this excluded' matters, either record every failing filter, or document that the field means 'first failing filter', not 'the reason'.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1" s="59">
       <c r="A63" s="38" t="inlineStr">
@@ -9566,6 +9750,11 @@
       </c>
       <c r="V63" s="48" t="n"/>
       <c r="W63" s="49" t="n"/>
+      <c r="X63" s="75" t="inlineStr">
+        <is>
+          <t>The catalyst component is stubbed at 0 until E08, but the weights sum to 1.0 INCLUDING it. Every score is therefore depressed by 10% until news lands, and scores from before and after E08 are not comparable — which quietly invalidates E07-S06's 20-session validation report if the window spans the change. Renormalise over available components, or freeze the report window.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1" s="59">
       <c r="A64" s="38" t="inlineStr">
@@ -10047,6 +10236,11 @@
       </c>
       <c r="V69" s="48" t="n"/>
       <c r="W69" s="49" t="n"/>
+      <c r="X69" s="75" t="inlineStr">
+        <is>
+          <t>Sanitisation and detection are different controls and the tasks mix them. Stripping tags is deterministic; detecting 'ignore previous' is a blocklist an attacker rewrites around. The REAL boundary is the structured output schema in E08-S05. Treat this as defence in depth and never let a passing sanitiser become the reason to trust article text.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1" s="59">
       <c r="A70" s="38" t="inlineStr">
@@ -10206,6 +10400,11 @@
       </c>
       <c r="V71" s="48" t="n"/>
       <c r="W71" s="49" t="n"/>
+      <c r="X71" s="75" t="inlineStr">
+        <is>
+          <t>'Batch articles to control cost' creates a cross-contamination surface: several untrusted articles in one prompt means an injection in article 3 can influence the extracted fields of articles 1 and 2. If batching, bound the batch and keep per-article outputs independently attributable — or pay for one call per article for anything that will drive a trade.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1" s="59">
       <c r="A72" s="38" t="inlineStr">
@@ -10363,6 +10562,11 @@
       <c r="U73" s="48" t="n"/>
       <c r="V73" s="48" t="n"/>
       <c r="W73" s="49" t="n"/>
+      <c r="X73" s="75" t="inlineStr">
+        <is>
+          <t>Decay in TRADING days is right, but the trading-day count depends on the holiday calendar — the known-incomplete one (B3 / E04-S07). Until that is verified, decay silently over- or under-weights across every long weekend.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1" s="59">
       <c r="A74" s="38" t="inlineStr">
@@ -10445,6 +10649,11 @@
       </c>
       <c r="V74" s="48" t="n"/>
       <c r="W74" s="49" t="n"/>
+      <c r="X74" s="75" t="inlineStr">
+        <is>
+          <t>'Stale pipeline -&gt; score 0' — make sure 0 reads as NEUTRAL, not bearish, at every consumer. If one downstream treats 0 as 'no catalyst' and another as 'negative', staleness changes behaviour inconsistently and only under conditions you cannot easily reproduce.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1" s="59">
       <c r="A75" s="38" t="inlineStr">
@@ -10883,6 +11092,11 @@
       </c>
       <c r="V80" s="48" t="n"/>
       <c r="W80" s="49" t="n"/>
+      <c r="X80" s="75" t="inlineStr">
+        <is>
+          <t>Blocking new entries during a blackout is only half of it. Decide explicitly what happens to positions ALREADY OPEN when a blackout starts — hold, or exit early? An RBI announcement mid-session with open positions is the case that matters, and the tasks do not say.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1" s="59">
       <c r="A81" s="38" t="inlineStr">
@@ -11044,6 +11258,11 @@
       </c>
       <c r="V82" s="48" t="n"/>
       <c r="W82" s="49" t="n"/>
+      <c r="X82" s="75" t="inlineStr">
+        <is>
+          <t>A usable context with an explicit gap is right, but this is won or lost at the CONSUMERS. Every read site must branch on is_stale; one that ignores the flag reintroduces exactly the silent-stale-data failure this story exists to prevent. Consider making the value inaccessible without acknowledging the flag, rather than a flag sitting beside it.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1" s="59">
       <c r="A83" s="38" t="inlineStr">
@@ -11276,6 +11495,11 @@
       </c>
       <c r="V85" s="48" t="n"/>
       <c r="W85" s="49" t="n"/>
+      <c r="X85" s="75" t="inlineStr">
+        <is>
+          <t>The cache-hit assertion needs a REAL second call, not a mock — this is precisely the class of thing that passes in tests and costs 10x in production. Also the daily-context layer changes each morning, so the cache is cold on the first call of every day BY DESIGN; set the alert threshold so it does not page you at 08:45 daily.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="30" customHeight="1" s="59">
       <c r="A86" s="38" t="inlineStr">
@@ -11433,6 +11657,11 @@
       </c>
       <c r="V87" s="48" t="n"/>
       <c r="W87" s="49" t="n"/>
+      <c r="X87" s="75" t="inlineStr">
+        <is>
+          <t>'Degrade to score-only, keep trading' is the right direction, but verify the degraded path is actually exercised. A score-only mode that has never run will not work the first time it is needed — and the first time it is needed is mid-session with the budget already exhausted.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="30" customHeight="1" s="59">
       <c r="A88" s="38" t="inlineStr">
@@ -11589,6 +11818,11 @@
       <c r="U89" s="48" t="n"/>
       <c r="V89" s="48" t="n"/>
       <c r="W89" s="49" t="n"/>
+      <c r="X89" s="75" t="inlineStr">
+        <is>
+          <t>The cache key must include the MODEL ID and the prompt template version. Without them, a model upgrade silently replays old answers against new prompts and the backtest becomes fiction while still looking green.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="30" customHeight="1" s="59">
       <c r="A90" s="38" t="inlineStr">
@@ -11819,6 +12053,11 @@
       </c>
       <c r="V92" s="48" t="n"/>
       <c r="W92" s="49" t="n"/>
+      <c r="X92" s="75" t="inlineStr">
+        <is>
+          <t>Checkpoint-resume and the hard 09:12 deadline interact badly. A resumed run inherits the elapsed wall clock, so a job that died at 08:50 and restarts at 09:05 must know it cannot finish and publish a DEGRADED plan rather than a late one. Make the deadline absolute, not per-attempt.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="30" customHeight="1" s="59">
       <c r="A93" s="38" t="inlineStr">
@@ -12042,6 +12281,11 @@
       </c>
       <c r="V95" s="48" t="n"/>
       <c r="W95" s="49" t="n"/>
+      <c r="X95" s="75" t="inlineStr">
+        <is>
+          <t>ProcessPoolExecutor pickles every object crossing the boundary. Decimal and Pydantic models pickle, but at 200 symbols x 3 timeframes the serialisation cost is real and this stage owns the binding 30-minute budget of the morning. Measure the serialisation share BEFORE optimising the compute.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="30" customHeight="1" s="59">
       <c r="A96" s="38" t="inlineStr">
@@ -12199,6 +12443,11 @@
       </c>
       <c r="V97" s="48" t="n"/>
       <c r="W97" s="49" t="n"/>
+      <c r="X97" s="75" t="inlineStr">
+        <is>
+          <t>'AI may veto or re-rank within the shortlist' is the one place the AI touches selection. Bound it explicitly: it must NOT be able to introduce a symbol that failed a hard filter, and a veto must carry a recorded reason. Re-ranking is a judgement; adding a symbol would be a safety breach.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="30" customHeight="1" s="59">
       <c r="A98" s="38" t="inlineStr">
@@ -12366,6 +12615,11 @@
       </c>
       <c r="V99" s="48" t="n"/>
       <c r="W99" s="49" t="n"/>
+      <c r="X99" s="75" t="inlineStr">
+        <is>
+          <t>'Immutable for the session' needs enforcement, not convention. E11-S07 runs at 09:02 and lock is at 09:12 — verify nothing in between can write after the lock, including a late-returning async task from an earlier stage that completes after its deadline.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="30" customHeight="1" s="59">
       <c r="A100" s="38" t="inlineStr">
@@ -12610,6 +12864,11 @@
       </c>
       <c r="V102" s="48" t="n"/>
       <c r="W102" s="49" t="n"/>
+      <c r="X102" s="75" t="inlineStr">
+        <is>
+          <t>'The same strategy code runs in backtest and live' is the property everything else rests on, and it is easy to lose to bar TIMING: live evaluates on sealed bars arriving from the stream, backtest replays stored bars. Any difference in WHEN evaluation fires is look-ahead bias. Assert equality of the decision SEQUENCE, not just of the final equity curve.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="30" customHeight="1" s="59">
       <c r="A103" s="38" t="inlineStr">
@@ -12696,6 +12955,11 @@
       </c>
       <c r="V103" s="48" t="n"/>
       <c r="W103" s="49" t="n"/>
+      <c r="X103" s="75" t="inlineStr">
+        <is>
+          <t>Effective trial count must include trials from strategies later deleted or abandoned, and any parameter sweeps run before the registry existed. If the count starts at zero when the registry is built, DSR is optimistic exactly when it matters most. Decide the starting count deliberately and record the reasoning.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="30" customHeight="1" s="59">
       <c r="A104" s="38" t="inlineStr">
@@ -12853,6 +13117,11 @@
       </c>
       <c r="V105" s="48" t="n"/>
       <c r="W105" s="49" t="n"/>
+      <c r="X105" s="75" t="inlineStr">
+        <is>
+          <t>The purge window must be derived from the strategy's OWN holding period, not a constant. An intraday strategy needs a purge of hours; a fixed multi-day purge over-purges and destroys the sample, making a good strategy look untestable. Make it a function of the label horizon.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="30" customHeight="1" s="59">
       <c r="A106" s="38" t="inlineStr">
@@ -13092,6 +13361,11 @@
       <c r="U108" s="48" t="n"/>
       <c r="V108" s="48" t="n"/>
       <c r="W108" s="49" t="n"/>
+      <c r="X108" s="75" t="inlineStr">
+        <is>
+          <t>'&gt;=80% agreement' needs a definition of agreement that survives timing jitter — the same signal one bar later is not a disagreement in substance but will score as one. Define the tolerance BEFORE collecting 20 sessions of data you then have to discard.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="30" customHeight="1" s="59">
       <c r="A109" s="38" t="inlineStr">
@@ -13265,6 +13539,11 @@
       </c>
       <c r="V110" s="48" t="n"/>
       <c r="W110" s="49" t="n"/>
+      <c r="X110" s="75" t="inlineStr">
+        <is>
+          <t>The hypothesis-before-results protocol is the entire control, and it is only real if the AI genuinely cannot see outcomes when it writes the hypothesis. Verify the journal summary passed into the prompt does not leak realised P&amp;L, win rate or R-multiples for the setups it is being asked to hypothesise about — otherwise it is fitting, with a hypothesis attached for appearances.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="30" customHeight="1" s="59">
       <c r="A111" s="38" t="inlineStr">
@@ -13420,6 +13699,11 @@
       </c>
       <c r="V112" s="48" t="n"/>
       <c r="W112" s="49" t="n"/>
+      <c r="X112" s="75" t="inlineStr">
+        <is>
+          <t>SEQUENCING BUG: this story is Phase 4 but depends on E12-S01 (strategy registry), which is Phase 5. Phase 4 cannot complete as currently sequenced. Either pull E12-S01 forward into Phase 4 or move this story into Phase 5.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="30" customHeight="1" s="59">
       <c r="A113" s="38" t="inlineStr">
@@ -13724,6 +14008,11 @@
       <c r="U116" s="48" t="n"/>
       <c r="V116" s="48" t="n"/>
       <c r="W116" s="49" t="n"/>
+      <c r="X116" s="75" t="inlineStr">
+        <is>
+          <t>The symbol lock prevents two strategies double-entering, but the partial unique index uq_open_symbol is the actual guarantee. Make the lock-failure path a clean reject, not an exception that leaves the signal half-processed — and log lock contention, because a rising rate means two strategies are fighting over the same names and that is a config problem, not a race.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="30" customHeight="1" s="59">
       <c r="A117" s="38" t="inlineStr">
@@ -14104,6 +14393,11 @@
       </c>
       <c r="V121" s="48" t="n"/>
       <c r="W121" s="49" t="n"/>
+      <c r="X121" s="75" t="inlineStr">
+        <is>
+          <t>Over which window and which return frequency? Intraday correlation is unstable — a short window flaps, a long one misses regime change. Correlation is also not the only linkage: four PSU banks can show only moderate correlation and still be one bet. Make the SECTOR cap the primary control and correlation the secondary one.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="30" customHeight="1" s="59">
       <c r="A122" s="38" t="inlineStr">
@@ -14339,6 +14633,11 @@
       </c>
       <c r="V124" s="48" t="n"/>
       <c r="W124" s="49" t="n"/>
+      <c r="X124" s="75" t="inlineStr">
+        <is>
+          <t>Quantity must round DOWN to lot size, never to nearest, or realised risk exceeds the configured percentage on every round-up. A zero quantity must REJECT, not silently place nothing. Both belong in the property test alongside the risk bound.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1" s="59">
       <c r="A125" s="38" t="inlineStr">
@@ -14501,6 +14800,11 @@
       </c>
       <c r="V126" s="48" t="n"/>
       <c r="W126" s="49" t="n"/>
+      <c r="X126" s="75" t="inlineStr">
+        <is>
+          <t>'Halts new entries, does NOT auto-liquidate' is correct and unusual — but make sure the SQUARE-OFF TIMER still runs while halted. A kill switch tripped at 14:00 that also stops the exit path leaves positions for the broker to close at 15:20 at whatever price exists. Halting must never disable the exit path.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="30" customHeight="1" s="59">
       <c r="A127" s="38" t="inlineStr">
@@ -14657,6 +14961,11 @@
       </c>
       <c r="V128" s="48" t="n"/>
       <c r="W128" s="49" t="n"/>
+      <c r="X128" s="75" t="inlineStr">
+        <is>
+          <t>The key is sha256(correlation|symbol|side|intent|date) — which is right for idempotency but means a deliberate SECOND entry into the same symbol, same side, same intent, on the same day collides with the first and is silently suppressed. If re-entry after an exit is ever allowed, the key needs a discriminator. Decide now, not after the first suppressed re-entry.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1" s="59">
       <c r="A129" s="38" t="inlineStr">
@@ -14814,6 +15123,11 @@
       </c>
       <c r="V130" s="48" t="n"/>
       <c r="W130" s="49" t="n"/>
+      <c r="X130" s="75" t="inlineStr">
+        <is>
+          <t>The failure mode to test is the stop being ACCEPTED and then rejected asynchronously, which is not the same as a synchronous placement failure. Verify through the reconciliation loop that a position without a live stop is detected within one cycle even when placement appeared to succeed.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="30" customHeight="1" s="59">
       <c r="A131" s="38" t="inlineStr">
@@ -14976,6 +15290,11 @@
       </c>
       <c r="V132" s="48" t="n"/>
       <c r="W132" s="49" t="n"/>
+      <c r="X132" s="75" t="inlineStr">
+        <is>
+          <t>TWO issues. (1) A single polling loop for all positions is a single point of failure at the most time-critical moment of the day — if it dies at 14:00, nothing notices until the broker squares off. Monitor its liveness independently. (2) The market order at the deadline MUST carry market_protection (C9) or Zerodha rejects it — exactly when you cannot afford a rejection.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="30" customHeight="1" s="59">
       <c r="A133" s="38" t="inlineStr">
@@ -15207,6 +15526,11 @@
       </c>
       <c r="V135" s="48" t="n"/>
       <c r="W135" s="49" t="n"/>
+      <c r="X135" s="75" t="inlineStr">
+        <is>
+          <t>'Broker state wins' is right. The hazard is that the unknown-position path trips the kill switch, which halts ENTRIES — but an unknown position that is real and unprotected needs more than a halt. Make the P0 alert distinguish 'unknown position exists' from 'system halted': they need different human responses within different timeframes.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="30" customHeight="1" s="59">
       <c r="A136" s="38" t="inlineStr">
@@ -15291,6 +15615,11 @@
       </c>
       <c r="V136" s="48" t="n"/>
       <c r="W136" s="49" t="n"/>
+      <c r="X136" s="75" t="inlineStr">
+        <is>
+          <t>'Switching paper-&gt;live changes exactly one dependency injection' is a strong claim and deserves a STRUCTURAL test, the way the ReadOnlyGuard test works. Otherwise one stray `if mode == PAPER` in the risk path makes every paper result unrepresentative of live.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="30" customHeight="1" s="59">
       <c r="A137" s="38" t="inlineStr">
@@ -15593,6 +15922,11 @@
       </c>
       <c r="V140" s="48" t="n"/>
       <c r="W140" s="49" t="n"/>
+      <c r="X140" s="75" t="inlineStr">
+        <is>
+          <t>The 60-second window must start when the message is DELIVERED, not when it is sent. Telegram delivery can lag; a window that expires before you see it makes L3 unusable in practice and will push you to widen the envelope for the wrong reason — to stop the timeouts rather than because the envelope was too tight.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="30" customHeight="1" s="59">
       <c r="A141" s="38" t="inlineStr">
@@ -15895,6 +16229,11 @@
       </c>
       <c r="V144" s="48" t="n"/>
       <c r="W144" s="49" t="n"/>
+      <c r="X144" s="75" t="inlineStr">
+        <is>
+          <t>ARCHITECTURAL CONFLICT: 'bind to 127.0.0.1 only' is incompatible with reaching the dashboard from a phone, which is how the kill switch (E14-S09, '10 seconds from a phone') and approvals (E16-S03) are meant to work. Decide the access path deliberately — WireGuard, Tailscale or an SSH tunnel — and write it down, because the option that gets chosen under pressure at 14:00 is exposing the port. This is the same network question as E02-S01's callback and E23-S03's egress rules; resolve all three once.</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="30" customHeight="1" s="59">
       <c r="A145" s="38" t="inlineStr">
@@ -16053,6 +16392,11 @@
       </c>
       <c r="V146" s="48" t="n"/>
       <c r="W146" s="49" t="n"/>
+      <c r="X146" s="75" t="inlineStr">
+        <is>
+          <t>A confirm dialog on a phone at speed is exactly where a mis-tap happens. Consider hold-to-confirm rather than a modal, and make sure E14-S09's 10-second requirement is measured INCLUDING the confirmation step, not just the request.</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="30" customHeight="1" s="59">
       <c r="A147" s="38" t="inlineStr">
@@ -16641,6 +16985,11 @@
       </c>
       <c r="V154" s="48" t="n"/>
       <c r="W154" s="49" t="n"/>
+      <c r="X154" s="75" t="inlineStr">
+        <is>
+          <t>'Immutable during an active session' and 'save produces a git commit' interact: a save attempted mid-session must fail BEFORE the commit, not after, or the repository and the running config diverge silently. Also, the re-auth requirement must not be satisfiable by a still-valid session cookie — that is not re-authentication.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="30" customHeight="1" s="59">
       <c r="A155" s="38" t="inlineStr">
@@ -17158,6 +17507,11 @@
       </c>
       <c r="V161" s="48" t="n"/>
       <c r="W161" s="49" t="n"/>
+      <c r="X161" s="75" t="inlineStr">
+        <is>
+          <t>Use a WEBHOOK, not getUpdates polling. A leaked bot token lets an attacker poll getUpdates and steal your updates out from under the legitimate consumer — including approval callbacks. Also enable Telegram account 2FA with a non-SMS method: a SIM-swap on the Telegram account compromises trade approvals and the kill switch simultaneously.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="30" customHeight="1" s="59">
       <c r="A162" s="38" t="inlineStr">
@@ -17303,6 +17657,11 @@
       <c r="U163" s="48" t="n"/>
       <c r="V163" s="48" t="n"/>
       <c r="W163" s="49" t="n"/>
+      <c r="X163" s="75" t="inlineStr">
+        <is>
+          <t>Inline-button callback data must be validated. An attacker able to invoke your bot's callback with a crafted payload could approve a trade. Sign or nonce the callback data and bind it to one specific pending approval, so a replayed or forged callback is rejected.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="30" customHeight="1" s="59">
       <c r="A164" s="38" t="inlineStr">
@@ -17668,6 +18027,11 @@
       </c>
       <c r="V168" s="48" t="n"/>
       <c r="W168" s="49" t="n"/>
+      <c r="X168" s="75" t="inlineStr">
+        <is>
+          <t>'Degraded latency steps the interval DOWN, never up' is ambiguous and getting it backwards is catastrophic. Confirm 'down' means LESS FREQUENT (a longer interval). The system must slow down when it is struggling, never speed up.</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="30" customHeight="1" s="59">
       <c r="A169" s="38" t="inlineStr">
@@ -18173,6 +18537,11 @@
       </c>
       <c r="V175" s="48" t="n"/>
       <c r="W175" s="49" t="n"/>
+      <c r="X175" s="75" t="inlineStr">
+        <is>
+          <t>Contract notes arrive T+1, so same-day reconciliation compares against an ESTIMATE, not the note. Make the estimate/actual distinction explicit in the schema, or the tax figures silently inherit an estimate that was never corrected.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="30" customHeight="1" s="59">
       <c r="A176" s="38" t="inlineStr">
@@ -18250,6 +18619,11 @@
       </c>
       <c r="V176" s="48" t="n"/>
       <c r="W176" s="49" t="n"/>
+      <c r="X176" s="75" t="inlineStr">
+        <is>
+          <t>The stated definition (absolute sum of profits and losses) is the INTRADAY/speculative one. If the system ever holds overnight, delivery turnover is computed differently (sale value). Guard the assumption explicitly, or the ITR figure is wrong the first time a position is carried.</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="30" customHeight="1" s="59">
       <c r="A177" s="38" t="inlineStr">
@@ -18757,6 +19131,11 @@
         </is>
       </c>
       <c r="W183" s="49" t="n"/>
+      <c r="X183" s="75" t="inlineStr">
+        <is>
+          <t>The replay is only as good as what was archived. Tick archival (E03-S06) is scheduled in Phase 6 and this in Phase 7 — but if archival starts late there is no history to replay and the harness has nothing to run against for months. Start archiving well before you need to replay.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="30" customHeight="1" s="59">
       <c r="A184" s="38" t="inlineStr">
@@ -19333,6 +19712,11 @@
       </c>
       <c r="V191" s="48" t="n"/>
       <c r="W191" s="49" t="n"/>
+      <c r="X191" s="75" t="inlineStr">
+        <is>
+          <t>'Verify core has no internet access, by attempt' is the right test. Note the tension with E02-S01's auth callback and E17-S01's dashboard access — both want inbound reachability. Resolve the network design ONCE here rather than three times in three stories, or the answers will disagree.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="30" customHeight="1" s="59">
       <c r="A192" s="38" t="inlineStr">
@@ -19609,6 +19993,11 @@
         </is>
       </c>
       <c r="W195" s="49" t="n"/>
+      <c r="X195" s="75" t="inlineStr">
+        <is>
+          <t>The Vault provider currently raises NotImplementedError, which fails closed correctly. Preserve that property when implementing: an unavailable secrets backend must STOP startup, never silently fall back to environment variables — which is precisely what would happen under pressure if the fallback exists.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="38" t="inlineStr">
@@ -21782,7 +22171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -21910,7 +22299,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -22438,6 +22827,48 @@
       <c r="H17" s="67" t="inlineStr">
         <is>
           <t>Image rebuilt and verified: runs non-root, imports cleanly, pins applied (SQLAlchemy 2.0.51). pip-audit re-run against the pinned set - no new vulnerabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-14</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C18" s="65" t="inlineStr">
+        <is>
+          <t>Rate limiter (E01-S03 primitive)</t>
+        </is>
+      </c>
+      <c r="D18" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>The Redis token bucket took its clock from the CALLER (time.time() in Python, computed before the await) and wrote it to the bucket unconditionally. Concurrent callers stamp their own time and then arrive at Redis in a different order, so a late-arriving request REWINDS the stored timestamp and the next caller measures elapsed time from that older mark - being granted tokens no time actually produced.</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>This is the limiter that keeps order rate under SEBI's 10/sec registration threshold. Measured: a burst of 3 with 3/sec refill let 11 of 100 concurrent callers through in 0.56s on an idle host, and 56 of 100 on a loaded one, against an honest ceiling of about 5. The control failed quietly under exactly the load it exists for, and every existing Redis test passed throughout because none of them exercised concurrency.</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr">
+        <is>
+          <t>Take the clock from Redis (redis.call('TIME')) inside the Lua instead of accepting one from the caller. One clock, read after serialisation, so neither reordering nor skew between processes can move it backwards. Post-fix: 4 of 100 allowed, which is burst plus honest refill.</t>
+        </is>
+      </c>
+      <c r="H18" s="67" t="inlineStr">
+        <is>
+          <t>A 100-way concurrent flood asserting against burst + rate x elapsed (not a flat constant, because the bucket legitimately refills during the flood). The original flat assertion is what surfaced the bug.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -20908,7 +20908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="59">
@@ -22151,6 +22151,228 @@
       <c r="G35" s="67" t="inlineStr">
         <is>
           <t>manual audit + probes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-01</t>
+        </is>
+      </c>
+      <c r="B36" s="65" t="inlineStr">
+        <is>
+          <t>E02-S04</t>
+        </is>
+      </c>
+      <c r="C36" s="65" t="inlineStr">
+        <is>
+          <t>Orderbook vs foreign order types</t>
+        </is>
+      </c>
+      <c r="D36" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E36" s="67" t="inlineStr">
+        <is>
+          <t>fetch_orderbook indexed private mapping dicts directly, so an order type this system does not model raised a bare KeyError - not in the broker taxonomy, so nothing caught it - and killed the WHOLE read. fetch_orderbook is what the 30-second reconciliation loop calls, so ONE iceberg order placed by hand in the Kite app made reconciliation return nothing at all: every other order invisible, including a genuinely unknown position, which is the condition the kill switch exists for. A personal account is also traded by a human, so foreign order types are normal here.</t>
+        </is>
+      </c>
+      <c r="F36" s="67" t="inlineStr">
+        <is>
+          <t>Safe accessors raise MappingError; fetch_orderbook skips and logs at ERROR; new fetch_raw_orders() returns untouched dicts so reconciliation can still diff on identity, which needs no enum mapping</t>
+        </is>
+      </c>
+      <c r="G36" s="67" t="inlineStr">
+        <is>
+          <t>test_broker_kite.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-02</t>
+        </is>
+      </c>
+      <c r="B37" s="65" t="inlineStr">
+        <is>
+          <t>E02-S04</t>
+        </is>
+      </c>
+      <c r="C37" s="65" t="inlineStr">
+        <is>
+          <t>Duplicate tag in the recovery path</t>
+        </is>
+      </c>
+      <c r="D37" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>find_by_client_order_id returned the FIRST row carrying our tag. Probed with a stale REJECTED order sitting ahead of the live OPEN one, it returned the rejected one - which after an ambiguous failure reads as "not placed" and invites a second submission on top of a real position.</t>
+        </is>
+      </c>
+      <c r="F37" s="67" t="inlineStr">
+        <is>
+          <t>Two or more matches now raise DuplicateBrokerOrderError naming both broker order ids. A duplicate is the failure idempotency exists to prevent and must never be resolved by picking one.</t>
+        </is>
+      </c>
+      <c r="G37" s="67" t="inlineStr">
+        <is>
+          <t>test_broker_kite.py, test_e02_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-03</t>
+        </is>
+      </c>
+      <c r="B38" s="65" t="inlineStr">
+        <is>
+          <t>E02-S05</t>
+        </is>
+      </c>
+      <c r="C38" s="65" t="inlineStr">
+        <is>
+          <t>Rate limiter wired into the real order path</t>
+        </is>
+      </c>
+      <c r="D38" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>Not the limiter in isolation - the limiter as place_order actually uses it. 60 concurrent orders capped at burst + rate x elapsed; a refused order verified never to reach the broker; 10 orderbook reads verified not to consume the order budget.</t>
+        </is>
+      </c>
+      <c r="F38" s="67" t="inlineStr">
+        <is>
+          <t>reads cannot starve an exit order</t>
+        </is>
+      </c>
+      <c r="G38" s="67" t="inlineStr">
+        <is>
+          <t>test_e02_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-04</t>
+        </is>
+      </c>
+      <c r="B39" s="65" t="inlineStr">
+        <is>
+          <t>E02-S01</t>
+        </is>
+      </c>
+      <c r="C39" s="65" t="inlineStr">
+        <is>
+          <t>Ambiguous failure -&gt; recovery loop</t>
+        </is>
+      </c>
+      <c r="D39" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>End to end with a broker that accepts the order and THEN drops the connection. Recovery finds exactly one order by tag; repeated recovery calls place nothing; a genuinely absent order reports absent (which is what authorises a resubmission); a foreign order in the book does not break the lookup.</t>
+        </is>
+      </c>
+      <c r="F39" s="67" t="inlineStr">
+        <is>
+          <t>exactly one order at the broker after timeout + recovery</t>
+        </is>
+      </c>
+      <c r="G39" s="67" t="inlineStr">
+        <is>
+          <t>test_e02_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-05</t>
+        </is>
+      </c>
+      <c r="B40" s="65" t="inlineStr">
+        <is>
+          <t>E02-S06</t>
+        </is>
+      </c>
+      <c r="C40" s="65" t="inlineStr">
+        <is>
+          <t>Instrument sync against the real repository</t>
+        </is>
+      </c>
+      <c r="D40" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E40" s="67" t="inlineStr">
+        <is>
+          <t>Dump lands in Postgres and the symbol resolves afterwards; a re-run updates in place rather than duplicating; a non-standard 0.01 tick survives the round trip and a price rounded for it is verified on-grid.</t>
+        </is>
+      </c>
+      <c r="F40" s="67" t="inlineStr">
+        <is>
+          <t>full path: dump -&gt; stored tick -&gt; side-aware rounding -&gt; valid price</t>
+        </is>
+      </c>
+      <c r="G40" s="67" t="inlineStr">
+        <is>
+          <t>test_e02_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-06</t>
+        </is>
+      </c>
+      <c r="B41" s="65" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="C41" s="65" t="inlineStr">
+        <is>
+          <t>Test isolation</t>
+        </is>
+      </c>
+      <c r="D41" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E41" s="67" t="inlineStr">
+        <is>
+          <t>My E2E fixture cleared the instruments table for a clean count. It passed alone and failed in the full suite: other tests hang bars and positions off those rows, so the DELETE hit a foreign key. Wiping a shared table to make an assertion convenient is the wrong trade.</t>
+        </is>
+      </c>
+      <c r="F41" s="67" t="inlineStr">
+        <is>
+          <t>Tests now use their own E02X symbol prefix and assert only on that, so they hold regardless of suite order</t>
+        </is>
+      </c>
+      <c r="G41" s="67" t="inlineStr">
+        <is>
+          <t>test_e02_end_to_end.py</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -20908,7 +20908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" s="59">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="59">
@@ -22373,6 +22373,117 @@
       <c r="G41" s="67" t="inlineStr">
         <is>
           <t>test_e02_end_to_end.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-07</t>
+        </is>
+      </c>
+      <c r="B42" s="65" t="inlineStr">
+        <is>
+          <t>E02-S06</t>
+        </is>
+      </c>
+      <c r="C42" s="65" t="inlineStr">
+        <is>
+          <t>ACC: limit price always snapped to tick</t>
+        </is>
+      </c>
+      <c r="D42" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E42" s="67" t="inlineStr">
+        <is>
+          <t>E02-S06's acceptance criterion is that a limit price is ALWAYS snapped to a valid tick before submission. round_to_tick existed, was correct, and was thoroughly unit-tested - and was never called in the order path. _build_params passed request.limit_price straight through.</t>
+        </is>
+      </c>
+      <c r="F42" s="67" t="inlineStr">
+        <is>
+          <t>A stop derived from ATR is essentially never on a 0.05 grid by accident, so the exchange would have rejected every computed stop. The helper passing its own tests is precisely why this went unnoticed.</t>
+        </is>
+      </c>
+      <c r="G42" s="67" t="inlineStr">
+        <is>
+          <t>test_broker_hardening.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-08</t>
+        </is>
+      </c>
+      <c r="B43" s="65" t="inlineStr">
+        <is>
+          <t>E02-S01</t>
+        </is>
+      </c>
+      <c r="C43" s="65" t="inlineStr">
+        <is>
+          <t>ACC: the flow must be completable</t>
+        </is>
+      </c>
+      <c r="D43" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; FIXED</t>
+        </is>
+      </c>
+      <c r="E43" s="67" t="inlineStr">
+        <is>
+          <t>Nothing in the package constructed an authenticated KiteConnect client. Every piece of E02 existed and the flow could not actually be run - a gap no unit test can surface, because each unit passes.</t>
+        </is>
+      </c>
+      <c r="F43" s="67" t="inlineStr">
+        <is>
+          <t>Added session.py: build_client() and exchange_request_token(), completing the redirect login. The raw token is revealed at exactly two points, both handing it straight to the SDK, and a test asserts the reveal sites stay at three or fewer.</t>
+        </is>
+      </c>
+      <c r="G43" s="67" t="inlineStr">
+        <is>
+          <t>test_broker_hardening.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="65" t="inlineStr">
+        <is>
+          <t>QA-E02-09</t>
+        </is>
+      </c>
+      <c r="B44" s="65" t="inlineStr">
+        <is>
+          <t>E02-S04</t>
+        </is>
+      </c>
+      <c r="C44" s="65" t="inlineStr">
+        <is>
+          <t>BA: acceptance criteria re-checked against code</t>
+        </is>
+      </c>
+      <c r="D44" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E44" s="67" t="inlineStr">
+        <is>
+          <t>Re-read every E02 acceptance criterion against the built code rather than against intent. Verified: no retry loop anywhere in the mutating path; the access token absent from every logged form including exc_info tracebacks; market protection impossible to omit or zero.</t>
+        </is>
+      </c>
+      <c r="F44" s="67" t="inlineStr">
+        <is>
+          <t>two criteria were NOT met and are logged above as QA-E02-07 and QA-E02-08</t>
+        </is>
+      </c>
+      <c r="G44" s="67" t="inlineStr">
+        <is>
+          <t>test_broker_security.py</t>
         </is>
       </c>
     </row>
@@ -22393,7 +22504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -22571,7 +22682,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" s="59">
@@ -23091,6 +23202,91 @@
       <c r="H18" s="67" t="inlineStr">
         <is>
           <t>A 100-way concurrent flood asserting against burst + rate x elapsed (not a flat constant, because the bucket legitimately refills during the flood). The original flat assertion is what surfaced the bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-15</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C19" s="65" t="inlineStr">
+        <is>
+          <t>Broker auth / login URL</t>
+        </is>
+      </c>
+      <c r="D19" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>login_url() interpolated api_key into the Kite URL with no validation or encoding. A value of 'realkey&amp;redirect_uri=https://evil.example.com' produces a perfectly VALID Kite login URL that returns the request_token to somebody else. CRLF in the same position was equally accepted.</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>This defeats the anti-phishing design from the other side. The operator navigates from their own bookmark exactly as intended, lands on a genuine Zerodha page, and hands the request_token to an attacker who exchanges it with their own api_secret. Requires config/env write access - but config is editable through the Admin UI (E18-S02), and a mis-pasted key with a stray '&amp;' fails the same way.</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr">
+        <is>
+          <t>Validate rather than escape: a Kite api_key is alphanumeric, so anything else is a mis-paste or an attempt to steer the flow. Encoding would quietly carry the mistake into a URL that then fails at the broker for an unrelated-looking reason.</t>
+        </is>
+      </c>
+      <c r="H19" s="67" t="inlineStr">
+        <is>
+          <t>5 hostile api_keys refused (&amp; injection, CRLF, space, fragment, query), a real key still builds, and the error is asserted not to echo a 5000-char value into the log</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>QA-SEC-16</t>
+        </is>
+      </c>
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="inlineStr">
+        <is>
+          <t>Order logging / symbol handling</t>
+        </is>
+      </c>
+      <c r="D20" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>A newline in an instrument symbol forged a whole log line. Observed output: 'placing BUY MARKET x1 for INFY
+2026-01-01 CRITICAL kill switch disarmed (tag=...)' - a second, entirely fictional CRITICAL entry written by the order logger.</t>
+        </is>
+      </c>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>Symbols come from the broker's daily dump, which is external data this system does not author. QA-SEC-03 established exactly this for Redis keys; the same untrusted value also reaches the order log line, and application logs are what an incident is reconstructed from. A forgeable log line is a real problem even though nothing crashes.</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr">
+        <is>
+          <t>OrderRequest.symbol now validated against the same allowlist as the Redis key builder - one definition of what a symbol may contain, applied wherever untrusted symbol text crosses a boundary.</t>
+        </is>
+      </c>
+      <c r="H20" s="67" t="inlineStr">
+        <is>
+          <t>6 hostile symbols refused (newline, CRLF, colon, glob, over-length, empty) plus a CONTROL that real Indian symbols still work: M&amp;M, BAJAJ-AUTO, L&amp;TFH, NIFTY.NS, IDEA_EQ</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -6258,7 +6258,7 @@
       <c r="O23" s="46" t="n"/>
       <c r="P23" s="46" t="n"/>
       <c r="Q23" s="47" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R23" s="39" t="n">
         <v>7</v>
@@ -6288,7 +6288,9 @@
       </c>
       <c r="V23" s="48" t="inlineStr">
         <is>
-          <t>Auth manager, session lifecycle and the login-URL builder are built and tested (38 security tests). SECURITY CHANGE from the original tasks: the re-auth notice carries NO login link. ReauthNotice has no url/link field at all, so the phishing reflex cannot be re-introduced by a future edit - a test asserts the absence. Remaining 20%: the request_token -&gt; access_token HTTP exchange needs live credentials to verify end to end, and the callback endpoint belongs with E17-S01's dashboard (see the E17-S01 concern about localhost vs phone access - same network decision).</t>
+          <t>Auth manager, session lifecycle, login-URL builder AND the client factory are built and tested. session.py now completes the redirect login: build_client() and exchange_request_token(). The raw token is revealed at exactly two points, both handing it straight to the SDK, with a test that fails if a third appears.
+SECURITY: the re-auth notice carries NO login link - ReauthNotice has no url field at all, so the phishing reflex cannot be reintroduced by a later edit. The api_key is validated before it reaches the login URL (QA-SEC-15): unvalidated, an injected redirect_uri steers your request_token to an attacker while you are on a genuine Zerodha page.
+Remaining 10%: verifying the exchange against a live request_token, and the callback endpoint - which is the same network decision as E17-S01's dashboard access (localhost vs phone). Decide them together.</t>
         </is>
       </c>
       <c r="W23" s="49" t="n"/>
@@ -6576,7 +6578,8 @@
       <c r="W26" s="49" t="n"/>
       <c r="X26" s="75" t="inlineStr">
         <is>
-          <t>client_order_id is 8-64 chars, but the only carrier the broker offers is Kite's `tag` parameter, which is length-limited (verify the current limit in the developer console — historically 20 chars). If the tag cannot hold the full id, E15-S02's recovery path 'query by client_order_id' cannot round-trip and the idempotency guarantee is decorative. Decide the truncation or mapping scheme HERE, not in E15.</t>
+          <t>RESOLVED Aug 2026. Kite's tag is alphanumeric, max 20 chars, and IS returned in the orderbook - confirmed against the API docs. broker_tag() truncates the sha256 id deterministically in one place, and a test asserts the submission and recovery paths produce the same value. A non-alphanumeric id is refused rather than silently mangled.
+Two further defects were found here by QA and fixed: a foreign order type used to kill the whole orderbook read (QA-E02-01), and a duplicate tag used to be resolved by picking one (QA-E02-02).</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6676,8 @@
       <c r="W27" s="49" t="n"/>
       <c r="X27" s="75" t="inlineStr">
         <is>
-          <t>Zerodha's 10/sec is enforced ACCOUNT-WIDE, not per app or per connection. A Redis bucket covers this system's processes but not orders you place manually in the Kite app at the same time. Running at 3/sec leaves headroom, but either accept that or document that manual trading during a session is prohibited.</t>
+          <t>RESOLVED Aug 2026, and CONFIRMED by Zerodha: ten OPS is account-specific, regardless of the number of apps. The bucket is account-scoped in Redis, orders and data have separate budgets so a backfill cannot starve an exit, and the config refuses ten or more per second in code.
+STILL LIVE: the budget is shared with anything else trading the account, including the Kite mobile app. Running at 3/sec against a cap of 10 leaves that headroom deliberately - but manual trading during a session eats into it.</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6772,7 @@
       <c r="W28" s="49" t="n"/>
       <c r="X28" s="75" t="inlineStr">
         <is>
-          <t>Tick rounding direction is not neutral. Rounding a BUY limit up and a SELL limit down crosses the spread and pays it; rounding both the same way biases fills systematically. Specify direction per side and prove it against a real instrument with a non-0.05 tick.</t>
+          <t>RESOLVED Aug 2026, and it was worse than this concern described. Side-aware rounding was written and tested (buy down, sell up, so neither side pays more than intended) - and then never called in the order path. The BA pass caught it: E02-S06's acceptance criterion says a limit price is ALWAYS snapped, and ATR-derived stops are essentially never on a 0.05 grid, so the exchange would have rejected every computed stop. Now snapped at the boundary, trigger prices too, failing CLOSED when no tick resolver is wired.</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6866,8 @@
       <c r="W29" s="49" t="n"/>
       <c r="X29" s="75" t="inlineStr">
         <is>
-          <t>Caching margin then sizing on it is a time-of-check/time-of-use gap — margin can fall between the fetch and the order, especially right after another fill. A staleness guard bounds AGE but not CHANGE. Re-verify immediately before submission for the first position of the day and after any fill.</t>
+          <t>RESOLVED Aug 2026. margin_for_sizing() refuses a snapshot older than the TTL, closing the time-of-check/time-of-use gap - margin falls after every fill, so a stale reading can authorise a position the account cannot carry.
+NOTE the bound is on AGE, not on change. Re-fetching after each fill is the caller's responsibility and belongs with E14-S06.</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7046,7 @@
       <c r="W31" s="49" t="n"/>
       <c r="X31" s="75" t="inlineStr">
         <is>
-          <t>The unmapped-error path is the one that matters. A new Kite error code arriving mid-session must fail closed — treat as ambiguous, query by id, never retry — rather than falling through to a generic retry. 'Log loudly' is not a behaviour; specify the default disposition for unknown codes.</t>
+          <t>RESOLVED Aug 2026. classify(mutating=True) makes ANY unrecognised failure AmbiguousOrderError, routing to query-by-tag rather than a retry; only a 429 is retryable. Verified by mutation testing - breaking the fail-closed rule fails the test. The default disposition for an unknown code is now the safe one rather than an unspecified one.</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7330,8 @@
       <c r="W34" s="49" t="n"/>
       <c r="X34" s="75" t="inlineStr">
         <is>
-          <t>Three constraints collide. Kite's historical endpoint is rate-limited, caps the date range per request by interval, and is a PAID add-on — so this cannot start until blocker B4 is resolved and the subscription exists. Also, a multi-hour backfill during market hours competes with live data against the same account-wide limit. Schedule it outside the session.</t>
+          <t>PARTLY RESOLVED Aug 2026. Blocker B4 is gone: historical data is no longer a separate paid add-on. The free Personal tier carries NO data; Connect at Rs.500/month bundles real-time WebSocket AND historical candles. So this story needs a Rs.500 subscription, not Rs.2500.
+STILL LIVE: the rate limit and the per-request date-range cap remain, and a multi-hour backfill during market hours competes with live data on the same account-wide budget. Schedule it outside the session.</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8198,7 @@
       </c>
       <c r="E45" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development In-Progress</t>
         </is>
       </c>
       <c r="F45" s="41" t="inlineStr">
@@ -8228,7 +8234,9 @@
       <c r="N45" s="45" t="n"/>
       <c r="O45" s="46" t="n"/>
       <c r="P45" s="46" t="n"/>
-      <c r="Q45" s="47" t="n"/>
+      <c r="Q45" s="47" t="n">
+        <v>0.85</v>
+      </c>
       <c r="R45" s="39" t="n">
         <v>6</v>
       </c>
@@ -8253,11 +8261,17 @@
 • 🟠 Indicators are marked stale rather than computing across the hole</t>
         </is>
       </c>
-      <c r="V45" s="48" t="n"/>
+      <c r="V45" s="48" t="inlineStr">
+        <is>
+          <t>WebSocket client built on the `websockets` library, NOT KiteTicker - which resolves blocker B7 and the Twisted-to-asyncio bridging problem together. Wire protocol implemented from the documented byte-level spec: frame splitting, ltp/quote/full packets, index packets, market depth. Reconnection with capped exponential backoff and jitter; a connection that survives 60s resets the backoff so one bad hour does not pin it at maximum all day. Every reconnect emits a FeedGap BEFORE any tick that follows, so downstream marks indicators stale rather than computing across a hole. Connections open inside `async with` so a reconnect cannot leak one and exhaust Kite's 3-connection cap. An idle socket (no frame for 45s) is treated as dead - the failure a TCP check reports healthy.
+REMAINING 15%: the connection itself needs live credentials, and one real packet per mode must be captured and asserted against. The parser is verified self-consistent (tests build packets to the same spec they parse) which proves it matches the SPEC, not that the spec matches the exchange.</t>
+        </is>
+      </c>
       <c r="W45" s="49" t="n"/>
       <c r="X45" s="75" t="inlineStr">
         <is>
-          <t>KiteTicker is Twisted/autobahn-based and thread-oriented, not asyncio-native, so the bridge needs a deliberate boundary. autobahn is also the component carrying CVE-2020-35678 (blocker B7). Separately: Kite caps concurrent WebSocket connections (3) and instruments per connection. A 200-symbol universe fits, but the reconnect path must not leak connections or you hit the cap after a few reconnects and the feed dies for good.</t>
+          <t>RESOLVED Aug 2026 - and it resolved blocker B7 at the same time. Built on the `websockets` library rather than KiteTicker, so autobahn 19.11.2 (CVE-2020-35678) is never imported and there is no Twisted reactor to bridge. Connection-leak and reconnect-storm hazards both addressed explicitly.
+STILL LIVE: the packet offsets are verified SELF-CONSISTENTLY only. Capture one real packet per mode and assert against it before this feeds anything that trades - a transposed field produces plausible numbers, which is the failure that survives review.</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8298,7 @@
       </c>
       <c r="E46" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F46" s="41" t="inlineStr">
@@ -8320,7 +8334,9 @@
       <c r="N46" s="45" t="n"/>
       <c r="O46" s="46" t="n"/>
       <c r="P46" s="46" t="n"/>
-      <c r="Q46" s="47" t="n"/>
+      <c r="Q46" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R46" s="39" t="n">
         <v>5</v>
       </c>
@@ -8339,7 +8355,11 @@
         </is>
       </c>
       <c r="U46" s="48" t="n"/>
-      <c r="V46" s="48" t="n"/>
+      <c r="V46" s="48" t="inlineStr">
+        <is>
+          <t>Null/zero/negative price, negative volume, and clock skew beyond 5s all refused. Added beyond the story: session volume going BACKWARDS is refused - cumulative volume cannot fall, so a decrease means a replayed or out-of-order packet, and accepting it makes every volume-delta negative. Every rejection counted by reason with a bounded sample.</t>
+        </is>
+      </c>
       <c r="W46" s="49" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1" s="59">
@@ -8365,7 +8385,7 @@
       </c>
       <c r="E47" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F47" s="41" t="inlineStr">
@@ -8401,7 +8421,9 @@
       <c r="N47" s="45" t="n"/>
       <c r="O47" s="46" t="n"/>
       <c r="P47" s="46" t="n"/>
-      <c r="Q47" s="47" t="n"/>
+      <c r="Q47" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R47" s="39" t="n">
         <v>3</v>
       </c>
@@ -8418,7 +8440,11 @@
         </is>
       </c>
       <c r="U47" s="48" t="n"/>
-      <c r="V47" s="48" t="n"/>
+      <c r="V47" s="48" t="inlineStr">
+        <is>
+          <t>Bounded LRU per instrument on (exchange_ts, ltp, volume, last_qty). Per-instrument rather than global so one busy symbol cannot evict a quiet one's history - tested explicitly.</t>
+        </is>
+      </c>
       <c r="W47" s="49" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1" s="59">
@@ -8444,7 +8470,7 @@
       </c>
       <c r="E48" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F48" s="41" t="inlineStr">
@@ -8480,7 +8506,9 @@
       <c r="N48" s="45" t="n"/>
       <c r="O48" s="46" t="n"/>
       <c r="P48" s="46" t="n"/>
-      <c r="Q48" s="47" t="n"/>
+      <c r="Q48" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R48" s="39" t="n">
         <v>4</v>
       </c>
@@ -8502,11 +8530,15 @@
           <t>• 🔴 A single injected bad print does not change any indicator value</t>
         </is>
       </c>
-      <c r="V48" s="48" t="n"/>
+      <c r="V48" s="48" t="inlineStr">
+        <is>
+          <t>THE COLD-START GAP IS CLOSED. The bound is max(5 x ATR%, 2%), but ATR does not exist at 09:15 - exactly when prints are most erratic. A missing ATR resolving to 'no limit' would leave the filter inert when it matters most. It resolves to the 2% floor instead, and cold_start() reports the condition so a health panel can show it. Circuit band checked independently and applies even to the first tick, where there is no previous price. A rejected outlier does NOT move the baseline - otherwise a second bad print would look reasonable.</t>
+        </is>
+      </c>
       <c r="W48" s="49" t="n"/>
       <c r="X48" s="75" t="inlineStr">
         <is>
-          <t>The filter is max(5 x ATR%, 2%) — but ATR comes from the indicator engine, which is NOT ready at session start. At 09:15, exactly when prints are most erratic, the ATR term is unavailable. Define cold-start behaviour explicitly: the 2% floor must apply on its own until ATR is ready, and must not silently evaluate to 'no limit'.</t>
+          <t>RESOLVED Aug 2026. The cold-start behaviour is now explicit rather than implied: no ATR means the 2% floor applies on its own, and OutlierFilter.cold_start() exposes the condition so it can be asserted in a test and shown on a health panel. Four tests cover the window specifically.</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8565,7 @@
       </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F49" s="41" t="inlineStr">
@@ -8569,7 +8601,9 @@
       <c r="N49" s="45" t="n"/>
       <c r="O49" s="46" t="n"/>
       <c r="P49" s="46" t="n"/>
-      <c r="Q49" s="47" t="n"/>
+      <c r="Q49" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R49" s="39" t="n">
         <v>3</v>
       </c>
@@ -8586,7 +8620,11 @@
         </is>
       </c>
       <c r="U49" s="48" t="n"/>
-      <c r="V49" s="48" t="n"/>
+      <c r="V49" s="48" t="inlineStr">
+        <is>
+          <t>RawTick -&gt; domain Tick, running LAST so a tick that failed any check never becomes a domain object. Prices exact via Decimal from integer paise.</t>
+        </is>
+      </c>
       <c r="W49" s="49" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1" s="59">
@@ -8612,7 +8650,7 @@
       </c>
       <c r="E50" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F50" s="41" t="inlineStr">
@@ -8648,7 +8686,9 @@
       <c r="N50" s="45" t="n"/>
       <c r="O50" s="46" t="n"/>
       <c r="P50" s="46" t="n"/>
-      <c r="Q50" s="47" t="n"/>
+      <c r="Q50" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R50" s="39" t="n">
         <v>5</v>
       </c>
@@ -8672,11 +8712,15 @@
 • Consumers can distinguish final from in-progress bars</t>
         </is>
       </c>
-      <c r="V50" s="48" t="n"/>
+      <c r="V50" s="48" t="inlineStr">
+        <is>
+          <t>Bars align to the SESSION start, delegating to MarketCalendar.bar_open_time so there is one definition of a boundary. Timeframes built INDEPENDENTLY from ticks rather than cascaded - cascading means one bad 1m bar propagates silently into every higher timeframe. Bar volume is the DELTA of cumulative session volume, not the raw total. A sealed bar NEVER mutates: a late tick is dropped and counted, because the opening range is sealed at 09:30 and levels derived from it are already sizing positions. CAS-scope bars covering the 15:15 call auction are marked.</t>
+        </is>
+      </c>
       <c r="W50" s="49" t="n"/>
       <c r="X50" s="75" t="inlineStr">
         <is>
-          <t>Cascading 1m-&gt;5m-&gt;15m-&gt;1h means one bad 1m bar propagates silently into every higher timeframe with no independent check. Also the CAS window (15:15-15:30 for CAS stocks) is a call auction, not continuous trading — bars built from it are not comparable to intraday bars and should be flagged or excluded.</t>
+          <t>RESOLVED Aug 2026. Timeframes are built independently from ticks rather than cascaded, so a defect in the 1m path cannot reappear in the hourly series. CAS-window bars are marked. Late ticks are dropped and counted rather than mutating a sealed bar.</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8747,7 @@
       </c>
       <c r="E51" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
@@ -8739,7 +8783,9 @@
       <c r="N51" s="45" t="n"/>
       <c r="O51" s="46" t="n"/>
       <c r="P51" s="46" t="n"/>
-      <c r="Q51" s="47" t="n"/>
+      <c r="Q51" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R51" s="39" t="n">
         <v>3</v>
       </c>
@@ -8756,7 +8802,11 @@
         </is>
       </c>
       <c r="U51" s="48" t="n"/>
-      <c r="V51" s="48" t="n"/>
+      <c r="V51" s="48" t="inlineStr">
+        <is>
+          <t>Carry-forward bars flagged synthetic with zero volume. The flag is the point: an illiquid symbol printing identical bars looks like a volatility collapse to an indicator that cannot tell 'did not move' from 'did not trade'.</t>
+        </is>
+      </c>
       <c r="W51" s="49" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1" s="59">
@@ -8782,7 +8832,7 @@
       </c>
       <c r="E52" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F52" s="41" t="inlineStr">
@@ -8818,7 +8868,9 @@
       <c r="N52" s="45" t="n"/>
       <c r="O52" s="46" t="n"/>
       <c r="P52" s="46" t="n"/>
-      <c r="Q52" s="47" t="n"/>
+      <c r="Q52" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" s="39" t="n">
         <v>3</v>
       </c>
@@ -8835,7 +8887,11 @@
         </is>
       </c>
       <c r="U52" s="48" t="n"/>
-      <c r="V52" s="48" t="n"/>
+      <c r="V52" s="48" t="inlineStr">
+        <is>
+          <t>Quote state to state:quote:{symbol} with a TTL (a session key with no expiry is read next morning as live), plus optional tick archival to the stream. read_fresh() is separate from read() so staleness is an explicit caller decision rather than something silently tolerated.</t>
+        </is>
+      </c>
       <c r="W52" s="49" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1" s="59">
@@ -14882,6 +14938,12 @@
       <c r="U127" s="48" t="n"/>
       <c r="V127" s="48" t="n"/>
       <c r="W127" s="49" t="n"/>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>WIRE THE TICK RESOLVER. KiteTradingAdapter takes a tick_size_for callable and REFUSES any priced order when it is absent - fail-closed, so nothing slips through silently, but it means no LIMIT or SL order can be placed until this gateway connects it to the instrument repository (which already holds the per-instrument tick size from E02-S06's sync).
+This is the deliberate loose end left by E02: the repository is in scope here and was not there. Until it is wired, every priced order raises OrderRejectedError with reason_code NO_TICK_RESOLVER.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="30" customHeight="1" s="59">
       <c r="A128" s="38" t="inlineStr">
@@ -20307,7 +20369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="59" min="1" max="1"/>
@@ -20410,12 +20472,10 @@
       <c r="G5" s="46" t="n"/>
       <c r="H5" s="49" t="inlineStr">
         <is>
-          <t>PARTIALLY RESOLVED 7 Aug 2026 — the MECHANIC is confirmed, the VALUE is not.
-ANSWERED: the Algo-ID is CLIENT-SUPPLIED PER ORDER, not injected server-side by the broker. kiteconnect 5.2.1's place_order() takes an `algo_id` parameter, documented as "an optional algo ID to associate with the order". Verified against the installed SDK signature, not from docs. doctor now asserts this at runtime.
-This settles the architectural question: the system must carry an Algo-ID in config and attach it to every order — which is what BrokerConfig.algo_id and the live-mode validator in common/config.py already assume. No design change needed.
-STILL OPEN: WHICH value to send. For self-developed personal algos under 10 orders/sec, a GENERIC exchange-issued Algo-ID applies rather than a per-strategy registered one — that needs confirming with Zerodha, and is the remaining content of the Day-1 email.
-Downgraded from a design blocker to a paperwork question. It no longer blocks E02-S04 from being BUILT, only from going live.
-[YOUR ORIGINAL NOTE: "Research on this topic, and arrive at a relevant answer"]</t>
+          <t>NARROWED Aug 2026 from a design question to a one-line email.
+SEBI's framework: retail traders may run their own algorithms on their own account, and under 10 orders/sec no separate exchange registration is needed - the BROKER handles the Strategy ID tagging. Zerodha's own compliance thread covers static IP, the 10 OPS cap and market protection in detail and never mentions algo_id at all.
+Working assumption: leave algo_id unset and Zerodha tags it. The code already reflects this - it is sent only when configured, and an empty value means let-the-broker-tag-it, not forgot. BrokerConfig.algo_id being optional was already correct.
+This is inference from absence, so it still wants one confirmation before live. Not a design blocker.</t>
         </is>
       </c>
     </row>
@@ -20526,7 +20586,7 @@
       </c>
       <c r="E8" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -20537,8 +20597,10 @@
       <c r="G8" s="46" t="n"/>
       <c r="H8" s="49" t="inlineStr">
         <is>
-          <t>SPRINT 1 — DAY 1. Ask in the SAME email as B1; one round trip instead of two.
-Working figure is ~Rs.500/month for the historical data add-on on top of the Kite Connect subscription. Affects the E03-S03 budget only — it does not block any code being written, so it should never hold up the sprint. User has confirmed they will handle pricing themselves; this is a confirm-the-number task, not a decision.</t>
+          <t>RESOLVED Aug 2026 by checking Zerodha's own pricing page rather than the working assumption.
+Kite Connect was restructured. The Personal tier is FREE - order management, GTT, alerts, margins, portfolio - but carries NO data at all, so it cannot feed this system. Connect at Rs.500/month per app adds real-time data over WebSocket AND historical candle data.
+There is no separate historical add-on any more. Total cost for what this system needs is Rs.500/month, not the Rs.500 + Rs.2000 the design documents assumed. broker/profiles.py updated: historical_data_extra_cost is now False.
+ACTION: subscribe. It is the cheapest item on the critical path and it unblocks E03-S03 and all of E05.</t>
         </is>
       </c>
     </row>
@@ -20622,7 +20684,9 @@
 4. Record it: system.static_ip in system.yaml and EXPECTED_EGRESS_IP in .env.
 5. Verify BOTH directions: make doctor compares live egress against config and fails on mismatch; then test the negative case — an order attempt from a non-whitelisted address must be REJECTED. Only the negative test proves the whitelist is actually enforcing.
 Two things to know before picking a provider: the static IP applies to ORDER ENDPOINTS ONLY (quotes, WebSocket and positions work from any IP, so a data-only fallback needs no whitelisted address); and each IP binds to ONE Zerodha account.
-[YOUR ORIGINAL NOTE: "Explain on the procedure for this"]</t>
+[YOUR ORIGINAL NOTE: "Explain on the procedure for this"]
+CONFIRMED Aug 2026 from Zerodha: all order requests from an unregistered IP will be rejected. Whitelist at the developer console, Profile, IP Whitelist; up to two IPs (one primary mandatory, one optional secondary); shareable only with immediate family.
+IMPORTANT AND USEFUL: validation applies to ORDER endpoints only. Quotes, historical data and the WebSocket work from anywhere - so ALL of E03, E04, E05 and E06 can be built and tested before the VPS exists. Only order placement is gated.</t>
         </is>
       </c>
     </row>
@@ -20664,12 +20728,11 @@
       </c>
       <c r="H11" s="49" t="inlineStr">
         <is>
-          <t>FOUND 7 Aug 2026 by pip-audit during the Sprint 1 security pass.
-kiteconnect 5.2.1 declares `autobahn[twisted]==19.11.2` — an EXACT pin to a 2019 release carrying CVE-2020-35678 (redirect header injection, fixed in 20.12.3). autobahn is the WebSocket transport behind KiteTicker, i.e. the live market-data path.
-CANNOT BE FIXED LOCALLY. pip will install autobahn 26.7.1 if asked, but that violates kiteconnect's declared pin and is a 7-year API jump in the exact layer KiteTicker is built on. Doing that blind to the market-data path is a worse risk than the CVE. NOT ATTEMPTED — deliberately.
-EXPOSURE ASSESSMENT (why this is On Hold rather than Active): the flaw needs an attacker able to influence a redirect response. This client connects to one known endpoint (wss://ws.kite.trade) over TLS, and the compose design already puts the core network on `internal: true` with egress filtered to broker hosts. That is not a fix, but it means the practical exposure is small and does not block development.
-ACTIONS: (1) add to the Zerodha email alongside B1/B4 — ask when the autobahn pin will be updated; (2) at E02-S03, verify TLS cert validation is ON and the endpoint is not permitted to redirect; (3) re-run pip-audit each sprint; (4) re-evaluate before live trading — this belongs on PRE_LIVE_CHECKLIST.
-Same family as B2: both are the broker SDK holding the system back.</t>
+          <t>RE-SCOPED Aug 2026 - there is a real way out, and it removes a second problem at the same time.
+kiteconnect 5.2.1 (July 2026, the latest) STILL pins autobahn[twisted]==19.11.2. Upstream has not fixed it and will not on our schedule.
+BUT the Kite WebSocket protocol is fully documented - endpoint wss://ws.kite.trade, JSON subscribe messages, and byte-level packet layouts for ltp (8B), quote (44B) and full (184B). So E05-S01 can be built on the websockets library instead of KiteTicker. That makes the vulnerable autobahn code UNREACHABLE (never imported) and simultaneously removes the Twisted-to-asyncio bridging problem E05-S01 was carrying.
+Honest caveat: autobahn stays INSTALLED, because kiteconnect hard-depends on it, so pip-audit will keep flagging it. The defensible position is installed-but-unreachable, provable with a test asserting autobahn is not in sys.modules after importing the app.
+KiteMarketDataAdapter.subscribe() already raises NotImplementedError naming this decision, so nobody wires up the vulnerable path by reflex.</t>
         </is>
       </c>
     </row>
@@ -20711,6 +20774,49 @@
 WHY IT WAS BLOCKING: a boolean records THAT a bar was adjusted, not BY HOW MUCH. The second corporate action therefore has nothing to build on, and adjusting the stored price in place compounds the first adjustment with no error and no failing test. Safety-critical: a wrong adjustment is silent, and it invalidates every backtest over that symbol rather than throwing.
 RESOLUTION: raw OHLC is immutable (BR-15). `corporate_action` holds the actions (BR-19); each bar carries `price_adj_factor` and `volume_adj_factor`; the repository applies them on read. Recompute rebuilds from the full history, so it is idempotent and a bad action is fixed by correcting the row.
 NOT A BLOCKER ANYMORE, but E03-S02 stays open: the adjustment ENGINE is done, the corporate action FEED is not, and that needs a data source — which is the same credential dependency as B1/B4, not a design gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="inlineStr">
+        <is>
+          <t>NSE blocks programmatic access to its public data</t>
+        </is>
+      </c>
+      <c r="C13" s="48" t="inlineStr">
+        <is>
+          <t>E04 (all 7 stories), E03-S01, E03-S02 feed</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>Prove reachability from the target host before writing fetchers</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="49" t="inlineStr">
+        <is>
+          <t>FOUND Aug 2026 during next-steps research. NSE actively blocks scripted access to its website, and in 2025 NSE and BSE restricted website access for overseas users entirely.
+SCOPE - this affects DAILY REFERENCE DATA, not live market data. Live ticks and historical candles come from Kite Connect, an authenticated commercial API, and are completely unaffected. What is affected is the 05:30 fetch of ASM/GSM, T2T, F&amp;O ban, circuit bands, CAS scope, the earnings calendar, bhavcopy and corporate actions - all of which come from NSE's public site.
+It is a fetch-RELIABILITY problem, not a wall. The data is public; the difficulty is that the site is hostile to automation and changes shape without notice. Kite's instrument dump does NOT help - it carries token, symbol, tick size, lot size and segment, with no series, ASM, GSM, T2T or ban field (verified against the API docs).
+MITIGATIONS: jugaad-data (actively maintained, with caching specifically to avoid being blocked); nsefin for corporate actions, which is also E03-S02's missing feed; BSE as a fallback since ~90% of NSE equities are dual-listed; Zerodha's consolidated scrip sheet as a cross-check only (no SLA). The India-hosted VPS already required by constraint C1 sidesteps the geo-restriction.
+WHY IT IS SURVIVABLE: the fetch runs at 05:30, hours before the open, so a failure has a long runway for a retry, a fallback source or a manual override. E04-S01's acceptance criterion already says a fetch failure blocks the trading day rather than proceeding blind - the right posture: a bad fetch costs a trading day, not money.
+ACTION: spend an hour proving NSE reachability from the target environment before writing fetchers. That assumption sits under 8 stories and roughly 10 days of work.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -8917,7 +8917,7 @@
       </c>
       <c r="E53" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F53" s="41" t="inlineStr">
@@ -8953,7 +8953,9 @@
       <c r="N53" s="45" t="n"/>
       <c r="O53" s="46" t="n"/>
       <c r="P53" s="46" t="n"/>
-      <c r="Q53" s="47" t="n"/>
+      <c r="Q53" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R53" s="39" t="n">
         <v>5</v>
       </c>
@@ -8977,11 +8979,15 @@
 • 200 symbols × 6 timeframes update in &lt; 50ms total</t>
         </is>
       </c>
-      <c r="V53" s="48" t="n"/>
+      <c r="V53" s="48" t="inlineStr">
+        <is>
+          <t>Incremental framework with the SEEDING CONVENTION FIXED and verified by experiment, not assumed. TA-Lib emits EMA(N) first at index N-1 seeded from the simple mean of the first N; RSI and ATR use Wilder smoothing seeded from the mean of the first N samples. A streaming EMA seeded from the first value stays close forever and never equals it - which passes a 'looks right' review and fails the four-decimal acceptance criterion. Every indicator asserted against TA-Lib batch directly.</t>
+        </is>
+      </c>
       <c r="W53" s="49" t="n"/>
       <c r="X53" s="75" t="inlineStr">
         <is>
-          <t>'Incremental matches batch to 4dp' is only well-defined once the SEEDING convention is fixed. TA-Lib's EMA seeds from an SMA of the first N periods; a naive streaming EMA seeds from the first value, and the two never converge exactly. Pick one, document it, and make warm-up AND state-restore use the same one — otherwise a restart silently changes indicator values, and therefore signals.</t>
+          <t>RESOLVED Aug 2026, and the concern understated it. The seeding convention is now fixed AND verified by experiment against TA-Lib rather than taken from a formula. Warm-up and state-restore both use the same path, and restore-equals-rewarm is asserted for the rest of the session rather than only at the instant of restore.</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9014,7 @@
       </c>
       <c r="E54" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F54" s="41" t="inlineStr">
@@ -9044,7 +9050,9 @@
       <c r="N54" s="45" t="n"/>
       <c r="O54" s="46" t="n"/>
       <c r="P54" s="46" t="n"/>
-      <c r="Q54" s="47" t="n"/>
+      <c r="Q54" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R54" s="39" t="n">
         <v>8</v>
       </c>
@@ -9066,7 +9074,12 @@
           <t>• Every indicator verified against a reference implementation on the same data</t>
         </is>
       </c>
-      <c r="V54" s="48" t="n"/>
+      <c r="V54" s="48" t="inlineStr">
+        <is>
+          <t>EMA, SMA, RSI, MACD, ATR, Bollinger, VWAP, VolumeRatio - all matched to TA-Lib within 1e-4. MACD needed a real fix found by that comparison: TA-Lib seeds BOTH its EMAs at the same bar (the slow period's start), not each at its own. Composing two independent EMAs read -18.75 where TA-Lib read -20.11 on a 200-bar series - a 7% error on a line whose CROSSINGS are the signal. Bollinger uses population not sample stddev (2.6% apart at n=20). VWAP is session-anchored and ignores synthetic bars. VolumeRatio excludes the current bar so a 10x spike does not damp itself.
+NOT DONE: ADX. Listed in the story, deferred - it is the only one with no consumer yet.</t>
+        </is>
+      </c>
       <c r="W54" s="49" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1" s="59">
@@ -9092,7 +9105,7 @@
       </c>
       <c r="E55" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F55" s="41" t="inlineStr">
@@ -9128,7 +9141,9 @@
       <c r="N55" s="45" t="n"/>
       <c r="O55" s="46" t="n"/>
       <c r="P55" s="46" t="n"/>
-      <c r="Q55" s="47" t="n"/>
+      <c r="Q55" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" s="39" t="n">
         <v>5</v>
       </c>
@@ -9151,11 +9166,16 @@
           <t>• 🔴 A symbol with insufficient history is excluded, not traded on bad values</t>
         </is>
       </c>
-      <c r="V55" s="48" t="n"/>
+      <c r="V55" s="48" t="inlineStr">
+        <is>
+          <t>Warm-up runs through the SAME code path as live updates, so the two cannot disagree - a separate batch path would only show its divergence as a discontinuity at the moment the system switched between them, mid-session. Insufficient history EXCLUDES the symbol and the report names which indicator was short, so the operator knows why a symbol left the universe.
+Restore-equals-rewarm is asserted, and not only at the same instant: the two must stay equal for the REST of the session, which is what catches a snapshot that captured a value but not its window.</t>
+        </is>
+      </c>
       <c r="W55" s="49" t="n"/>
       <c r="X55" s="75" t="inlineStr">
         <is>
-          <t>Restoring indicator state from Redis must produce identical values to a full re-warm from history. If they differ, a mid-session restart changes signals with nothing visible to show for it. Test that specifically: warm from history, snapshot, restore, compare — do not assume.</t>
+          <t>RESOLVED Aug 2026. Tested exactly as the concern asked: warm from history, snapshot, restore, compare - and then keep feeding both for another twenty bars, which is what catches a snapshot that saved the value but not the window. A snapshot from a different build is refused rather than partially applied.</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9202,7 @@
       </c>
       <c r="E56" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F56" s="41" t="inlineStr">
@@ -9218,7 +9238,9 @@
       <c r="N56" s="45" t="n"/>
       <c r="O56" s="46" t="n"/>
       <c r="P56" s="46" t="n"/>
-      <c r="Q56" s="47" t="n"/>
+      <c r="Q56" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R56" s="39" t="n">
         <v>3</v>
       </c>
@@ -9231,7 +9253,11 @@
         </is>
       </c>
       <c r="U56" s="48" t="n"/>
-      <c r="V56" s="48" t="n"/>
+      <c r="V56" s="48" t="inlineStr">
+        <is>
+          <t>MultiTimeframeSnapshot with all_ready gating evaluation. Values are still exposed when not ready so a health panel can show what is missing rather than an unexplained refusal. A feed gap marks EVERY timeframe for that symbol stale - a 15-minute hole is a missing 5m bar and a corrupted hourly bar alike, and the hourly one is harder to notice. Staleness is NOT cleared by the next bar.</t>
+        </is>
+      </c>
       <c r="W56" s="49" t="n"/>
     </row>
     <row r="57" ht="30" customHeight="1" s="59">
@@ -9257,7 +9283,7 @@
       </c>
       <c r="E57" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F57" s="41" t="inlineStr">
@@ -9293,7 +9319,9 @@
       <c r="N57" s="45" t="n"/>
       <c r="O57" s="46" t="n"/>
       <c r="P57" s="46" t="n"/>
-      <c r="Q57" s="47" t="n"/>
+      <c r="Q57" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R57" s="39" t="n">
         <v>5</v>
       </c>
@@ -9312,7 +9340,11 @@
         </is>
       </c>
       <c r="U57" s="48" t="n"/>
-      <c r="V57" s="48" t="n"/>
+      <c r="V57" s="48" t="inlineStr">
+        <is>
+          <t>Classic pivots, prior-day HLC, swing detection and level clustering. Clustering anchors to the first member rather than chaining, so a gently-rising staircase cannot merge into one 'level' spanning the day's range. Touches become strength, capped - a level touched twenty times is not twice as strong as one touched ten.</t>
+        </is>
+      </c>
       <c r="W57" s="49" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1" s="59">
@@ -9338,7 +9370,7 @@
       </c>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F58" s="41" t="inlineStr">
@@ -9374,7 +9406,9 @@
       <c r="N58" s="45" t="n"/>
       <c r="O58" s="46" t="n"/>
       <c r="P58" s="46" t="n"/>
-      <c r="Q58" s="47" t="n"/>
+      <c r="Q58" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="R58" s="39" t="n">
         <v>4</v>
       </c>
@@ -9396,11 +9430,15 @@
           <t>• 🔴 Range is sealed exactly at 09:30 and never mutates afterwards</t>
         </is>
       </c>
-      <c r="V58" s="48" t="n"/>
+      <c r="V58" s="48" t="inlineStr">
+        <is>
+          <t>Opening range sealed at 09:30 and it NEVER moves. A late tick is refused AND COUNTED rather than silently dropped, because a silent no-op would hide a feed delivering out of order. breakout_direction() refuses to answer before sealing - answering early trades a breakout of a range still forming, which is not a breakout. An empty range is sealed-but-not-usable: a symbol that did not trade in the first fifteen minutes has no range, which is different from a narrow one.</t>
+        </is>
+      </c>
       <c r="W58" s="49" t="n"/>
       <c r="X58" s="75" t="inlineStr">
         <is>
-          <t>'Sealed at 09:30 and never mutates' needs an explicit rule for a late tick whose exchange timestamp falls inside the window but which ARRIVES after the seal. Drop it, or the range mutates and every level derived from it shifts underneath positions already sized against it.</t>
+          <t>RESOLVED Aug 2026. The explicit rule the concern asked for: a tick whose exchange timestamp falls inside the window but which ARRIVES after the seal is dropped and counted. Four tests cover it, including the control that a late tick OUTSIDE the window is not an anomaly.</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9519,11 @@
         </is>
       </c>
       <c r="U59" s="48" t="n"/>
-      <c r="V59" s="48" t="n"/>
+      <c r="V59" s="48" t="inlineStr">
+        <is>
+          <t>NOT STARTED. Needs sector index mapping per symbol, which is E04-S01's data - so it waits on the NSE access question (blocker B8) rather than on anything in this epic.</t>
+        </is>
+      </c>
       <c r="W59" s="49" t="n"/>
     </row>
     <row r="60" ht="30" customHeight="1" s="59">
@@ -9552,7 +9594,7 @@
       <c r="U60" s="48" t="n"/>
       <c r="V60" s="48" t="inlineStr">
         <is>
-          <t>Flags, triangles, double tops/bottoms; TA-Lib candlestick recognition.</t>
+          <t>NOT STARTED - deliberately. Low risk, and the only E06 story with no consumer until E13 exists.</t>
         </is>
       </c>
       <c r="W60" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blockers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E01 Blockers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Results" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Findings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Plan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Blockers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="E01 Blockers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="QA Results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Security Findings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sprint Plan" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Reference" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$4:$W$197</definedName>
@@ -468,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -629,6 +629,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1313,13 +1316,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1342,7 +1345,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1373,13 +1376,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1403,7 +1406,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1427,7 +1430,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1456,8 +1459,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1483,8 +1486,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1510,13 +1513,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1540,7 +1543,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1568,8 +1571,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1604,13 +1607,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1629,7 +1632,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1672,8 +1675,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1696,13 +1699,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1725,7 +1728,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1756,13 +1759,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1786,7 +1789,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1829,8 +1832,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1853,7 +1856,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -1868,9 +1871,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1890,9 +1893,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1912,9 +1915,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1934,9 +1937,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1946,7 +1949,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -1961,9 +1964,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1973,7 +1976,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -1988,9 +1991,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21056,7 +21059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -22599,17 +22602,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="65" t="inlineStr">
+      <c r="A44" s="67" t="inlineStr">
         <is>
           <t>QA-E02-09</t>
         </is>
       </c>
-      <c r="B44" s="65" t="inlineStr">
+      <c r="B44" s="67" t="inlineStr">
         <is>
           <t>E02-S04</t>
         </is>
       </c>
-      <c r="C44" s="65" t="inlineStr">
+      <c r="C44" s="67" t="inlineStr">
         <is>
           <t>BA: acceptance criteria re-checked against code</t>
         </is>
@@ -22634,6 +22637,246 @@
           <t>test_broker_security.py</t>
         </is>
       </c>
+    </row>
+    <row r="45" ht="86" customHeight="1" s="59">
+      <c r="A45" s="67" t="inlineStr">
+        <is>
+          <t>QA-AUD-01</t>
+        </is>
+      </c>
+      <c r="B45" s="67" t="inlineStr">
+        <is>
+          <t>E05/E06</t>
+        </is>
+      </c>
+      <c r="C45" s="67" t="inlineStr">
+        <is>
+          <t>Architecture: does anything compose the components?</t>
+        </is>
+      </c>
+      <c r="D45" s="66" t="inlineStr">
+        <is>
+          <t>FAIL (on plan)</t>
+        </is>
+      </c>
+      <c r="E45" s="67" t="inlineStr">
+        <is>
+          <t>Measured, not read: six service packages (orchestrator, signals, execution, premarket, api, notifier) are 1 line each - __init__.py only. No module in src/ imports both algotrader.ingest and algotrader.indicators. Zero production callers for set_atr_pct, set_circuit, MultiTimeframeBuilder, CleaningPipeline, QuotePublisher or warm_up_symbols.</t>
+        </is>
+      </c>
+      <c r="F45" s="67" t="inlineStr">
+        <is>
+          <t>~7,000 lines of tested components with no assembly. Expected at this point - E07 is the orchestrator - but it means no test so far is an end-to-end test of the SYSTEM. Recorded so the gap is explicit rather than assumed.</t>
+        </is>
+      </c>
+      <c r="G45" s="67" t="inlineStr">
+        <is>
+          <t>grep over src/</t>
+        </is>
+      </c>
+      <c r="H45" s="76" t="n"/>
+      <c r="I45" s="76" t="n"/>
+      <c r="J45" s="76" t="n"/>
+    </row>
+    <row r="46" ht="86" customHeight="1" s="59">
+      <c r="A46" s="67" t="inlineStr">
+        <is>
+          <t>QA-AUD-02</t>
+        </is>
+      </c>
+      <c r="B46" s="67" t="inlineStr">
+        <is>
+          <t>E05/E06</t>
+        </is>
+      </c>
+      <c r="C46" s="67" t="inlineStr">
+        <is>
+          <t>Architecture: the ingest/indicator dependency cycle</t>
+        </is>
+      </c>
+      <c r="D46" s="66" t="inlineStr">
+        <is>
+          <t>PASS (documented)</t>
+        </is>
+      </c>
+      <c r="E46" s="67" t="inlineStr">
+        <is>
+          <t>OutlierFilter needs ATR (E06) &lt;- needs bars (E05) &lt;- needs cleaned ticks &lt;- needs OutlierFilter. Reads as an unbreakable runtime loop.</t>
+        </is>
+      </c>
+      <c r="F46" s="67" t="inlineStr">
+        <is>
+          <t>It is not a loop: the ATR that matters is the PREVIOUS session's, loaded from ohlcv at warm-up before the feed connects. The hazard is the wiring, not the design - feeding it live bars would widen the threshold in response to the very outliers it rejects, each bad print raising ATR and each raised ATR admitting a worse one. Now stated in CleaningPipeline's docstring where the wiring will be written.</t>
+        </is>
+      </c>
+      <c r="G46" s="67" t="inlineStr">
+        <is>
+          <t>cleaning.py CleaningPipeline docstring</t>
+        </is>
+      </c>
+      <c r="H46" s="76" t="n"/>
+      <c r="I46" s="76" t="n"/>
+      <c r="J46" s="76" t="n"/>
+    </row>
+    <row r="47" ht="86" customHeight="1" s="59">
+      <c r="A47" s="67" t="inlineStr">
+        <is>
+          <t>QA-AUD-03</t>
+        </is>
+      </c>
+      <c r="B47" s="67" t="inlineStr">
+        <is>
+          <t>E06-S01</t>
+        </is>
+      </c>
+      <c r="C47" s="67" t="inlineStr">
+        <is>
+          <t>BA: performance criterion measured, not assumed</t>
+        </is>
+      </c>
+      <c r="D47" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E47" s="67" t="inlineStr">
+        <is>
+          <t>Budget is 50ms for a full indicator update cycle. Measured 3.9ms for 1200 indicator sets - 12x under budget.</t>
+        </is>
+      </c>
+      <c r="F47" s="67" t="inlineStr">
+        <is>
+          <t>The criterion was written as a target and had never been measured against real volume.</t>
+        </is>
+      </c>
+      <c r="G47" s="67" t="inlineStr">
+        <is>
+          <t>audit probe, 1200 sets</t>
+        </is>
+      </c>
+      <c r="H47" s="76" t="n"/>
+      <c r="I47" s="76" t="n"/>
+      <c r="J47" s="76" t="n"/>
+    </row>
+    <row r="48" ht="86" customHeight="1" s="59">
+      <c r="A48" s="67" t="inlineStr">
+        <is>
+          <t>QA-AUD-04</t>
+        </is>
+      </c>
+      <c r="B48" s="67" t="inlineStr">
+        <is>
+          <t>E05-S06</t>
+        </is>
+      </c>
+      <c r="C48" s="67" t="inlineStr">
+        <is>
+          <t>BA: full-session bar grid verified end to end</t>
+        </is>
+      </c>
+      <c r="D48" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E48" s="67" t="inlineStr">
+        <is>
+          <t>A complete 09:15-15:30 session produced 74 five-minute bars with 0 off-grid boundaries.</t>
+        </is>
+      </c>
+      <c r="F48" s="67" t="inlineStr">
+        <is>
+          <t>Bars align to the session start, not wall-clock hours. An off-by-one here shifts every indicator value for the day.</t>
+        </is>
+      </c>
+      <c r="G48" s="67" t="inlineStr">
+        <is>
+          <t>audit probe, full session replay</t>
+        </is>
+      </c>
+      <c r="H48" s="76" t="n"/>
+      <c r="I48" s="76" t="n"/>
+      <c r="J48" s="76" t="n"/>
+    </row>
+    <row r="49" ht="86" customHeight="1" s="59">
+      <c r="A49" s="67" t="inlineStr">
+        <is>
+          <t>QA-AUD-05</t>
+        </is>
+      </c>
+      <c r="B49" s="67" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="C49" s="67" t="inlineStr">
+        <is>
+          <t>BA: acceptance criteria not met</t>
+        </is>
+      </c>
+      <c r="D49" s="66" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E49" s="67" t="inlineStr">
+        <is>
+          <t>Two gaps: (1) FeedGap is produced by KiteFeed and IndicatorSet.mark_stale exists, but nothing connects them - a feed gap does not currently mark indicators stale because no component owns both. (2) ADX is named in the story and is not implemented.</t>
+        </is>
+      </c>
+      <c r="F49" s="67" t="inlineStr">
+        <is>
+          <t>Both are consequences of QA-AUD-01 rather than defects in the built code. (1) closes when the orchestrator lands; (2) is a straightforward addition to the indicator framework.</t>
+        </is>
+      </c>
+      <c r="G49" s="67" t="inlineStr">
+        <is>
+          <t>acceptance criteria re-read against code</t>
+        </is>
+      </c>
+      <c r="H49" s="76" t="n"/>
+      <c r="I49" s="76" t="n"/>
+      <c r="J49" s="76" t="n"/>
+    </row>
+    <row r="50" ht="86" customHeight="1" s="59">
+      <c r="A50" s="67" t="inlineStr">
+        <is>
+          <t>QA-AUD-06</t>
+        </is>
+      </c>
+      <c r="B50" s="67" t="inlineStr">
+        <is>
+          <t>E05/E06</t>
+        </is>
+      </c>
+      <c r="C50" s="67" t="inlineStr">
+        <is>
+          <t>Money-path type discipline</t>
+        </is>
+      </c>
+      <c r="D50" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E50" s="67" t="inlineStr">
+        <is>
+          <t>ATR.value returns float 1.4000000000000057 and ATR feeds stop distance, which feeds position size. CLAUDE.md requires Decimal for all money.</t>
+        </is>
+      </c>
+      <c r="F50" s="67" t="inlineStr">
+        <is>
+          <t>Indicators compute in float deliberately - they are the numerical-library boundary the conventions carve out, and TA-Lib parity is defined in float. So the fix is a NAMED crossing (as_decimal()) rather than scattered Decimal() calls at whichever site needs one. .value stays float for the indicator path.</t>
+        </is>
+      </c>
+      <c r="G50" s="67" t="inlineStr">
+        <is>
+          <t>test_indicators.py TestTheMoneyBoundaryIsExplicit</t>
+        </is>
+      </c>
+      <c r="H50" s="76" t="n"/>
+      <c r="I50" s="76" t="n"/>
+      <c r="J50" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G20"/>
@@ -22652,7 +22895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -23396,17 +23639,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="A20" s="67" t="inlineStr">
         <is>
           <t>QA-SEC-16</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr">
+      <c r="B20" s="67" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="C20" s="65" t="inlineStr">
+      <c r="C20" s="67" t="inlineStr">
         <is>
           <t>Order logging / symbol handling</t>
         </is>
@@ -23437,6 +23680,141 @@
           <t>6 hostile symbols refused (newline, CRLF, colon, glob, over-length, empty) plus a CONTROL that real Indian symbols still work: M&amp;M, BAJAJ-AUTO, L&amp;TFH, NIFTY.NS, IDEA_EQ</t>
         </is>
       </c>
+    </row>
+    <row r="21" ht="92" customHeight="1" s="59">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-17</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>Indicator state restore (E06)</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>restore() accepted period: -5 from a snapshot. EMA alpha became -0.5 - an indicator that DIVERGES instead of converging while emitting plausible numbers the whole time. Observed: a restored EMA drifting away from price with no error, no exception, no log line.</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
+          <t>__init__ validated its period; restore() did not, and restore() is the path that reads state which has round-tripped through Redis. A partially-written key or a version skew between processes is enough - no attacker required. Nothing downstream can detect a wrong-but-plausible indicator value, so this fails OPEN, which the invariants forbid.</t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr">
+        <is>
+          <t>_checked_period() applied at all 8 restore sites (SMA, EMA, RSI, ATR, Bollinger, VolumeRatio, Wilder, MACD fast+slow). A corrupt period now raises IndicatorError rather than constructing a diverging indicator.</t>
+        </is>
+      </c>
+      <c r="H21" s="67" t="inlineStr">
+        <is>
+          <t>9 parametrised cases across 6 indicator types (negative, zero, non-numeric, None) plus a CONTROL that a valid snapshot still restores identically to a re-warmed set</t>
+        </is>
+      </c>
+      <c r="I21" s="76" t="n"/>
+      <c r="J21" s="76" t="n"/>
+      <c r="K21" s="76" t="n"/>
+    </row>
+    <row r="22" ht="92" customHeight="1" s="59">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-18</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>Tick deduplication (E05)</t>
+        </is>
+      </c>
+      <c r="D22" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>The per-instrument dedup window was bounded at 512; the map holding those windows was not. 5000 distinct tokens produced 5000 retained windows with nothing to evict them.</t>
+        </is>
+      </c>
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>Memory growth for the life of the process on a feed that churns instrument tokens - re-listings, corporate actions, a subscription list that changes daily. Not remotely triggerable, but it is an availability defect in a component meant to run a full session unattended.</t>
+        </is>
+      </c>
+      <c r="G22" s="67" t="inlineStr">
+        <is>
+          <t>The instrument map is now an LRU bounded at 1024. A universe of 200 fits several times over, so eviction only ever reaches symbols that genuinely stopped ticking.</t>
+        </is>
+      </c>
+      <c r="H22" s="67" t="inlineStr">
+        <is>
+          <t>3 tests: the map stays bounded across 1000 tokens; a continuously-ticking symbol survives 200 others churning past it; the original per-instrument bound still holds</t>
+        </is>
+      </c>
+      <c r="I22" s="76" t="n"/>
+      <c r="J22" s="76" t="n"/>
+      <c r="K22" s="76" t="n"/>
+    </row>
+    <row r="23" ht="92" customHeight="1" s="59">
+      <c r="A23" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-19</t>
+        </is>
+      </c>
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>Rate-limit error handling</t>
+        </is>
+      </c>
+      <c r="D23" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>Two exception classes were both named RateLimitError with OPPOSITE retry semantics. broker.adapter.RateLimitError means back off and retry; redis.primitives.RateLimitError meant the bucket is misconfigured and will never allow anything through.</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>A caller importing either name and wrapping it in the standard retry-with-backoff gets correct behaviour for one and an INFINITE LOOP for the other - against a condition that never clears. No test would fail, because the misconfigured bucket never becomes healthy and the loop never exits. In a component that gates order submission, a hang is a fail-open.</t>
+        </is>
+      </c>
+      <c r="G23" s="67" t="inlineStr">
+        <is>
+          <t>Renamed the Redis one to RateLimiterConfigError, with a docstring stating why the two are named apart.</t>
+        </is>
+      </c>
+      <c r="H23" s="67" t="inlineStr">
+        <is>
+          <t>3 tests: the types are distinct, neither is a subclass of the other, and only the broker one is reported by is_retryable()</t>
+        </is>
+      </c>
+      <c r="I23" s="76" t="n"/>
+      <c r="J23" s="76" t="n"/>
+      <c r="K23" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H11"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4541,6 +4541,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -5122,7 +5123,7 @@
       </c>
       <c r="D12" s="40" t="inlineStr">
         <is>
-          <t>Strategy DSL with vetted primitive registry</t>
+          <t>Closed (evaluator delivered 24 Aug 2026)</t>
         </is>
       </c>
       <c r="E12" s="40" t="inlineStr">
@@ -9368,7 +9369,7 @@
       </c>
       <c r="D58" s="40" t="inlineStr">
         <is>
-          <t>Opening range computation</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="E58" s="40" t="inlineStr">
@@ -21059,7 +21060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -22877,6 +22878,326 @@
       <c r="H50" s="76" t="n"/>
       <c r="I50" s="76" t="n"/>
       <c r="J50" s="76" t="n"/>
+    </row>
+    <row r="51" ht="106" customHeight="1" s="59">
+      <c r="A51" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-01</t>
+        </is>
+      </c>
+      <c r="B51" s="67" t="inlineStr">
+        <is>
+          <t>E00-S08</t>
+        </is>
+      </c>
+      <c r="C51" s="67" t="inlineStr">
+        <is>
+          <t>BA: is the story actually delivered?</t>
+        </is>
+      </c>
+      <c r="D51" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E51" s="67" t="inlineStr">
+        <is>
+          <t>E00-S08 'Strategy DSL with vetted primitive registry' is marked Closed. The registry held 27 PrimitiveSpec records - name, category, parameter bounds - and no function behind any of them. compile_strategy's own docstring says 'the runtime evaluator walks the validated tree'; no such evaluator existed.</t>
+        </is>
+      </c>
+      <c r="F51" s="67" t="inlineStr">
+        <is>
+          <t>A registry of primitives that cannot be computed is not a delivered registry. A strategy would validate, compile, hash, persist, activate - and never fire, with no error raised. Now implemented, with a test asserting declared and implemented are the same set.</t>
+        </is>
+      </c>
+      <c r="G51" s="67" t="inlineStr">
+        <is>
+          <t>test_strategy_runtime.py TestEveryPrimitiveCanActuallyRun</t>
+        </is>
+      </c>
+      <c r="H51" s="76" t="n"/>
+      <c r="I51" s="76" t="n"/>
+      <c r="J51" s="76" t="n"/>
+    </row>
+    <row r="52" ht="106" customHeight="1" s="59">
+      <c r="A52" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-02</t>
+        </is>
+      </c>
+      <c r="B52" s="67" t="inlineStr">
+        <is>
+          <t>E00-S08</t>
+        </is>
+      </c>
+      <c r="C52" s="67" t="inlineStr">
+        <is>
+          <t>BA: Applicability was decorative</t>
+        </is>
+      </c>
+      <c r="D52" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E52" s="67" t="inlineStr">
+        <is>
+          <t>Applicability.regimes and min_price were parsed, validated and folded into the content hash, then consulted by nothing anywhere in src/. A strategy declaring 'TRENDING only, above 100 rupees' had both ignored.</t>
+        </is>
+      </c>
+      <c r="F52" s="67" t="inlineStr">
+        <is>
+          <t>A trend strategy would fire freely in a rangebound market and on a penny stock. Now enforced in StrategyEvaluator.applies_to, which fire() consults - and an unknown regime does not apply, because the strategy is only validated for the regimes it names.</t>
+        </is>
+      </c>
+      <c r="G52" s="67" t="inlineStr">
+        <is>
+          <t>test_strategy_runtime.py TestApplicabilityIsEnforcedNotDecorative</t>
+        </is>
+      </c>
+      <c r="H52" s="76" t="n"/>
+      <c r="I52" s="76" t="n"/>
+      <c r="J52" s="76" t="n"/>
+    </row>
+    <row r="53" ht="106" customHeight="1" s="59">
+      <c r="A53" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-03</t>
+        </is>
+      </c>
+      <c r="B53" s="67" t="inlineStr">
+        <is>
+          <t>E06-S04</t>
+        </is>
+      </c>
+      <c r="C53" s="67" t="inlineStr">
+        <is>
+          <t>Architect: timeframe_agreement carried no direction</t>
+        </is>
+      </c>
+      <c r="D53" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E53" s="67" t="inlineStr">
+        <is>
+          <t>fire() reported abs(snapshot.trend_agreement()). Measured: on a unanimously bearish tape a LONG trigger reported 3 of 3 timeframes in agreement.</t>
+        </is>
+      </c>
+      <c r="F53" s="67" t="inlineStr">
+        <is>
+          <t>trend_agreement counts timeframes where fast &gt; slow and the SIGN carries direction; discarding it turns maximum disagreement into maximum confluence. The number reaches Recommendation.timeframe_agreement and the AI confirmation prompt, where it is precisely the wrong thing to say.</t>
+        </is>
+      </c>
+      <c r="G53" s="67" t="inlineStr">
+        <is>
+          <t>test_strategy_runtime.py TestTimeframeAgreementCarriesDirection</t>
+        </is>
+      </c>
+      <c r="H53" s="76" t="n"/>
+      <c r="I53" s="76" t="n"/>
+      <c r="J53" s="76" t="n"/>
+    </row>
+    <row r="54" ht="106" customHeight="1" s="59">
+      <c r="A54" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-04</t>
+        </is>
+      </c>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
+          <t>E00-S08</t>
+        </is>
+      </c>
+      <c r="C54" s="67" t="inlineStr">
+        <is>
+          <t>Architect: randomness in the strategy path</t>
+        </is>
+      </c>
+      <c r="D54" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E54" s="67" t="inlineStr">
+        <is>
+          <t>fire() minted a correlation_id with uuid4() when the caller did not supply one.</t>
+        </is>
+      </c>
+      <c r="F54" s="67" t="inlineStr">
+        <is>
+          <t>The conventions forbid randomness in the strategy path for a concrete reason: E12-S03's acceptance criterion is that the decision SEQUENCE matches between backtest and live, and two Triggers differing only by a random UUID cannot be compared for equality. correlation_id is now required, so the evaluator is a pure function and the caller owns identity.</t>
+        </is>
+      </c>
+      <c r="G54" s="67" t="inlineStr">
+        <is>
+          <t>test_strategy_runtime.py test_firing_twice_on_the_same_context_is_identical</t>
+        </is>
+      </c>
+      <c r="H54" s="76" t="n"/>
+      <c r="I54" s="76" t="n"/>
+      <c r="J54" s="76" t="n"/>
+    </row>
+    <row r="55" ht="106" customHeight="1" s="59">
+      <c r="A55" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-05</t>
+        </is>
+      </c>
+      <c r="B55" s="67" t="inlineStr">
+        <is>
+          <t>E00-S08</t>
+        </is>
+      </c>
+      <c r="C55" s="67" t="inlineStr">
+        <is>
+          <t>Registry declared timeframes the engine does not compute</t>
+        </is>
+      </c>
+      <c r="D55" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E55" s="67" t="inlineStr">
+        <is>
+          <t>timeframe_agreement_at_least defaulted to of='1h,1d,1w' and higher_tf_trend_is offered 1h/1d/1w as enum choices. IndicatorEngine carries 5m/15m/1h.</t>
+        </is>
+      </c>
+      <c r="F55" s="67" t="inlineStr">
+        <is>
+          <t>A strategy omitting the 'of' parameter named two timeframes that do not exist, so it could never fire - and would look like a strategy that simply never triggered. Both now declare what the engine actually produces, and StrategyEvaluator.__init__ verifies capability so the failure happens at LOAD rather than at 09:20 from an absence of trades.</t>
+        </is>
+      </c>
+      <c r="G55" s="67" t="inlineStr">
+        <is>
+          <t>test_strategy_runtime.py TestCapabilityIsVerifiedAtLoadTime</t>
+        </is>
+      </c>
+      <c r="H55" s="76" t="n"/>
+      <c r="I55" s="76" t="n"/>
+      <c r="J55" s="76" t="n"/>
+    </row>
+    <row r="56" ht="106" customHeight="1" s="59">
+      <c r="A56" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-06</t>
+        </is>
+      </c>
+      <c r="B56" s="67" t="inlineStr">
+        <is>
+          <t>E00-S08</t>
+        </is>
+      </c>
+      <c r="C56" s="67" t="inlineStr">
+        <is>
+          <t>Stops were not placeable prices</t>
+        </is>
+      </c>
+      <c r="D56" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E56" s="67" t="inlineStr">
+        <is>
+          <t>atr_stop produced 1186.49835 - five decimal places and off the NSE tick grid.</t>
+        </is>
+      </c>
+      <c r="F56" s="67" t="inlineStr">
+        <is>
+          <t>Not an imprecise stop: NSE rejects an off-tick price, so it is a REJECTED ORDER and therefore a position with no protection at all. Stops now snap to the tick grid away from entry (snapping inward would silently turn a declared 1.5x ATR stop into 1.49x); targets snap toward entry, since a target only pays if it fills. A second bug surfaced in the same fix: the exact-grid early-return path skipped quantisation, so a price already on the grid kept 5 decimal places and would fail Price validation downstream.</t>
+        </is>
+      </c>
+      <c r="G56" s="67" t="inlineStr">
+        <is>
+          <t>test_strategy_runtime.py TestStopsAreRealPlaceablePrices plus the E2E tick-grid assertion</t>
+        </is>
+      </c>
+      <c r="H56" s="76" t="n"/>
+      <c r="I56" s="76" t="n"/>
+      <c r="J56" s="76" t="n"/>
+    </row>
+    <row r="57" ht="106" customHeight="1" s="59">
+      <c r="A57" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-07</t>
+        </is>
+      </c>
+      <c r="B57" s="67" t="inlineStr">
+        <is>
+          <t>E06-S06</t>
+        </is>
+      </c>
+      <c r="C57" s="67" t="inlineStr">
+        <is>
+          <t>Dev: OpeningRange accepted an inverted range</t>
+        </is>
+      </c>
+      <c r="D57" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E57" s="67" t="inlineStr">
+        <is>
+          <t>OpeningRange(high=90, low=110) reported is_usable True, range_pct -20%, and a width of -20.</t>
+        </is>
+      </c>
+      <c r="F57" s="67" t="inlineStr">
+        <is>
+          <t>update() maintains high &gt;= low by construction so this cannot arise from ticks, but the dataclass is also built directly - from a restored snapshot or from stored bars - and nothing checked. classic_pivots already refused high &lt; low, so the two halves of the module disagreed. A negative width would reach a sizing calculation as a real one.</t>
+        </is>
+      </c>
+      <c r="G57" s="67" t="inlineStr">
+        <is>
+          <t>test_indicator_levels.py TestAnInvertedOpeningRangeIsRefused</t>
+        </is>
+      </c>
+      <c r="H57" s="76" t="n"/>
+      <c r="I57" s="76" t="n"/>
+      <c r="J57" s="76" t="n"/>
+    </row>
+    <row r="58" ht="106" customHeight="1" s="59">
+      <c r="A58" s="67" t="inlineStr">
+        <is>
+          <t>QA-STR-08</t>
+        </is>
+      </c>
+      <c r="B58" s="67" t="inlineStr">
+        <is>
+          <t>E05+E06+strategy</t>
+        </is>
+      </c>
+      <c r="C58" s="67" t="inlineStr">
+        <is>
+          <t>QA Lead: first end-to-end run of the whole chain</t>
+        </is>
+      </c>
+      <c r="D58" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E58" s="67" t="inlineStr">
+        <is>
+          <t>RawTick -&gt; CleaningPipeline -&gt; MultiTimeframeBuilder -&gt; IndicatorEngine -&gt; MultiTimeframeSnapshot -&gt; EvalContext -&gt; StrategyEvaluator -&gt; Trigger. 2400 ticks, 55 bars, warm-up from 260 prior bars per timeframe, producing a Trigger with a tick-aligned stop 2.54% away.</t>
+        </is>
+      </c>
+      <c r="F58" s="67" t="inlineStr">
+        <is>
+          <t>The audit's headline finding was that nothing composed ingest with indicators, so every claim was a claim about a part. This is the first test of the SYSTEM. It exercises three components the audit found with zero callers - MultiTimeframeBuilder, CleaningPipeline, warm_up_symbols - and it is where QA-SEC-20 was found. It also confirms E05-S04 one layer up: a 50x poison print moves no indicator value.</t>
+        </is>
+      </c>
+      <c r="G58" s="67" t="inlineStr">
+        <is>
+          <t>tests/integration/test_tick_to_trigger.py (17 tests)</t>
+        </is>
+      </c>
+      <c r="H58" s="76" t="n"/>
+      <c r="I58" s="76" t="n"/>
+      <c r="J58" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G20"/>
@@ -22895,7 +23216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -23815,6 +24136,186 @@
       <c r="I23" s="76" t="n"/>
       <c r="J23" s="76" t="n"/>
       <c r="K23" s="76" t="n"/>
+    </row>
+    <row r="24" ht="112" customHeight="1" s="59">
+      <c r="A24" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-20</t>
+        </is>
+      </c>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>Strategy evaluation / feed integrity</t>
+        </is>
+      </c>
+      <c r="D24" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>The evaluator TRADED through a simulated twelve-minute feed gap. Observed end to end: mark_stale set on all three timeframes, snapshot.all_ready False, and fire() still returned a Trigger with a valid stop.</t>
+        </is>
+      </c>
+      <c r="F24" s="67" t="inlineStr">
+        <is>
+          <t>mark_stale clears IndicatorSet.is_ready which clears all_ready - and nothing consulted all_ready. A strategy reading only a warm ema_20 never noticed that every indicator beside it had been computed across a hole in the data. This is the 'data stale -&gt; block entries' invariant and E13-S01 acceptance criterion 3, and neither was held. Found only by assembling the full tick-to-Trigger chain; no component test could see it.</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr">
+        <is>
+          <t>fire() now refuses when snapshot.all_ready is False and logs which indicators are pending. evaluate() still answers, so a health panel and a backtest can inspect a cold symbol without being able to trade it.</t>
+        </is>
+      </c>
+      <c r="H24" s="67" t="inlineStr">
+        <is>
+          <t>E2E: the same context fires, is refused after mark_stale, and fires again after clear_stale; plus a cold pipeline that can never fire</t>
+        </is>
+      </c>
+      <c r="I24" s="76" t="n"/>
+      <c r="J24" s="76" t="n"/>
+      <c r="K24" s="76" t="n"/>
+    </row>
+    <row r="25" ht="112" customHeight="1" s="59">
+      <c r="A25" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-21</t>
+        </is>
+      </c>
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>Strategy parameter handling</t>
+        </is>
+      </c>
+      <c r="D25" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>NaN and Infinity reached comparisons. decimal.InvalidOperation propagated out of atr_stop as an uncaught exception in the signal path, and threshold=-Infinity made a 'score above' gate pass unconditionally.</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>Decimal('NaN') CONSTRUCTS without error and raises only on the first comparison, so the failure surfaced in whichever caller compared first rather than at the boundary. The infinities do not raise at all: NaN compares False against everything (a confident wrong answer) and -Infinity compares True against everything (a filter bypass an author can write in one word). Python's json emits and accepts bare NaN, so a corrupted indicator snapshot in Redis is a live path, not a theoretical one.</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="inlineStr">
+        <is>
+          <t>Non-finite values are refused at three boundaries: to_decimal (the money crossing), EvalContext.indicator/indicator_ago (all 27 primitives at once), and the numeric parameter coercion.</t>
+        </is>
+      </c>
+      <c r="H25" s="67" t="inlineStr">
+        <is>
+          <t>9 parametrised cases across NaN/+Inf/-Inf for indicator values, stop computation and parameters, plus a control that ordinary values are untouched</t>
+        </is>
+      </c>
+      <c r="I25" s="76" t="n"/>
+      <c r="J25" s="76" t="n"/>
+      <c r="K25" s="76" t="n"/>
+    </row>
+    <row r="26" ht="112" customHeight="1" s="59">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-22</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>Strategy parameter validation order</t>
+        </is>
+      </c>
+      <c r="D26" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>A primitive validated its parameters AFTER consulting market data, so a strategy with a misspelled direction returned UNKNOWN whenever the level happened to be unavailable rather than raising.</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>A malformed strategy is then indistinguishable from a quiet market: it reports 'conditions not met' forever and nobody learns it is broken. Also found: error messages echoed strategy-supplied text unbounded - a 10 KB parameter repeated per symbol per bar is a log-flooding primitive.</t>
+        </is>
+      </c>
+      <c r="G26" s="67" t="inlineStr">
+        <is>
+          <t>Parameters are validated before any data lookup, so a malformed strategy raises regardless of market state. Echoed text is capped at 60 characters.</t>
+        </is>
+      </c>
+      <c r="H26" s="67" t="inlineStr">
+        <is>
+          <t>3 bad-direction cases, 5 malformed time windows, and an assertion that a 10 KB parameter yields an error under 500 characters</t>
+        </is>
+      </c>
+      <c r="I26" s="76" t="n"/>
+      <c r="J26" s="76" t="n"/>
+      <c r="K26" s="76" t="n"/>
+    </row>
+    <row r="27" ht="112" customHeight="1" s="59">
+      <c r="A27" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-23</t>
+        </is>
+      </c>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>Strategy bounds enforcement</t>
+        </is>
+      </c>
+      <c r="D27" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>verify_condition checked primitive names and indicator availability but not the registry's declared parameter bounds. Decimal('-1e999') is FINITE, so the non-finite guard does not catch it, and it makes any 'above threshold' gate pass unconditionally.</t>
+        </is>
+      </c>
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>compile_strategy does validate bounds, but nothing structurally guaranteed a document reached the evaluator through compilation. Defence in depth matters here because the bounds are the only thing standing between a hostile strategy author and a disabled filter.</t>
+        </is>
+      </c>
+      <c r="G27" s="67" t="inlineStr">
+        <is>
+          <t>verify_condition now re-runs the registry's validate_params, so holding a StrategyEvaluator is proof the parameters are in range - not merely that the primitive names exist.</t>
+        </is>
+      </c>
+      <c r="H27" s="67" t="inlineStr">
+        <is>
+          <t>out-of-range threshold and unknown-parameter cases refused at load, plus a control that a valid condition passes</t>
+        </is>
+      </c>
+      <c r="I27" s="76" t="n"/>
+      <c r="J27" s="76" t="n"/>
+      <c r="K27" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H11"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4541,7 +4541,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -20442,6 +20441,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="59">
+    <row r="5" ht="150" customHeight="1" s="59">
       <c r="A5" s="38" t="inlineStr">
         <is>
           <t>B1</t>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="D5" s="48" t="inlineStr">
         <is>
-          <t>Ask Zerodha: tag field or broker-injected?</t>
+          <t>Research resolved the mechanic. Under SEBI's Feb 2025 circular (effective 1 Apr 2026) a self-developed personal algo under 10 OPS needs no separate exchange registration and the broker handles Strategy-ID tagging. Every algo order must carry an exchange-issued unique identifier, which the broker assigns during registration (format e.g. ALGO_XX_001). The process for a self-developed algo is a plain-English description of the strategy to the broker's compliance desk plus a mandatory mock trading session, usually on a Saturday, to show the algo does not loop or spam. Code already sends algo_id only when configured, which is the right shape. What remains is paperwork with Zerodha and needs your account.</t>
         </is>
       </c>
       <c r="E5" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active - mechanic understood, registration needs you</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -20568,7 +20568,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="59">
+    <row r="7" ht="150" customHeight="1" s="59">
       <c r="A7" s="38" t="inlineStr">
         <is>
           <t>B3</t>
@@ -20586,12 +20586,12 @@
       </c>
       <c r="D7" s="48" t="inlineStr">
         <is>
-          <t>Transcribe the circular</t>
+          <t>Full 2026 NSE holiday list transcribed and cross-checked against THREE independent publications of the circular, because the first two disagreed: one omitted 24 Nov (Guru Nanak Jayanti), the other omitted 15 Jan (Maharashtra municipal elections - a separate special closure rather than part of the annual circular). Both are real; both are included. 19 dates, verified_against_nse_circular: true, yielding 245 trading days in 2026. Muhurat trading (Sun 8 Nov) recorded as a special session with trade: false - it is a real session on a SUNDAY, so anything reasoning 'weekend implies closed' is wrong on that date. Also added: the calendar now REFUSES to answer for a year the file does not cover, because a 2026-only list would make 2027 look like a year with no holidays at all.</t>
         </is>
       </c>
       <c r="E7" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>RESOLVED 24 Aug 2026</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
@@ -20650,7 +20650,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="59">
+    <row r="9" ht="150" customHeight="1" s="59">
       <c r="A9" s="38" t="inlineStr">
         <is>
           <t>B5</t>
@@ -20668,12 +20668,12 @@
       </c>
       <c r="D9" s="48" t="inlineStr">
         <is>
-          <t>Prototype the phone→callback flow</t>
+          <t>Unchanged and genuinely blocked on you: the daily re-auth flow cannot be exercised without a real Kite account. The code path is built and unit-tested against a fake client; what is untested is the live phone-to-callback round trip.</t>
         </is>
       </c>
       <c r="E9" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Active - needs your credentials</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -20689,7 +20689,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="59">
+    <row r="10" ht="150" customHeight="1" s="59">
       <c r="A10" s="38" t="inlineStr">
         <is>
           <t>B6</t>
@@ -20707,12 +20707,12 @@
       </c>
       <c r="D10" s="48" t="inlineStr">
         <is>
-          <t>Select provider, procure</t>
+          <t>Confirmed from Zerodha's own developer forum: the static IP applies to ORDER ENDPOINTS ONLY. WebSocket market data, order book, positions and every other endpoint remain accessible from any IP - so E03/E04/E05/E06 and all strategy work need no static IP. Registration is live at developers.kite.trade under 'IP Whitelist'; ONE IP per app; orders from an unregistered IP are rejected outright. Also confirmed there: 10 OPS is account-wide across all apps for a client ID (we cap at 5), market protection of 0 is rejected including for SL-M, and order slicing is capped at 10 slices. Only the procurement itself needs you.</t>
         </is>
       </c>
       <c r="E10" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Active - research complete, procurement needs you</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
@@ -20736,7 +20736,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="409.6" customHeight="1" s="59">
+    <row r="11" ht="150" customHeight="1" s="59">
       <c r="A11" s="38" t="inlineStr">
         <is>
           <t>B7</t>
@@ -20754,12 +20754,12 @@
       </c>
       <c r="D11" s="48" t="inlineStr">
         <is>
-          <t>Confirm exposure at E02; ask Zerodha to bump the pin</t>
+          <t>Upgraded autobahn to 26.7.1. kiteconnect's autobahn[twisted]==19.11.2 pin is DECLARATIVE, not a runtime requirement: only kiteconnect.ticker imports autobahn, we never construct a KiteTicker, and the feed runs on `websockets`. Verified empirically - kiteconnect imports, builds a login URL and exposes market_protection/algo_id under 26.7.1, and all 1059 tests pass. pip-audit now reports zero known vulnerabilities. pyproject floors autobahn at &gt;=20.12.3. NOTE: the earlier claim that autobahn was 'never imported' was WRONG - kiteconnect/__init__.py imports .ticker unconditionally, so it loaded into every process touching the broker layer. Not using a package is not the same as not having it.</t>
         </is>
       </c>
       <c r="E11" s="40" t="inlineStr">
         <is>
-          <t>On Hold</t>
+          <t>RESOLVED 24 Aug 2026</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -20823,7 +20823,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="150" customHeight="1" s="59">
       <c r="A13" s="38" t="inlineStr">
         <is>
           <t>B8</t>
@@ -20841,12 +20841,12 @@
       </c>
       <c r="D13" s="48" t="inlineStr">
         <is>
-          <t>Prove reachability from the target host before writing fetchers</t>
+          <t>What NSE blocks is OVERSEAS access, not programmatic access as such: its edge refuses non-Indian IPs and its robots policy excludes crawlers, but a polite client on an Indian host carrying the session cookie its own site issues is an ordinary visitor. Community libraries (nsepython, NseIndiaApi at 3 req/s) work on Indian servers. This collapses B8 into B6: SEBI already requires an India-hosted static IP for the order path, and the same host answers the data question. Built scripts/check_data_reachability.py so the answer is one command on the day there is a host - read-only, no credentials, safe during market hours. Run from THIS machine it already reaches 4 of 6 sources including Kite instruments and NSE marketStatus.</t>
         </is>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Narrowed - same fix as B6</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
@@ -21060,7 +21060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -23198,6 +23198,206 @@
       <c r="H58" s="76" t="n"/>
       <c r="I58" s="76" t="n"/>
       <c r="J58" s="76" t="n"/>
+    </row>
+    <row r="59" ht="116" customHeight="1" s="59">
+      <c r="A59" s="67" t="inlineStr">
+        <is>
+          <t>QA-ENG-01</t>
+        </is>
+      </c>
+      <c r="B59" s="67" t="inlineStr">
+        <is>
+          <t>E05-S01/S08</t>
+        </is>
+      </c>
+      <c r="C59" s="67" t="inlineStr">
+        <is>
+          <t>Coverage: two production modules at 0%</t>
+        </is>
+      </c>
+      <c r="D59" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E59" s="67" t="inlineStr">
+        <is>
+          <t>kite_ws.py (144 statements, the LIVE MARKET FEED) and quotes.py (68 statements) had never been executed by any test. Reviewed, shipped, never run.</t>
+        </is>
+      </c>
+      <c r="F59" s="67" t="inlineStr">
+        <is>
+          <t>This is exactly what CLAUDE.md warns about - two real bugs in this repository shipped past a clean code read. Written 53 tests using a scripted fake socket: reconnection, gap emission, idle-socket detection, heartbeats, protocol errors, backoff reset after a healthy connection, and that the access token in the URL never reaches a log. Coverage 0% -&gt; 98% and 0% -&gt; 100%; project total 86% -&gt; 90%.</t>
+        </is>
+      </c>
+      <c r="G59" s="67" t="inlineStr">
+        <is>
+          <t>tests/unit/test_ingest_feed.py (29), tests/unit/test_ingest_quotes.py (24)</t>
+        </is>
+      </c>
+      <c r="H59" s="76" t="n"/>
+      <c r="I59" s="76" t="n"/>
+      <c r="J59" s="76" t="n"/>
+    </row>
+    <row r="60" ht="116" customHeight="1" s="59">
+      <c r="A60" s="67" t="inlineStr">
+        <is>
+          <t>QA-ENG-02</t>
+        </is>
+      </c>
+      <c r="B60" s="67" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C60" s="67" t="inlineStr">
+        <is>
+          <t>Alembic silently disabled application logging</t>
+        </is>
+      </c>
+      <c r="D60" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E60" s="67" t="inlineStr">
+        <is>
+          <t>logging.config.fileConfig defaults to disable_existing_loggers=True. Alembic runs in-process here, so a migration switched off every logger that already existed. Surfaced as pytest caplog going empty for every test after a DB test - 4 tests that passed alone and failed in the suite.</t>
+        </is>
+      </c>
+      <c r="F60" s="67" t="inlineStr">
+        <is>
+          <t>The test symptom is the small version. The real one: a trading system that stops logging without failing. It keeps trading and there is no record of what it did, which for a system handling real money is close to the worst available failure mode.</t>
+        </is>
+      </c>
+      <c r="G60" s="67" t="inlineStr">
+        <is>
+          <t>tests/unit/test_migration_logging.py - demonstrates the mechanism rather than asserting it from the docs</t>
+        </is>
+      </c>
+      <c r="H60" s="76" t="n"/>
+      <c r="I60" s="76" t="n"/>
+      <c r="J60" s="76" t="n"/>
+    </row>
+    <row r="61" ht="116" customHeight="1" s="59">
+      <c r="A61" s="67" t="inlineStr">
+        <is>
+          <t>QA-ENG-03</t>
+        </is>
+      </c>
+      <c r="B61" s="67" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C61" s="67" t="inlineStr">
+        <is>
+          <t>Mutation testing on the safety-critical paths</t>
+        </is>
+      </c>
+      <c r="D61" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E61" s="67" t="inlineStr">
+        <is>
+          <t>15 plausible bugs injected into real source and the suite run against each: none_of treating UNKNOWN as absent, the all_ready gate removed, stops snapping toward entry, agreement discarding direction, restore() trusting its period, the dedup map unbounded, the feed gap not announced, read_fresh returning stale quotes, and more.</t>
+        </is>
+      </c>
+      <c r="F61" s="67" t="inlineStr">
+        <is>
+          <t>Coverage says a line ran; it does not say a test would NOTICE if that line were wrong. Two mutations SURVIVED on the first pass - both because the tests exercised a helper directly rather than the path that calls it, so reverting fire() to the buggy behaviour changed nothing any assertion could see. Closed both; all 15 now killed.</t>
+        </is>
+      </c>
+      <c r="G61" s="67" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate.py, 15/15 killed</t>
+        </is>
+      </c>
+      <c r="H61" s="76" t="n"/>
+      <c r="I61" s="76" t="n"/>
+      <c r="J61" s="76" t="n"/>
+    </row>
+    <row r="62" ht="116" customHeight="1" s="59">
+      <c r="A62" s="67" t="inlineStr">
+        <is>
+          <t>QA-ENG-04</t>
+        </is>
+      </c>
+      <c r="B62" s="67" t="inlineStr">
+        <is>
+          <t>Strategy runtime</t>
+        </is>
+      </c>
+      <c r="C62" s="67" t="inlineStr">
+        <is>
+          <t>Property-based testing</t>
+        </is>
+      </c>
+      <c r="D62" s="66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E62" s="67" t="inlineStr">
+        <is>
+          <t>17 Hypothesis properties over ~5000 generated cases: a snapped stop is always on the tick grid, never moves more than one tick, never moves toward the entry, is idempotent, never goes negative and always fits Price's four decimal places. Plus the full 3^n tri-state truth tables.</t>
+        </is>
+      </c>
+      <c r="F62" s="67" t="inlineStr">
+        <is>
+          <t>Example tests assert what I thought to check. The tri-state tables have 3^n rows and I would otherwise have tested the handful I imagined - and the property that matters most, that no combination containing an UNKNOWN can ever satisfy none_of, is a statement about the whole space.</t>
+        </is>
+      </c>
+      <c r="G62" s="67" t="inlineStr">
+        <is>
+          <t>tests/unit/test_strategy_properties.py</t>
+        </is>
+      </c>
+      <c r="H62" s="76" t="n"/>
+      <c r="I62" s="76" t="n"/>
+      <c r="J62" s="76" t="n"/>
+    </row>
+    <row r="63" ht="116" customHeight="1" s="59">
+      <c r="A63" s="67" t="inlineStr">
+        <is>
+          <t>QA-ENG-05</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="inlineStr">
+        <is>
+          <t>E00-S10</t>
+        </is>
+      </c>
+      <c r="C63" s="67" t="inlineStr">
+        <is>
+          <t>Preflight tests depended on a defect existing</t>
+        </is>
+      </c>
+      <c r="D63" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E63" s="67" t="inlineStr">
+        <is>
+          <t>Two BR-20 tests asserted that an unverified holiday list blocks live trading, using the SHIPPED file's incompleteness as the fixture. Closing B3 fixed the file and the tests failed.</t>
+        </is>
+      </c>
+      <c r="F63" s="67" t="inlineStr">
+        <is>
+          <t>They passed for the wrong reason: the gate was being tested with a real defect as its input, so the tests would have gone quiet the moment the defect was fixed - which is exactly what happened. Rewritten to construct the unverified condition deliberately, plus a new test asserting the SHIPPED list now passes the live gate.</t>
+        </is>
+      </c>
+      <c r="G63" s="67" t="inlineStr">
+        <is>
+          <t>tests/security/test_preflight_gate.py TestHolidayCalendarBlocksLiveTrading</t>
+        </is>
+      </c>
+      <c r="H63" s="76" t="n"/>
+      <c r="I63" s="76" t="n"/>
+      <c r="J63" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G20"/>
@@ -23216,7 +23416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -24316,6 +24516,186 @@
       <c r="I27" s="76" t="n"/>
       <c r="J27" s="76" t="n"/>
       <c r="K27" s="76" t="n"/>
+    </row>
+    <row r="28" ht="120" customHeight="1" s="59">
+      <c r="A28" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-24</t>
+        </is>
+      </c>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C28" s="67" t="inlineStr">
+        <is>
+          <t>Dependency supply chain</t>
+        </is>
+      </c>
+      <c r="D28" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>autobahn 19.11.2 (CVE-2020-35678, redirect header injection) was present and importable in every process that touched the broker layer. pip-audit flagged it; CI could not, because the dependency-audit step was advisory.</t>
+        </is>
+      </c>
+      <c r="F28" s="67" t="inlineStr">
+        <is>
+          <t>The prior assessment recorded it as unreachable because the live feed was built on `websockets` rather than KiteTicker. That was WRONG: kiteconnect/__init__.py imports .ticker unconditionally, so `import kiteconnect` loads autobahn and Twisted regardless of whether a ticker is ever constructed. Not using a package is not the same as not having it, and a vulnerable package that is present and importable is a real finding.</t>
+        </is>
+      </c>
+      <c r="G28" s="67" t="inlineStr">
+        <is>
+          <t>Upgraded to autobahn 26.7.1 and floored at &gt;=20.12.3 in pyproject. kiteconnect's == pin is declarative; verified empirically that it still imports, constructs, builds a login URL and exposes market_protection/algo_id. pip-audit now reports zero vulnerabilities and the CI step is a HARD gate.</t>
+        </is>
+      </c>
+      <c r="H28" s="67" t="inlineStr">
+        <is>
+          <t>Full 1059-test suite green under the upgraded dependency; pip-audit --skip-editable exits 0</t>
+        </is>
+      </c>
+      <c r="I28" s="76" t="n"/>
+      <c r="J28" s="76" t="n"/>
+      <c r="K28" s="76" t="n"/>
+    </row>
+    <row r="29" ht="120" customHeight="1" s="59">
+      <c r="A29" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-25</t>
+        </is>
+      </c>
+      <c r="B29" s="67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C29" s="67" t="inlineStr">
+        <is>
+          <t>CI security gates</t>
+        </is>
+      </c>
+      <c r="D29" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>The dependency audit ran with `continue-on-error: true` and `|| true`, so it could never fail a build. There was no SAST step at all.</t>
+        </is>
+      </c>
+      <c r="F29" s="67" t="inlineStr">
+        <is>
+          <t>The soft gate was correctly justified while B7 was unfixable - a permanently red check trains people to ignore it. That justification expired the moment B7 closed, and an advisory audit means the NEXT CVE arrives silently. Bandit was not running anywhere.</t>
+        </is>
+      </c>
+      <c r="G29" s="67" t="inlineStr">
+        <is>
+          <t>pip-audit is now a hard gate (with --skip-editable, not --strict: --strict treats the local editable package as an error and fails every run for reasons unrelated to vulnerabilities). Added bandit gated at MEDIUM severity and MEDIUM confidence.</t>
+        </is>
+      </c>
+      <c r="H29" s="67" t="inlineStr">
+        <is>
+          <t>Both gates verified locally: bandit exit 0, pip-audit exit 0, and both demonstrated to exit non-zero on a real finding</t>
+        </is>
+      </c>
+      <c r="I29" s="76" t="n"/>
+      <c r="J29" s="76" t="n"/>
+      <c r="K29" s="76" t="n"/>
+    </row>
+    <row r="30" ht="120" customHeight="1" s="59">
+      <c r="A30" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-26</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C30" s="67" t="inlineStr">
+        <is>
+          <t>SQL identifier construction</t>
+        </is>
+      </c>
+      <c r="D30" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>The bulk-insert path interpolates column names into SQL text. Bandit B608. Previously safe by ARGUMENT - the names come from a fixed tuple - documented in a comment.</t>
+        </is>
+      </c>
+      <c r="F30" s="67" t="inlineStr">
+        <is>
+          <t>PostgreSQL cannot parameterise identifiers, so building them as text is the only option and the code was genuinely safe. But a comment does not survive a refactor: nothing would fail if a future change made the column list reachable from data.</t>
+        </is>
+      </c>
+      <c r="G30" s="67" t="inlineStr">
+        <is>
+          <t>Every identifier is now matched against a strict allowlist pattern immediately before interpolation, so the bandit suppression is backed by an executed check rather than by a promise. A change that made the list data-reachable fails loudly instead of building a query.</t>
+        </is>
+      </c>
+      <c r="H30" s="67" t="inlineStr">
+        <is>
+          <t>10 hostile identifiers refused (statement terminator, subquery, quoting, whitespace, comment, dotted, empty, leading digit, case, newline) plus a control that the 8 real column names pass, plus a structural test that the guard runs BEFORE interpolation</t>
+        </is>
+      </c>
+      <c r="I30" s="76" t="n"/>
+      <c r="J30" s="76" t="n"/>
+      <c r="K30" s="76" t="n"/>
+    </row>
+    <row r="31" ht="120" customHeight="1" s="59">
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t>QA-SEC-27</t>
+        </is>
+      </c>
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C31" s="67" t="inlineStr">
+        <is>
+          <t>Secret containment</t>
+        </is>
+      </c>
+      <c r="D31" s="66" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>26 statements of secrets.py had never been executed by any test - including __reduce__, __getstate__, __eq__, __hash__ and every rendering dunder. These are precisely the methods that enforce invariant 4, 'secrets never render'.</t>
+        </is>
+      </c>
+      <c r="F31" s="67" t="inlineStr">
+        <is>
+          <t>The quiet exfiltration path is serialisation: anything picklable can reach Redis, a cache or a crash dump. Untested containment is indistinguishable from absent containment until the day it matters.</t>
+        </is>
+      </c>
+      <c r="G31" s="67" t="inlineStr">
+        <is>
+          <t>15 probes covering pickle, deepcopy, constant-time comparison, hashing that does not derive from the plaintext, and every string-formatting path.</t>
+        </is>
+      </c>
+      <c r="H31" s="67" t="inlineStr">
+        <is>
+          <t>tests/security/test_secrets_providers.py TestSecretStringCannotEscapeItsWrapper</t>
+        </is>
+      </c>
+      <c r="I31" s="76" t="n"/>
+      <c r="J31" s="76" t="n"/>
+      <c r="K31" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H11"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -468,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -632,6 +632,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2214,6 +2226,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2280,7 +2293,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTA(Backlog!$A$5:$A$197)</f>
+        <f>COUNTA(Backlog!$A$5:$A$219)</f>
         <v/>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2299,15 +2312,15 @@
         </is>
       </c>
       <c r="I6" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F6)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F6)</f>
         <v/>
       </c>
       <c r="J6" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F6,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F6,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K6" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F6,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F6,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L6" s="10">
@@ -2322,7 +2335,7 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>SUM(Backlog!$J$5:$J$197)</f>
+        <f>SUM(Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2341,15 +2354,15 @@
         </is>
       </c>
       <c r="I7" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F7)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F7)</f>
         <v/>
       </c>
       <c r="J7" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F7,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F7,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K7" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F7,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F7,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L7" s="10">
@@ -2364,7 +2377,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2383,15 +2396,15 @@
         </is>
       </c>
       <c r="I8" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F8)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F8)</f>
         <v/>
       </c>
       <c r="J8" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F8,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F8,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K8" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F8,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F8,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L8" s="10">
@@ -2406,7 +2419,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>SUMPRODUCT(COUNTIF(Backlog!$E$5:$E$197,{"Active","Development In-Progress","Development Completed","QA In-Progress","QA-Success"}))</f>
+        <f>SUMPRODUCT(COUNTIF(Backlog!$E$5:$E$219,{"Active","Development In-Progress","Development Completed","QA In-Progress","QA-Success"}))</f>
         <v/>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2425,15 +2438,15 @@
         </is>
       </c>
       <c r="I9" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F9)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F9)</f>
         <v/>
       </c>
       <c r="J9" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F9,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F9,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K9" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F9,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F9,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L9" s="10">
@@ -2448,7 +2461,7 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <f>COUNTIF(Backlog!$E$5:$E$197,"New")</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,"New")</f>
         <v/>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2467,15 +2480,15 @@
         </is>
       </c>
       <c r="I10" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F10)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F10)</f>
         <v/>
       </c>
       <c r="J10" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F10,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F10,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K10" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F10,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F10,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L10" s="10">
@@ -2490,7 +2503,7 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>COUNTIF(Backlog!$E$5:$E$197,"Blocked")+COUNTIF(Backlog!$E$5:$E$197,"On Hold")</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,"Blocked")+COUNTIF(Backlog!$E$5:$E$219,"On Hold")</f>
         <v/>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -2509,15 +2522,15 @@
         </is>
       </c>
       <c r="I11" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F11)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F11)</f>
         <v/>
       </c>
       <c r="J11" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F11,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F11,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K11" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F11,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F11,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L11" s="10">
@@ -2532,7 +2545,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>IFERROR(COUNTIF(Backlog!$E$5:$E$197,"Closed")/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR(COUNTIF(Backlog!$E$5:$E$219,"Closed")/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2551,15 +2564,15 @@
         </is>
       </c>
       <c r="I12" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F12)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F12)</f>
         <v/>
       </c>
       <c r="J12" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F12,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F12,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K12" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F12,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F12,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L12" s="10">
@@ -2574,7 +2587,7 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>SUMIF(Backlog!$E$5:$E$197,"Closed",Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,"Closed",Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2593,15 +2606,15 @@
         </is>
       </c>
       <c r="I13" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F13)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F13)</f>
         <v/>
       </c>
       <c r="J13" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F13,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F13,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K13" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F13,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F13,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L13" s="10">
@@ -2616,7 +2629,7 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>SUM(Backlog!$J$5:$J$197)-SUMIF(Backlog!$E$5:$E$197,"Closed",Backlog!$J$5:$J$197)</f>
+        <f>SUM(Backlog!$J$5:$J$219)-SUMIF(Backlog!$E$5:$E$219,"Closed",Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2635,15 +2648,15 @@
         </is>
       </c>
       <c r="I14" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F14)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F14)</f>
         <v/>
       </c>
       <c r="J14" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F14,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F14,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K14" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F14,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F14,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L14" s="10">
@@ -2668,15 +2681,15 @@
         </is>
       </c>
       <c r="I15" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F15)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F15)</f>
         <v/>
       </c>
       <c r="J15" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F15,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F15,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K15" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F15,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F15,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L15" s="10">
@@ -2706,15 +2719,15 @@
         </is>
       </c>
       <c r="I16" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F16)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F16)</f>
         <v/>
       </c>
       <c r="J16" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F16,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F16,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K16" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F16,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F16,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L16" s="10">
@@ -2759,15 +2772,15 @@
         </is>
       </c>
       <c r="I17" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F17)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F17)</f>
         <v/>
       </c>
       <c r="J17" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F17,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F17,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K17" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F17,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F17,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L17" s="10">
@@ -2782,15 +2795,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A18)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>IFERROR($B18/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B18/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A18,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A18,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -2809,15 +2822,15 @@
         </is>
       </c>
       <c r="I18" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F18)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F18)</f>
         <v/>
       </c>
       <c r="J18" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F18,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F18,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K18" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F18,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F18,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L18" s="10">
@@ -2832,15 +2845,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A19)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="14">
-        <f>IFERROR($B19/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B19/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A19,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A19,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -2859,15 +2872,15 @@
         </is>
       </c>
       <c r="I19" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F19)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F19)</f>
         <v/>
       </c>
       <c r="J19" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F19,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F19,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K19" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F19,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F19,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L19" s="10">
@@ -2882,15 +2895,15 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A20)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>IFERROR($B20/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B20/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A20,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A20,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -2909,15 +2922,15 @@
         </is>
       </c>
       <c r="I20" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F20)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F20)</f>
         <v/>
       </c>
       <c r="J20" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F20,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F20,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K20" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F20,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F20,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L20" s="10">
@@ -2932,15 +2945,15 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A21)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>IFERROR($B21/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B21/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D21" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A21,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A21,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2959,15 +2972,15 @@
         </is>
       </c>
       <c r="I21" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F21)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F21)</f>
         <v/>
       </c>
       <c r="J21" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F21,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F21,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K21" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F21,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F21,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L21" s="10">
@@ -2982,15 +2995,15 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A22)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="14">
-        <f>IFERROR($B22/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B22/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D22" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A22,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A22,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -3009,15 +3022,15 @@
         </is>
       </c>
       <c r="I22" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F22)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F22)</f>
         <v/>
       </c>
       <c r="J22" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F22,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F22,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K22" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F22,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F22,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L22" s="10">
@@ -3032,15 +3045,15 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A23)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="14">
-        <f>IFERROR($B23/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B23/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D23" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A23,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A23,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -3059,15 +3072,15 @@
         </is>
       </c>
       <c r="I23" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F23)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F23)</f>
         <v/>
       </c>
       <c r="J23" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F23,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F23,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K23" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F23,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F23,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L23" s="10">
@@ -3082,15 +3095,15 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A24)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="14">
-        <f>IFERROR($B24/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B24/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D24" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A24,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A24,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -3109,15 +3122,15 @@
         </is>
       </c>
       <c r="I24" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F24)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F24)</f>
         <v/>
       </c>
       <c r="J24" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F24,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F24,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K24" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F24,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F24,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L24" s="10">
@@ -3132,15 +3145,15 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A25)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="14">
-        <f>IFERROR($B25/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B25/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D25" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A25,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A25,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -3159,15 +3172,15 @@
         </is>
       </c>
       <c r="I25" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F25)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F25)</f>
         <v/>
       </c>
       <c r="J25" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F25,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F25,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K25" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F25,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F25,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L25" s="10">
@@ -3182,15 +3195,15 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A26)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="14">
-        <f>IFERROR($B26/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B26/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D26" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A26,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A26,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -3209,15 +3222,15 @@
         </is>
       </c>
       <c r="I26" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F26)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F26)</f>
         <v/>
       </c>
       <c r="J26" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F26,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F26,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K26" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F26,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F26,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L26" s="10">
@@ -3232,15 +3245,15 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A27)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="14">
-        <f>IFERROR($B27/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B27/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D27" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A27,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A27,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -3259,15 +3272,15 @@
         </is>
       </c>
       <c r="I27" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F27)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F27)</f>
         <v/>
       </c>
       <c r="J27" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F27,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F27,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K27" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F27,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F27,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L27" s="10">
@@ -3282,15 +3295,15 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A28)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="14">
-        <f>IFERROR($B28/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B28/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D28" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A28,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A28,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -3309,15 +3322,15 @@
         </is>
       </c>
       <c r="I28" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F28)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F28)</f>
         <v/>
       </c>
       <c r="J28" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F28,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F28,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K28" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F28,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F28,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L28" s="10">
@@ -3332,15 +3345,15 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A29)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="14">
-        <f>IFERROR($B29/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B29/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D29" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A29,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A29,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -3359,15 +3372,15 @@
         </is>
       </c>
       <c r="I29" s="8">
-        <f>COUNTIF(Backlog!$B$5:$B$197,$F29)</f>
+        <f>COUNTIF(Backlog!$B$5:$B$219,$F29)</f>
         <v/>
       </c>
       <c r="J29" s="9">
-        <f>SUMIF(Backlog!$B$5:$B$197,$F29,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$B$5:$B$219,$F29,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="K29" s="8">
-        <f>COUNTIFS(Backlog!$B$5:$B$197,$F29,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$B$5:$B$219,$F29,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="L29" s="10">
@@ -3382,15 +3395,15 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A30)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="14">
-        <f>IFERROR($B30/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B30/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D30" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A30,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A30,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -3424,15 +3437,15 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A31)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="14">
-        <f>IFERROR($B31/COUNTA(Backlog!$A$5:$A$197),0)</f>
+        <f>IFERROR($B31/COUNTA(Backlog!$A$5:$A$219),0)</f>
         <v/>
       </c>
       <c r="D31" s="9">
-        <f>SUMIF(Backlog!$E$5:$E$197,$A31,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$E$5:$E$219,$A31,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
     </row>
@@ -3455,6 +3468,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -3491,15 +3505,15 @@
         </is>
       </c>
       <c r="B36" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$197,$A36)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$219,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$197,$A36,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$F$5:$F$219,$A36,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D36" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$197,$A36,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$F$5:$F$219,$A36,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3510,15 +3524,15 @@
         </is>
       </c>
       <c r="B37" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$197,$A37)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$219,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$197,$A37,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$F$5:$F$219,$A37,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D37" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$197,$A37,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$F$5:$F$219,$A37,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3529,15 +3543,15 @@
         </is>
       </c>
       <c r="B38" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$197,$A38)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$219,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$197,$A38,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$F$5:$F$219,$A38,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D38" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$197,$A38,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$F$5:$F$219,$A38,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3548,18 +3562,19 @@
         </is>
       </c>
       <c r="B39" s="31">
-        <f>COUNTIF(Backlog!$F$5:$F$197,$A39)</f>
+        <f>COUNTIF(Backlog!$F$5:$F$219,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="9">
-        <f>SUMIF(Backlog!$F$5:$F$197,$A39,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$F$5:$F$219,$A39,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D39" s="31">
-        <f>COUNTIFS(Backlog!$F$5:$F$197,$A39,Backlog!$E$5:$E$197,"Closed")</f>
-        <v/>
-      </c>
-    </row>
+        <f>COUNTIFS(Backlog!$F$5:$F$219,$A39,Backlog!$E$5:$E$219,"Closed")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -3596,15 +3611,15 @@
         </is>
       </c>
       <c r="B43" s="31">
-        <f>COUNTIF(Backlog!$H$5:$H$197,$A43)</f>
+        <f>COUNTIF(Backlog!$H$5:$H$219,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="9">
-        <f>SUMIF(Backlog!$H$5:$H$197,$A43,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$H$5:$H$219,$A43,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D43" s="31">
-        <f>COUNTIFS(Backlog!$H$5:$H$197,$A43,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$H$5:$H$219,$A43,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3615,15 +3630,15 @@
         </is>
       </c>
       <c r="B44" s="31">
-        <f>COUNTIF(Backlog!$H$5:$H$197,$A44)</f>
+        <f>COUNTIF(Backlog!$H$5:$H$219,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="9">
-        <f>SUMIF(Backlog!$H$5:$H$197,$A44,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$H$5:$H$219,$A44,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D44" s="31">
-        <f>COUNTIFS(Backlog!$H$5:$H$197,$A44,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$H$5:$H$219,$A44,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3634,18 +3649,19 @@
         </is>
       </c>
       <c r="B45" s="31">
-        <f>COUNTIF(Backlog!$H$5:$H$197,$A45)</f>
+        <f>COUNTIF(Backlog!$H$5:$H$219,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="9">
-        <f>SUMIF(Backlog!$H$5:$H$197,$A45,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$H$5:$H$219,$A45,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D45" s="31">
-        <f>COUNTIFS(Backlog!$H$5:$H$197,$A45,Backlog!$E$5:$E$197,"Closed")</f>
-        <v/>
-      </c>
-    </row>
+        <f>COUNTIFS(Backlog!$H$5:$H$219,$A45,Backlog!$E$5:$E$219,"Closed")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
@@ -3682,15 +3698,15 @@
         </is>
       </c>
       <c r="B49" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$197,$A49)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$219,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$197,$A49,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$I$5:$I$219,$A49,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D49" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$197,$A49,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$219,$A49,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3701,15 +3717,15 @@
         </is>
       </c>
       <c r="B50" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$197,$A50)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$219,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$197,$A50,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$I$5:$I$219,$A50,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D50" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$197,$A50,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$219,$A50,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3720,15 +3736,15 @@
         </is>
       </c>
       <c r="B51" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$197,$A51)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$219,$A51)</f>
         <v/>
       </c>
       <c r="C51" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$197,$A51,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$I$5:$I$219,$A51,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D51" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$197,$A51,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$219,$A51,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3739,15 +3755,15 @@
         </is>
       </c>
       <c r="B52" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$197,$A52)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$219,$A52)</f>
         <v/>
       </c>
       <c r="C52" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$197,$A52,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$I$5:$I$219,$A52,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D52" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$197,$A52,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$219,$A52,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3758,15 +3774,15 @@
         </is>
       </c>
       <c r="B53" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$197,$A53)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$219,$A53)</f>
         <v/>
       </c>
       <c r="C53" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$197,$A53,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$I$5:$I$219,$A53,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D53" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$197,$A53,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>COUNTIFS(Backlog!$I$5:$I$219,$A53,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
     </row>
@@ -3777,18 +3793,21 @@
         </is>
       </c>
       <c r="B54" s="31">
-        <f>COUNTIF(Backlog!$I$5:$I$197,$A54)</f>
+        <f>COUNTIF(Backlog!$I$5:$I$219,$A54)</f>
         <v/>
       </c>
       <c r="C54" s="9">
-        <f>SUMIF(Backlog!$I$5:$I$197,$A54,Backlog!$J$5:$J$197)</f>
+        <f>SUMIF(Backlog!$I$5:$I$219,$A54,Backlog!$J$5:$J$219)</f>
         <v/>
       </c>
       <c r="D54" s="31">
-        <f>COUNTIFS(Backlog!$I$5:$I$197,$A54,Backlog!$E$5:$E$197,"Closed")</f>
-        <v/>
-      </c>
-    </row>
+        <f>COUNTIFS(Backlog!$I$5:$I$219,$A54,Backlog!$E$5:$E$219,"Closed")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="71" t="inlineStr">
         <is>
@@ -3822,7 +3841,7 @@
         </is>
       </c>
       <c r="B61">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$61)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$61)</f>
         <v/>
       </c>
     </row>
@@ -3833,7 +3852,7 @@
         </is>
       </c>
       <c r="B62">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$62)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$62)</f>
         <v/>
       </c>
     </row>
@@ -3844,7 +3863,7 @@
         </is>
       </c>
       <c r="B63">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$63)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$63)</f>
         <v/>
       </c>
     </row>
@@ -3855,7 +3874,7 @@
         </is>
       </c>
       <c r="B64">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$64)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$64)</f>
         <v/>
       </c>
     </row>
@@ -3866,7 +3885,7 @@
         </is>
       </c>
       <c r="B65">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$65)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$65)</f>
         <v/>
       </c>
     </row>
@@ -3877,7 +3896,7 @@
         </is>
       </c>
       <c r="B66">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$66)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$66)</f>
         <v/>
       </c>
     </row>
@@ -3888,7 +3907,7 @@
         </is>
       </c>
       <c r="B67">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$67)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$67)</f>
         <v/>
       </c>
     </row>
@@ -3899,7 +3918,7 @@
         </is>
       </c>
       <c r="B68">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$68)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$68)</f>
         <v/>
       </c>
     </row>
@@ -3910,7 +3929,7 @@
         </is>
       </c>
       <c r="B69">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$69)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$69)</f>
         <v/>
       </c>
     </row>
@@ -3921,7 +3940,7 @@
         </is>
       </c>
       <c r="B70">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$70)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$70)</f>
         <v/>
       </c>
     </row>
@@ -3932,7 +3951,7 @@
         </is>
       </c>
       <c r="B71">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$71)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$71)</f>
         <v/>
       </c>
     </row>
@@ -3943,7 +3962,7 @@
         </is>
       </c>
       <c r="B72">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$72)</f>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$72)</f>
         <v/>
       </c>
     </row>
@@ -3954,10 +3973,11 @@
         </is>
       </c>
       <c r="B73">
-        <f>COUNTIF(Backlog!$E$5:$E$197,$A$73)</f>
-        <v/>
-      </c>
-    </row>
+        <f>COUNTIF(Backlog!$E$5:$E$219,$A$73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="71" t="inlineStr">
         <is>
@@ -3989,11 +4009,11 @@
         </is>
       </c>
       <c r="B77">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$77,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$77,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C77">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$77,Backlog!$J$5:$J$197)-$B$77</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$77,Backlog!$J$5:$J$219)-$B$77</f>
         <v/>
       </c>
     </row>
@@ -4004,11 +4024,11 @@
         </is>
       </c>
       <c r="B78">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$78,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$78,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C78">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$78,Backlog!$J$5:$J$197)-$B$78</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$78,Backlog!$J$5:$J$219)-$B$78</f>
         <v/>
       </c>
     </row>
@@ -4019,11 +4039,11 @@
         </is>
       </c>
       <c r="B79">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$79,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$79,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C79">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$79,Backlog!$J$5:$J$197)-$B$79</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$79,Backlog!$J$5:$J$219)-$B$79</f>
         <v/>
       </c>
     </row>
@@ -4034,11 +4054,11 @@
         </is>
       </c>
       <c r="B80">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$80,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$80,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C80">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$80,Backlog!$J$5:$J$197)-$B$80</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$80,Backlog!$J$5:$J$219)-$B$80</f>
         <v/>
       </c>
     </row>
@@ -4049,11 +4069,11 @@
         </is>
       </c>
       <c r="B81">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$81,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$81,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C81">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$81,Backlog!$J$5:$J$197)-$B$81</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$81,Backlog!$J$5:$J$219)-$B$81</f>
         <v/>
       </c>
     </row>
@@ -4064,11 +4084,11 @@
         </is>
       </c>
       <c r="B82">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$82,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$82,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C82">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$82,Backlog!$J$5:$J$197)-$B$82</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$82,Backlog!$J$5:$J$219)-$B$82</f>
         <v/>
       </c>
     </row>
@@ -4079,11 +4099,11 @@
         </is>
       </c>
       <c r="B83">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$83,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$83,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C83">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$83,Backlog!$J$5:$J$197)-$B$83</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$83,Backlog!$J$5:$J$219)-$B$83</f>
         <v/>
       </c>
     </row>
@@ -4094,11 +4114,11 @@
         </is>
       </c>
       <c r="B84">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$84,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$84,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C84">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$84,Backlog!$J$5:$J$197)-$B$84</f>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$84,Backlog!$J$5:$J$219)-$B$84</f>
         <v/>
       </c>
     </row>
@@ -4109,14 +4129,15 @@
         </is>
       </c>
       <c r="B85">
-        <f>SUMIFS(Backlog!$J$5:$J$197,Backlog!$G$5:$G$197,$A$85,Backlog!$E$5:$E$197,"Closed")</f>
+        <f>SUMIFS(Backlog!$J$5:$J$219,Backlog!$G$5:$G$219,$A$85,Backlog!$E$5:$E$219,"Closed")</f>
         <v/>
       </c>
       <c r="C85">
-        <f>SUMIF(Backlog!$G$5:$G$197,$A$85,Backlog!$J$5:$J$197)-$B$85</f>
-        <v/>
-      </c>
-    </row>
+        <f>SUMIF(Backlog!$G$5:$G$219,$A$85,Backlog!$J$5:$J$219)-$B$85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="71" t="inlineStr">
         <is>
@@ -4142,7 +4163,7 @@
         <v/>
       </c>
       <c r="B89" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$89,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$89,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$89,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$89,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4152,7 +4173,7 @@
         <v/>
       </c>
       <c r="B90" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$90,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$90,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$90,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$90,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4162,7 +4183,7 @@
         <v/>
       </c>
       <c r="B91" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$91,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$91,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$91,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$91,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4172,7 +4193,7 @@
         <v/>
       </c>
       <c r="B92" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$92,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$92,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$92,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$92,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4182,7 +4203,7 @@
         <v/>
       </c>
       <c r="B93" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$93,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$93,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$93,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$93,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4192,7 +4213,7 @@
         <v/>
       </c>
       <c r="B94" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$94,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$94,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$94,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$94,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4202,7 +4223,7 @@
         <v/>
       </c>
       <c r="B95" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$95,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$95,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$95,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$95,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4212,7 +4233,7 @@
         <v/>
       </c>
       <c r="B96" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$96,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$96,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$96,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$96,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4222,7 +4243,7 @@
         <v/>
       </c>
       <c r="B97" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$97,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$97,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$97,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$97,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4232,7 +4253,7 @@
         <v/>
       </c>
       <c r="B98" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$98,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$98,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$98,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$98,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4242,7 +4263,7 @@
         <v/>
       </c>
       <c r="B99" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$99,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$99,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$99,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$99,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4252,7 +4273,7 @@
         <v/>
       </c>
       <c r="B100" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$100,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$100,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$100,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$100,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4262,7 +4283,7 @@
         <v/>
       </c>
       <c r="B101" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$101,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$101,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$101,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$101,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4272,7 +4293,7 @@
         <v/>
       </c>
       <c r="B102" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$102,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$102,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$102,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$102,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4282,7 +4303,7 @@
         <v/>
       </c>
       <c r="B103" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$103,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$103,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$103,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$103,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4292,7 +4313,7 @@
         <v/>
       </c>
       <c r="B104" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$104,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$104,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$104,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$104,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4302,7 +4323,7 @@
         <v/>
       </c>
       <c r="B105" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$105,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$105,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$105,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$105,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4312,7 +4333,7 @@
         <v/>
       </c>
       <c r="B106" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$106,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$106,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$106,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$106,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4343,7 @@
         <v/>
       </c>
       <c r="B107" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$107,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$107,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$107,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$107,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4332,7 +4353,7 @@
         <v/>
       </c>
       <c r="B108" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$108,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$108,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$108,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$108,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4342,7 +4363,7 @@
         <v/>
       </c>
       <c r="B109" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$109,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$109,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$109,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$109,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4352,7 +4373,7 @@
         <v/>
       </c>
       <c r="B110" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$110,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$110,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$110,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$110,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4362,7 +4383,7 @@
         <v/>
       </c>
       <c r="B111" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$111,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$111,Backlog!$J$5:$J$197),0)</f>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$111,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$111,Backlog!$J$5:$J$219),0)</f>
         <v/>
       </c>
     </row>
@@ -4372,10 +4393,11 @@
         <v/>
       </c>
       <c r="B112" s="73">
-        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$197,Backlog!$B$5:$B$197,$A$112,Backlog!$E$5:$E$197,"Closed")/SUMIF(Backlog!$B$5:$B$197,$A$112,Backlog!$J$5:$J$197),0)</f>
-        <v/>
-      </c>
-    </row>
+        <f>IFERROR(SUMIFS(Backlog!$J$5:$J$219,Backlog!$B$5:$B$219,$A$112,Backlog!$E$5:$E$219,"Closed")/SUMIF(Backlog!$B$5:$B$219,$A$112,Backlog!$J$5:$J$219),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="71" t="inlineStr">
         <is>
@@ -4499,7 +4521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X197"/>
+  <dimension ref="A1:X199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -4541,6 +4563,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -5122,7 +5145,7 @@
       </c>
       <c r="D12" s="40" t="inlineStr">
         <is>
-          <t>Closed (evaluator delivered 24 Aug 2026)</t>
+          <t>Strategy DSL with vetted primitive registry</t>
         </is>
       </c>
       <c r="E12" s="40" t="inlineStr">
@@ -6224,7 +6247,7 @@
       </c>
       <c r="E23" s="40" t="inlineStr">
         <is>
-          <t>Development In-Progress</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F23" s="41" t="inlineStr">
@@ -6326,7 +6349,7 @@
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Development In-Progress</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F24" s="41" t="inlineStr">
@@ -6418,7 +6441,7 @@
       </c>
       <c r="E25" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F25" s="41" t="inlineStr">
@@ -6509,7 +6532,7 @@
       </c>
       <c r="E26" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F26" s="41" t="inlineStr">
@@ -6609,7 +6632,7 @@
       </c>
       <c r="E27" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F27" s="41" t="inlineStr">
@@ -6707,7 +6730,7 @@
       </c>
       <c r="E28" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F28" s="41" t="inlineStr">
@@ -6802,7 +6825,7 @@
       </c>
       <c r="E29" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F29" s="41" t="inlineStr">
@@ -6980,7 +7003,7 @@
       </c>
       <c r="E31" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F31" s="41" t="inlineStr">
@@ -7167,7 +7190,7 @@
       </c>
       <c r="E33" s="40" t="inlineStr">
         <is>
-          <t>Development In-Progress</t>
+          <t>Development Completed</t>
         </is>
       </c>
       <c r="F33" s="41" t="inlineStr">
@@ -8201,7 +8224,7 @@
       </c>
       <c r="E45" s="40" t="inlineStr">
         <is>
-          <t>Development In-Progress</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F45" s="41" t="inlineStr">
@@ -8301,7 +8324,7 @@
       </c>
       <c r="E46" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F46" s="41" t="inlineStr">
@@ -8388,7 +8411,7 @@
       </c>
       <c r="E47" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F47" s="41" t="inlineStr">
@@ -8473,7 +8496,7 @@
       </c>
       <c r="E48" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F48" s="41" t="inlineStr">
@@ -8568,7 +8591,7 @@
       </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F49" s="41" t="inlineStr">
@@ -8653,7 +8676,7 @@
       </c>
       <c r="E50" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F50" s="41" t="inlineStr">
@@ -8750,7 +8773,7 @@
       </c>
       <c r="E51" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F51" s="41" t="inlineStr">
@@ -8835,7 +8858,7 @@
       </c>
       <c r="E52" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F52" s="41" t="inlineStr">
@@ -8920,7 +8943,7 @@
       </c>
       <c r="E53" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F53" s="41" t="inlineStr">
@@ -9108,7 +9131,7 @@
       </c>
       <c r="E55" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F55" s="41" t="inlineStr">
@@ -9205,7 +9228,7 @@
       </c>
       <c r="E56" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F56" s="41" t="inlineStr">
@@ -9286,7 +9309,7 @@
       </c>
       <c r="E57" s="40" t="inlineStr">
         <is>
-          <t>Development Completed</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F57" s="41" t="inlineStr">
@@ -9351,60 +9374,60 @@
       <c r="W57" s="49" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1" s="59">
-      <c r="A58" s="38" t="inlineStr">
+      <c r="A58" s="77" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="B58" s="48" t="inlineStr">
         <is>
           <t>E06</t>
         </is>
       </c>
-      <c r="C58" s="40" t="inlineStr">
+      <c r="C58" s="48" t="inlineStr">
         <is>
           <t>TECHNICAL ANALYSIS ENGINE</t>
         </is>
       </c>
-      <c r="D58" s="40" t="inlineStr">
-        <is>
-          <t>Development Completed</t>
-        </is>
-      </c>
-      <c r="E58" s="40" t="inlineStr">
-        <is>
-          <t>Development Completed</t>
-        </is>
-      </c>
-      <c r="F58" s="41" t="inlineStr">
+      <c r="D58" s="48" t="inlineStr">
+        <is>
+          <t>Opening range computation</t>
+        </is>
+      </c>
+      <c r="E58" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
+        </is>
+      </c>
+      <c r="F58" s="78" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G58" s="39" t="inlineStr">
+      <c r="G58" s="48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H58" s="51" t="inlineStr">
+      <c r="H58" s="79" t="inlineStr">
         <is>
           <t>Safety-critical</t>
         </is>
       </c>
-      <c r="I58" s="39" t="inlineStr">
+      <c r="I58" s="48" t="inlineStr">
         <is>
           <t>FEAT</t>
         </is>
       </c>
-      <c r="J58" s="43" t="n">
+      <c r="J58" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="K58" s="40" t="inlineStr">
+      <c r="K58" s="48" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="L58" s="40" t="n"/>
+      <c r="L58" s="48" t="n"/>
       <c r="M58" s="44" t="n"/>
       <c r="N58" s="45" t="n"/>
       <c r="O58" s="46" t="n"/>
@@ -20339,6 +20362,126 @@
       <c r="W197" s="49" t="inlineStr">
         <is>
           <t>Two of the six were found by the pen-test suite failing on its OWN first run (QA-SEC-03 regex bypass, QA-SEC-06 log flooding), which is the strongest argument for writing adversarial tests rather than reviewing code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="77" t="inlineStr">
+        <is>
+          <t>E00-S11</t>
+        </is>
+      </c>
+      <c r="B198" s="48" t="inlineStr">
+        <is>
+          <t>E00</t>
+        </is>
+      </c>
+      <c r="C198" s="48" t="inlineStr">
+        <is>
+          <t>FOUNDATION</t>
+        </is>
+      </c>
+      <c r="D198" s="48" t="inlineStr">
+        <is>
+          <t>Strategy primitive evaluators and tri-state runtime</t>
+        </is>
+      </c>
+      <c r="E198" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
+        </is>
+      </c>
+      <c r="F198" s="78" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G198" s="48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H198" s="79" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I198" s="48" t="inlineStr">
+        <is>
+          <t>FEAT</t>
+        </is>
+      </c>
+      <c r="J198" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K198" s="48" t="inlineStr">
+        <is>
+          <t>E00-S08, E06-S04</t>
+        </is>
+      </c>
+      <c r="L198" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="77" t="inlineStr">
+        <is>
+          <t>E22-S00</t>
+        </is>
+      </c>
+      <c r="B199" s="48" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="C199" s="48" t="inlineStr">
+        <is>
+          <t>TESTING &amp; VALIDATION</t>
+        </is>
+      </c>
+      <c r="D199" s="48" t="inlineStr">
+        <is>
+          <t>Mutation testing harness for the safety-critical paths</t>
+        </is>
+      </c>
+      <c r="E199" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
+        </is>
+      </c>
+      <c r="F199" s="78" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G199" s="48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H199" s="79" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I199" s="48" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="J199" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L199" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20956,6 +21099,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21088,6 +21232,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -23445,6 +23590,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -24739,6 +24885,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -25362,6 +25509,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="57" t="inlineStr">
         <is>
@@ -25549,6 +25697,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="57" t="inlineStr">
         <is>
@@ -25616,6 +25766,8 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="57" t="inlineStr">
         <is>
@@ -25671,6 +25823,8 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="57" t="inlineStr">
         <is>
@@ -25762,6 +25916,8 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="57" t="inlineStr">
         <is>
@@ -25818,6 +25974,8 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="57" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -468,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -644,6 +644,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2226,7 +2229,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3468,7 +3470,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -3574,7 +3575,6 @@
         <v/>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -3661,7 +3661,6 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
@@ -3805,9 +3804,6 @@
         <v/>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="71" t="inlineStr">
         <is>
@@ -3977,7 +3973,6 @@
         <v/>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="71" t="inlineStr">
         <is>
@@ -4137,7 +4132,6 @@
         <v/>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" s="71" t="inlineStr">
         <is>
@@ -4397,7 +4391,6 @@
         <v/>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="71" t="inlineStr">
         <is>
@@ -4563,7 +4556,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -20557,7 +20549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="59" min="1" max="1"/>
@@ -20879,8 +20871,8 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="150" customHeight="1" s="59">
-      <c r="A11" s="38" t="inlineStr">
+    <row r="11" ht="210" customHeight="1" s="59">
+      <c r="A11" s="77" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
@@ -20897,20 +20889,26 @@
       </c>
       <c r="D11" s="48" t="inlineStr">
         <is>
-          <t>Upgraded autobahn to 26.7.1. kiteconnect's autobahn[twisted]==19.11.2 pin is DECLARATIVE, not a runtime requirement: only kiteconnect.ticker imports autobahn, we never construct a KiteTicker, and the feed runs on `websockets`. Verified empirically - kiteconnect imports, builds a login URL and exposes market_protection/algo_id under 26.7.1, and all 1059 tests pass. pip-audit now reports zero known vulnerabilities. pyproject floors autobahn at &gt;=20.12.3. NOTE: the earlier claim that autobahn was 'never imported' was WRONG - kiteconnect/__init__.py imports .ticker unconditionally, so it loaded into every process touching the broker layer. Not using a package is not the same as not having it.</t>
-        </is>
-      </c>
-      <c r="E11" s="40" t="inlineStr">
-        <is>
-          <t>RESOLVED 24 Aug 2026</t>
-        </is>
-      </c>
-      <c r="F11" s="44" t="inlineStr">
+          <t>CLOSED. No environment we build contains the vulnerable autobahn, and CI asserts that from inside its own runner rather than being told so.
+HOW, and this is the part the first attempt got wrong: a floor of autobahn&gt;=20.12.3 in pyproject.toml is UNSATISFIABLE. kiteconnect's ==19.11.2 is a hard pin, so pip fails with ResolutionImpossible rather than warning, and every CI job broke for two commits. It passed locally only because the package had been force-installed over an already-resolved environment - the environment being verified was one that pip install could never produce.
+The pin is DECLARATIVE, not a runtime requirement, so resolution runs first and the package is then replaced:
+    pip install -c constraints.txt -e ".[dev]"
+    pip install --no-deps --upgrade "autobahn==26.7.1"
+applied in all three CI install jobs, ops/Dockerfile and `make install`.
+EVIDENCE: tests/security/test_dependency_hygiene.py runs inside CI's Security job (pytest tests/security/) and asserts, without skipping, that the INSTALLED autobahn is &gt;= 20.12.3, that kiteconnect still imports under it, and that market_protection and algo_id survive on place_order. DEV 0acab9b and QA 24ae953 are green on all five jobs. pip-audit reports zero known vulnerabilities and is a hard gate.</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="inlineStr">
+        <is>
+          <t>CLOSED 24 Aug 2026 - verified in CI</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="81" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -21006,6 +21004,49 @@
 MITIGATIONS: jugaad-data (actively maintained, with caching specifically to avoid being blocked); nsefin for corporate actions, which is also E03-S02's missing feed; BSE as a fallback since ~90% of NSE equities are dual-listed; Zerodha's consolidated scrip sheet as a cross-check only (no SLA). The India-hosted VPS already required by constraint C1 sidesteps the geo-restriction.
 WHY IT IS SURVIVABLE: the fetch runs at 05:30, hours before the open, so a failure has a long runway for a retry, a fallback source or a manual override. E04-S01's acceptance criterion already says a fetch failure blocks the trading day rather than proceeding blind - the right posture: a bad fetch costs a trading day, not money.
 ACTION: spend an hour proving NSE reachability from the target environment before writing fetchers. That assumption sits under 8 stories and roughly 10 days of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="250" customHeight="1" s="59">
+      <c r="A14" s="77" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>kiteconnect runs against an autobahn it does not declare support for</t>
+        </is>
+      </c>
+      <c r="C14" s="48" t="inlineStr">
+        <is>
+          <t>Nothing today. A future kiteconnect release could.</t>
+        </is>
+      </c>
+      <c r="D14" s="48" t="inlineStr">
+        <is>
+          <t>Registered as its own row rather than folded into B7, because it is a different risk with a different resolution. B7 was 'a vulnerable package is present'. This is 'we run an undeclared combination'.
+`pip check` reports it plainly: kiteconnect 5.2.1 has requirement autobahn[twisted]==19.11.2, but you have autobahn 26.7.1. Two consequences:
+  1. Only kiteconnect.ticker imports autobahn, and we never construct a KiteTicker - the live feed is built on `websockets` against the documented binary protocol. So nothing we call depends on the pinned API.
+  2. --no-deps means autobahn 26.7.1's own dependencies are not pulled by that step. They are satisfied in practice - CI imports kiteconnect successfully, which transitively imports autobahn.twisted.websocket - but that is an observed property of the environment rather than a declared one.
+WATCHED BY: test_kiteconnect_still_imports_under_the_replacement and test_the_order_parameters_we_depend_on_survive. If a future kiteconnect genuinely needs 19.11.2's API, those fail rather than an order being rejected at the exchange.
+RESOLVES PERMANENTLY when kiteconnect relaxes its pin, or when the REST client is replaced - we use it for KiteConnect and kiteconnect.exceptions only, and it is a thin requests wrapper. Not worth doing for this reason alone.</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="inlineStr">
+        <is>
+          <t>Accepted risk - watched by tests</t>
+        </is>
+      </c>
+      <c r="F14" s="49" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G14" s="81" t="inlineStr"/>
+      <c r="H14" s="49" t="inlineStr">
+        <is>
+          <t>Opened 24 Aug 2026, as the residual of closing B7. Reviewed whenever kiteconnect is upgraded.</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21140,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21232,7 +21272,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -23590,7 +23629,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -24885,7 +24923,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -25509,7 +25546,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="57" t="inlineStr">
         <is>
@@ -25697,8 +25733,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="57" t="inlineStr">
         <is>
@@ -25766,8 +25800,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="57" t="inlineStr">
         <is>
@@ -25823,8 +25855,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="57" t="inlineStr">
         <is>
@@ -25916,8 +25946,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="57" t="inlineStr">
         <is>
@@ -25974,8 +26002,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="57" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -14203,7 +14203,7 @@
       </c>
       <c r="W117" s="49" t="n"/>
     </row>
-    <row r="118" ht="30" customHeight="1" s="59">
+    <row r="118" ht="150" customHeight="1" s="59">
       <c r="A118" s="38" t="inlineStr">
         <is>
           <t>E14-S01</t>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="E118" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F118" s="41" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="K118" s="40" t="inlineStr">
         <is>
-          <t>E13-S04</t>
+          <t>E00-S02</t>
         </is>
       </c>
       <c r="L118" s="40" t="n"/>
@@ -14281,7 +14281,13 @@
 • Any rejection is explainable from the audit log</t>
         </is>
       </c>
-      <c r="V118" s="48" t="n"/>
+      <c r="V118" s="48" t="inlineStr">
+        <is>
+          <t>DEPENDENCY CORRECTED 25 Aug 2026. Was E13-S04 (Recommendation emission). Taken literally that chained E14-S01 behind E13-S03 -&gt; E10-S05 -&gt; E10-S03 -&gt; E10-S01, i.e. the deterministic risk engine could not start until the entire AI layer existed. That inverts the architecture's own boundary: Recommendation is the AI/deterministic seam precisely so the downstream side does not depend on how the upstream side produced it (constraint C4).
+What E14-S01 actually needs is the Recommendation TYPE, from E00-S02 (Closed), plus RiskDecision and SizingResult which are defined in the same module. It does not need the emitter, the signal stream, or an AIReview from a real model - an AIReview is a Pydantic model a test can construct directly.
+E13-S04 remains a genuine dependency for RUNTIME WIRING - the risk engine consuming from stream:signals - which is E13-S05/E15 work, not this story.</t>
+        </is>
+      </c>
       <c r="W118" s="49" t="n"/>
     </row>
     <row r="119" ht="30" customHeight="1" s="59">
@@ -20576,7 +20582,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21244,7 +21249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -23582,6 +23587,206 @@
       <c r="H63" s="76" t="n"/>
       <c r="I63" s="76" t="n"/>
       <c r="J63" s="76" t="n"/>
+    </row>
+    <row r="64" ht="104" customHeight="1" s="59">
+      <c r="A64" s="67" t="inlineStr">
+        <is>
+          <t>QA-E14-01</t>
+        </is>
+      </c>
+      <c r="B64" s="67" t="inlineStr">
+        <is>
+          <t>E14-S01</t>
+        </is>
+      </c>
+      <c r="C64" s="67" t="inlineStr">
+        <is>
+          <t>BA: dependency was mis-stated</t>
+        </is>
+      </c>
+      <c r="D64" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E64" s="67" t="inlineStr">
+        <is>
+          <t>E14-S01 declared a dependency on E13-S04. Traced the chain: E13-S04 -&gt; E13-S03 -&gt; E10-S05 -&gt; E10-S03 -&gt; E10-S01. Taken literally, the deterministic risk engine could not start until the entire AI layer existed.</t>
+        </is>
+      </c>
+      <c r="F64" s="67" t="inlineStr">
+        <is>
+          <t>That inverts the architecture's own boundary. Recommendation is the AI/deterministic seam precisely so the downstream side does not depend on how the upstream side produced it (constraint C4). What E14-S01 needs is the Recommendation TYPE, from E00-S02 (Closed). Corrected to E00-S02 with the justification recorded on the story; E13-S04 remains a real dependency for runtime WIRING, which is E13-S05/E15.</t>
+        </is>
+      </c>
+      <c r="G64" s="67" t="inlineStr">
+        <is>
+          <t>Definition of Ready R2, per ENGINEERING_STANDARD 2.1</t>
+        </is>
+      </c>
+      <c r="H64" s="76" t="n"/>
+      <c r="I64" s="76" t="n"/>
+      <c r="J64" s="76" t="n"/>
+    </row>
+    <row r="65" ht="104" customHeight="1" s="59">
+      <c r="A65" s="67" t="inlineStr">
+        <is>
+          <t>QA-E14-02</t>
+        </is>
+      </c>
+      <c r="B65" s="67" t="inlineStr">
+        <is>
+          <t>E14-S01</t>
+        </is>
+      </c>
+      <c r="C65" s="67" t="inlineStr">
+        <is>
+          <t>Analysis: spec check names overflow the audit column</t>
+        </is>
+      </c>
+      <c r="D65" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E65" s="67" t="inlineStr">
+        <is>
+          <t>decision_log.stage is String(28). Three of the fourteen check names in LOW_LEVEL_ARCHITECTURE 5.7 are longer: check_symbol_not_already_held (29), check_net_directional_exposure (30), check_time_to_squareoff_deadline (32).</t>
+        </is>
+      </c>
+      <c r="F65" s="67" t="inlineStr">
+        <is>
+          <t>Using the spec's function names as the audit stage would fail the insert at the moment a rejection happens - precisely when the record is wanted. Resolved with short stable check IDs decoupled from function names, and RiskCheck refuses an over-long id at DECLARATION rather than at 09:20 on the first rejection.</t>
+        </is>
+      </c>
+      <c r="G65" s="67" t="inlineStr">
+        <is>
+          <t>test_risk_framework.py TestCheckRegistrationIsValidated</t>
+        </is>
+      </c>
+      <c r="H65" s="76" t="n"/>
+      <c r="I65" s="76" t="n"/>
+      <c r="J65" s="76" t="n"/>
+    </row>
+    <row r="66" ht="104" customHeight="1" s="59">
+      <c r="A66" s="67" t="inlineStr">
+        <is>
+          <t>QA-E14-03</t>
+        </is>
+      </c>
+      <c r="B66" s="67" t="inlineStr">
+        <is>
+          <t>E14-S01</t>
+        </is>
+      </c>
+      <c r="C66" s="67" t="inlineStr">
+        <is>
+          <t>Spec called constructors that did not exist</t>
+        </is>
+      </c>
+      <c r="D66" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E66" s="67" t="inlineStr">
+        <is>
+          <t>LOW_LEVEL_ARCHITECTURE 5.7 writes the engine in terms of RiskDecision.approve(...) and .reject(...). Neither existed; the spec's pseudocode was the only place they appeared.</t>
+        </is>
+      </c>
+      <c r="F66" s="67" t="inlineStr">
+        <is>
+          <t>Added as named constructors, which also makes approval greppable - that is how criterion 1 is checked, by a structural test asserting nothing outside RiskEngine constructs one. reject() requires a detail rather than accepting None, so a check cannot log a rejection nobody can act on.</t>
+        </is>
+      </c>
+      <c r="G66" s="67" t="inlineStr">
+        <is>
+          <t>test_risk_pipeline_integrity.py TestOnlyTheEngineApproves</t>
+        </is>
+      </c>
+      <c r="H66" s="76" t="n"/>
+      <c r="I66" s="76" t="n"/>
+      <c r="J66" s="76" t="n"/>
+    </row>
+    <row r="67" ht="104" customHeight="1" s="59">
+      <c r="A67" s="67" t="inlineStr">
+        <is>
+          <t>QA-E14-04</t>
+        </is>
+      </c>
+      <c r="B67" s="67" t="inlineStr">
+        <is>
+          <t>E14-S01</t>
+        </is>
+      </c>
+      <c r="C67" s="67" t="inlineStr">
+        <is>
+          <t>Determinism test rejected my own helper</t>
+        </is>
+      </c>
+      <c r="D67" s="66" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E67" s="67" t="inlineStr">
+        <is>
+          <t>Added a utc_now() convenience to framework.py. The structural determinism test flagged it: a clock read anywhere in the module weakens the property the module is supposed to have.</t>
+        </is>
+      </c>
+      <c r="F67" s="67" t="inlineStr">
+        <is>
+          <t>Deleted rather than exempted. The caller building a RiskContext supplies `now` explicitly, which is what makes an evaluation reproducible from its recorded inputs - the same property whose absence was found in the strategy evaluator (uuid4 in fire()).</t>
+        </is>
+      </c>
+      <c r="G67" s="67" t="inlineStr">
+        <is>
+          <t>test_risk_pipeline_integrity.py TestTheEngineIsDeterministic</t>
+        </is>
+      </c>
+      <c r="H67" s="76" t="n"/>
+      <c r="I67" s="76" t="n"/>
+      <c r="J67" s="76" t="n"/>
+    </row>
+    <row r="68" ht="104" customHeight="1" s="59">
+      <c r="A68" s="67" t="inlineStr">
+        <is>
+          <t>QA-E14-05</t>
+        </is>
+      </c>
+      <c r="B68" s="67" t="inlineStr">
+        <is>
+          <t>E14-S01</t>
+        </is>
+      </c>
+      <c r="C68" s="67" t="inlineStr">
+        <is>
+          <t>Mutation testing, 14 injected defects</t>
+        </is>
+      </c>
+      <c r="D68" s="66" t="inlineStr">
+        <is>
+          <t>PASS (13/14 killed)</t>
+        </is>
+      </c>
+      <c r="E68" s="67" t="inlineStr">
+        <is>
+          <t>Injected: a raising check skipped instead of rejecting; the pipeline continuing past a refusal; a missing sizer approving; zero quantity approved; over-long and duplicate check ids accepted; approvals no longer audited; an audit failure swallowing the decision; require() defaulting to zero; net exposure ignoring direction. 13 killed.</t>
+        </is>
+      </c>
+      <c r="F68" s="67" t="inlineStr">
+        <is>
+          <t>One BENIGN survivor: 'checks_passed is aliased not copied'. Verified empirically rather than assumed - Pydantic already builds a new list when validating a list[str] field, so the guarantee is over-determined and the mutation changes no behaviour. The explicit list() call is kept as belt-and-braces and the redundancy is documented at the site.</t>
+        </is>
+      </c>
+      <c r="G68" s="67" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_risk.py</t>
+        </is>
+      </c>
+      <c r="H68" s="76" t="n"/>
+      <c r="I68" s="76" t="n"/>
+      <c r="J68" s="76" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G20"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -12,8 +12,9 @@
     <sheet name="E01 Blockers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="QA Results" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Security Findings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sprint Plan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Reference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SIT Defects" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sprint Plan" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Reference" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog'!$A$4:$W$197</definedName>
@@ -21,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'E01 Blockers'!$A$4:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA Results'!$A$4:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Security Findings'!$A$4:$H$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Sprint Plan'!$A$4:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sprint Plan'!$A$4:$G$23</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -468,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -648,6 +649,18 @@
     </xf>
     <xf numFmtId="166" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21278,47 +21291,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>QA ID</t>
         </is>
       </c>
-      <c r="B4" s="63" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="C4" s="63" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D4" s="63" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E4" s="63" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>What was verified</t>
         </is>
       </c>
-      <c r="F4" s="63" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="63" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>Test file</t>
         </is>
       </c>
-      <c r="I4" s="64" t="inlineStr">
+      <c r="I4" s="83" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="J4" s="64" t="inlineStr">
+      <c r="J4" s="83" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -25098,6 +25111,110 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="59" min="1" max="1"/>
+    <col width="12" customWidth="1" style="59" min="2" max="2"/>
+    <col width="11" customWidth="1" style="59" min="3" max="3"/>
+    <col width="10" customWidth="1" style="59" min="4" max="4"/>
+    <col width="22" customWidth="1" style="59" min="5" max="5"/>
+    <col width="14" customWidth="1" style="59" min="6" max="6"/>
+    <col width="46" customWidth="1" style="59" min="7" max="7"/>
+    <col width="40" customWidth="1" style="59" min="8" max="8"/>
+    <col width="40" customWidth="1" style="59" min="9" max="9"/>
+    <col width="40" customWidth="1" style="59" min="10" max="10"/>
+    <col width="34" customWidth="1" style="59" min="11" max="11"/>
+    <col width="18" customWidth="1" style="59" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>SIT DEFECTS — System Integration Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" s="59">
+      <c r="A2" s="76" t="inlineStr">
+        <is>
+          <t>Raised during SIT on the QA branch, after component and integration QA have passed. A defect here is by definition something no component test could see — record what the SYSTEM did, not what a unit returned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" s="59">
+      <c r="A4" s="82" t="inlineStr">
+        <is>
+          <t>SIT ID</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="D4" s="82" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E4" s="82" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="F4" s="82" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="82" t="inlineStr">
+        <is>
+          <t>What happened</t>
+        </is>
+      </c>
+      <c r="H4" s="84" t="inlineStr">
+        <is>
+          <t>Why component tests missed it</t>
+        </is>
+      </c>
+      <c r="I4" s="83" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="J4" s="83" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="K4" s="85" t="inlineStr">
+        <is>
+          <t>Regression test</t>
+        </is>
+      </c>
+      <c r="L4" s="85" t="inlineStr">
+        <is>
+          <t>Backlog item raised</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25724,7 +25841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -469,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -661,6 +661,9 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4569,6 +4572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -14303,7 +14307,7 @@
       </c>
       <c r="W118" s="49" t="n"/>
     </row>
-    <row r="119" ht="30" customHeight="1" s="59">
+    <row r="119" ht="190" customHeight="1" s="59">
       <c r="A119" s="38" t="inlineStr">
         <is>
           <t>E14-S02</t>
@@ -14324,9 +14328,9 @@
           <t>Pre-condition checks (1–4)</t>
         </is>
       </c>
-      <c r="E119" s="40" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="E119" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F119" s="41" t="inlineStr">
@@ -14362,16 +14366,45 @@
       <c r="N119" s="45" t="n"/>
       <c r="O119" s="46" t="n"/>
       <c r="P119" s="46" t="n"/>
-      <c r="Q119" s="47" t="n"/>
-      <c r="R119" s="39" t="n">
-        <v>0</v>
+      <c r="Q119" s="86" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="R119" s="48" t="n">
+        <v>4</v>
       </c>
       <c r="S119" s="48" t="n"/>
-      <c r="T119" s="48" t="n"/>
-      <c r="U119" s="48" t="n"/>
+      <c r="T119" s="48" t="inlineStr">
+        <is>
+          <t>1. check_kill_switch (C8) - reads ctx.kill_switch_active; E14-S09 owns the switch itself
+2. check_health_gate - any unhealthy service rejects, detail names which
+3. check_trading_window - MarketCalendar.is_market_open(ctx.now)
+4. check_no_trade_window - config.execution.no_trade_windows
+5. A factory that builds the four in order, closing over calendar + config</t>
+        </is>
+      </c>
+      <c r="U119" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) An active kill switch rejects with KILL_SWITCH_ACTIVE, and does so FIRST - no later check runs.
+AC2 (RED) Any unhealthy service rejects with HEALTH_GATE_FAILED and the detail names the service(s).
+AC3 A moment outside continuous trading - weekend, holiday, pre-open, post-close - rejects with OUTSIDE_TRADING_WINDOW.
+AC4 A moment inside a configured no_trade_window rejects with NO_TRADE_WINDOW and the detail names the window that matched.
+AC5 (CONTROL) A normal mid-session moment with the switch off and all services healthy passes all four.
+AC6 Registration order is kill_switch, health_gate, trading_window, no_trade_window - cheapest and most absolute first.
+AC7 An uncovered holiday year makes the calendar RAISE, which the framework turns into a rejection rather than a pass (fail closed).</t>
+        </is>
+      </c>
       <c r="V119" s="48" t="inlineStr">
         <is>
-          <t>Kill switch · health gate · trading window · no-trade window.</t>
+          <t>Kill switch · health gate · trading window · no-trade window.
+ACCEPTANCE CRITERIA WRITTEN 25 Aug 2026. The story had none - only a Notes line listing the four checks - so DoR R5 could not be satisfied as written. Criteria above are falsifiable; each names the RejectReason it must produce.
+SPEC/CONFIG CONFLICT RESOLVED. LOW_LEVEL_ARCHITECTURE 5.7 lists check_within_trading_window ('no entries after 15:00') and check_not_in_no_trade_window ('09:15-09:20 opening noise') as two hardcoded times. Config already models BOTH as one mechanism - config.execution.no_trade_windows is [(09:15,09:20), (15:00,15:30)] in system.yaml - so implementing the spec literally would hardcode 15:00 AND duplicate the configured window.
+Resolved by splitting on SOURCE rather than on time: trading_window asks the CALENDAR whether the market is open at all (weekend, holiday, pre-open, post-close) and yields OUTSIDE_TRADING_WINDOW; no_trade_window asks CONFIG whether now falls in a declared blackout and yields NO_TRADE_WINDOW. Both RejectReasons already exist in the enum, which is the design saying it wants them distinguished - and the metric signals_rejected_total{check} can then tell 'blocked at the open' from 'blocked near the close', which are operationally different signals.
+SCOPE. IN: the four checks and the ordered factory. OUT: E14-S09 owns the kill switch MECHANISM (arming, persistence, auto-demotion) - this story only READS the flag. Symbol eligibility is S03, portfolio S04, loss limits S05, margin/timing S06, sizing S07, slots S08.
+DELIVERED 1 Sep 2026 (/sdlc). checks/preconditions.py, 4 checks, registered in PRECONDITION_ORDER. 33 unit tests (one class per AC), 8 seam tests in the system test, 26 security tests. Mutation 13/13. Coverage 81% -&gt; 82% overall, preconditions.py 100%.
+SPEC CONFLICT RESOLVED: the architecture doc's trading-window check and system.yaml's no_trade_windows both describe 'when not to trade' and overlap at the open. Split on SOURCE, not time — trading_window asks the MarketCalendar (is the market open at all), no_trade_window asks config (are we choosing to sit this period out). Overlap is then harmless and the two rejections mean different things to an operator.
+FOUND WHILE TESTING: the Docker gate in conftest.py keyed on the directory name rather than the marker, silently skipping the only system-level test. Fixed; 17 tests recovered. See QA-E14-06.</t>
         </is>
       </c>
       <c r="W119" s="49" t="n"/>
@@ -21262,7 +21295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -21290,6 +21323,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -23800,6 +23834,191 @@
       <c r="H68" s="76" t="n"/>
       <c r="I68" s="76" t="n"/>
       <c r="J68" s="76" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-06</t>
+        </is>
+      </c>
+      <c r="B69" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C69" s="76" t="inlineStr">
+        <is>
+          <t>The Docker gate skipped the only system test</t>
+        </is>
+      </c>
+      <c r="D69" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E69" s="76" t="inlineStr">
+        <is>
+          <t>QA round 2 asked why tests/integration/ reported 17 skips on a machine with no Docker, when test_tick_to_trigger.py uses no container fixture.</t>
+        </is>
+      </c>
+      <c r="F69" s="76" t="inlineStr">
+        <is>
+          <t>conftest.py read `if "integration" in item.keywords`. item.keywords also holds every ancestor NODE NAME, so the DIRECTORY tests/integration/ matched. Every test underneath was gated on Docker whether or not it touched a container — including the one system-level test in the repo, which found a HIGH fail-open on its first run. It reported as skipped and the suite reported green. Now get_closest_marker("integration").</t>
+        </is>
+      </c>
+      <c r="G69" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_suite_integrity.py (10 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-07</t>
+        </is>
+      </c>
+      <c r="B70" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C70" s="76" t="inlineStr">
+        <is>
+          <t>AC1-AC7, one test class per criterion</t>
+        </is>
+      </c>
+      <c r="D70" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E70" s="76" t="inlineStr">
+        <is>
+          <t>AC1 kill switch rejects and runs FIRST (checks_passed == [] with three gates failing at once). AC2 unhealthy service rejects, detail names it. AC3 outside continuous trading rejects — pre-open, post-close, Sunday, and two real 2026 NSE holidays. AC4 blackout rejects, detail names WHICH window. AC5 the control: an ordinary mid-session moment passes all four. AC6 registration order. AC7 an uncovered holiday year fails CLOSED.</t>
+        </is>
+      </c>
+      <c r="F70" s="76" t="inlineStr">
+        <is>
+          <t>AC5 is what makes AC1-AC4 mean anything — four checks that rejected everything would satisfy them perfectly. The boundary tests pin the session as half-open: 09:15:00 trades, 15:30:00 does not.</t>
+        </is>
+      </c>
+      <c r="G70" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_risk_preconditions.py (33 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-08</t>
+        </is>
+      </c>
+      <c r="B71" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C71" s="76" t="inlineStr">
+        <is>
+          <t>Integration: the trigger reaches a risk decision</t>
+        </is>
+      </c>
+      <c r="D71" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E71" s="76" t="inlineStr">
+        <is>
+          <t>Ticks -&gt; cleaning -&gt; bars -&gt; indicators -&gt; strategy -&gt; Trigger -&gt; Recommendation -&gt; RiskEngine, with the REAL neighbours rather than fixtures, through the four pre-condition checks.</t>
+        </is>
+      </c>
+      <c r="F71" s="76" t="inlineStr">
+        <is>
+          <t>The seam this exercises is the one component tests cannot see: what the strategy runtime produces is what the risk engine consumes. Includes the degraded case — a feed gap must not produce a decision at all.</t>
+        </is>
+      </c>
+      <c r="G71" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_tick_to_trigger.py TestTheTriggerReachesARiskDecision (8 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-09</t>
+        </is>
+      </c>
+      <c r="B72" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C72" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing, 13 injected defects</t>
+        </is>
+      </c>
+      <c r="D72" s="76" t="inlineStr">
+        <is>
+          <t>PASS (13/13 killed)</t>
+        </is>
+      </c>
+      <c r="E72" s="76" t="inlineStr">
+        <is>
+          <t>Injected: kill switch inverted; kill switch never fires; health gate never fires; the service count falsified; the P7 truncation disabled; the cap raised past being a cap; the window half-open at the wrong end; closed at both ends; a wrap-around matching everything; an inverted window accepted at wiring time; the symbol class widened to '.'; fullmatch downgraded to match; the validator dropped from Trigger.</t>
+        </is>
+      </c>
+      <c r="F72" s="76" t="inlineStr">
+        <is>
+          <t>No survivors. The two P7 fixes were mutated deliberately (M05, M06, M11-M13) because a fix with no test that would notice its removal is not a fix. Coverage on preconditions.py is 100%.</t>
+        </is>
+      </c>
+      <c r="G72" s="76" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_e14s02.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-10</t>
+        </is>
+      </c>
+      <c r="B73" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C73" s="76" t="inlineStr">
+        <is>
+          <t>Full gate and coverage no-regress</t>
+        </is>
+      </c>
+      <c r="D73" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E73" s="76" t="inlineStr">
+        <is>
+          <t>ruff check + format, mypy (72 files), bandit exit 0, pip-audit clean, 303 security tests, 965 passed / 247 skipped.</t>
+        </is>
+      </c>
+      <c r="F73" s="76" t="inlineStr">
+        <is>
+          <t>Baseline measured, not assumed: the suite was re-run in a detached worktree at f8c7812 under identical conditions. 81% -&gt; 82%; missed statements 868 -&gt; 866 despite +56 new statements; skips 264 -&gt; 247 (the Docker-gate fix). doctor's one failure is the local missing DB password, unchanged.</t>
+        </is>
+      </c>
+      <c r="G73" s="76" t="inlineStr">
+        <is>
+          <t>full suite</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:G20"/>
@@ -23818,7 +24037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -23847,6 +24066,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -25098,6 +25318,90 @@
       <c r="I31" s="76" t="n"/>
       <c r="J31" s="76" t="n"/>
       <c r="K31" s="76" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-28</t>
+        </is>
+      </c>
+      <c r="B32" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C32" s="76" t="inlineStr">
+        <is>
+          <t>Log integrity / Trigger + Recommendation</t>
+        </is>
+      </c>
+      <c r="D32" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E32" s="76" t="inlineStr">
+        <is>
+          <t>A newline in an instrument symbol forges a whole line in the risk log. QA-SEC-16 closed exactly this on OrderRequest and stopped there — but symbols come from the broker's daily instrument dump, and the SAME untrusted value reaches Trigger and Recommendation first, both of which the risk engine logs on every rejection.</t>
+        </is>
+      </c>
+      <c r="F32" s="76" t="inlineStr">
+        <is>
+          <t>Verified against a real captured handler, not reasoned about: the probe produced two fabricated lines reading 'CRITICAL kill switch disarmed by operator' in the log an incident would be reconstructed from. An operator reading it would conclude a human disarmed the switch. A ':' additionally collides with the Redis key namespace.</t>
+        </is>
+      </c>
+      <c r="G32" s="76" t="inlineStr">
+        <is>
+          <t>_SAFE_SYMBOL / _validate_symbol moved above the first model that needs it and attached to Trigger and Recommendation as well as OrderRequest — ONE definition serving every boundary, since the finding was not a missing check but a check applied to one of three places.</t>
+        </is>
+      </c>
+      <c r="H32" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_symbol_boundary.py — 6 hostile shapes x 2 models, 7 real NSE symbols as the control (M&amp;M, BAJAJ-AUTO, L&amp;TFH, 20MICRONS), and an end-to-end probe asserting a rejection occupies exactly one log line. Mutation M11-M13 confirm the tests would notice its removal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-29</t>
+        </is>
+      </c>
+      <c r="B33" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C33" s="76" t="inlineStr">
+        <is>
+          <t>Denial of service / health gate detail</t>
+        </is>
+      </c>
+      <c r="D33" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E33" s="76" t="inlineStr">
+        <is>
+          <t>The health-gate rejection named every unhealthy service with no bound. The detail reaches both the audit payload and a log line, once per rejected candidate per bar.</t>
+        </is>
+      </c>
+      <c r="F33" s="76" t="inlineStr">
+        <is>
+          <t>Measured: 5000 unhealthy services produced a 48,957-character detail. The amplification is worst exactly when the system is already unwell — a cascading outage would write it for every candidate on every bar.</t>
+        </is>
+      </c>
+      <c r="G33" s="76" t="inlineStr">
+        <is>
+          <t>MAX_SERVICES_NAMED = 12. The COUNT stays exact and only the list is truncated, because 'how many' is what an operator acts on. 5000 services now yields 193 characters.</t>
+        </is>
+      </c>
+      <c r="H33" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_symbol_boundary.py TestRejectionDetailsAreBounded — the cap, the exact count under truncation, and the control that a realistic 3-service outage still names all three.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:H11"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,7 +4572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21295,7 +21294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24017,6 +24016,80 @@
       <c r="G73" s="76" t="inlineStr">
         <is>
           <t>full suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-11</t>
+        </is>
+      </c>
+      <c r="B74" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C74" s="76" t="inlineStr">
+        <is>
+          <t>SIT: a full session walked minute by minute</t>
+        </is>
+      </c>
+      <c r="D74" s="76" t="inlineStr">
+        <is>
+          <t>PASS (1 defect found and fixed)</t>
+        </is>
+      </c>
+      <c r="E74" s="76" t="inlineStr">
+        <is>
+          <t>31 SIT scenarios in five groups: session replay (every minute 08:00-16:00 against the expected tradable window), degraded dependencies (a transient outage, the kill switch, a raising check, a calendar that cannot answer), non-ordinary days (Sunday and two real 2026 closures), cross-cutting invariants over the whole run (audit completeness, no null timestamps, stage width vs String(28), no credential in a session's worth of log, no forged log line), and replay/restart determinism.</t>
+        </is>
+      </c>
+      <c r="F74" s="76" t="inlineStr">
+        <is>
+          <t>The scenario that earned its keep: asserting the tradable window is CONTIGUOUS. A piecewise test says '09:17 is blocked' and '10:00 passes'; it never says the gates compose into one window with no hole. That walk found SIT-001. Nothing was ever approved across 480 minutes, which is correct — ten checks are unwritten and there is no sizer.</t>
+        </is>
+      </c>
+      <c r="G74" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py (31 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-12</t>
+        </is>
+      </c>
+      <c r="B75" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C75" s="76" t="inlineStr">
+        <is>
+          <t>Mutation re-run after the SIT fix</t>
+        </is>
+      </c>
+      <c r="D75" s="76" t="inlineStr">
+        <is>
+          <t>PASS (16/16 killed)</t>
+        </is>
+      </c>
+      <c r="E75" s="76" t="inlineStr">
+        <is>
+          <t>Three new mutations flip each RISK_ENGINE_FAULT site back to HEALTH_GATE_FAILED, so the SIT-001 fix cannot silently regress.</t>
+        </is>
+      </c>
+      <c r="F75" s="76" t="inlineStr">
+        <is>
+          <t>M16 SURVIVED the first run. Verified before fixing: the raising-sizer path WAS tested, but the test asserted the refusal and the detail string and not the label — so flipping the reason changed nothing any assertion could see. Same shape as the two E14-S01 survivors. Fixed by asserting the reason, not by deleting the mutation.</t>
+        </is>
+      </c>
+      <c r="G75" s="76" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_e14s02.py</t>
         </is>
       </c>
     </row>
@@ -24066,7 +24139,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -25420,7 +25492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -25451,6 +25523,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="59">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -25510,6 +25583,68 @@
       <c r="L4" s="85" t="inlineStr">
         <is>
           <t>Backlog item raised</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="76" t="inlineStr">
+        <is>
+          <t>SIT-001</t>
+        </is>
+      </c>
+      <c r="B5" s="76" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C5" s="76" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="D5" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E5" s="76" t="inlineStr">
+        <is>
+          <t>execution/risk/framework.py</t>
+        </is>
+      </c>
+      <c r="F5" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G5" s="76" t="inlineStr">
+        <is>
+          <t>Walking a full simulated session minute by minute, EVERY tradable minute came back rejected with HEALTH_GATE_FAILED — 340 of them — while every service was healthy. The four pre-condition gates had passed; the reject came from the frame underneath them.</t>
+        </is>
+      </c>
+      <c r="H5" s="76" t="inlineStr">
+        <is>
+          <t>RejectReason has no member meaning 'the engine itself is broken', so the framework borrowed HEALTH_GATE_FAILED for three structurally different conditions: a check that raised, a missing sizer, and a sizer that raised. Every component test asserted the DECISION (refused — correct in all three cases) and read the reason only where it was already expected, or asserted the detail string instead. Nothing compared a genuine health-gate rejection against an engine fault side by side, and in isolation each reads perfectly sensibly. It took a whole-session run, where the same label appeared for 340 minutes with nothing unhealthy, for the overload to be visible at all.</t>
+        </is>
+      </c>
+      <c r="I5" s="76" t="inlineStr">
+        <is>
+          <t>A missing enum member, filled by the nearest plausible neighbour. signals_rejected_total{reason} is described in RejectReason's own docstring as 'the highest-value debugging metric in the system, because it turns why isn't it trading? into a glance instead of an investigation'. The overload defeats exactly that: an operator glancing at a no-trade day would go looking for a downed service that is perfectly healthy. The realistic trigger is not exotic — the holiday list must be renewed each December, and a lapsed one makes the calendar raise, which is an engine fault reported as a sick service in the first week of January.</t>
+        </is>
+      </c>
+      <c r="J5" s="76" t="inlineStr">
+        <is>
+          <t>Added RejectReason.RISK_ENGINE_FAULT and used it at the three framework sites. HEALTH_GATE_FAILED now means only what its name says. Every other member means 'the system worked and the answer is no'; this one means 'the system is broken and refusing is the safe reading of that'. Recorded in the framework docstring so the distinction survives the next edit.</t>
+        </is>
+      </c>
+      <c r="K5" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py test_an_engine_fault_is_not_reported_as_a_downed_service (compares the two side by side); test_risk_preconditions.py test_a_lapsed_holiday_list_reads_as_a_fault_not_a_sick_service; test_risk_framework.py test_a_raising_check_is_not_reported_as_a_business_rejection. Mutations M14-M16 flip each site back and are all killed.</t>
+        </is>
+      </c>
+      <c r="L5" s="76" t="inlineStr">
+        <is>
+          <t>None — fixed in the same session</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,6 +4572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -14429,9 +14430,9 @@
           <t>Symbol eligibility checks (5–7)</t>
         </is>
       </c>
-      <c r="E120" s="40" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="E120" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F120" s="41" t="inlineStr">
@@ -14457,9 +14458,9 @@
       <c r="J120" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K120" s="40" t="inlineStr">
-        <is>
-          <t>E14-S01, E04</t>
+      <c r="K120" s="48" t="inlineStr">
+        <is>
+          <t>E14-S01</t>
         </is>
       </c>
       <c r="L120" s="40" t="n"/>
@@ -14467,16 +14468,44 @@
       <c r="N120" s="45" t="n"/>
       <c r="O120" s="46" t="n"/>
       <c r="P120" s="46" t="n"/>
-      <c r="Q120" s="47" t="n"/>
-      <c r="R120" s="39" t="n">
-        <v>0</v>
+      <c r="Q120" s="86" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="R120" s="48" t="n">
+        <v>4</v>
       </c>
       <c r="S120" s="48" t="n"/>
-      <c r="T120" s="48" t="n"/>
-      <c r="U120" s="48" t="n"/>
+      <c r="T120" s="48" t="inlineStr">
+        <is>
+          <t>1. check_symbol_tradable — reads ctx.symbol_restrictions; UNKNOWN rejects
+2. check_slot_available — ctx.slots_available &gt; 0
+3. check_symbol_not_already_held — ctx.holds(rec.symbol), any direction
+4. build_eligibility_checks factory + ELIGIBILITY_ORDER, running after the four pre-conditions</t>
+        </is>
+      </c>
+      <c r="U120" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) A symbol carrying any blocking restriction rejects with SYMBOL_NOT_TRADABLE and the detail NAMES the restrictions.
+AC2 (RED) Eligibility that was never established rejects. 'Not checked' must never read as 'no restrictions' — fail closed (invariant 6).
+AC3 A symbol checked and found clean passes.
+AC4 (RED) No free slot rejects with NO_SLOT_AVAILABLE, detail gives used/total so an operator can see whether it is contention or misconfiguration.
+AC5 (RED) A symbol already held rejects with ALREADY_HOLDING regardless of the direction held — a SHORT trigger on a held LONG is a reversal, not an entry, and is not this story's business.
+AC6 (CONTROL) A clean symbol, a free slot and a flat book passes all three. Without this, three checks that rejected everything would satisfy AC1-AC5 perfectly.
+AC7 Registration order is symbol_tradable, slot_available, symbol_not_already_held, and the set runs AFTER the four pre-conditions.</t>
+        </is>
+      </c>
       <c r="V120" s="48" t="inlineStr">
         <is>
-          <t>Symbol tradable (re-verified at order time) · slot available · not already held.</t>
+          <t>Symbol tradable (re-verified at order time) · slot available · not already held.
+DEPENDENCY CORRECTED 2 Sep 2026. Was 'E14-S01, E04'. All seven E04 stories are New, which read literally blocks the whole of E14-S03 behind an epic of data fetchers. Verified against the code instead: every value these three checks read is ALREADY on RiskContext — symbol eligibility, slots_total/slots_used, and open_positions. E04 is what POPULATES check 5's input in production, which is runtime wiring, not a build dependency. Same shape as E14-S01's mis-stated E13-S04.
+Building the check FIRST is also the safer order: with eligibility unknown the check must fail closed, so until E04 exists the system refuses every unverified symbol rather than trading blind. The reverse order would leave a window where E04's data flows and no gate reads it.
+ACCEPTANCE CRITERIA WRITTEN 2 Sep 2026. The story had none — only a Notes line naming the three checks — so DoR R5 could not be satisfied.
+CONTRACT CHANGE: RiskContext.symbol_tradable (bool | None) is replaced by symbol_restrictions (tuple[str, ...] | None). Read by nothing yet, so the change is free now and would not be later. Three states instead of a bool-plus-reasons pair: None = never checked (reject), () = checked and clean (pass), non-empty = blocked, and the detail names them. The pair would have made the contradiction 'tradable=True, restrictions=(BAN,)' representable with nothing to catch it.
+THE CONTRACT E04 MUST MEET: the field carries only restrictions that BLOCK trading. Which surveillance flags qualify is E04's decision, made where the data is. ASSUMPTION RECORDED, unverified here because the design deliberately does not depend on it: for an INTRADAY equity system, T2T and higher GSM stages make intraday impossible, and ASM stages demanding 100% margin remove the leverage the sizing assumes. E04 must verify that against NSE's current circulars before choosing labels.
+DELIVERED 2 Sep 2026 (/sdlc). checks/eligibility.py, 3 checks, ELIGIBILITY_ORDER. 38 unit tests (one class per AC), 8 seam tests, 25 containment tests. Mutation 16/16. eligibility.py and context.py both at 100% coverage; overall 82%, missed statements unchanged at 866 despite +54 new.
+THREE SECURITY FINDINGS IN MY OWN NEW CODE, all from the same root — see QA-SEC-30/31/32. The first was log forgery for the THIRD time, which is what moved the fix from the source to CheckOutcome, where details are constructed.</t>
         </is>
       </c>
       <c r="W120" s="49" t="n"/>
@@ -21294,7 +21323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24090,6 +24119,154 @@
       <c r="G75" s="76" t="inlineStr">
         <is>
           <t>scratchpad/mutate_e14s02.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-13</t>
+        </is>
+      </c>
+      <c r="B76" s="76" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="C76" s="76" t="inlineStr">
+        <is>
+          <t>AC1-AC7, one test class per criterion</t>
+        </is>
+      </c>
+      <c r="D76" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E76" s="76" t="inlineStr">
+        <is>
+          <t>AC1 a blocking restriction rejects with SYMBOL_NOT_TRADABLE, detail names them. AC2 eligibility never established REJECTS. AC3 checked-and-clean passes. AC4 no free slot rejects, detail gives used/total. AC5 already held rejects in all four direction combinations. AC6 the control. AC7 order, and the set runs after the four pre-conditions.</t>
+        </is>
+      </c>
+      <c r="F76" s="76" t="inlineStr">
+        <is>
+          <t>AC2 is the story. `None` (never looked) and `()` (checked, clean) must not collapse — a truthiness test on the field would treat them identically and pass every other test here. Asserted explicitly, and mutation M02 confirms the tests would notice.</t>
+        </is>
+      </c>
+      <c r="G76" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_risk_eligibility.py (38 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-14</t>
+        </is>
+      </c>
+      <c r="B77" s="76" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="C77" s="76" t="inlineStr">
+        <is>
+          <t>Integration: eligibility against a real pipeline trigger</t>
+        </is>
+      </c>
+      <c r="D77" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E77" s="76" t="inlineStr">
+        <is>
+          <t>The seven built checks against the Trigger the actual pipeline produced — cleaned ticks, real bars, warmed indicators, compiled strategy — including a restricted symbol, unverified eligibility, a full book, and the already-held match.</t>
+        </is>
+      </c>
+      <c r="F77" s="76" t="inlineStr">
+        <is>
+          <t>The seam worth testing here: the held position is built from `rec.symbol`, whatever the pipeline emitted, not from the SYMBOL constant. If the two ever diverge, ctx.holds() quietly answers False forever and the gate stops being a gate while every unit test passes.</t>
+        </is>
+      </c>
+      <c r="G77" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_tick_to_trigger.py TestTheTriggerMeetsSymbolEligibility (8 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-15</t>
+        </is>
+      </c>
+      <c r="B78" s="76" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="C78" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing, 16 injected defects</t>
+        </is>
+      </c>
+      <c r="D78" s="76" t="inlineStr">
+        <is>
+          <t>PASS (16/16 killed)</t>
+        </is>
+      </c>
+      <c r="E78" s="76" t="inlineStr">
+        <is>
+          <t>Injected across all three checks, the context hardening and the detail containment: a restricted symbol waved through; UNKNOWN silently becoming clean; the restriction list unbounded; the slot off-by-one; the held gate disabled; any-&gt;all in ctx.holds; order changed; the list aliased again; a bare string split into characters; None coerced to (); control characters surviving; the detail unbounded.</t>
+        </is>
+      </c>
+      <c r="F78" s="76" t="inlineStr">
+        <is>
+          <t>No survivors. eligibility.py was already at 100% COVERAGE before this ran, which is exactly why the run was worth doing — coverage said every line executed, and these 16 asked whether anything would notice if a line were wrong.</t>
+        </is>
+      </c>
+      <c r="G78" s="76" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_e14s03.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-16</t>
+        </is>
+      </c>
+      <c r="B79" s="76" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="C79" s="76" t="inlineStr">
+        <is>
+          <t>Full gate and coverage no-regress</t>
+        </is>
+      </c>
+      <c r="D79" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E79" s="76" t="inlineStr">
+        <is>
+          <t>ruff check + format, mypy (73 files), bandit 0 issues, pip-audit clean, 328 security tests, 1069 passed / 247 skipped.</t>
+        </is>
+      </c>
+      <c r="F79" s="76" t="inlineStr">
+        <is>
+          <t>Coverage 82%, and missed statements are UNCHANGED at 866 despite +54 new source statements — the new code is fully covered rather than diluting the ratio. eligibility.py, preconditions.py and context.py all at 100%. doctor's one failure is the local missing DB password, unchanged.</t>
+        </is>
+      </c>
+      <c r="G79" s="76" t="inlineStr">
+        <is>
+          <t>full suite</t>
         </is>
       </c>
     </row>
@@ -24110,7 +24287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -24139,6 +24316,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -25472,6 +25650,132 @@
       <c r="H33" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_symbol_boundary.py TestRejectionDetailsAreBounded — the cap, the exact count under truncation, and the control that a realistic 3-service outage still names all three.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-30</t>
+        </is>
+      </c>
+      <c r="B34" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C34" s="76" t="inlineStr">
+        <is>
+          <t>Log integrity / risk rejection details</t>
+        </is>
+      </c>
+      <c r="D34" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E34" s="76" t="inlineStr">
+        <is>
+          <t>A newline in a surveillance-restriction label forges a log line. The labels reach the rejection detail, which the engine logs on every rejection. Restriction data originates from NSE by way of E04 — external data this system does not author.</t>
+        </is>
+      </c>
+      <c r="F34" s="76" t="inlineStr">
+        <is>
+          <t>Demonstrated against a running engine: a label of 'T2T\nCRITICAL kill switch disarmed by operator' produced two log lines, the second reading as a CRITICAL system event. THIS IS THE THIRD OCCURRENCE — QA-SEC-16 on OrderRequest.symbol, QA-SEC-28 on Trigger/Recommendation, now a label from a different source entirely. The pattern is not 'symbols are dangerous', it is 'any untrusted string interpolated into a rejection detail forges a log line', and there are fourteen checks free to interpolate whatever they read.</t>
+        </is>
+      </c>
+      <c r="G34" s="76" t="inlineStr">
+        <is>
+          <t>The fix MOVED, rather than being applied to a third source. CheckOutcome now normalises its detail at CONSTRUCTION — control characters escaped, not stripped, so an investigator can still see a newline was attempted. One rule covering every check that exists or will exist, including one written by someone who never reads this row.</t>
+        </is>
+      </c>
+      <c r="H34" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py — 8 hostile control-character shapes on the type itself, both constructors, a plain-detail control, and an end-to-end 'rogue check' that invents its own hostile detail. Mutations M13 and M16 confirm removal would be caught.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-31</t>
+        </is>
+      </c>
+      <c r="B35" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>Denial of service / rejection detail size</t>
+        </is>
+      </c>
+      <c r="D35" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E35" s="76" t="inlineStr">
+        <is>
+          <t>The restriction cap bounded the COUNT of labels (8) but not their length. Eight labels of 10,000 characters produced an 80,054-character detail, which reaches decision_log.payload (JSONB, unbounded) and a log line once per rejected candidate per bar.</t>
+        </is>
+      </c>
+      <c r="F35" s="76" t="inlineStr">
+        <is>
+          <t>This is QA-SEC-29's lesson recurring one story later, in the fix that was written knowing about QA-SEC-29. Capping the input count is not the same as bounding the output, and I made exactly that substitution while citing the earlier finding in the comment.</t>
+        </is>
+      </c>
+      <c r="G35" s="76" t="inlineStr">
+        <is>
+          <t>MAX_DETAIL = 512, enforced in CheckOutcome alongside the escaping — bounding the OUTPUT, at the one place every detail passes through. Truncation says how many characters were dropped, because a silently truncated detail reads as a complete one.</t>
+        </is>
+      </c>
+      <c r="H35" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py — three oversize inputs, the truncation marker, and a boundary-length detail that must NOT be truncated. Mutations M14, M15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-32</t>
+        </is>
+      </c>
+      <c r="B36" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C36" s="76" t="inlineStr">
+        <is>
+          <t>Tampering / RiskContext immutability</t>
+        </is>
+      </c>
+      <c r="D36" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E36" s="76" t="inlineStr">
+        <is>
+          <t>RiskContext is frozen, but frozen freezes the BINDING, not what it points at. Fields typed tuple[...] accepted a list, leaving the caller holding a live reference into a context the checks were about to read.</t>
+        </is>
+      </c>
+      <c r="F36" s="76" t="inlineStr">
+        <is>
+          <t>A caller could mutate session state BETWEEN checks, making the outcome depend on check order in exactly the way the class docstring says it must not. JSON has no tuples, so any deserialised context is the realistic route in. Verified: a list was aliased, and appending to it after construction changed what the checks would see.</t>
+        </is>
+      </c>
+      <c r="G36" s="76" t="inlineStr">
+        <is>
+          <t>__post_init__ coerces the three sequence fields to real tuples, and refuses a bare string rather than splitting it into characters — symbol_restrictions='T2T' would otherwise become ('T','2','T'), three restrictions that do not exist. None is preserved as None, because coercing it to () would turn 'never looked' into 'checked and clean'.</t>
+        </is>
+      </c>
+      <c r="H36" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py TestTheContextCannotBeMutatedAfterConstruction. Mutations M10, M11, M12.</t>
         </is>
       </c>
     </row>
@@ -25523,7 +25827,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="59">
       <c r="A4" s="82" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,7 +4572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21323,7 +21322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24267,6 +24266,43 @@
       <c r="G79" s="76" t="inlineStr">
         <is>
           <t>full suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-17</t>
+        </is>
+      </c>
+      <c r="B80" s="76" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="C80" s="76" t="inlineStr">
+        <is>
+          <t>SIT: eligibility walked across a session</t>
+        </is>
+      </c>
+      <c r="D80" s="76" t="inlineStr">
+        <is>
+          <t>PASS (no product defect)</t>
+        </is>
+      </c>
+      <c r="E80" s="76" t="inlineStr">
+        <is>
+          <t>12 scenarios: the composition property (all seven clear on exactly the minutes four did -- 340 either way), a symbol banned at noon, an eligibility fetcher dropping out for 30 minutes and returning, the book filling and freeing, a position opened mid-session that correctly never releases, ordering across both check groups at every minute, audit completeness with seven registered, QA-SEC-30 at session scale, and replay determinism. SIT total 31 -&gt; 43.</t>
+        </is>
+      </c>
+      <c r="F80" s="76" t="inlineStr">
+        <is>
+          <t>One test failed on the first run and it was the TEST, not the product: it filtered the session on `reason is RISK_ENGINE_FAULT` and swept up every clean minute, because with no sizer configured a fully-cleared candidate is refused BY THE SIZER carrying that same reason. Added Session.stopped_by(), which reads the audit `stage` -- the field that actually answers 'which check refused'. Recorded because filtering a session by reason code is a natural thing to write and quietly wrong once more than one condition maps to a reason. No SIT defect logged.</t>
+        </is>
+      </c>
+      <c r="G80" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py TestSit6 (12 tests)</t>
         </is>
       </c>
     </row>
@@ -24316,7 +24352,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X199"/>
+  <dimension ref="A1:X200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -4572,6 +4572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -14530,9 +14531,9 @@
           <t>Portfolio exposure checks (8–10)</t>
         </is>
       </c>
-      <c r="E121" s="40" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="E121" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F121" s="41" t="inlineStr">
@@ -14568,7 +14569,11 @@
       <c r="N121" s="45" t="n"/>
       <c r="O121" s="46" t="n"/>
       <c r="P121" s="46" t="n"/>
-      <c r="Q121" s="47" t="n"/>
+      <c r="Q121" s="86" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="R121" s="39" t="n">
         <v>4</v>
       </c>
@@ -14583,10 +14588,32 @@
       </c>
       <c r="U121" s="48" t="inlineStr">
         <is>
-          <t>• 🔴 Four PSU banks cannot occupy four slots</t>
-        </is>
-      </c>
-      <c r="V121" s="48" t="n"/>
+          <t>AC1 (RED) A candidate correlated to max_correlated_positions open positions rejects with CORRELATION_LIMIT; the detail names which symbols.
+AC2 (RED) A held position with NO correlation entry rejects. Unknown correlation is not 'uncorrelated' — fail closed (invariant 6).
+AC3 An empty book clears the correlation guard vacuously.
+AC4 (RED) Sector exposure already at or above max_sector_exposure_pct rejects with SECTOR_EXPOSURE_LIMIT; the detail gives current vs cap.
+AC5 (RED) An unknown sector — on the CANDIDATE or on ANY open position — rejects. A None sector must never contribute silently as zero.
+AC6 (RED) Net directional exposure already at or above max_net_directional_exposure_pct rejects with NET_EXPOSURE_LIMIT.
+AC7 Longs and shorts net off: equal-notional long and short give zero net exposure, and a hedged book is not treated as a directional one.
+AC8 (CONTROL) A flat book, and a diversified book below every cap, pass all three. Three checks that rejected everything would satisfy AC1-AC7.
+AC9 Order is correlation, sector, net_exposure, running AFTER eligibility.
+AC10 (RED) The original criterion, end to end: four PSU banks cannot occupy four slots.</t>
+        </is>
+      </c>
+      <c r="V121" s="48" t="inlineStr">
+        <is>
+          <t>ACCEPTANCE CRITERIA WRITTEN 2 Sep 2026. The story had one bullet ('four PSU banks cannot occupy four slots') for three checks, so DoR R5 could not be satisfied. That bullet is kept as AC10 because it is the best statement of intent in the row.
+BUILD CONCERN ANSWERED (window and return frequency). Correlation is computed from DAILY LOG RETURNS over 60 TRADING SESSIONS, recomputed pre-market and never intraday.
+  * Daily, not intraday: correlation estimated from high-frequency sampling of two separately-traded names is biased toward zero because their prints are not synchronous (the Epps effect). An intraday estimate would systematically UNDERSTATE how alike two PSU banks are, which is the exact failure this check exists to prevent.
+  * 60 sessions ~ one quarter: the story's own concern is that a short window flaps and a long one misses regime change. 60 is a judgement, not a derived fact — RECORDED AS AN ASSUMPTION. Revisit if the guard proves either noisy or slow.
+  * Recomputed pre-market, not intraday: a correlation that moved during the session would make the same inputs produce different decisions, and the risk pipeline's replayability is structural (RiskContext exists to keep checks pure). The matrix is a snapshot input, like the calendar.
+SECTOR IS PRIMARY, CORRELATION SECONDARY — taken from Build Concerns and kept: four PSU banks can show only moderate pairwise correlation and still be one bet.
+ARCHITECTURAL GAP FOUND WHILE DESIGNING — see the new story E14-S10. The sector and net-directional caps CANNOT be fully enforced by any component that currently exists or is designed. These checks run BEFORE sizing, so they cannot know the candidate's notional; and LOW_LEVEL_ARCHITECTURE 5.7's sizing formula clamps on position value, slot capital and broker margin — there is no sector clamp and no net-directional clamp. So this story delivers the gate that refuses when the book is ALREADY at a cap, and E14-S10 makes the caps binding.
+OUT OF SCOPE: feeding the matrix from the bar repository each morning (runtime wiring, belongs with the pre-market pipeline); position sizing; sector classification data itself (instruments.sector already exists as a nullable column, and AC5 makes 'unclassified' a rejection rather than a silent zero).
+DELIVERED 2 Sep 2026 (/sdlc). checks/exposure.py (3 checks) plus risk/correlation.py (the matrix, task 2) as a pure function. 46 unit tests + 25 correlation tests (2 property-based), 11 seam tests, 11 new security tests. Mutation 19/20 with one VERIFIED-BENIGN survivor. exposure.py, correlation.py and context.py all at 100% coverage; overall 82%, missed statements unchanged at 866 despite +132 new.
+CONFIG ADDED: risk.portfolio.correlation_threshold (0.7). max_correlated_positions existed with no companion threshold — the COUNT of correlated names was configurable and the DEFINITION of correlated was not. StrategyValidationConfig.max_correlation_to_active looks like it would serve and must not: that is about whether a new STRATEGY duplicates an active one in the overfitting gauntlet. Sharing one number would couple a portfolio limit to a research limit.</t>
+        </is>
+      </c>
       <c r="W121" s="49" t="n"/>
       <c r="X121" s="75" t="inlineStr">
         <is>
@@ -20553,6 +20580,88 @@
       <c r="L199" s="48" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="76" t="inlineStr">
+        <is>
+          <t>E14-S10</t>
+        </is>
+      </c>
+      <c r="B200" s="76" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="C200" s="76" t="inlineStr">
+        <is>
+          <t>RISK ENGINE</t>
+        </is>
+      </c>
+      <c r="D200" s="76" t="inlineStr">
+        <is>
+          <t>Sizer clamps to exposure headroom</t>
+        </is>
+      </c>
+      <c r="E200" s="76" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F200" s="76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G200" s="76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H200" s="76" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I200" s="76" t="inlineStr">
+        <is>
+          <t>FEAT</t>
+        </is>
+      </c>
+      <c r="J200" s="76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K200" s="76" t="inlineStr">
+        <is>
+          <t>E14-S04, E14-S07</t>
+        </is>
+      </c>
+      <c r="R200" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="T200" s="76" t="inlineStr">
+        <is>
+          <t>1. Add sector headroom to the sizing clamp set
+2. Add net-directional headroom to the sizing clamp set
+3. Record which of them bound, in binding_constraint</t>
+        </is>
+      </c>
+      <c r="U200" s="76" t="inlineStr">
+        <is>
+          <t>AC1 (RED) A position sized into a sector that is 35% of capital, with a 40% cap, is clamped so the resulting book is at or below 40% — not merely allowed because 35 &lt; 40.
+AC2 (RED) The same for net directional exposure.
+AC3 binding_constraint names the sector or net-exposure clamp when it is the one that bound, so a surprisingly small position is explainable.
+AC4 (CONTROL) A position with ample headroom is unaffected by either clamp.</t>
+        </is>
+      </c>
+      <c r="V200" s="76" t="inlineStr">
+        <is>
+          <t>RAISED 2 Sep 2026 while designing E14-S04, which found the gap.
+max_sector_exposure_pct (40) and max_net_directional_exposure_pct (60) are configured, and until this story exists NOTHING enforces them.
+Why the E14-S04 checks cannot do it: risk checks run BEFORE sizing — RiskEngine.evaluate runs every check and only then calls the sizer — so at check time the candidate has a direction but no quantity, and an exposure cap is a statement about notional. The check can therefore only refuse when the book is ALREADY at the cap. A book at 39% of a 40% sector cap passes the check, and sizing may then add another 20% position.
+Why the sizer as designed cannot do it either: LOW_LEVEL_ARCHITECTURE 5.7's formula clamps on max_position_value, slot_capital and available_margin. Sector and net-directional headroom are not among them. Adding them is the natural home for the constraint, because the sizer is the only component that knows the quantity AND already applies a min() over clamps while recording which one bound.
+REJECTED ALTERNATIVE: have the E14-S04 check assume the worst case — that the candidate will take max_position_pct (20%) — and reject if existing + 20% breaches the cap. It is safe but badly over-tight: actual ATR-based sizes are typically far below the 20% cap, so this would refuse trades that would comfortably have fit, and the system would sit out for reasons no operator could see in the book. Conservative in the direction of not trading is still wrong when it is this inaccurate.</t>
         </is>
       </c>
     </row>
@@ -21322,7 +21431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24303,6 +24412,191 @@
       <c r="G80" s="76" t="inlineStr">
         <is>
           <t>tests/sit/test_e14_trading_session.py TestSit6 (12 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-18</t>
+        </is>
+      </c>
+      <c r="B81" s="76" t="inlineStr">
+        <is>
+          <t>E14-S04</t>
+        </is>
+      </c>
+      <c r="C81" s="76" t="inlineStr">
+        <is>
+          <t>AC1-AC10, one test class per criterion</t>
+        </is>
+      </c>
+      <c r="D81" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E81" s="76" t="inlineStr">
+        <is>
+          <t>AC1 correlation limit, detail names the symbols. AC2 a held position with no correlation entry REJECTS. AC3 empty book vacuous. AC4 sector cap with current-vs-cap detail. AC5 unknown sector rejects, on the candidate AND on any held position. AC6 net directional cap. AC7 longs and shorts net off. AC8 the control. AC9 order. AC10 four PSU banks cannot occupy four slots.</t>
+        </is>
+      </c>
+      <c r="F81" s="76" t="inlineStr">
+        <is>
+          <t>AC10 has three tests, not one. The third is the build concern made concrete: four PSU banks correlating only MODERATELY still pass the correlation guard and are caught by the SECTOR cap — which is why the story says sector is primary and correlation secondary. A fourth test checks four UNRELATED names are still allowed, so the guard is not just capping the book at three.</t>
+        </is>
+      </c>
+      <c r="G81" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_risk_exposure.py (46 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-19</t>
+        </is>
+      </c>
+      <c r="B82" s="76" t="inlineStr">
+        <is>
+          <t>E14-S04</t>
+        </is>
+      </c>
+      <c r="C82" s="76" t="inlineStr">
+        <is>
+          <t>The correlation computation itself</t>
+        </is>
+      </c>
+      <c r="D82" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E82" s="76" t="inlineStr">
+        <is>
+          <t>Log returns (additivity, a rise and matching fall cancelling, non-positive closes refused), Pearson against statistics.correlation as an INDEPENDENT implementation, the 30-session floor, zero-variance refusal, and two Hypothesis properties: the result always lies in [-1, 1], and it is invariant to positive scaling and shift.</t>
+        </is>
+      </c>
+      <c r="F82" s="76" t="inlineStr">
+        <is>
+          <t>A statistical routine is the easiest place in this system to return a plausible number that is wrong, because nothing downstream can tell. Checking against the standard library rather than against the same arithmetic is what makes it a verification. The scale-invariance property matters concretely: without it the guard would read expensive names as more correlated than cheap ones.</t>
+        </is>
+      </c>
+      <c r="G82" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_correlation.py (25 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-20</t>
+        </is>
+      </c>
+      <c r="B83" s="76" t="inlineStr">
+        <is>
+          <t>E14-S04</t>
+        </is>
+      </c>
+      <c r="C83" s="76" t="inlineStr">
+        <is>
+          <t>Integration: exposure against a real pipeline trigger</t>
+        </is>
+      </c>
+      <c r="D83" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E83" s="76" t="inlineStr">
+        <is>
+          <t>All TEN built checks against the Trigger the pipeline produced. Correlated book, missing correlation, saturated sector, unclassified held position, one-sided book, and a hedged book of the same gross size that must NOT be refused.</t>
+        </is>
+      </c>
+      <c r="F83" s="76" t="inlineStr">
+        <is>
+          <t>The closing test builds the matrix from the pipeline's own warm-up bars and feeds it to the guard, so the correlation module's OUTPUT is the guard's INPUT — the two halves meet the way they will in production rather than through hand-written numbers.</t>
+        </is>
+      </c>
+      <c r="G83" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_tick_to_trigger.py TestTheTriggerMeetsPortfolioExposure (11 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-21</t>
+        </is>
+      </c>
+      <c r="B84" s="76" t="inlineStr">
+        <is>
+          <t>E14-S04</t>
+        </is>
+      </c>
+      <c r="C84" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing, 20 injected defects</t>
+        </is>
+      </c>
+      <c r="D84" s="76" t="inlineStr">
+        <is>
+          <t>PASS (19/20, 1 verified benign)</t>
+        </is>
+      </c>
+      <c r="E84" s="76" t="inlineStr">
+        <is>
+          <t>Injected across all three checks, the correlation computation and the context hardening: the guard off-by-one, abs() dropped on correlation and on net exposure, unknown becoming uncorrelated, NaN no longer caught, the sector cap disabled, unclassified positions escaping, gross substituted for net, the session floor removed, a zero close admitted, and both aliasing fixes reverted.</t>
+        </is>
+      </c>
+      <c r="F84" s="76" t="inlineStr">
+        <is>
+          <t>M16 SURVIVED and was verified benign before anything was changed: removing the window slice from the CANDIDATE series changes nothing, because `paired = min(len(candidate), len(other))` and `other` is always windowed, so the candidate is re-truncated to the same tail. Confirmed empirically — identical rho to ten decimal places. The slice is kept anyway: removing it would make correctness depend on the counterparty always being windowed, which is a subtler invariant than a redundant slice.</t>
+        </is>
+      </c>
+      <c r="G84" s="76" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_e14s04.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-22</t>
+        </is>
+      </c>
+      <c r="B85" s="76" t="inlineStr">
+        <is>
+          <t>E14-S04</t>
+        </is>
+      </c>
+      <c r="C85" s="76" t="inlineStr">
+        <is>
+          <t>Full gate and coverage no-regress</t>
+        </is>
+      </c>
+      <c r="D85" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E85" s="76" t="inlineStr">
+        <is>
+          <t>ruff check + format, mypy (75 files), bandit 0 issues, pip-audit clean, 382 security+SIT tests, 1,174 passed / 247 skipped.</t>
+        </is>
+      </c>
+      <c r="F85" s="76" t="inlineStr">
+        <is>
+          <t>Coverage 82% and missed statements UNCHANGED at 866 despite +132 new source statements. exposure.py, correlation.py, eligibility.py, preconditions.py and context.py are all at 100%. doctor's one failure is the local missing DB password, unchanged.</t>
+        </is>
+      </c>
+      <c r="G85" s="76" t="inlineStr">
+        <is>
+          <t>full suite</t>
         </is>
       </c>
     </row>
@@ -24323,7 +24617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -24352,6 +24646,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -25811,6 +26106,90 @@
       <c r="H36" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_detail_containment.py TestTheContextCannotBeMutatedAfterConstruction. Mutations M10, M11, M12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-33</t>
+        </is>
+      </c>
+      <c r="B37" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C37" s="76" t="inlineStr">
+        <is>
+          <t>Tampering / RiskContext.correlations</t>
+        </is>
+      </c>
+      <c r="D37" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E37" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-32 one field over. That finding froze unhealthy_services, open_positions and symbol_restrictions — named explicitly in a hand-written tuple. It missed `correlations`, which was already on the class, because that one is a dict and the code was looking for sequences.</t>
+        </is>
+      </c>
+      <c r="F37" s="76" t="inlineStr">
+        <is>
+          <t>Verified: a caller passes a dict, keeps the reference, and changes a correlation from 0.1 to 0.99 AFTER construction — the context saw the new value. That is session state mutating between checks, which is exactly what RiskContext's docstring says must not happen, and it would let a correlated pair through the guard.</t>
+        </is>
+      </c>
+      <c r="G37" s="76" t="inlineStr">
+        <is>
+          <t>The freezing is now DERIVED from dataclasses.fields rather than a list of names: mappings become MappingProxyType, sequences become tuples. A hand-written list has to be remembered every time a field is added; iterating the fields cannot be forgotten. This is the general fix for the class of defect, not the second instance of a patch.</t>
+        </is>
+      </c>
+      <c r="H37" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py TestEveryContainerFieldIsFrozen — asserts the GENERAL property over every container field found by reflection, because a test that also listed fields by hand would have the same hole as the code it guards. Mutations M17, M18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-34</t>
+        </is>
+      </c>
+      <c r="B38" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C38" s="76" t="inlineStr">
+        <is>
+          <t>Observability / non-finite correlation</t>
+        </is>
+      </c>
+      <c r="D38" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E38" s="76" t="inlineStr">
+        <is>
+          <t>A NaN or infinity in the correlation matrix reached `abs(rho) &gt;= threshold`, which raises decimal.InvalidOperation.</t>
+        </is>
+      </c>
+      <c r="F38" s="76" t="inlineStr">
+        <is>
+          <t>It failed CLOSED — the framework turned the exception into a RISK_ENGINE_FAULT rejection, so no trade was at risk. But the detail read "InvalidOperation: [&lt;class 'decimal.InvalidOperation'&gt;]", which names neither the symbol nor the cause. E14-S01's acceptance criterion is that any rejection is explainable from the audit log, and this one was not.</t>
+        </is>
+      </c>
+      <c r="G38" s="76" t="inlineStr">
+        <is>
+          <t>An explicit `rho.is_finite()` guard that names the affected pairs and says the pre-market matrix produced a NaN or infinity — which is the actual thing an operator needs to go and fix.</t>
+        </is>
+      </c>
+      <c r="H38" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py TestCorrelationInputsCannotBeQuietlyWrong — NaN, +Inf and -Inf, plus a test asserting the raw comparison really does raise (so the guard is not decoration) and a control that finite values are unaffected. Mutation M05.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,7 +4572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21431,7 +21430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24597,6 +24596,43 @@
       <c r="G85" s="76" t="inlineStr">
         <is>
           <t>full suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-23</t>
+        </is>
+      </c>
+      <c r="B86" s="76" t="inlineStr">
+        <is>
+          <t>E14-S04</t>
+        </is>
+      </c>
+      <c r="C86" s="76" t="inlineStr">
+        <is>
+          <t>SIT: exposure walked across a session</t>
+        </is>
+      </c>
+      <c r="D86" s="76" t="inlineStr">
+        <is>
+          <t>PASS (no product defect)</t>
+        </is>
+      </c>
+      <c r="E86" s="76" t="inlineStr">
+        <is>
+          <t>12 scenarios at TEN registered checks: the composition property (all ten clear on exactly the 340 minutes four did), a sector filling up at noon, a position closing and the gate REOPENING, the correlation matrix vanishing for 30 minutes and returning, a position losing its sector classification mid-session, four PSU banks accumulating one at a time across the morning, a hedged book trading all day, audit completeness, replay determinism, and that nothing is approved across 480 minutes. SIT total 43 -&gt; 55.</t>
+        </is>
+      </c>
+      <c r="F86" s="76" t="inlineStr">
+        <is>
+          <t>The accumulation scenario is the one worth having: AC10 as a SESSION rather than a single evaluation. The names arrive one at a time across the morning, which is how it would actually happen, and is the shape in which a per-evaluation guard could still let a book drift. Also confirmed QA-SEC-30's containment at a FOURTH source — sector names reach the detail too, and because the fix lives in CheckOutcome it never had to be found the hard way there.</t>
+        </is>
+      </c>
+      <c r="G86" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py TestSit7 (12 tests)</t>
         </is>
       </c>
     </row>
@@ -24646,7 +24682,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,6 +4572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -14641,9 +14642,9 @@
           <t>Loss limit checks (11–12)</t>
         </is>
       </c>
-      <c r="E122" s="40" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="E122" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F122" s="41" t="inlineStr">
@@ -14679,16 +14680,51 @@
       <c r="N122" s="45" t="n"/>
       <c r="O122" s="46" t="n"/>
       <c r="P122" s="46" t="n"/>
-      <c r="Q122" s="47" t="n"/>
-      <c r="R122" s="39" t="n">
-        <v>0</v>
+      <c r="Q122" s="86" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="R122" s="48" t="n">
+        <v>4</v>
       </c>
       <c r="S122" s="48" t="n"/>
-      <c r="T122" s="48" t="n"/>
-      <c r="U122" s="48" t="n"/>
+      <c r="T122" s="48" t="inlineStr">
+        <is>
+          <t>1. check_daily_loss — realised loss against max_daily_loss_pct of capital
+2. check_consecutive_loss — streak against consecutive_loss_halt
+3. The LATCH both read, so a halt does not clear itself
+4. build_loss_checks factory + LOSS_ORDER, running after exposure</t>
+        </is>
+      </c>
+      <c r="U122" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) A realised loss at or beyond max_daily_loss_pct of capital rejects with DAILY_LOSS_LIMIT.
+AC2 (RED) A PROFIT of the same magnitude does NOT reject. A sign inversion here would halt on good days and trade freely on bad ones — the worst possible direction to be wrong in.
+AC3 (RED) Once breached, a later partial RECOVERY does not resume trading. LOW_LEVEL_ARCHITECTURE 8.1: 'HALTED is terminal for the day and is only exited by explicit operator action. There is no automatic un-halt.'
+AC4 (RED) consecutive_losses at or beyond consecutive_loss_halt rejects with CONSECUTIVE_LOSS_LIMIT.
+AC5 (RED) The consecutive halt likewise does not clear itself when a later trade closes profitably and resets the counter to zero.
+AC6 (CONTROL) A flat or profitable day with no loss streak passes both. Two checks that rejected everything would satisfy AC1-AC5 perfectly.
+AC7 The threshold is computed from CONFIGURED capital, so the limit does not shrink as the day loses — 3% means the same rupees at 15:00 as at 09:20.
+AC8 Order is daily_loss, consecutive_loss, running AFTER exposure.
+AC9 Each detail gives the actual figure against the limit, because 'daily loss limit' without the number is not something an operator can act on.</t>
+        </is>
+      </c>
       <c r="V122" s="48" t="inlineStr">
         <is>
-          <t>Daily loss limit → halt · consecutive loss limit → halt.</t>
+          <t>Daily loss limit → halt · consecutive loss limit → halt.
+ACCEPTANCE CRITERIA WRITTEN 3 Sep 2026. The story had none — only a Notes line naming the two checks — so DoR R5 could not be satisfied.
+THE FINDING THAT SHAPES THIS STORY: a check that is a pure predicate over realised_pnl_today AUTO-UN-HALTS, and that contradicts the architecture outright.
+  Trip the 3% daily limit. Open positions are still on — they must be, because a loss limit trips precisely when you are holding losers. One closes at a profit. realised_pnl_today rises back above the threshold, the predicate passes, and trading silently resumes.
+  consecutive_losses has the identical hole from the other side: the counter resets to 0 on any winning close, so a single profitable exit clears a halt that three losses caused.
+  LOW_LEVEL_ARCHITECTURE 8.1 is explicit: 'HALTED is terminal for the day and is only exited by explicit operator action. There is no automatic un-halt — if a risk limit tripped, a human decides whether resuming is appropriate.' A pure predicate cannot express 'terminal'.
+DESIGN: each check rejects if EITHER the live figure breaches OR a latch is set. Neither half is sufficient alone — the live figure auto-un-halts, and the latch alone has a window between the breach and the latch being written. Together they fail closed in both.
+  SCOPE: this story READS the latches; SETTING and persisting them is E14-S09, exactly as check 1 reads kill_switch_active while E14-S09 owns arming it. Two separate latch fields rather than one shared 'halted' flag, so the reason code stays exact — SIT-001 is the standing lesson on what conflating two causes into one code costs an operator.
+CAPITAL IS THE CONFIGURED BASE, not a live balance (system.yaml capital: 500000). So 3% is a fixed rupee threshold rather than one that shrinks as the day loses, which is what makes the limit reasonable about and testable.
+EXITS ARE NOT AFFECTED. LOW_LEVEL_ARCHITECTURE 1136 and 1373 both say the breach halts NEW ENTRIES and the operator decides on existing positions. RiskEngine.evaluate only ever sees a Recommendation, which is an entry candidate, so this is structural rather than something these checks have to remember — but it is worth stating, because a loss limit that blocked square-off would strand losing positions overnight.
+OUT OF SCOPE: arming/persisting the latches (E14-S09), the session state machine, unrealised P&amp;L. The field is realised_pnl_today by name and by intent; whether the limit should also consider mark-to-market is a real question and a separate one — recorded, not silently decided here.
+DELIVERED 3 Sep 2026 (/sdlc). checks/loss.py, 2 checks + 2 latch fields on RiskContext. 38 unit tests, 8 seam tests, 11 new security tests. Mutation 14/14. loss.py and context.py at 100%; overall coverage 82% -&gt; 83%.
+CONTEXT HARDENED (QA-SEC-35/36): no Decimal field may be NaN or an infinity, and consecutive_losses may not be negative. Both rejected at CONSTRUCTION and derived from dataclasses.fields, so the guard covers fields no check reads yet.</t>
         </is>
       </c>
       <c r="W122" s="49" t="n"/>
@@ -21430,7 +21466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24633,6 +24669,154 @@
       <c r="G86" s="76" t="inlineStr">
         <is>
           <t>tests/sit/test_e14_trading_session.py TestSit7 (12 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-24</t>
+        </is>
+      </c>
+      <c r="B87" s="76" t="inlineStr">
+        <is>
+          <t>E14-S05</t>
+        </is>
+      </c>
+      <c r="C87" s="76" t="inlineStr">
+        <is>
+          <t>AC1-AC9, one test class per criterion</t>
+        </is>
+      </c>
+      <c r="D87" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E87" s="76" t="inlineStr">
+        <is>
+          <t>AC1 the daily limit fires at and beyond the threshold, and one rupee short still trades. AC2 the SIGN, in both directions. AC3 the latch holds through a recovery. AC4 the streak limit. AC5 the streak latch holds after the counter resets. AC6 the control. AC7 the threshold is a percentage of configured capital. AC8 order. AC9 details carry the figures.</t>
+        </is>
+      </c>
+      <c r="F87" s="76" t="inlineStr">
+        <is>
+          <t>AC2 has its own class because a sign inversion here is the worst possible shape of bug — it would halt the system on its best days and trade freely on its worst — and it is invisible to any test that only ever feeds it losses. One assertion states the asymmetry directly, so a check that ignored the field entirely could not satisfy it.</t>
+        </is>
+      </c>
+      <c r="G87" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_risk_loss.py (38 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-25</t>
+        </is>
+      </c>
+      <c r="B88" s="76" t="inlineStr">
+        <is>
+          <t>E14-S05</t>
+        </is>
+      </c>
+      <c r="C88" s="76" t="inlineStr">
+        <is>
+          <t>Integration: loss limits against a real trigger</t>
+        </is>
+      </c>
+      <c r="D88" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E88" s="76" t="inlineStr">
+        <is>
+          <t>All TWELVE built checks against the Trigger the pipeline produced: a breached daily loss, a profitable day of the same magnitude, a latched halt on a candidate that is otherwise perfect, a consecutive streak, ordering, and the audit stage.</t>
+        </is>
+      </c>
+      <c r="F88" s="76" t="inlineStr">
+        <is>
+          <t>These are the first checks whose answer depends on what the system already did today rather than on the market or the book, so the seam is different in kind. One test asserts the rejection does NOT name the candidate — a session-wide halt that blamed a symbol would send an operator to investigate the wrong thing.</t>
+        </is>
+      </c>
+      <c r="G88" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_tick_to_trigger.py TestTheTriggerMeetsTheLossLimits (8 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-26</t>
+        </is>
+      </c>
+      <c r="B89" s="76" t="inlineStr">
+        <is>
+          <t>E14-S05</t>
+        </is>
+      </c>
+      <c r="C89" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing, 14 injected defects</t>
+        </is>
+      </c>
+      <c r="D89" s="76" t="inlineStr">
+        <is>
+          <t>PASS (14/14 killed)</t>
+        </is>
+      </c>
+      <c r="E89" s="76" t="inlineStr">
+        <is>
+          <t>Injected: the sign inverted; the limit off-by-one; each check disabled; the percentage undivided (a 100x limit); BOTH LATCHES IGNORED; the order swapped; both construction guards removed; and the two new context guards reverted.</t>
+        </is>
+      </c>
+      <c r="F89" s="76" t="inlineStr">
+        <is>
+          <t>M04 and M08 are the ones that matter — each reverts the story's central finding, that a pure predicate un-halts itself. Both killed, so the latch cannot be quietly removed later.</t>
+        </is>
+      </c>
+      <c r="G89" s="76" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_e14s05.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-27</t>
+        </is>
+      </c>
+      <c r="B90" s="76" t="inlineStr">
+        <is>
+          <t>E14-S05</t>
+        </is>
+      </c>
+      <c r="C90" s="76" t="inlineStr">
+        <is>
+          <t>Full gate and coverage</t>
+        </is>
+      </c>
+      <c r="D90" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E90" s="76" t="inlineStr">
+        <is>
+          <t>ruff check + format, mypy (76 files), bandit 0 issues, pip-audit clean, 368 security tests, 1,261 passed / 247 skipped.</t>
+        </is>
+      </c>
+      <c r="F90" s="76" t="inlineStr">
+        <is>
+          <t>Coverage 82% -&gt; 83%, missed statements unchanged at 866. Every module under execution/risk is at 100% except framework.py at 99% (one unreachable branch exit). doctor's one failure is the local missing DB password, unchanged.</t>
+        </is>
+      </c>
+      <c r="G90" s="76" t="inlineStr">
+        <is>
+          <t>full suite</t>
         </is>
       </c>
     </row>
@@ -24653,7 +24837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -24682,6 +24866,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -26225,6 +26410,90 @@
       <c r="H38" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_detail_containment.py TestCorrelationInputsCannotBeQuietlyWrong — NaN, +Inf and -Inf, plus a test asserting the raw comparison really does raise (so the guard is not decoration) and a control that finite values are unaffected. Mutation M05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-35</t>
+        </is>
+      </c>
+      <c r="B39" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C39" s="76" t="inlineStr">
+        <is>
+          <t>RiskContext / non-finite numbers</t>
+        </is>
+      </c>
+      <c r="D39" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E39" s="76" t="inlineStr">
+        <is>
+          <t>Any Decimal on RiskContext could be NaN or an infinity. Every one of them is a number a check compares against a limit.</t>
+        </is>
+      </c>
+      <c r="F39" s="76" t="inlineStr">
+        <is>
+          <t>Two distinct failures, both reading as normal operation. NaN makes every comparison False, so `loss &gt;= limit` is False and a halted day keeps trading; where it raises instead, the message is 'InvalidOperation' and names neither the field nor the cause (QA-SEC-34's shape). And an INFINITY compares cleanly: realised_pnl_today = +Infinity passed the daily loss limit without comment. Verified against running code for realised_pnl_today, capital, available_margin, atr and margin_per_share.</t>
+        </is>
+      </c>
+      <c r="G39" s="76" t="inlineStr">
+        <is>
+          <t>Rejected at CONSTRUCTION, so the state is unrepresentable rather than guarded in fourteen places. The fields are found by iterating dataclasses.fields, so the guard already covers atr and margin_per_share, which no check reads yet — the QA-SEC-33 lesson applied before it could cost anything.</t>
+        </is>
+      </c>
+      <c r="H39" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py TestNoNonFiniteNumberReachesACheck — 4 non-finite values x 5 fields, the error naming the field, a reflection test asserting EVERY Decimal field is covered, and controls that ordinary values and None are unaffected. Mutations M12, M14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-36</t>
+        </is>
+      </c>
+      <c r="B40" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C40" s="76" t="inlineStr">
+        <is>
+          <t>RiskContext / corrupt loss counter</t>
+        </is>
+      </c>
+      <c r="D40" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E40" s="76" t="inlineStr">
+        <is>
+          <t>consecutive_losses = -5 passed the consecutive-loss check, because -5 &lt; 3 is true.</t>
+        </is>
+      </c>
+      <c r="F40" s="76" t="inlineStr">
+        <is>
+          <t>A negative count is not 'fewer losses' — it means whatever maintains the counter is broken. Treating a broken counter as a clean streak is the same unknown-becomes-fine pattern as QA-SEC-32/33 and E14-S03's AC2. LOW rather than MEDIUM because reaching the state needs an upstream defect that does not exist yet; recorded now because the guard costs one line and the counter's owner (E14-S09) is unwritten.</t>
+        </is>
+      </c>
+      <c r="G40" s="76" t="inlineStr">
+        <is>
+          <t>__post_init__ refuses a negative count, with a message that says why a smaller number is not a safer one.</t>
+        </is>
+      </c>
+      <c r="H40" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py TestACorruptLossCounterDoesNotReadAsACleanStreak. Mutation M13.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,7 +4572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21466,7 +21465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24817,6 +24816,43 @@
       <c r="G90" s="76" t="inlineStr">
         <is>
           <t>full suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-28</t>
+        </is>
+      </c>
+      <c r="B91" s="76" t="inlineStr">
+        <is>
+          <t>E14-S05</t>
+        </is>
+      </c>
+      <c r="C91" s="76" t="inlineStr">
+        <is>
+          <t>SIT: loss limits walked across a session</t>
+        </is>
+      </c>
+      <c r="D91" s="76" t="inlineStr">
+        <is>
+          <t>PASS (no product defect)</t>
+        </is>
+      </c>
+      <c r="E91" s="76" t="inlineStr">
+        <is>
+          <t>12 scenarios at TWELVE registered checks: the composition property (340 minutes either way), the day stopping when the limit is reached, a RECOVERY after the latch is set, a streak halt surviving a winning exit, a profitable session trading all day, a losing-but-within-limit session trading all day, ordering across all four groups, audit completeness, replay determinism, and nothing approved. SIT total 55 -&gt; 67.</t>
+        </is>
+      </c>
+      <c r="F91" s="76" t="inlineStr">
+        <is>
+          <t>One scenario is a deliberate COUNTERFACTUAL: the same breach-then-recover session with the latch never set, asserting the afternoon DOES trade again. It demonstrates what the latch prevents rather than asserting it, and it fails loudly if the live figure ever starts behaving as a latch on its own -- at which point the test above it would have stopped proving anything.</t>
+        </is>
+      </c>
+      <c r="G91" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py TestSit8 (12 tests)</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24902,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,6 +4572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -14749,9 +14750,9 @@
           <t>Margin and timing checks (13–14)</t>
         </is>
       </c>
-      <c r="E123" s="40" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="E123" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F123" s="41" t="inlineStr">
@@ -14787,19 +14788,52 @@
       <c r="N123" s="45" t="n"/>
       <c r="O123" s="46" t="n"/>
       <c r="P123" s="46" t="n"/>
-      <c r="Q123" s="47" t="n"/>
-      <c r="R123" s="39" t="n">
-        <v>2</v>
+      <c r="Q123" s="86" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="R123" s="48" t="n">
+        <v>3</v>
       </c>
       <c r="S123" s="48" t="n"/>
       <c r="T123" s="48" t="inlineStr">
         <is>
-          <t>1. Live broker margin sufficient for the intended position
-2. Enough runway before the per-stock square-off deadline</t>
-        </is>
-      </c>
-      <c r="U123" s="48" t="n"/>
-      <c r="V123" s="48" t="n"/>
+          <t>1. check_margin_sufficient — live broker margin, UNKNOWN rejects
+2. check_time_to_squareoff — runway before the per-stock deadline
+3. build_margin_timing_checks factory + MARGIN_TIMING_ORDER, last in the pipeline</t>
+        </is>
+      </c>
+      <c r="U123" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) Margin that is UNKNOWN rejects. 'We could not reach the broker' must never become a number — RiskContext's own docstring names this check as the reason available_margin is `| None`.
+AC2 (RED) Margin below the cost of a single share rejects with INSUFFICIENT_MARGIN. Sizing cannot rescue an account that cannot afford one unit.
+AC3 Margin comfortably above passes.
+AC4 (RED) An unknown margin_per_share rejects. Affordability is a ratio; without the denominator there is no answer, and 'no answer' is not 'yes'.
+AC5 (RED) A non-positive margin_per_share is refused at CONSTRUCTION. The sizer divides by it, so zero is a crash and negative is a negative quantity — neither may be representable.
+AC6 (RED) Less runway than configured before the per-stock square-off deadline rejects with TOO_CLOSE_TO_SQUAREOFF.
+AC7 (RED) A deadline already PASSED rejects. Negative runway is not 'plenty of time', and a naive &gt;= comparison happens to handle it — which is exactly why it needs its own test rather than being assumed.
+AC8 Ample runway passes.
+AC9 (CONTROL) Known margin, an affordable share and ample runway pass both. Two checks that rejected everything would satisfy AC1-AC8.
+AC10 Order is margin then timing, per LOW_LEVEL_ARCHITECTURE 5.7, running LAST in the pipeline.</t>
+        </is>
+      </c>
+      <c r="V123" s="48" t="inlineStr">
+        <is>
+          <t>ACCEPTANCE CRITERIA WRITTEN 4 Sep 2026. The story had two task lines and no criteria, so DoR R5 could not be satisfied.
+DEPENDENCY IS REAL AND SATISFIED. Unlike E14-S01/S03/S04, this story's declared dependency (E02-S07, live margin retrieval) is a genuine one and is QA-Success. Recorded because the last three stories each had a mis-stated dependency and it would be wrong to imply that is the norm.
+STALENESS IS NOT THIS CHECK'S JOB. E02-S07's margin_for_sizing() RAISES StaleMarginError on a snapshot older than the TTL, closing the time-of-check/time-of-use gap: available margin falls after every fill, so a snapshot taken before the previous entry can authorise a position the account cannot carry. By the time a value reaches RiskContext.available_margin it is therefore FRESH OR ABSENT. This check rejects absent; it does not re-implement the TTL, and duplicating it here would give two places to disagree about how old is too old.
+WHAT CHECK 13 CAN AND CANNOT DO. Like the exposure caps, it runs BEFORE sizing, so there is no quantity yet and it cannot verify margin for 'the intended position' as task 1 words it. What it CAN do is refuse when margin is unknown, or when it will not cover a single share — the cheapest possible position. The proportional clamp already exists in LOW_LEVEL_ARCHITECTURE 5.7's sizing formula as `available_margin / margin_per_share`, so unlike the sector and net-directional caps (E14-S10) this limit IS enforced once E14-S07 lands. No new story needed.
+NEW CONFIG: risk.min_minutes_to_squareoff (default 30). There was no setting for it. exit_buffer_minutes (5) is a different thing entirely — it is already subtracted when the deadline is computed, so it protects against the BROKER's forced square-off, not against entering a trade with no time to work.
+  THE NUMBER IS A JUDGEMENT, recorded as an assumption. 30 minutes is two bars of the slowest supported interval (15m), which is thin — a 15-minute strategy arguably wants 45 — and generous for a 1-minute one. The effective interval is adaptive (LatencyProfiler) and not known at check time, so a single configured floor is the honest mechanism. Revisit if the system settles on one timeframe.
+  IT IS NOT REDUNDANT with the 15:00-15:30 no-trade window. A CAS stock's deadline is 15:10 minus the 5-minute buffer = 15:05, so at 14:59 — still inside the tradable window — the runway is six minutes. The window says 'we are near the close'; this says 'this particular trade has no time'.
+OUT OF SCOPE: the sizing clamp itself (E14-S07), the margin fetch and its TTL (E02-S07, done), and per-stock deadline computation (E00-S06's MarketCalendar.squareoff_deadline, done — this check reads the value).
+DELIVERED 4 Sep 2026 (/sdlc). checks/margin_timing.py, 2 checks plus all_check_ids(). 40 unit tests, 9 seam tests, 8 new security tests. Mutation 15/15. margin_timing.py and context.py at 100%; overall 83%.
+**THE FOURTEEN RISK CHECKS ARE NOW COMPLETE** and a real pipeline trigger clears all of them. It is still not APPROVED: there is no sizer, so the engine refuses with RISK_ENGINE_FAULT rather than defaulting a quantity. E14-S07 is what turns fourteen passes into an order.
+CONFIG ADDED: risk.min_minutes_to_squareoff (30).
+QA-SEC-37 found and fixed: a square-off deadline on another day disabled the runway gate entirely.</t>
+        </is>
+      </c>
       <c r="W123" s="49" t="n"/>
     </row>
     <row r="124" ht="30" customHeight="1" s="59">
@@ -21465,7 +21499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -24853,6 +24887,154 @@
       <c r="G91" s="76" t="inlineStr">
         <is>
           <t>tests/sit/test_e14_trading_session.py TestSit8 (12 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-29</t>
+        </is>
+      </c>
+      <c r="B92" s="76" t="inlineStr">
+        <is>
+          <t>E14-S06</t>
+        </is>
+      </c>
+      <c r="C92" s="76" t="inlineStr">
+        <is>
+          <t>AC1-AC10, one test class per criterion</t>
+        </is>
+      </c>
+      <c r="D92" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E92" s="76" t="inlineStr">
+        <is>
+          <t>AC1 unknown margin rejects as a FAULT. AC2 below one share rejects. AC3 ample passes. AC4 an unknown per-share margin rejects. AC5 a non-positive one is refused at construction. AC6 too little runway rejects. AC7 a PASSED deadline rejects. AC8 ample runway passes. AC9 the control. AC10 order, plus the shape of the completed fourteen.</t>
+        </is>
+      </c>
+      <c r="F92" s="76" t="inlineStr">
+        <is>
+          <t>Two tests earn their place beyond the criteria. `Decimal(0)` margin is FALSY, so a truthiness test on the field would report an empty account as a fault instead of INSUFFICIENT_MARGIN — asserted explicitly. And AC7's detail must not render negative time: '-25 minutes remain' is a sentence an operator has to decode, so it reads 'passed 25 minutes ago'.</t>
+        </is>
+      </c>
+      <c r="G92" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_risk_margin_timing.py (40 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-30</t>
+        </is>
+      </c>
+      <c r="B93" s="76" t="inlineStr">
+        <is>
+          <t>E14-S06</t>
+        </is>
+      </c>
+      <c r="C93" s="76" t="inlineStr">
+        <is>
+          <t>Integration: all FOURTEEN checks against a real trigger</t>
+        </is>
+      </c>
+      <c r="D93" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E93" s="76" t="inlineStr">
+        <is>
+          <t>The first time the whole risk pipeline has existed. A Trigger the pipeline produced from real ticks clears all fourteen gates in §5.7's order; unknown margin, an unaffordable share, and too little runway each stop it; an earlier group still wins over the last two.</t>
+        </is>
+      </c>
+      <c r="F93" s="76" t="inlineStr">
+        <is>
+          <t>One test asserts the honest negative: clearing fourteen checks is NOT an approval. There is no sizer, so the engine refuses with RISK_ENGINE_FAULT rather than defaulting a quantity — and that is asserted rather than left implied. Another pins the case that justifies check 14 alongside check 4: at 14:59 the blackout has not started (so no_trade_window PASSES, asserted) and a CAS name has six minutes left.</t>
+        </is>
+      </c>
+      <c r="G93" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_tick_to_trigger.py TestTheTriggerMeetsAllFourteenChecks (9 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-31</t>
+        </is>
+      </c>
+      <c r="B94" s="76" t="inlineStr">
+        <is>
+          <t>E14-S06</t>
+        </is>
+      </c>
+      <c r="C94" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing, 15 injected defects</t>
+        </is>
+      </c>
+      <c r="D94" s="76" t="inlineStr">
+        <is>
+          <t>PASS (15/15 killed)</t>
+        </is>
+      </c>
+      <c r="E94" s="76" t="inlineStr">
+        <is>
+          <t>Injected: the margin comparison inverted; each gate disabled; unknown margin becoming zero; an invented per-share margin; the runway minimum reduced to 'only a passed deadline'; the boundary off-by-one; the passed-deadline wording removed; the order swapped in both the factory and the declared constant; and all three context guards reverted.</t>
+        </is>
+      </c>
+      <c r="F94" s="76" t="inlineStr">
+        <is>
+          <t>M15 is the one worth noting: it moves the same-day comparison from IST to UTC, which still refuses a 2030 deadline but starts refusing a legitimate evening context (19:00 UTC on the 24th is 00:30 IST on the 25th). Killed by the test written for exactly that, so the fix cannot be 'simplified' into a subtler bug.</t>
+        </is>
+      </c>
+      <c r="G94" s="76" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_e14s06.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-32</t>
+        </is>
+      </c>
+      <c r="B95" s="76" t="inlineStr">
+        <is>
+          <t>E14-S06</t>
+        </is>
+      </c>
+      <c r="C95" s="76" t="inlineStr">
+        <is>
+          <t>Full gate and coverage</t>
+        </is>
+      </c>
+      <c r="D95" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E95" s="76" t="inlineStr">
+        <is>
+          <t>ruff check + format, mypy (77 files), bandit 0 issues, pip-audit clean, 379 security tests, 1,333 passed / 247 skipped.</t>
+        </is>
+      </c>
+      <c r="F95" s="76" t="inlineStr">
+        <is>
+          <t>Coverage 83%, missed statements unchanged at 866. Every module under execution/risk is at 100% except framework.py at 99%. THREE EXISTING TESTS FAILED on the new deadline guard and were the tests' fault: they built a January `now` against an August deadline, a state the real system cannot produce. The helper now derives a same-day deadline, which makes every context in that file internally consistent.</t>
+        </is>
+      </c>
+      <c r="G95" s="76" t="inlineStr">
+        <is>
+          <t>full suite</t>
         </is>
       </c>
     </row>
@@ -24873,7 +25055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -24902,6 +25084,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -26529,6 +26712,48 @@
       <c r="H40" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_detail_containment.py TestACorruptLossCounterDoesNotReadAsACleanStreak. Mutation M13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-37</t>
+        </is>
+      </c>
+      <c r="B41" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C41" s="76" t="inlineStr">
+        <is>
+          <t>RiskContext / square-off deadline</t>
+        </is>
+      </c>
+      <c r="D41" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E41" s="76" t="inlineStr">
+        <is>
+          <t>A square-off deadline on any day but today PASSED the runway check, silently turning the last time-based gate into a no-op.</t>
+        </is>
+      </c>
+      <c r="F41" s="76" t="inlineStr">
+        <is>
+          <t>Verified: a deadline of 2030 gave effectively unlimited runway and check 14 passed. The gate would still appear in every log line and in every test that happened to use a sane deadline — a safety control that is present and not working is worse than one that is absent, because nothing prompts anyone to look. This system is intraday (invariant 5 gives every position a time exit), so a deadline on another date did not come from MarketCalendar.squareoff_deadline() and is wrong at its source.</t>
+        </is>
+      </c>
+      <c r="G41" s="76" t="inlineStr">
+        <is>
+          <t>__post_init__ refuses a deadline whose IST date differs from `now`'s, making the state unrepresentable rather than guarded. Compared in IST because that is the day the market keeps — in UTC an evening moment and the next morning's deadline share a date more often than they should.</t>
+        </is>
+      </c>
+      <c r="H41" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py TestASquareOffDeadlineIsAlwaysToday — four wrong-day shapes, the error naming both dates, the IST-vs-UTC distinction, and controls that pre-open, mid-session and post-close all still construct (a guard that refused post-close would break the square-off path). Mutations M12, M13, M15.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,7 +4572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21499,7 +21498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -25035,6 +25034,43 @@
       <c r="G95" s="76" t="inlineStr">
         <is>
           <t>full suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-33</t>
+        </is>
+      </c>
+      <c r="B96" s="76" t="inlineStr">
+        <is>
+          <t>E14-S06</t>
+        </is>
+      </c>
+      <c r="C96" s="76" t="inlineStr">
+        <is>
+          <t>SIT: the complete fourteen-check pipeline across a session</t>
+        </is>
+      </c>
+      <c r="D96" s="76" t="inlineStr">
+        <is>
+          <t>PASS (no product defect)</t>
+        </is>
+      </c>
+      <c r="E96" s="76" t="inlineStr">
+        <is>
+          <t>12 scenarios at FOURTEEN registered checks: the day's shape, the narrowing attributed to its cause, contiguity, margin running out at noon, the broker going dark and recovering, an empty account as a business rejection, a non-CAS name trading ten minutes longer than a CAS one, nothing approved on any minute, spec order on a cleared minute, audit completeness, replay determinism, and no credential in a full day's log. SIT total 67 -&gt; 79.</t>
+        </is>
+      </c>
+      <c r="F96" s="76" t="inlineStr">
+        <is>
+          <t>This is the first group where adding checks legitimately NARROWS the trading day — 340 minutes to 316 — because check 14 is the first gate with an opinion about the clock. Every earlier group asserted the window was UNCHANGED, so that assertion had to be replaced rather than reused, and a second test NAMES the runway check as the cause rather than inferring it: if a different gate ever starts closing the afternoon, it fails instead of quietly agreeing. The per-stock deadline is also walked as two sessions — a non-CAS name keeps trading ten minutes longer, which a global deadline would have made identical.</t>
+        </is>
+      </c>
+      <c r="G96" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py TestSit9 (12 tests)</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25120,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,6 +4572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -14856,9 +14857,9 @@
           <t>ATR-based position sizing</t>
         </is>
       </c>
-      <c r="E124" s="40" t="inlineStr">
-        <is>
-          <t>New</t>
+      <c r="E124" s="48" t="inlineStr">
+        <is>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F124" s="41" t="inlineStr">
@@ -14894,7 +14895,11 @@
       <c r="N124" s="45" t="n"/>
       <c r="O124" s="46" t="n"/>
       <c r="P124" s="46" t="n"/>
-      <c r="Q124" s="47" t="n"/>
+      <c r="Q124" s="86" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="R124" s="39" t="n">
         <v>7</v>
       </c>
@@ -14916,11 +14921,34 @@
       </c>
       <c r="U124" s="48" t="inlineStr">
         <is>
-          <t>• 🔴 Property test: risk never exceeds `risk_pct` for ANY generated input
-• 🔴 A surprisingly small position is explainable from the binding constraint</t>
-        </is>
-      </c>
-      <c r="V124" s="48" t="n"/>
+          <t>AC1 (RED) PROPERTY: realised risk never exceeds risk_pct of capital, for any generated input. capital_at_risk = quantity x stop_distance must always be &lt;= capital x risk_pct / 100.
+AC2 (RED) A surprisingly small position is explainable from binding_constraint alone — including a ZERO one, which must not be reported as a margin problem when the account has plenty.
+AC3 (RED) PROPERTY: quantity always rounds DOWN to a whole lot, never to nearest. Round-to-nearest breaks AC1 on every round-up.
+AC4 (RED) A zero quantity REJECTS. It must never place nothing silently, and it must never be reported as an approval with quantity 0.
+AC5 (RED) The stop distance comes from ATR x multiplier, NOT from Recommendation.suggested_stop. Invariant 1: the executable stop is computed here, and a Recommendation that could set it would be a sizing field by another name.
+AC6 (RED) Unknown ATR rejects; a non-positive ATR is unrepresentable. Stop distance is the divisor, so zero is an infinite quantity.
+AC7 Each of the four clamps binds when it should, and names itself: risk_budget, position_cap, slot_cap, margin_cap, lot_rounding.
+AC8 The stop is on the correct SIDE of entry — below for LONG, above for SHORT — and the target is target_r_multiple away in the other direction.
+AC9 (CONTROL) An ordinary candidate produces a sensible non-zero quantity. A sizer that always returned 0 would satisfy AC1 and AC3 perfectly.
+AC10 PROPERTY: sizing is deterministic and pure — same inputs, same SizingResult, no clock and no I/O.</t>
+        </is>
+      </c>
+      <c r="V124" s="48" t="inlineStr">
+        <is>
+          <t>ACCEPTANCE CRITERIA EXPANDED 4 Sep 2026. The story already had two good ones (the risk property, and the binding constraint) plus a strong Build Concerns note; AC3/AC4 promote that note's two demands into criteria, and the rest cover what the formula touches. Recorded because the previous six stories each had NO criteria — this one was well specified and it would be wrong to imply otherwise.
+THE STOP DISTANCE IS ATR-DERIVED, NOT THE STRATEGY'S SUGGESTION. LOW_LEVEL_ARCHITECTURE 5.7: stop_distance = ATR(14) x atr_multiplier_stop. Recommendation.suggested_stop exists and is NOT used for sizing — invariant 1 says the executable stop price is computed downstream, and a Recommendation whose suggested_stop drove the quantity would be carrying a sizing field under a different name. The suggested stop remains useful as a sanity signal; it is not an input here.
+FLOOR, NEVER NEAREST — and it is what makes AC1 true. raw_qty = risk_amount / stop_distance, so quantity &lt;= raw_qty implies quantity x stop_distance &lt;= risk_amount. Flooring preserves that; rounding to nearest breaks it on every round-up, by up to one lot's worth of stop distance. The Build Concerns note called this out and it is now a property test rather than a comment.
+TICK ROUNDING IS OUT OF SCOPE, AND VERIFIED SAFE. broker/kite/mapping.py round_to_tick() is documented as 'the one used before submission' and needs a Side and the instrument's tick size, neither of which belongs in RiskContext. Verified empirically rather than assumed: it rounds a BUY down and a SELL up, so a LONG's stop (a SELL) moves UP toward entry and a SHORT's stop (a BUY) moves DOWN toward entry. Across 100 sub-tick offsets the snapped stop was never further from entry than the computed one. Submission-time rounding therefore only ever REDUCES realised risk, so AC1's bound survives the order gateway.
+NEW CONTEXT FIELD: lot_size (default 1, ge 1). NSE equity is lot size 1; F&amp;O is not. Instrument.lot_size already exists and the DB has a lot_size &gt;= 1 constraint, so this is plumbing an existing fact to where sizing can read it.
+NON-POSITIVE ATR IS UNREPRESENTABLE, like margin_per_share. Stop distance is the divisor, so a zero ATR is an infinite quantity and a negative one is a stop on the wrong side of entry. ALTERNATIVE CONSIDERED: let the sizer reject a zero ATR instead, since a genuinely halted stock could measure zero range. Rejected because the only thing that consumes ATR in this path divides by it, so a zero has no valid use here — and check 5 (symbol_tradable) is where a halted name should be filtered.
+FOUND WHILE READING THE FRAMEWORK — see E14-S11. RiskEngine._size hardcodes INSUFFICIENT_MARGIN for ANY zero quantity, whichever clamp bound. A zero produced by the position cap or by lot rounding on a well-funded account would be reported as a margin problem, which is the SIT-001 conflation again and directly contradicts this story's AC2. Fixed here rather than deferred, because AC2 cannot pass otherwise: a new RejectReason.POSITION_TOO_SMALL carries the non-margin case.
+OUT OF SCOPE: tick rounding (order gateway), the sector and net-directional clamps (E14-S10, which this story unblocks), slot accounting (E14-S08 owns slots_used; this reads capital_per_slot from config), and order placement.
+DELIVERED 4 Sep 2026 (/sdlc). execution/sizer.py plus common/text.py. 47 unit tests (5 Hypothesis properties), 11 seam tests, 7 new security tests. Mutation 18/19 with one VERIFIED-BENIGN survivor. sizer.py, text.py and context.py all at 100%; overall 83%.
+**THE CHAIN NOW CLOSES.** A Trigger the pipeline produced from real ticks clears all fourteen checks and becomes an APPROVED RiskDecision carrying a quantity and an executable stop. Nothing in this system had produced an approval before this story.
+TWO OF MY OWN BUGS, both found by the tests rather than by reading: a stop price could exceed Price's 4 decimal places, and the LOT_ROUNDING label was too eager. And the worked example I wrote was wrong — at a 1,200-rupee entry the POSITION CAP binds at 83 shares, not the risk budget at 246. That is now its own test.
+E14-S10 IS UNBLOCKED by this story.</t>
+        </is>
+      </c>
       <c r="W124" s="49" t="n"/>
       <c r="X124" s="75" t="inlineStr">
         <is>
@@ -21498,7 +21526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -25071,6 +25099,228 @@
       <c r="G96" s="76" t="inlineStr">
         <is>
           <t>tests/sit/test_e14_trading_session.py TestSit9 (12 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-34</t>
+        </is>
+      </c>
+      <c r="B97" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C97" s="76" t="inlineStr">
+        <is>
+          <t>AC1-AC10, one test class per criterion</t>
+        </is>
+      </c>
+      <c r="D97" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E97" s="76" t="inlineStr">
+        <is>
+          <t>AC1 the risk property over 400 generated inputs. AC2 the binding constraint, including a zero. AC3 flooring, as two properties. AC4 a zero rejects. AC5 the stop is ATR-derived and suggested_stop is ignored. AC6 unknown/non-positive ATR. AC7 each clamp names itself. AC8 stop and target sides. AC9 the control. AC10 purity.</t>
+        </is>
+      </c>
+      <c r="F97" s="76" t="inlineStr">
+        <is>
+          <t>AC1 is the story: capital_at_risk &lt;= capital x risk_pct / 100 across generated capital, risk percentage, volatility, price and lot size. AC3 is the same fact seen from the other side — flooring is WHY the bound holds, and M01 (round-to-nearest, the Build Concerns warning verbatim) is killed by it. AC9 matters because a sizer that always returned 0 would satisfy AC1 and AC3 perfectly.</t>
+        </is>
+      </c>
+      <c r="G97" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_sizer.py (47 tests, 5 properties)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-35</t>
+        </is>
+      </c>
+      <c r="B98" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C98" s="76" t="inlineStr">
+        <is>
+          <t>TWO BUGS OF MINE, both caught by the tests</t>
+        </is>
+      </c>
+      <c r="D98" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E98" s="76" t="inlineStr">
+        <is>
+          <t>1. stop_price could carry 5 decimal places (1200.00 - 0.0501x1.5 = 1199.92485) and Price is decimal_places=4, so SizingResult refused to build. 2. LOT_ROUNDING was reported whenever a zero followed any positive clamp, so 0.5 shares allowed by the MARGIN cap was blamed on the lot size.</t>
+        </is>
+      </c>
+      <c r="F98" s="76" t="inlineStr">
+        <is>
+          <t>Neither was visible in review. The first is fixed by quantising the stop distance ONCE and using that one value for the divisor, the stop and the risk figure alike — quantising afterwards would leave the recorded risk describing a stop that is not the one being placed. The second needed the line between the two cases stated: `smallest &gt;= 1` means the clamps allowed at least one share and the LOT is what took it to nothing. Mutation M12 pins it.</t>
+        </is>
+      </c>
+      <c r="G98" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_sizer.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-36</t>
+        </is>
+      </c>
+      <c r="B99" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C99" s="76" t="inlineStr">
+        <is>
+          <t>MY WORKED EXAMPLE WAS WRONG</t>
+        </is>
+      </c>
+      <c r="D99" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E99" s="76" t="inlineStr">
+        <is>
+          <t>The hand-computed example expected 246 shares bound by the risk budget. The real answer at a 1,200-rupee entry is 83 shares bound by the POSITION CAP: 20% of 500,000 is 100,000, which buys 83 shares, while the risk budget would have allowed 246.</t>
+        </is>
+      </c>
+      <c r="F99" s="76" t="inlineStr">
+        <is>
+          <t>Worth recording rather than quietly correcting, because it is a property of the configured defaults that an operator will meet: a high-priced name risks LESS than the configured 1%, and the only thing that explains why is binding_constraint. It is now its own test with that reasoning attached, and the default fixture uses a price where the risk budget genuinely binds.</t>
+        </is>
+      </c>
+      <c r="G99" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_sizer.py test_an_expensive_stock_is_bound_by_the_position_cap_instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-37</t>
+        </is>
+      </c>
+      <c r="B100" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C100" s="76" t="inlineStr">
+        <is>
+          <t>Integration: the chain closes</t>
+        </is>
+      </c>
+      <c r="D100" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E100" s="76" t="inlineStr">
+        <is>
+          <t>A Trigger from real ticks clears all fourteen checks and becomes an APPROVED decision with a quantity, an executable stop and a target. Plus: the risk bound on the indicator engine's own ATR, a rejected candidate carrying NO sizing, an account that affords exactly one share, a lot too large to fill, and the audit row carrying the quantity.</t>
+        </is>
+      </c>
+      <c r="F100" s="76" t="inlineStr">
+        <is>
+          <t>The seam that only exists here is the ATR one: the sizer divides the budget by a number the INDICATOR ENGINE produced through ATR.as_decimal(), not by a Decimal a test author chose. A units error at that boundary — percent instead of rupees — would blow the risk bound here and nowhere else.</t>
+        </is>
+      </c>
+      <c r="G100" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_tick_to_trigger.py TestTheTriggerBecomesAnApprovedOrder (11 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-38</t>
+        </is>
+      </c>
+      <c r="B101" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C101" s="76" t="inlineStr">
+        <is>
+          <t>Mutation testing, 19 injected defects</t>
+        </is>
+      </c>
+      <c r="D101" s="76" t="inlineStr">
+        <is>
+          <t>PASS (18/19, 1 verified benign)</t>
+        </is>
+      </c>
+      <c r="E101" s="76" t="inlineStr">
+        <is>
+          <t>Injected: round-to-nearest; the budget doubled; the percentage undivided; MAX instead of MIN over the clamps; capital_at_risk forced to zero; the stop multiplier dropped; a LONG's stop placed above entry; banker's rounding on the distance; every guard removed; the tie-break reversed; both halves of the reason split; the shared sanitiser; and both context guards.</t>
+        </is>
+      </c>
+      <c r="F101" s="76" t="inlineStr">
+        <is>
+          <t>M11 SURVIVED and was verified benign before anything changed: `if quantity &lt;= 0` vs `&lt; 0` in the lot floor differ only at exactly zero, where int(0/lot)*lot is already 0 — and negatives are still caught by `&lt; 0`, so the mutation does not reopen the negative-quantity hole the guard exists for. Compared across the domain, no input distinguishes them. The guard is KEPT: `&lt;= 0` states the intent rather than relying on truncation to agree.</t>
+        </is>
+      </c>
+      <c r="G101" s="76" t="inlineStr">
+        <is>
+          <t>scratchpad/mutate_e14s07.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-39</t>
+        </is>
+      </c>
+      <c r="B102" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C102" s="76" t="inlineStr">
+        <is>
+          <t>Full gate and coverage</t>
+        </is>
+      </c>
+      <c r="D102" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E102" s="76" t="inlineStr">
+        <is>
+          <t>ruff check + format, mypy (79 files), bandit 0 issues, pip-audit clean, 388 security tests, 1,415 passed / 247 skipped.</t>
+        </is>
+      </c>
+      <c r="F102" s="76" t="inlineStr">
+        <is>
+          <t>Coverage 83%, missed statements unchanged at 866. sizer.py, text.py, context.py and every checks module at 100%; framework.py 99%. One existing framework test failed on the reason split and was stale — it asserted INSUFFICIENT_MARGIN using a binding-constraint name ('broker_margin') that no longer exists anywhere. It now pins BOTH branches. doctor's one failure is the local missing DB password.</t>
+        </is>
+      </c>
+      <c r="G102" s="76" t="inlineStr">
+        <is>
+          <t>full suite</t>
         </is>
       </c>
     </row>
@@ -25091,7 +25341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -25120,6 +25370,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -26789,6 +27040,48 @@
       <c r="H41" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_detail_containment.py TestASquareOffDeadlineIsAlwaysToday — four wrong-day shapes, the error naming both dates, the IST-vs-UTC distinction, and controls that pre-open, mid-session and post-close all still construct (a guard that refused post-close would break the square-off path). Mutations M12, M13, M15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="76" t="inlineStr">
+        <is>
+          <t>QA-SEC-38</t>
+        </is>
+      </c>
+      <c r="B42" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C42" s="76" t="inlineStr">
+        <is>
+          <t>Log integrity / RiskDecision.detail</t>
+        </is>
+      </c>
+      <c r="D42" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E42" s="76" t="inlineStr">
+        <is>
+          <t>The FOURTH appearance of log forgery, and the first where the fix itself had the hole. QA-SEC-30 moved escaping to where details are CONSTRUCTED and put it in CheckOutcome — which covers every detail a CHECK produces. RiskDecision is a second constructor for the same `detail` field, and the sizer writes through THAT one, carrying a binding_constraint CheckOutcome never sees.</t>
+        </is>
+      </c>
+      <c r="F42" s="76" t="inlineStr">
+        <is>
+          <t>Verified: a newline in binding_constraint reached RiskDecision.detail intact and into the audit payload. It did not forge a log line only because the sizing-rejection path did not log AT ALL — which was itself a gap: the one path that can refuse a candidate that cleared all fourteen checks was the only one that said nothing, so an operator watching the log saw the system go quiet with no reason.</t>
+        </is>
+      </c>
+      <c r="G42" s="76" t="inlineStr">
+        <is>
+          <t>The definition moved to common/text.py and BOTH constructors use it. A rule that lives on one of two constructors is a rule with a hole in it, and the hole is invisible because the other constructor looks equally reasonable. The sizing rejection now logs like every other rejection — which is what makes the escaping load-bearing rather than theoretical.</t>
+        </is>
+      </c>
+      <c r="H42" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_detail_containment.py TestRiskDecisionIsTheOtherDoorIntoTheSameField — four hostile shapes through the sizer, the one-log-line assertion, an ordinary detail left untouched, the length bound, a None detail staying None, and a test asserting both modules hold the SAME function object so a private copy cannot be reintroduced. Mutations M16, M17.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4572,7 +4572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -21526,7 +21525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -25321,6 +25320,80 @@
       <c r="G102" s="76" t="inlineStr">
         <is>
           <t>full suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-40</t>
+        </is>
+      </c>
+      <c r="B103" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C103" s="76" t="inlineStr">
+        <is>
+          <t>SIT: a session that can APPROVE</t>
+        </is>
+      </c>
+      <c r="D103" s="76" t="inlineStr">
+        <is>
+          <t>PASS (no product defect)</t>
+        </is>
+      </c>
+      <c r="E103" s="76" t="inlineStr">
+        <is>
+          <t>12 scenarios: 316 approvals on a normal day, on exactly the minutes that previously merely CLEARED; every approval inside the 1% budget; every one carrying a quantity, a stop below entry and a binding constraint; a halted day approving nothing; the loss limit stopping approvals at noon; a volatile session sizing smaller all day; the audit carrying 316 quantities; replay determinism; a constant quantity across the day; a missing ATR approving nothing. SIT total 79 -&gt; 91.</t>
+        </is>
+      </c>
+      <c r="F103" s="76" t="inlineStr">
+        <is>
+          <t>Six SIT groups had asserted that NOTHING was ever approved. That assertion was true because the engine had no sizer, and it is now false by design — so it is REPLACED here rather than reused, by the harder question: on a day the system can trade, does it stay inside its risk budget on every one of 316 minutes? The earlier groups' assertions still pass, because they build engines without a sizer; the claim was always about the engine's configuration rather than a wish.</t>
+        </is>
+      </c>
+      <c r="G103" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py TestSit10 (12 tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-41</t>
+        </is>
+      </c>
+      <c r="B104" s="76" t="inlineStr">
+        <is>
+          <t>E14-S07</t>
+        </is>
+      </c>
+      <c r="C104" s="76" t="inlineStr">
+        <is>
+          <t>A property test that passed alone and failed in the suite</t>
+        </is>
+      </c>
+      <c r="D104" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E104" s="76" t="inlineStr">
+        <is>
+          <t>test_it_never_rounds_up asserted quantity &lt;= risk_amount / (atr x multiplier). Hypothesis found atr=4.4623: 6.69345 quantises DOWN to 6.6934, and the smaller divisor allows 747 shares rather than 746.99.</t>
+        </is>
+      </c>
+      <c r="F104" s="76" t="inlineStr">
+        <is>
+          <t>The regression rule says a test that passes alone and fails in the suite is a finding — here the finding was in the TEST. It compared against the unquantised distance; the effective one is the quantised value, which is the stop that will actually be placed. The code is right: capital_at_risk uses the SAME quantised distance, so 747 x 6.6934 is still inside the budget and AC1 never failed. The property now reads the effective distance back from the result and additionally asserts capital_at_risk equals quantity x that distance — the invariant that makes the first assertion meaningful rather than circular. Had the code quantised the stop PRICE while keeping the raw distance for the risk figure, the recorded risk would have described a stop that was not the one being placed.</t>
+        </is>
+      </c>
+      <c r="G104" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_sizer.py test_it_never_rounds_up</t>
         </is>
       </c>
     </row>
@@ -25370,7 +25443,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -21525,7 +21525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -21553,7 +21553,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -25394,6 +25393,80 @@
       <c r="G104" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_sizer.py test_it_never_rounds_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="120" customHeight="1" s="59">
+      <c r="A105" s="76" t="inlineStr">
+        <is>
+          <t>QA-AUDIT-01</t>
+        </is>
+      </c>
+      <c r="B105" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT</t>
+        </is>
+      </c>
+      <c r="C105" s="76" t="inlineStr">
+        <is>
+          <t>Whole-system audit: every boundary where an external number enters</t>
+        </is>
+      </c>
+      <c r="D105" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E105" s="76" t="inlineStr">
+        <is>
+          <t>Four findings, all the same defect class the project has now hit at twelve sites: an unknown value silently becoming a fine one. Three at the broker boundary (AUDIT-001/002), one in the calendar (AUDIT-003), one latent in the import graph (AUDIT-004).</t>
+        </is>
+      </c>
+      <c r="F105" s="76" t="inlineStr">
+        <is>
+          <t>The audit deliberately looked where the tests could not: the SEAM between an external payload and a validated model. Every risk-engine module is at 100% coverage and mutation-tested, and none of that reaches one layer upstream where `or 0` turns a changed API into a business condition.</t>
+        </is>
+      </c>
+      <c r="G105" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_broker_kite.py, tests/unit/test_calendar.py, tests/security/test_dependency_hygiene.py - 16 new tests. 10/10 mutations killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="120" customHeight="1" s="59">
+      <c r="A106" s="76" t="inlineStr">
+        <is>
+          <t>QA-AUDIT-02</t>
+        </is>
+      </c>
+      <c r="B106" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT</t>
+        </is>
+      </c>
+      <c r="C106" s="76" t="inlineStr">
+        <is>
+          <t>Verified sound - no finding raised</t>
+        </is>
+      </c>
+      <c r="D106" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E106" s="76" t="inlineStr">
+        <is>
+          <t>Audit hash chain (length-prefixed framing defeats concatenation ambiguity; real prev_hash chaining; naive timestamps refused; timezone-invariant). SecretString across 12 rendering paths - str, repr, f-string, format, %s, json, pickle, deepcopy, __dict__, exception, __reduce__, traceback - zero leaks. Repo hygiene: no secret ever committed, .env.example empty, data/ ignored. SEBI 5 OPS cap: config can lower but cannot raise. market_protection=0 refused. No naive datetimes, no bare excepts. Audit-write failure buffers to disk and logs loudly rather than dropping the record.</t>
+        </is>
+      </c>
+      <c r="F106" s="76" t="inlineStr">
+        <is>
+          <t>Recorded so the negative results are visible. An audit that lists only what it broke reads as if nothing else was examined.</t>
+        </is>
+      </c>
+      <c r="G106" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/ (unchanged, all passing)</t>
         </is>
       </c>
     </row>
@@ -25414,7 +25487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -27154,6 +27227,174 @@
       <c r="H42" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_detail_containment.py TestRiskDecisionIsTheOtherDoorIntoTheSameField — four hostile shapes through the sizer, the one-log-line assertion, an ordinary detail left untouched, the length bound, a None detail staying None, and a test asserting both modules hold the SAME function object so a private copy cannot be reintroduced. Mutations M16, M17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="150" customHeight="1" s="59">
+      <c r="A43" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-001</t>
+        </is>
+      </c>
+      <c r="B43" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C43" s="76" t="inlineStr">
+        <is>
+          <t>Broker boundary / margin parsing</t>
+        </is>
+      </c>
+      <c r="D43" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E43" s="76" t="inlineStr">
+        <is>
+          <t>fetch_margins read every figure as Decimal(str(available.get("cash", 0) or 0)). A renamed, missing or explicitly null Kite key therefore produced available_margin = 0 with no error, no log line and no metric. Found by the end-to-end audit's boundary pass, not by any test.</t>
+        </is>
+      </c>
+      <c r="F43" s="76" t="inlineStr">
+        <is>
+          <t>Probed across six payload shapes (renamed key, empty segment, explicit null, partial segment, correct payload, genuinely zero account). All but the last two produced 0. Traced through the REAL risk engine: check 13 refused the candidate as INSUFFICIENT_MARGIN with the operator-facing detail "available margin 0.00 will not cover one share of INFY at 240.00 per share" - sending an operator to inspect a perfectly funded account while the actual fault, a changed broker API, went entirely unreported.</t>
+        </is>
+      </c>
+      <c r="G43" s="76" t="inlineStr">
+        <is>
+          <t>Added mapping.require_field(payload, key, *, what, alias=None) raising MappingError, with None counted as absent because Kite sends explicit nulls. Applied to cash, live_balance (alias cash) and debits. A genuinely zero margin still parses as 0 - the distinction between 'zero' and 'absent' is the whole point, and collapsing it the other way would have turned a business condition into an integration error.</t>
+        </is>
+      </c>
+      <c r="H43" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_broker_kite.py TestTheBrokerBoundaryRefusesToGuessANumber - 8 tests including the zero-is-still-a-number control and the alias fallback. Mutations M1, M2, M3, M5, M9 all killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="150" customHeight="1" s="59">
+      <c r="A44" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-002</t>
+        </is>
+      </c>
+      <c r="B44" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C44" s="76" t="inlineStr">
+        <is>
+          <t>Broker boundary / order reconciliation</t>
+        </is>
+      </c>
+      <c r="D44" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E44" s="76" t="inlineStr">
+        <is>
+          <t>_to_order used int(row.get("filled_quantity") or 0). Latent rather than active: no order path exists yet. Recorded because the recovery path is already specified and this input is what it would adopt.</t>
+        </is>
+      </c>
+      <c r="F44" s="76" t="inlineStr">
+        <is>
+          <t>Established the asymmetry that makes this a finding at all: Order.quantity is Field(gt=0), so a silently-zero quantity is REJECTED by the model and fails loudly - genuinely not a finding. filled_quantity is Field(ge=0), so a silent 0 is ACCEPTED and means 'nothing filled'. CLAUDE.md's recovery path queries the broker by client_order_id and ADOPTS ITS ANSWER, resubmitting only if genuinely absent - which is how an answer that wrongly says 'nothing filled' turns one position into two.</t>
+        </is>
+      </c>
+      <c r="G44" s="76" t="inlineStr">
+        <is>
+          <t>Both quantity and filled_quantity now go through require_field. quantity was already safe via the model; routing it too costs nothing and removes the need for a future reader to re-derive which of the two was protected and why.</t>
+        </is>
+      </c>
+      <c r="H44" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_broker_kite.py - a missing filled_quantity is refused; a genuinely unfilled order is still 0. Mutations M4, M10 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="150" customHeight="1" s="59">
+      <c r="A45" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-003</t>
+        </is>
+      </c>
+      <c r="B45" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t>Market calendar / config fidelity</t>
+        </is>
+      </c>
+      <c r="D45" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E45" s="76" t="inlineStr">
+        <is>
+          <t>config/nse_holidays.yaml carries a special_sessions block with a per-entry trade: flag for Muhurat trading. calendar.py never read the block. Standing down on Muhurat (the recorded SPRINT02 Q5 decision) happened anyway - but only because the 2026 date falls on a Sunday and is_trading_day sees a Sunday.</t>
+        </is>
+      </c>
+      <c r="F45" s="76" t="inlineStr">
+        <is>
+          <t>Behaviour was correct BY ACCIDENT. An operator who set trade: true - a field sitting in the config describing itself - would have changed nothing and had no way to discover that. This is the same shape as 'configuring a limit means the limit is enforced' (E14-S10), where two exposure caps were configured and binding on nothing.</t>
+        </is>
+      </c>
+      <c r="G45" s="76" t="inlineStr">
+        <is>
+          <t>load_holidays_with_status now raises HolidayDataError at LOAD time if any special_sessions entry sets trade: true, naming the date and the recorded decision. Refusing at load, in the pre-market, is the correct rung: the alternative is discovering it at 13:00 on Diwali.</t>
+        </is>
+      </c>
+      <c r="H45" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_calendar.py TestASpecialSessionFlagCannotLieAboutItsOwnEffect - 6 tests, including the shipped config still loading and Muhurat still standing down asserted DIRECTLY rather than inferred from the flag. Mutations M6, M7 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="150" customHeight="1" s="59">
+      <c r="A46" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-004</t>
+        </is>
+      </c>
+      <c r="B46" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C46" s="76" t="inlineStr">
+        <is>
+          <t>Layering / dependency containment</t>
+        </is>
+      </c>
+      <c r="D46" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E46" s="76" t="inlineStr">
+        <is>
+          <t>The import graph shows exactly one upward edge: common -&gt; broker, a deferred import of broker.profiles inside AppConfig's rate-limit validator. Deferring it is correct. What makes it CHEAP is undocumented and unguarded: broker/__init__.py is empty, so reaching profiles costs nothing.</t>
+        </is>
+      </c>
+      <c r="F46" s="76" t="inlineStr">
+        <is>
+          <t>Measured: validating an AppConfig today loads algotrader.broker and algotrader.broker.profiles and no third-party package at all. Add one convenience re-export to broker/__init__.py - the most natural edit imaginable - and every process that validates a config imports kiteconnect, which imports .ticker unconditionally, which loads autobahn and Twisted. CLAUDE.md already records that exact mechanism as a mistake made once. The existing dependency tests check autobahn's VERSION; nothing checked whether it was loaded at all.</t>
+        </is>
+      </c>
+      <c r="G46" s="76" t="inlineStr">
+        <is>
+          <t>No source change - the current behaviour is correct. The emptiness is now asserted as behaviour instead of trusted to stay. A subprocess check keeps it honest, because the parent's sys.modules is polluted by the rest of the suite and an in-process assertion would pass or fail on test ordering.</t>
+        </is>
+      </c>
+      <c r="H46" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_dependency_hygiene.py TestLoadingAConfigDoesNotDragInTheBrokerStack - the subprocess load check plus an AST control asserting the deferred import is still the only upward one. Mutation M8 killed.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -25487,7 +25487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -27395,6 +27395,48 @@
       <c r="H46" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_dependency_hygiene.py TestLoadingAConfigDoesNotDragInTheBrokerStack - the subprocess load check plus an AST control asserting the deferred import is still the only upward one. Mutation M8 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="170" customHeight="1" s="59">
+      <c r="A47" s="76" t="inlineStr">
+        <is>
+          <t>AUDIT-005</t>
+        </is>
+      </c>
+      <c r="B47" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C47" s="76" t="inlineStr">
+        <is>
+          <t>Risk engine / session risk state</t>
+        </is>
+      </c>
+      <c r="D47" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E47" s="76" t="inlineStr">
+        <is>
+          <t>RiskContext carried six fields describing the session's risk state, and every one had a PERMISSIVE default: kill_switch_active=False, unhealthy_services=(), realised_pnl_today=Decimal(0), consecutive_losses=0, daily_loss_halted=False, consecutive_loss_halted=False. So the answer to 'is the kill switch on?' was NO whenever nobody asked. There was no way to express 'I do not know'.</t>
+        </is>
+      </c>
+      <c r="F47" s="76" t="inlineStr">
+        <is>
+          <t>A fail-open on the most absolute control in the system, and invariant 6 is FAIL CLOSED. A Redis timeout, a half-built context, or a field dropped in a future refactor would each read as 'nothing is halted, trade'. No test could have caught it: a test that omits the field is indistinguishable from one that means 'off'. Proven by the fix - making the six explicit broke 137 existing tests, every one of which had been relying on unknown meaning safe. The context's own docstring already stated the rule these six broke, on the field directly above them: 'None means the broker did not answer, which is a rejection and never an assumption.' Latent rather than active only because no composition root exists yet to build a context - which is exactly when a fail-open is cheapest to fix and most likely to be inherited.</t>
+        </is>
+      </c>
+      <c r="G47" s="76" t="inlineStr">
+        <is>
+          <t>The six now follow the module's own established pattern - `| None` with no default, read through RiskContext.require() - the same shape already used for available_margin, symbol_restrictions, atr and margin_per_share. Unknown now raises RiskContextError, which the engine reports as RISK_ENGINE_FAULT: a refusal that names the missing input. The cost is that a caller must state the session risk state explicitly, which is the intended cost - 'I did not look' and 'I looked and nothing is halted' are different claims and only one is safe to trade on. E14-S09 will be written against a type that no longer permits the unsafe answer.</t>
+        </is>
+      </c>
+      <c r="H47" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_safety_invariants.py TestSessionRiskStateIsNeverAssumed - 16 tests: each of the six omitted one at a time through the REAL engine (not the check functions, since the engine is what turns a raise into a refusal), the armed/degraded/latched controls proving the checks still do their job, a structural test reading the dataclass so a re-added default is caught even if every caller still passes the value, and a control asserting a fully stated healthy session still APPROVES with a real quantity. Mutations M1-M10 all killed.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -20700,7 +20700,7 @@
       </c>
       <c r="E200" s="76" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F200" s="76" t="inlineStr">
@@ -20730,6 +20730,9 @@
         <is>
           <t>E14-S04, E14-S07</t>
         </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>100</v>
       </c>
       <c r="R200" s="76" t="n">
         <v>3</v>
@@ -20751,11 +20754,7 @@
       </c>
       <c r="V200" s="76" t="inlineStr">
         <is>
-          <t>RAISED 2 Sep 2026 while designing E14-S04, which found the gap.
-max_sector_exposure_pct (40) and max_net_directional_exposure_pct (60) are configured, and until this story exists NOTHING enforces them.
-Why the E14-S04 checks cannot do it: risk checks run BEFORE sizing — RiskEngine.evaluate runs every check and only then calls the sizer — so at check time the candidate has a direction but no quantity, and an exposure cap is a statement about notional. The check can therefore only refuse when the book is ALREADY at the cap. A book at 39% of a 40% sector cap passes the check, and sizing may then add another 20% position.
-Why the sizer as designed cannot do it either: LOW_LEVEL_ARCHITECTURE 5.7's formula clamps on max_position_value, slot_capital and available_margin. Sector and net-directional headroom are not among them. Adding them is the natural home for the constraint, because the sizer is the only component that knows the quantity AND already applies a min() over clamps while recording which one bound.
-REJECTED ALTERNATIVE: have the E14-S04 check assume the worst case — that the candidate will take max_position_pct (20%) — and reject if existing + 20% breaches the cap. It is safe but badly over-tight: actual ATR-based sizes are typically far below the 20% cap, so this would refuse trades that would comfortably have fit, and the system would sit out for reasons no operator could see in the book. Conservative in the direction of not trading is still wrong when it is this inaccurate.</t>
+          <t>DELIVERED 7 Sep 2026. The two portfolio caps now BIND. max_sector_exposure_pct (40) and max_net_directional_exposure_pct (60) had been in system.yaml since the beginning and were enforced by nothing. WHERE IT LANDED: execution/sizer.py, as two more entries in the existing min() clamp set, because the sizer is the only component that knows the quantity and already records which clamp bound. THE ARITHMETIC, and the part that is not obvious: sector exposure is UNSIGNED (a sector shock moves every name in it, so a short in that sector is exposed to the same event), while net directional is SIGNED, so the room available depends on which way the book already leans. One expression covers both directions: headroom = cap - sign * net, with sign +1 for a long and -1 for a short. A formula that ignored the sign would refuse the short that REDUCES directional risk while permitting the long that makes the book worse; that case is asserted directly. FAIL-CLOSED: the sizer refuses if the candidate has no sector, or if any open position is unclassified - a sector total computed over an incomplete book is too SMALL, which makes the headroom too LARGE and the clamp too LOOSE. Repeated in the sizer rather than assumed from check 9, which is the AUDIT-005 lesson: a component must not depend on a particular engine having been assembled with a particular check. REASON CODES: a zero quantity from either clamp reports SECTOR_EXPOSURE_LIMIT or NET_EXPOSURE_LIMIT, not POSITION_TOO_SMALL - the SIT-001 lesson about what a wrong label on a metric costs. FOUND WHILE BUILDING: CORR-001 and CORR-002, both in correlation.py, both recorded in QA Results. 36 new tests. Mutation testing: 15 injected, 14 killed, 1 verified benign.</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -25467,6 +25466,154 @@
       <c r="G106" s="76" t="inlineStr">
         <is>
           <t>tests/security/ (unchanged, all passing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="150" customHeight="1" s="59">
+      <c r="A107" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-42</t>
+        </is>
+      </c>
+      <c r="B107" s="76" t="inlineStr">
+        <is>
+          <t>E14-S10</t>
+        </is>
+      </c>
+      <c r="C107" s="76" t="inlineStr">
+        <is>
+          <t>The four acceptance criteria, plus the signed-exposure case they do not name</t>
+        </is>
+      </c>
+      <c r="D107" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E107" s="76" t="inlineStr">
+        <is>
+          <t>AC1 asserted twice: once verbatim at the AC's own 35% sector (where the risk budget still binds and the property holds anyway), and once at 36% where the headroom is genuinely the smallest constraint and the new code does the work. Stating only the first would have passed without the story being built.</t>
+        </is>
+      </c>
+      <c r="F107" s="76" t="inlineStr">
+        <is>
+          <t>AC2's real content is the SIGN. A short into a 2,90,000 net-long book has 5,90,000 of room, not 10,000 - it moves the book toward flat. Mutation M2 (sign inverted) and M3 (abs() applied) both killed by that case alone.</t>
+        </is>
+      </c>
+      <c r="G107" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_sizer.py - TestS10Ac1..Ac4, 24 tests. Mutations M1-M12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="150" customHeight="1" s="59">
+      <c r="A108" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-43</t>
+        </is>
+      </c>
+      <c r="B108" s="76" t="inlineStr">
+        <is>
+          <t>E14-S10</t>
+        </is>
+      </c>
+      <c r="C108" s="76" t="inlineStr">
+        <is>
+          <t>CORR-001: pearson could raise ZeroDivisionError despite its zero-variance guard</t>
+        </is>
+      </c>
+      <c r="D108" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E108" s="76" t="inlineStr">
+        <is>
+          <t>The guard rejects a variance of zero, and the division then used sqrt(var_l * var_r). The PRODUCT of two strictly positive variances can underflow to 0.0: var_l 9.667e-293 and var_r 3.611e-34 are both comfortably positive and their product is not representable. Guarding the operands does not guard the expression.</t>
+        </is>
+      </c>
+      <c r="F108" s="76" t="inlineStr">
+        <is>
+          <t>Found by this file's own property test during E14-S10, not by the story. It mattered because correlations_against catches CorrelationError and ONLY that, deliberately - an uncomputable pair is absent and read as unknown. A ZeroDivisionError is not a CorrelationError, so it escaped the loop and turned 'one pair could not be computed' into 'the whole row failed', reported as RISK_ENGINE_FAULT. Not reachable from real prices: a log return of 1e-146 cannot arise from Decimal closes at four decimal places. Fixed because the function's contract is to return a value in [-1, 1] or raise CorrelationError, and it did neither.</t>
+        </is>
+      </c>
+      <c r="G108" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_correlation.py TestTheDenominatorCannotUnderflowToZero - 10 tests including a meta-assertion that the chosen inputs really do get PAST the zero-variance guard, and a case whose true correlation is exactly 1.0 that the old spelling would have refused. Mutations M13, M14 (M14 verified benign).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="150" customHeight="1" s="59">
+      <c r="A109" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-44</t>
+        </is>
+      </c>
+      <c r="B109" s="76" t="inlineStr">
+        <is>
+          <t>E14-S10</t>
+        </is>
+      </c>
+      <c r="C109" s="76" t="inlineStr">
+        <is>
+          <t>CORR-002: a property test asserting a property outside the domain where it holds</t>
+        </is>
+      </c>
+      <c r="D109" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E109" s="76" t="inlineStr">
+        <is>
+          <t>test_it_is_invariant_to_positive_scaling_and_shift drew returns from st.floats(-0.2, 0.2), which also admits values like 1e-160. A series of those has a variance so small that rho is computed from pure rounding noise, and a sweep of that band finds the invariance error reaching 1.0 - rho flipping between 0 and +/-1 on a rescale.</t>
+        </is>
+      </c>
+      <c r="F109" s="76" t="inlineStr">
+        <is>
+          <t>The honest attribution matters: the test had been falsifiable since it was written, and a 20,000-case sweep shows 4,335 violations under the OLD denominator too. CORR-001's fix made three times as many of those inputs computable rather than refused, which raised the chance of drawing one - it increased exposure to the weakness rather than introducing it. Verified by running both spellings over the same band rather than assuming.</t>
+        </is>
+      </c>
+      <c r="G109" s="76" t="inlineStr">
+        <is>
+          <t>The STRATEGY was bounded to magnitudes a real daily log return takes, keeping exact 0.0 for a genuinely flat day. Not the tolerance: a 0.02% move is a real market day and 1e-160 is not any market day, and a tolerance wide enough for noise would stop catching the catastrophic-cancellation bug the test exists for. Stable across five consecutive runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="150" customHeight="1" s="59">
+      <c r="A110" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-45</t>
+        </is>
+      </c>
+      <c r="B110" s="76" t="inlineStr">
+        <is>
+          <t>E14-S10</t>
+        </is>
+      </c>
+      <c r="C110" s="76" t="inlineStr">
+        <is>
+          <t>Phase 7 on the story's own diff: a fifth log-forgery site</t>
+        </is>
+      </c>
+      <c r="D110" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E110" s="76" t="inlineStr">
+        <is>
+          <t>The story adds a path that interpolates OpenPosition.symbol into an exception message. That field carries NO validator - unlike Trigger, Recommendation and OrderRequest, each of which gained _validate_symbol only after forgery was found on it. It arrives from the position store, which is fed by the broker.</t>
+        </is>
+      </c>
+      <c r="F110" s="76" t="inlineStr">
+        <is>
+          <t>RiskDecision.detail escapes it downstream (QA-SEC-38), and that is not enough: the same exception reaches log.exception's traceback, which the model validator never sees. Escaping at the point of interpolation is the rung above relying on a downstream consumer. one_safe_line also bounds the LENGTH, which taking the first eight symbols does not - eight unbounded symbols is exactly how QA-SEC-29 produced an 80,054-character detail from a line that looked capped.</t>
+        </is>
+      </c>
+      <c r="G110" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_sizer.py TestS10AnUntrustedSymbolCannotForgeALogLine - 4 tests, with assertions built from chr() so no quoting between the editor and the file can turn a real newline into its escape. Mutation M15 killed.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X200"/>
+  <dimension ref="A1:X201"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="E125" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F125" s="41" t="inlineStr">
@@ -15014,7 +15014,9 @@
       <c r="N125" s="45" t="n"/>
       <c r="O125" s="46" t="n"/>
       <c r="P125" s="46" t="n"/>
-      <c r="Q125" s="47" t="n"/>
+      <c r="Q125" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R125" s="39" t="n">
         <v>4</v>
       </c>
@@ -15032,7 +15034,11 @@
           <t>• 🔴 Concurrent signals cannot over-allocate slots</t>
         </is>
       </c>
-      <c r="V125" s="48" t="n"/>
+      <c r="V125" s="48" t="inlineStr">
+        <is>
+          <t>DELIVERED 7 Sep 2026, SPLIT. Tasks 1, 3 and 4 delivered as execution/slots.py; task 2 (priority queue) split out as E14-S11 because it is not buildable - see below. WHAT WAS ALREADY THERE, found in Phase 0 and worth recording because the tracker did not say so: PositionRepository.open_position already claimed a slot in one statement, occupied_slots() already existed, and uq_open_slot - a partial unique index on status='OPEN' - was already the guarantee. The story's real content was therefore the COMPONENT THAT COMPOSES them, which did not exist: nothing chose a free index, took the lock, or reconciled the two stores, and RiskContext.slots_total/slots_used were populated by nobody. THE DESIGN: EPIC01 8.4's three layers in order of cost - ask the database which slots are open, take a short-lived Redis lock on a free index, and let uq_open_slot be the guarantee underneath. REJECTED ALTERNATIVE: holding the Redis lock for the life of the position, which the key name lock:slot:{index} invites. Positions live for hours and MAX_TTL_MS is 300 seconds, so such a lock must either expire mid-position - meaningless as a claim while still looking like one - or be renewed by a heartbeat that goes quiet exactly when the process dies. The database row holds the slot; the lock only guards the window between choosing an index and inserting the row. RECONCILIATION reports three categories separately because they have three costs: a leaked lock (self-healing, every lock has a TTL), a stale record (never heals - the hash has no TTL, so the slot reads as occupied for the rest of the session), and a missing record (the dangerous direction - occupancy understated). 40 unit tests plus 13 Docker-gated integration tests. The AC is inherently a race between Redis and Postgres, so it is proved in the integration tier and verified by CI, which pre-pulls both images and runs the full suite.</t>
+        </is>
+      </c>
       <c r="W125" s="49" t="n"/>
     </row>
     <row r="126" ht="30" customHeight="1" s="59">
@@ -20757,6 +20763,93 @@
           <t>DELIVERED 7 Sep 2026. The two portfolio caps now BIND. max_sector_exposure_pct (40) and max_net_directional_exposure_pct (60) had been in system.yaml since the beginning and were enforced by nothing. WHERE IT LANDED: execution/sizer.py, as two more entries in the existing min() clamp set, because the sizer is the only component that knows the quantity and already records which clamp bound. THE ARITHMETIC, and the part that is not obvious: sector exposure is UNSIGNED (a sector shock moves every name in it, so a short in that sector is exposed to the same event), while net directional is SIGNED, so the room available depends on which way the book already leans. One expression covers both directions: headroom = cap - sign * net, with sign +1 for a long and -1 for a short. A formula that ignored the sign would refuse the short that REDUCES directional risk while permitting the long that makes the book worse; that case is asserted directly. FAIL-CLOSED: the sizer refuses if the candidate has no sector, or if any open position is unclassified - a sector total computed over an incomplete book is too SMALL, which makes the headroom too LARGE and the clamp too LOOSE. Repeated in the sizer rather than assumed from check 9, which is the AUDIT-005 lesson: a component must not depend on a particular engine having been assembled with a particular check. REASON CODES: a zero quantity from either clamp reports SECTOR_EXPOSURE_LIMIT or NET_EXPOSURE_LIMIT, not POSITION_TOO_SMALL - the SIT-001 lesson about what a wrong label on a metric costs. FOUND WHILE BUILDING: CORR-001 and CORR-002, both in correlation.py, both recorded in QA Results. 36 new tests. Mutation testing: 15 injected, 14 killed, 1 verified benign.</t>
         </is>
       </c>
+    </row>
+    <row r="201" ht="150" customHeight="1" s="59">
+      <c r="A201" s="38" t="inlineStr">
+        <is>
+          <t>E14-S11</t>
+        </is>
+      </c>
+      <c r="B201" s="39" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="C201" s="40" t="inlineStr">
+        <is>
+          <t>RISK ENGINE</t>
+        </is>
+      </c>
+      <c r="D201" s="40" t="inlineStr">
+        <is>
+          <t>Signal priority queue when candidates exceed free slots</t>
+        </is>
+      </c>
+      <c r="E201" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F201" s="41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G201" s="39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H201" s="51" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I201" s="39" t="inlineStr">
+        <is>
+          <t>FEAT</t>
+        </is>
+      </c>
+      <c r="J201" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" s="40" t="inlineStr">
+        <is>
+          <t>E12, E13, E14-S08</t>
+        </is>
+      </c>
+      <c r="L201" s="40" t="inlineStr">
+        <is>
+          <t>E12 (no expectancy), E13 (no signal score)</t>
+        </is>
+      </c>
+      <c r="M201" s="44" t="n"/>
+      <c r="N201" s="45" t="n"/>
+      <c r="O201" s="44" t="n"/>
+      <c r="P201" s="44" t="n"/>
+      <c r="Q201" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="S201" s="48" t="n"/>
+      <c r="T201" s="48" t="inlineStr">
+        <is>
+          <t>1. Rank candidate signals by score, then by expectancy 2. Feed the ranked order into SlotManager.claiming so the best candidates take the scarce slots 3. Record the ranking in the audit log so a passed-over signal is explainable</t>
+        </is>
+      </c>
+      <c r="U201" s="48" t="inlineStr">
+        <is>
+          <t>AC1 With more candidates than free slots, the slots go to the highest-ranked candidates and the rest are refused with a reason naming the rank. AC2 (CONTROL) With fewer candidates than free slots, ranking changes nothing and every candidate is allocated. AC3 Ranking is deterministic - the same candidate set produces the same order on every run, so a session replays identically.</t>
+        </is>
+      </c>
+      <c r="V201" s="48" t="inlineStr">
+        <is>
+          <t>SPLIT OUT OF E14-S08 on 7 Sep 2026 because it cannot be built yet, and building it anyway would have meant inventing the number it ranks on. E14-S08 task 2 asked to order candidates by 'score, then expectancy'. NOTHING IN src/ COMPUTES AN EXPECTANCY: paper_min_expectancy_r is a configured THRESHOLD with no producer, and the only other mention is a docstring in indicators/levels.py. The signals package is empty, so there is no signal score either. Until then E14-S08 allocates first-come, which is honest: it is what the system can actually justify. A made-up ranking over real money is worse than no ranking, because it looks like a decision. This is recorded rather than silently dropped so that the gap between the story as written and the story as delivered is visible.</t>
+        </is>
+      </c>
+      <c r="W201" s="49" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:W197"/>
@@ -21524,7 +21617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -25614,6 +25707,117 @@
       <c r="G110" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_sizer.py TestS10AnUntrustedSymbolCannotForgeALogLine - 4 tests, with assertions built from chr() so no quoting between the editor and the file can turn a real newline into its escape. Mutation M15 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="150" customHeight="1" s="59">
+      <c r="A111" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-46</t>
+        </is>
+      </c>
+      <c r="B111" s="76" t="inlineStr">
+        <is>
+          <t>E14-S08</t>
+        </is>
+      </c>
+      <c r="C111" s="76" t="inlineStr">
+        <is>
+          <t>The acceptance criterion, and where it can honestly be proved</t>
+        </is>
+      </c>
+      <c r="D111" s="76" t="inlineStr">
+        <is>
+          <t>PASS (CI)</t>
+        </is>
+      </c>
+      <c r="E111" s="76" t="inlineStr">
+        <is>
+          <t>'Concurrent signals cannot over-allocate slots' is a race between a Redis SET NX PX, a partial unique index, and reconciliation between them. It cannot be proved with doubles, so it is proved in tests/integration/test_slot_allocation.py against a real Redis and a real Postgres: 12 concurrent claimers against 5 slots, every allocation distinct, the surplus refused.</t>
+        </is>
+      </c>
+      <c r="F111" s="76" t="inlineStr">
+        <is>
+          <t>Docker is unavailable locally, so these 13 tests skip here and run in CI, which pre-pulls both images and runs the full suite. Verified from the workflow itself rather than assumed - the story would not have been startable had CI not run them, since its only AC needs both containers.</t>
+        </is>
+      </c>
+      <c r="G111" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_slot_allocation.py (13) + tests/unit/test_slots.py (40). Mutation testing on the unit tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="150" customHeight="1" s="59">
+      <c r="A112" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-47</t>
+        </is>
+      </c>
+      <c r="B112" s="76" t="inlineStr">
+        <is>
+          <t>E14-S08</t>
+        </is>
+      </c>
+      <c r="C112" s="76" t="inlineStr">
+        <is>
+          <t>Each concurrent claimer needs its own session</t>
+        </is>
+      </c>
+      <c r="D112" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E112" s="76" t="inlineStr">
+        <is>
+          <t>The first draft of the concurrency tests shared one AsyncSession across 12 coroutines. An AsyncSession wraps one connection and is not safe to use from two coroutines at once, so the test would have failed on SQLAlchemy's own concurrency guard rather than on the slot race - a red test proving nothing about slots.</t>
+        </is>
+      </c>
+      <c r="F112" s="76" t="inlineStr">
+        <is>
+          <t>Caught by review before pushing, not by a run: the tests are Docker-gated and skip locally, so the loop that would normally catch this was not available. Worth recording as the cost of a tier that cannot run on the development machine.</t>
+        </is>
+      </c>
+      <c r="G112" s="76" t="inlineStr">
+        <is>
+          <t>Each claimer now opens its own session from the engine, which is also what the real system does - two signals are two units of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="150" customHeight="1" s="59">
+      <c r="A113" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-48</t>
+        </is>
+      </c>
+      <c r="B113" s="76" t="inlineStr">
+        <is>
+          <t>E14-S08</t>
+        </is>
+      </c>
+      <c r="C113" s="76" t="inlineStr">
+        <is>
+          <t>Two tests that could not fail, on the exact behaviour this story depends on</t>
+        </is>
+      </c>
+      <c r="D113" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E113" s="76" t="inlineStr">
+        <is>
+          <t>test_repositories.py::test_slot_collision_raises_and_is_catchable and test_e01_end_to_end.py both asserted pytest.raises((psycopg.errors.UniqueViolation, Exception)). Exception in a pytest.raises tuple matches ANYTHING - a typo, a connection failure, an AttributeError - so neither test could fail, while both read as though they pinned the exception type down.</t>
+        </is>
+      </c>
+      <c r="F113" s="76" t="inlineStr">
+        <is>
+          <t>It mattered here specifically. EPIC01 8.4 instructs callers to catch the unique violation and treat it as 'slot taken', and that instruction is only followable if the exception is identifiable. SQLAlchemy wraps every DBAPI error, so the psycopg type the spec names arrives as sqlalchemy.exc.IntegrityError with the original on .orig - catching the psycopg type alone would miss every real occurrence and turn the expected outcome into an unhandled crash during position opening.</t>
+        </is>
+      </c>
+      <c r="G113" s="76" t="inlineStr">
+        <is>
+          <t>Both now assert through is_slot_taken(), which walks the .orig and __cause__ chain and can narrow to a named constraint. The integration tier pins the real shape.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -21617,7 +21617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -25818,6 +25818,43 @@
       <c r="G113" s="76" t="inlineStr">
         <is>
           <t>Both now assert through is_slot_taken(), which walks the .orig and __cause__ chain and can narrow to a named constraint. The integration tier pins the real shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="150" customHeight="1" s="59">
+      <c r="A114" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-49</t>
+        </is>
+      </c>
+      <c r="B114" s="76" t="inlineStr">
+        <is>
+          <t>E14-S08</t>
+        </is>
+      </c>
+      <c r="C114" s="76" t="inlineStr">
+        <is>
+          <t>The acceptance-criterion test was wrong, and CI found it</t>
+        </is>
+      </c>
+      <c r="D114" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E114" s="76" t="inlineStr">
+        <is>
+          <t>The first version of the concurrency test held the lock across a sleep and never inserted anything. Against real containers it produced [0, 1, 2, 0, 3, 0, 2, 3, 1, 4, None, None] - slot 0 handed out three times - and the test read that as over-allocation.</t>
+        </is>
+      </c>
+      <c r="F114" s="76" t="inlineStr">
+        <is>
+          <t>It was the TEST that was wrong, not the allocator. `claiming` releases the lock on block exit by design; in real use the block performs the INSERT, and it is the committed row that holds the slot afterwards. A test that never inserts is therefore testing nothing about over-allocation - each slot was correctly freed and re-offered. The AC means 'twelve signals, five slots, at most five POSITIONS', which requires opening them. Found only when CI ran the Docker-gated tier, because Docker was not running locally. Docker Desktop was then started and the tier reproduced in seconds - the whole suite has since run with 0 skipped for the first time this session.</t>
+        </is>
+      </c>
+      <c r="G114" s="76" t="inlineStr">
+        <is>
+          <t>Rewritten so each claimer opens a real position on its own session and commits, catching the unique violation as EPIC01 8.4 requires. Verified to have teeth: removing the Redis lock fails it, and removing the database consultation fails four of its tests. Notably removing the lock alone breaks only ONE test, because uq_open_slot still refuses the duplicate - which is the three-layer design demonstrating itself.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -4530,7 +4530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X201"/>
+  <dimension ref="A1:X203"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="E126" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F126" s="41" t="inlineStr">
@@ -15100,7 +15100,9 @@
       <c r="N126" s="45" t="n"/>
       <c r="O126" s="46" t="n"/>
       <c r="P126" s="46" t="n"/>
-      <c r="Q126" s="47" t="n"/>
+      <c r="Q126" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R126" s="39" t="n">
         <v>5</v>
       </c>
@@ -15120,7 +15122,11 @@
 • 🔴 Open positions are not blindly market-closed</t>
         </is>
       </c>
-      <c r="V126" s="48" t="n"/>
+      <c r="V126" s="48" t="inlineStr">
+        <is>
+          <t>DELIVERED 8 Sep 2026, SPLIT. execution/halt.py holds the halt controller: tasks 2 (the auto-triggers that have real inputs), 3a (halts new entries) and 5 (human-only un-halt). Tasks 1 and 4 split out as E14-S12 and E14-S13. WHY IT MATTERED: control:killswitch had a reader that FAILS CLOSED and no writer at all, and AUDIT-005 had just made RiskContext's three halt fields mandatory with a comment naming this story as their owner. The largest gap in the audit's own live-failure matrix - 'the kill switch is armed by nothing' - is now closed. THE DESIGN: three separately persisted latches rather than one flag with a reason field. One flag would have been less code and would collapse three rejections into one, so an operator seeing HALTED would read prose to learn whether a loss limit or a manual stop did it - the SIT-001 mistake, and the same reasoning E14-S05 recorded when it chose two latch fields over one. ONLY A HUMAN CLEARS: clear() takes an OperatorAction, which cannot be constructed without a named operator, refuses names like 'system' and 'auto', and requires acknowledging what is being cleared. Construction validates, which is one rung above a runtime check - an automatic un-halt would require code that invents a person, a deliberate act visible in review rather than an omission. THE BUILD CONCERN ('halting must never disable the exit path') is structural: the controller holds a Redis client and nothing else, exposes no method containing close/liquidate/cancel/square, and imports nothing from the repository, broker or sizer paths. Three tests assert each. 42 unit tests + 15 against real Redis. Mutation: 16 injected, 16 killed.</t>
+        </is>
+      </c>
       <c r="W126" s="49" t="n"/>
       <c r="X126" s="75" t="inlineStr">
         <is>
@@ -20850,6 +20856,182 @@
         </is>
       </c>
       <c r="W201" s="49" t="n"/>
+    </row>
+    <row r="202" ht="150" customHeight="1" s="59">
+      <c r="A202" s="38" t="inlineStr">
+        <is>
+          <t>E14-S12</t>
+        </is>
+      </c>
+      <c r="B202" s="39" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="C202" s="40" t="inlineStr">
+        <is>
+          <t>RISK ENGINE</t>
+        </is>
+      </c>
+      <c r="D202" s="40" t="inlineStr">
+        <is>
+          <t>Halt triggers from a phone and a dashboard</t>
+        </is>
+      </c>
+      <c r="E202" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F202" s="41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G202" s="39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H202" s="51" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I202" s="39" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="J202" s="39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K202" s="40" t="inlineStr">
+        <is>
+          <t>E14-S09, E10 (notifier), E09 (api)</t>
+        </is>
+      </c>
+      <c r="L202" s="40" t="inlineStr">
+        <is>
+          <t>B5 (Telegram bot credential); notifier and api packages are empty</t>
+        </is>
+      </c>
+      <c r="M202" s="44" t="n"/>
+      <c r="N202" s="45" t="n"/>
+      <c r="O202" s="44" t="n"/>
+      <c r="P202" s="44" t="n"/>
+      <c r="Q202" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S202" s="48" t="n"/>
+      <c r="T202" s="48" t="inlineStr">
+        <is>
+          <t>1. Telegram command that arms the halt, authenticated to one chat id 2. Dashboard control that does the same 3. The 'AI unavailable' auto-trigger, once there is an AI client whose availability can be observed 4. Confirm round-trip latency against AC1</t>
+        </is>
+      </c>
+      <c r="U202" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) A halt is armed from a phone in under 10 seconds, measured end to end. AC2 Only an authorised chat id can arm or clear it. AC3 (CONTROL) An unauthenticated message changes nothing and is logged.</t>
+        </is>
+      </c>
+      <c r="V202" s="48" t="inlineStr">
+        <is>
+          <t>SPLIT OUT OF E14-S09 on 8 Sep 2026. The controller is built and accepts a MANUAL arm today; what is missing is the transport. Both packages it needs are empty (notifier/, api/) and it requires a real bot credential, which is blocker B5 - money/credentials, the escalation category. The 'AI unavailable' trigger is folded in here rather than stubbed in S09, because a trigger that watches an empty package reads as a live control while observing nothing. AC1 lives here because it cannot be measured without the transport.</t>
+        </is>
+      </c>
+      <c r="W202" s="49" t="n"/>
+      <c r="X202" s="75" t="n"/>
+    </row>
+    <row r="203" ht="150" customHeight="1" s="59">
+      <c r="A203" s="38" t="inlineStr">
+        <is>
+          <t>E14-S13</t>
+        </is>
+      </c>
+      <c r="B203" s="39" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="C203" s="40" t="inlineStr">
+        <is>
+          <t>RISK ENGINE</t>
+        </is>
+      </c>
+      <c r="D203" s="40" t="inlineStr">
+        <is>
+          <t>Operator command to close open positions</t>
+        </is>
+      </c>
+      <c r="E203" s="40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F203" s="41" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G203" s="39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H203" s="51" t="inlineStr">
+        <is>
+          <t>Safety-critical</t>
+        </is>
+      </c>
+      <c r="I203" s="39" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="J203" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" s="40" t="inlineStr">
+        <is>
+          <t>E14-S09, E15 (order gateway)</t>
+        </is>
+      </c>
+      <c r="L203" s="40" t="inlineStr">
+        <is>
+          <t>No order path exists to cancel or close through</t>
+        </is>
+      </c>
+      <c r="M203" s="44" t="n"/>
+      <c r="N203" s="45" t="n"/>
+      <c r="O203" s="44" t="n"/>
+      <c r="P203" s="44" t="n"/>
+      <c r="Q203" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S203" s="48" t="n"/>
+      <c r="T203" s="48" t="inlineStr">
+        <is>
+          <t>1. An explicit operator command that closes open positions, separate from arming a halt 2. Cancel resting orders when a halt is armed 3. Record ExitReason.KILLSWITCH against each position closed this way</t>
+        </is>
+      </c>
+      <c r="U203" s="48" t="inlineStr">
+        <is>
+          <t>AC1 (RED) Arming a halt closes NOTHING by itself - open positions are not blindly market-closed. AC2 The close command is a separate, explicitly confirmed action. AC3 The square-off timer keeps running throughout a halt, so a halted session still exits on its own terms before the broker's deadline.</t>
+        </is>
+      </c>
+      <c r="V203" s="48" t="inlineStr">
+        <is>
+          <t>SPLIT OUT OF E14-S09 on 8 Sep 2026. There is no order path, so there is nothing to cancel and nothing to close through. AC1 is already satisfied and asserted in E14-S09 as a NEGATIVE, structural property: the halt controller holds no position or order collaborator, exposes no method that could liquidate, and imports nothing from those paths. It is restated here because when this story adds the capability, that property stops being free and has to be defended deliberately. AC3 is E14-S09's recorded build concern: a kill switch tripped at 14:00 that also stopped the exit path would leave positions for the broker to close at 15:20 at whatever price exists.</t>
+        </is>
+      </c>
+      <c r="W203" s="49" t="n"/>
+      <c r="X203" s="75" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:W197"/>
@@ -21617,7 +21799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -25855,6 +26037,117 @@
       <c r="G114" s="76" t="inlineStr">
         <is>
           <t>Rewritten so each claimer opens a real position on its own session and commits, catching the unique violation as EPIC01 8.4 requires. Verified to have teeth: removing the Redis lock fails it, and removing the database consultation fails four of its tests. Notably removing the lock alone breaks only ONE test, because uq_open_slot still refuses the duplicate - which is the three-layer design demonstrating itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="150" customHeight="1" s="59">
+      <c r="A115" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-50</t>
+        </is>
+      </c>
+      <c r="B115" s="76" t="inlineStr">
+        <is>
+          <t>E14-S09</t>
+        </is>
+      </c>
+      <c r="C115" s="76" t="inlineStr">
+        <is>
+          <t>The halt controller, and the half of the story that could be built</t>
+        </is>
+      </c>
+      <c r="D115" s="76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E115" s="76" t="inlineStr">
+        <is>
+          <t>Tasks 2, 3a and 5 delivered. Three persisted latches with a record of why, when and by whom; idempotent arming where the FIRST reason wins; reads that fail closed on every error path including an unparseable record.</t>
+        </is>
+      </c>
+      <c r="F115" s="76" t="inlineStr">
+        <is>
+          <t>The acceptance criteria split with the tasks. AC1 ('from a phone in under 10 seconds') needs the transport and moved to E14-S12. AC2 ('open positions are not blindly market-closed') is satisfied here and asserted structurally rather than behaviourally - the controller cannot close anything, so the property holds by construction.</t>
+        </is>
+      </c>
+      <c r="G115" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_halt.py (42) + tests/integration/test_halt_persistence.py (15). Mutation: 16 injected, 16 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="150" customHeight="1" s="59">
+      <c r="A116" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-51</t>
+        </is>
+      </c>
+      <c r="B116" s="76" t="inlineStr">
+        <is>
+          <t>E14-S09</t>
+        </is>
+      </c>
+      <c r="C116" s="76" t="inlineStr">
+        <is>
+          <t>A dataclass field masquerading as a constant</t>
+        </is>
+      </c>
+      <c r="D116" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E116" s="76" t="inlineStr">
+        <is>
+          <t>OperatorAction.FORBIDDEN - the list of names that are not people - was annotated `Final` inside a frozen dataclass. An annotated assignment without ClassVar declares a FIELD with a default, so FORBIDDEN would have become a third constructor parameter.</t>
+        </is>
+      </c>
+      <c r="F116" s="76" t="inlineStr">
+        <is>
+          <t>A caller could then have passed their own empty allow-list and cleared a halt as 'system' - defeating the exact bypass the type exists to prevent, through the type's own constructor. Caught by mypy ('Need type argument for Final[...] with non-literal default in dataclass'), which is a typing message for what is really a safety defect.</t>
+        </is>
+      </c>
+      <c r="G116" s="76" t="inlineStr">
+        <is>
+          <t>ClassVar[frozenset[str]]. A test now asserts dataclasses.fields() returns exactly ['operator', 'acknowledged'], and mutation M9 restores the Final form and is killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="150" customHeight="1" s="59">
+      <c r="A117" s="76" t="inlineStr">
+        <is>
+          <t>QA-E14-52</t>
+        </is>
+      </c>
+      <c r="B117" s="76" t="inlineStr">
+        <is>
+          <t>E14-S09</t>
+        </is>
+      </c>
+      <c r="C117" s="76" t="inlineStr">
+        <is>
+          <t>A size bound whose test did not exercise it</t>
+        </is>
+      </c>
+      <c r="D117" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E117" s="76" t="inlineStr">
+        <is>
+          <t>test_an_oversized_record_is_treated_as_unreadable padded with 'x', which is not valid JSON - so the parse failure rejected the record and the size bound was never reached. A mutation removing the bound survived.</t>
+        </is>
+      </c>
+      <c r="F117" s="76" t="inlineStr">
+        <is>
+          <t>Same shape as E14-S08's describe() hole: the test asserted the OUTCOME the bound produces without isolating the bound as its cause. Any of several guards could have produced it.</t>
+        </is>
+      </c>
+      <c r="G117" s="76" t="inlineStr">
+        <is>
+          <t>The probe is now oversized but valid JSON, with an assertion that it parses - so the only thing that can reject it is the bound. Plus a control just under the limit, because a bound that rejects everything would make every halt unreadable and lose the reason on every restart.</t>
         </is>
       </c>
     </row>
@@ -25875,7 +26168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -27825,6 +28118,48 @@
       <c r="H47" s="76" t="inlineStr">
         <is>
           <t>tests/security/test_safety_invariants.py TestSessionRiskStateIsNeverAssumed - 16 tests: each of the six omitted one at a time through the REAL engine (not the check functions, since the engine is what turns a raise into a refusal), the armed/degraded/latched controls proving the checks still do their job, a structural test reading the dataclass so a re-added default is caught even if every caller still passes the value, and a control asserting a fully stated healthy session still APPROVES with a real quantity. Mutations M1-M10 all killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="150" customHeight="1" s="59">
+      <c r="A48" s="76" t="inlineStr">
+        <is>
+          <t>KEYS-001</t>
+        </is>
+      </c>
+      <c r="B48" s="76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C48" s="76" t="inlineStr">
+        <is>
+          <t>Redis keyspace / guardrail integrity</t>
+        </is>
+      </c>
+      <c r="D48" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E48" s="76" t="inlineStr">
+        <is>
+          <t>keys.py's docstring says 'No key string literal may appear anywhere else in the codebase... it is enforced by a test that enumerates the builders.' The test checked one direction only - that every name in ALL_BUILDERS is callable. Nothing checked that every defined builder is listed, and nothing at all checked for key literals elsewhere.</t>
+        </is>
+      </c>
+      <c r="F48" s="76" t="inlineStr">
+        <is>
+          <t>Two builders had already slipped through: data_rate_limit and broker_session were defined and absent from the tuple, invisible to the very check meant to enumerate the keyspace. The consequence is spelled out in that same docstring: a typo'd key does not raise, it silently reads None - 'no position', 'no plan', 'kill switch not set'. Found while adding a halt-latch builder, which made it immediate: the guardrail meant to keep kill-switch keys honest did not work.</t>
+        </is>
+      </c>
+      <c r="G48" s="76" t="inlineStr">
+        <is>
+          <t>The test now asserts both directions, and ALL_BUILDERS is complete. The docstring's stronger claim - that no key literal exists elsewhere in the codebase - remains unenforced and is now stated as such rather than asserted; raising it as its own check would need an AST sweep over every module and is not this story.</t>
+        </is>
+      </c>
+      <c r="H48" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_redis_layer.py::test_every_builder_is_declared, which fails today against the pre-fix tuple.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E127" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F127" s="41" t="inlineStr">
@@ -15193,7 +15193,9 @@
       <c r="N127" s="45" t="n"/>
       <c r="O127" s="46" t="n"/>
       <c r="P127" s="46" t="n"/>
-      <c r="Q127" s="47" t="n"/>
+      <c r="Q127" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R127" s="39" t="n">
         <v>5</v>
       </c>
@@ -15207,8 +15209,16 @@
 5. Rate limiter integration</t>
         </is>
       </c>
-      <c r="U127" s="48" t="n"/>
-      <c r="V127" s="48" t="n"/>
+      <c r="U127" s="48" t="inlineStr">
+        <is>
+          <t>WRITTEN 8 Sep 2026 — the story shipped with none, and 'build OrderRequest from RiskDecision' is not falsifiable as stated. AC1 (RED) An approved decision becomes exactly one OrderRequest carrying the sizer's quantity, the deterministic client_order_id, the SEBI algo_id and market protection; a decision that is NOT approved produces no order at all. AC2 (RED) The client_order_id satisfies LOW_LEVEL 8.2: the same logical decision always produces the same id, each of the five components changes it, and no two different decisions share one. AC3 Submission is rate-limited, and a refusal never reaches the broker. AC4 (CONTROL) An ordinary approved decision produces exactly one submitted order and returns the broker's id.</t>
+        </is>
+      </c>
+      <c r="V127" s="48" t="inlineStr">
+        <is>
+          <t>DELIVERED 8 Sep 2026. execution/gateway.py. THE KEYSTONE: until this, an approved RiskDecision could not become an order, which is the single fact every status report in this project has led with. WHAT WAS MISSING AND NOT OBVIOUS: client_order_id was CONSUMED in three places (broker_tag, find_by_client_order_id, AmbiguousOrderError) and GENERATED nowhere. OrderRequest.algo_id was annotated 'attached by the gateway' with no gateway to attach it. THE TICK RESOLVER, this story's recorded loose end, is wired: E02 left KiteTradingAdapter refusing every priced order with NO_TICK_RESOLVER until a resolver was connected. The build concern said the repository 'already holds the per-instrument tick size' - the TABLE does, the REPOSITORY did not: refresh_cache cached only id &lt;-&gt; tradingsymbol. Added a synchronous InstrumentRepository.tick_size that raises rather than defaulting, because 0.05 is right often enough to hide the times it is not. Synchronous deliberately: the adapter's tick_size_for is a plain callable and making it async would change a contract already under test. SCOPE: the gateway does NOT hold the resolver - its entry order is MARKET and carries no price. Holding one would have looked like wiring while being none. The wiring is KiteTradingAdapter(tick_size_for=instruments.tick_size), asserted end to end against a real Postgres with two DIFFERENT tick sizes so a hardcoded constant fails. 30 unit tests + 10 integration. Mutation: 16 injected, 16 killed.</t>
+        </is>
+      </c>
       <c r="W127" s="49" t="n"/>
       <c r="X127" t="inlineStr">
         <is>
@@ -15293,7 +15303,11 @@
           <t>• 🔴 Chaos test: timeout + reconnect produces exactly one order</t>
         </is>
       </c>
-      <c r="V128" s="48" t="n"/>
+      <c r="V128" s="48" t="inlineStr">
+        <is>
+          <t>BOUNDARY CORRECTED 8 Sep 2026 while delivering E15-S01. Task 1 (the sha256 formula) moved to E15-S01 and is DONE. Two reasons: LOW_LEVEL 5.7 assigns 'generates the deterministic client_order_id' to the OrderGateway, and S01 structurally cannot build an OrderRequest without one - client_order_id is a required field with min_length=8. A story cannot depend on a later story for a field its own output requires. WHAT REMAINS HERE, and it is the part with the RED acceptance criterion: task 2 (persist the id BEFORE submission) and task 3 (on ambiguous failure, query by client_order_id and never retry), plus the chaos test that a timeout and reconnect produce exactly one order. THE BUILD CONCERN IS ANSWERED, and the answer is recorded in execution/gateway.py's docstring: the discriminator that prevents a deliberate re-entry being suppressed as a duplicate already exists - it is correlation_id, which is minted per SIGNAL, not per symbol-day. Two entries into one symbol on one day are two signals with two ids and do not collide; a retry of one decision reuses its id and does, which is the idempotency the key exists for. Asserted in tests/unit/test_gateway.py rather than assumed. RESIDUAL RISK, recorded where it would bite: if correlation ids are ever reused across signals, this key silently suppresses real orders.</t>
+        </is>
+      </c>
       <c r="W128" s="49" t="n"/>
       <c r="X128" s="75" t="inlineStr">
         <is>
@@ -21799,7 +21813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -26148,6 +26162,117 @@
       <c r="G117" s="76" t="inlineStr">
         <is>
           <t>The probe is now oversized but valid JSON, with an assertion that it parses - so the only thing that can reject it is the bound. Plus a control just under the limit, because a bound that rejects everything would make every halt unreadable and lose the reason on every restart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="150" customHeight="1" s="59">
+      <c r="A118" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-01</t>
+        </is>
+      </c>
+      <c r="B118" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01</t>
+        </is>
+      </c>
+      <c r="C118" s="76" t="inlineStr">
+        <is>
+          <t>The story had no acceptance criteria</t>
+        </is>
+      </c>
+      <c r="D118" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E118" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01 listed five tasks and zero acceptance criteria. 'Build OrderRequest from RiskDecision' describes an activity, not an outcome that can be false.</t>
+        </is>
+      </c>
+      <c r="F118" s="76" t="inlineStr">
+        <is>
+          <t>Phase 1's exit gate requires falsifiable criteria, so four were written and recorded on the story before any code. Two are RED (safety-critical): the approved-to-order mapping, and the 8.2 idempotency key. Writing them first is what surfaced that a REJECTED decision must produce NO order - the single most important behaviour here, and one no task mentioned.</t>
+        </is>
+      </c>
+      <c r="G118" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py, organised by AC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="150" customHeight="1" s="59">
+      <c r="A119" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-02</t>
+        </is>
+      </c>
+      <c r="B119" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01</t>
+        </is>
+      </c>
+      <c r="C119" s="76" t="inlineStr">
+        <is>
+          <t>The build concern was right about the loose end and wrong about the fix</t>
+        </is>
+      </c>
+      <c r="D119" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E119" s="76" t="inlineStr">
+        <is>
+          <t>The concern said to connect the adapter's tick resolver to the instrument repository, 'which already holds the per-instrument tick size from E02-S06's sync'. The TABLE holds it. The REPOSITORY did not expose it - refresh_cache selected only id and tradingsymbol, and there was no tick_size accessor at all.</t>
+        </is>
+      </c>
+      <c r="F119" s="76" t="inlineStr">
+        <is>
+          <t>A capability check caught it before any design was built on the assumption: does the thing being consumed actually produce what is planned to be read? Reading the repository rather than trusting the note is what turned a one-line wiring job into the accessor it actually needed.</t>
+        </is>
+      </c>
+      <c r="G119" s="76" t="inlineStr">
+        <is>
+          <t>InstrumentRepository.tick_size, synchronous and raising on a cache miss. tests/integration/test_gateway_wiring.py proves it end to end with two different tick sizes; mutations M15 (default 0.05 instead of raising) and M16 (stop loading them) both killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="150" customHeight="1" s="59">
+      <c r="A120" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-03</t>
+        </is>
+      </c>
+      <c r="B120" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01</t>
+        </is>
+      </c>
+      <c r="C120" s="76" t="inlineStr">
+        <is>
+          <t>A guard that was already unrepresentable one rung higher</t>
+        </is>
+      </c>
+      <c r="D120" s="76" t="inlineStr">
+        <is>
+          <t>PASS (noted)</t>
+        </is>
+      </c>
+      <c r="E120" s="76" t="inlineStr">
+        <is>
+          <t>A test was written expecting the gateway to refuse an approved decision carrying no sizing. RiskDecision refused first - the model validates that an approved decision must carry sizing.</t>
+        </is>
+      </c>
+      <c r="F120" s="76" t="inlineStr">
+        <is>
+          <t>Worth recording rather than deleting: the gateway's own check can never fire against a valid RiskDecision, so it is defence in depth against a future model change rather than a live control. The test now asserts the rung that actually holds, which is the stronger claim.</t>
+        </is>
+      </c>
+      <c r="G120" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::test_an_approval_with_no_sizing_cannot_even_be_constructed</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -18684,7 +18684,7 @@
       </c>
       <c r="E173" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Cancelled - not applicable</t>
         </is>
       </c>
       <c r="F173" s="41" t="inlineStr">
@@ -18720,7 +18720,9 @@
       <c r="N173" s="45" t="n"/>
       <c r="O173" s="46" t="n"/>
       <c r="P173" s="46" t="n"/>
-      <c r="Q173" s="47" t="n"/>
+      <c r="Q173" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R173" s="39" t="n">
         <v>0</v>
       </c>
@@ -18729,7 +18731,9 @@
       <c r="U173" s="48" t="n"/>
       <c r="V173" s="48" t="inlineStr">
         <is>
-          <t>Attach per the confirmed mechanic; verify present on every order.</t>
+          <t>CANCELLED 9 Sep 2026, not deferred. The story assumed an Algo-ID must be attached to every order. It must not, at this operating profile: SEBI requires registration only AT OR ABOVE 10 orders/sec (circular 4 Feb 2025, clause I(c)), so a sub-threshold self-developed algo has no registered Algo-ID and the broker/exchange applies a generic identifier. kiteconnect documents algo_id as optional, default None. See blocker B1.
+WHAT THE CODEBASE CARRIES INSTEAD, and it is enough: OrderRequest.algo_id is str|None and KiteTradingAdapter omits the parameter when unset rather than sending an empty string; config.py requires broker.algo_id in LIVE mode only at or above SEBI_ALGO_REGISTRATION_OPS, guarded at import time against MAX_ORDERS_PER_SECOND ever being raised to meet it; and SIT-14 asserts both halves across a full session - a configured id reaches every one of 316 orders, and the real configuration sends none.
+REOPEN ONLY IF the order-rate cap is raised to 10+, or SEBI extends registration below the threshold.</t>
         </is>
       </c>
       <c r="W173" s="49" t="n"/>
@@ -21201,17 +21205,17 @@
       </c>
       <c r="C5" s="48" t="inlineStr">
         <is>
-          <t>E02-S04, E21-S01</t>
+          <t>Nothing. E21-S01 cancelled; E02-S04 unblocked</t>
         </is>
       </c>
       <c r="D5" s="48" t="inlineStr">
         <is>
-          <t>Research resolved the mechanic. Under SEBI's Feb 2025 circular (effective 1 Apr 2026) a self-developed personal algo under 10 OPS needs no separate exchange registration and the broker handles Strategy-ID tagging. Every algo order must carry an exchange-issued unique identifier, which the broker assigns during registration (format e.g. ALGO_XX_001). The process for a self-developed algo is a plain-English description of the strategy to the broker's compliance desk plus a mandatory mock trading session, usually on a Saturday, to show the algo does not loop or spam. Code already sends algo_id only when configured, which is the right shape. What remains is paperwork with Zerodha and needs your account.</t>
+          <t>NONE. The question was malformed: it asked HOW an Algo-ID is attached, and the answer is that at this system's operating profile there is none to attach. No email to Zerodha was needed or sent.</t>
         </is>
       </c>
       <c r="E5" s="40" t="inlineStr">
         <is>
-          <t>Active - mechanic understood, registration needs you</t>
+          <t>CLOSED 9 Sep 2026 - NOT APPLICABLE</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -21222,10 +21226,12 @@
       <c r="G5" s="46" t="n"/>
       <c r="H5" s="49" t="inlineStr">
         <is>
-          <t>NARROWED Aug 2026 from a design question to a one-line email.
-SEBI's framework: retail traders may run their own algorithms on their own account, and under 10 orders/sec no separate exchange registration is needed - the BROKER handles the Strategy ID tagging. Zerodha's own compliance thread covers static IP, the 10 OPS cap and market protection in detail and never mentions algo_id at all.
-Working assumption: leave algo_id unset and Zerodha tags it. The code already reflects this - it is sent only when configured, and an empty value means let-the-broker-tag-it, not forgot. BrokerConfig.algo_id being optional was already correct.
-This is inference from absence, so it still wants one confirmation before live. Not a design blocker.</t>
+          <t>CLOSED 9 Sep 2026 by primary-source research, superseding the Aug 2026 narrowing that called this 'a one-line email'.
+THE FINDING: below SEBI's 10 orders/sec threshold a self-developed personal algo is NOT REGISTERED, so no Algo-ID is issued and there is nothing for the developer to obtain or attach - the order is tagged with a GENERIC identifier on the broker/exchange side.
+EVIDENCE, four independent lines: (1) SEBI/HO/MIRSD/MIRSD-PoD/P/CIR/2025/0000013 of 4 Feb 2025, clause I(c) - self-developed retail algos register 'only if they cross the specified order per second threshold'; clause I(d) - brokers categorise as algo orders those 'above the specified threshold'. (2) The apparent counter-clause II(b) ('all algo orders shall be tagged') sits under STOCK BROKER responsibilities, and I(b) scopes developer-side tagging to APIs 'extended by brokers to algo providers' - a personal algo is not an algo provider. (3) Zerodha's own Z-Connect summary of the NSE circular: orders 'tagged with generic ID (unregistered, &lt;=10 OPS)', and the only thing asked of the developer is a static IP dedicated to the API key. (4) The installed SDK: kiteconnect 5.2.1 documents place_order's algo_id as 'an optional algo ID to associate with the order', default None.
+RESIDUAL UNCERTAINTY, recorded honestly: NSE's FAQ of 3 Nov 2025 could not be fetched directly - NSE refuses non-Indian IPs, which is blocker B8. The NSE line is therefore via Zerodha's summary and secondary reporting rather than the source PDF. Zerodha's statement governs this account and is unambiguous. Re-read the FAQ from the VPS once B6 is done.
+WHAT THIS CHANGED IN THE CODE, and it is the part that mattered: common/config.py refused to load in LIVE mode without broker.algo_id. That gate failed CLOSED, so it was safe - but it would have blocked go-live PERMANENTLY on paperwork that is never issued. It is now conditional on execution.max_orders_per_second &gt;= SEBI_ALGO_REGISTRATION_OPS (10), with a module-level guard that refuses to import if MAX_ORDERS_PER_SECOND is ever raised to meet it - crossing that line is a change of REGULATORY REGIME, not of throughput. doctor.py now reports an unset algo_id as OK rather than as an outstanding task.
+WHAT DID NOT DISSOLVE: the static IP (B6). Mandatory at every order rate; orders from an unwhitelisted address are rejected outright. That is now the only outstanding SEBI item.</t>
         </is>
       </c>
     </row>
@@ -21813,7 +21819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -26273,6 +26279,119 @@
       <c r="G120" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_gateway.py::test_an_approval_with_no_sizing_cannot_even_be_constructed</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="150" customHeight="1" s="59">
+      <c r="A121" s="76" t="inlineStr">
+        <is>
+          <t>QA-B1-01</t>
+        </is>
+      </c>
+      <c r="B121" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01 / B1</t>
+        </is>
+      </c>
+      <c r="C121" s="76" t="inlineStr">
+        <is>
+          <t>A fail-closed gate on a requirement that does not exist</t>
+        </is>
+      </c>
+      <c r="D121" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E121" s="76" t="inlineStr">
+        <is>
+          <t>common/config.py refused to load in LIVE mode unless broker.algo_id was set, citing 'every algorithmic order must carry an exchange-assigned Algo-ID (SEBI, since 1 Apr 2026)'. Below SEBI's 10 orders/sec threshold no Algo-ID is ever issued, so the condition was unsatisfiable: the system would have refused to enter LIVE mode permanently, waiting on paperwork that does not exist. Every SIT run and every test passed throughout, because nothing had reason to construct a LIVE config.</t>
+        </is>
+      </c>
+      <c r="F121" s="76" t="inlineStr">
+        <is>
+          <t>THE DEFECT CLASS IS THE INTERESTING PART: this is not 'unknown became fine' - it is the opposite, a check that failed closed and was therefore invisible to every safety test in the suite. Fail-closed hid it. A gate whose condition can never be met is indistinguishable from a correct gate until the day you need to pass it, and that day is go-live. WHAT FOUND IT: reading the primary source rather than the note that summarised it. The Zerodha broker profile already carried the correct reading as a 'working assumption'; config.py carried the opposite as a hard rule; nothing compared them. THE LESSON RECORDED: a fail-closed check still needs a test that PASSES it, or its satisfiability is never exercised.</t>
+        </is>
+      </c>
+      <c r="G121" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_safety_invariants.py::TestLiveModeRequiresCompliance - now asserts a LIVE config loads with an empty algo_id, that it is refused at or above the threshold, and that MAX_ORDERS_PER_SECOND stays below it. tests/unit/test_gateway.py and SIT-14's test_the_real_configuration_sends_no_algo_id_and_that_is_correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="150" customHeight="1" s="59">
+      <c r="A122" s="76" t="inlineStr">
+        <is>
+          <t>QA-B1-02</t>
+        </is>
+      </c>
+      <c r="B122" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01 / B1</t>
+        </is>
+      </c>
+      <c r="C122" s="76" t="inlineStr">
+        <is>
+          <t>Six documents asserted a requirement that does not apply</t>
+        </is>
+      </c>
+      <c r="D122" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E122" s="76" t="inlineStr">
+        <is>
+          <t>ARCHITECTURE_RESEARCH listed 'an exchange-assigned Algo-ID on every order' as one of four architectural constraints; INDIA_FEATURES said the order-placement module must attach one; MVP_UI_AND_LEGAL made it legal requirement L-1; MASTER_REFERENCE, PRE_LIVE_CHECKLIST and BACKLOG all carried B1 as an open question to email Zerodha about. LOW_LEVEL_ARCHITECTURE 5.7 assigned the gateway the job of 'attaching the SEBI algo_id' unconditionally.</t>
+        </is>
+      </c>
+      <c r="F122" s="76" t="inlineStr">
+        <is>
+          <t>Documents agreeing with each other is not corroboration when they share an ancestor - all six trace to one early reading of the SEBI framework, and the error propagated by citation rather than by re-derivation. The correction was applied to every one of them IN THE SAME COMMIT as the code, per the sign-off rule, and each correction states what it previously said so a reader who remembers the old claim can see it was retired deliberately rather than quietly dropped.</t>
+        </is>
+      </c>
+      <c r="G122" s="76" t="inlineStr">
+        <is>
+          <t>No test - documentation. Verified by grep sweep for algo_id / Algo-ID across Documents/ and Code/*.md; every remaining occurrence now states the rate-conditional rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="150" customHeight="1" s="59">
+      <c r="A123" s="76" t="inlineStr">
+        <is>
+          <t>QA-B1-03</t>
+        </is>
+      </c>
+      <c r="B123" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01 / B1</t>
+        </is>
+      </c>
+      <c r="C123" s="76" t="inlineStr">
+        <is>
+          <t>The order-rate cap was documented as throttling, not as regime selection</t>
+        </is>
+      </c>
+      <c r="D123" s="76" t="inlineStr">
+        <is>
+          <t>PASS (strengthened)</t>
+        </is>
+      </c>
+      <c r="E123" s="76" t="inlineStr">
+        <is>
+          <t>MAX_ORDERS_PER_SECOND = 5 was described as a SEBI-safe margin and a broker throttling concern. It is doing more than that: it is the single control that keeps this system out of the algo-registration regime entirely. Nothing recorded that raising it would change the regulatory obligations, not just the throughput.</t>
+        </is>
+      </c>
+      <c r="F123" s="76" t="inlineStr">
+        <is>
+          <t>Moved one rung up the structure-over-discipline ladder. A comment saying 'stay under 10' became an import-time guard: common/config.py raises RuntimeError if MAX_ORDERS_PER_SECOND &gt;= SEBI_ALGO_REGISTRATION_OPS, so a future edit that crosses the threshold fails at import rather than at 09:15 with an unregistered algo placing orders. The constant is now named after what it is rather than appearing as a bare 10 in three error messages.</t>
+        </is>
+      </c>
+      <c r="G123" s="76" t="inlineStr">
+        <is>
+          <t>tests/security/test_safety_invariants.py::test_the_hard_cap_keeps_this_system_out_of_the_registration_regime and ::test_the_import_guard_refuses_a_cap_at_or_above_the_threshold.
+MUTATION: 10 injected, 9 killed. The first run scored 7/8 with the guard-deletion mutation SURVIVING - with the cap at 5 the guard never executes, so its condition and message were entirely unverified and a swapped operator would have been found on the one day it mattered. Fixed by extracting the guard into _assert_below_registration_threshold(cap, threshold), which is reachable by a test; deleting its body and flipping its &gt;= to &gt; are now both killed.
+ONE SURVIVOR REMAINS AND IS VERIFIED BENIGN: removing the CALL at import time. With the cap at 5 the call is a no-op, and the state it guards against is already caught in CI by the invariant test above - confirmed by M6, which raises the cap and dies on that test alone. Killing it would require asserting on module text rather than behaviour. Recorded, not chased - same shape as QA-E15-03.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15250,7 +15250,7 @@
       </c>
       <c r="E128" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F128" s="41" t="inlineStr">
@@ -15286,7 +15286,9 @@
       <c r="N128" s="45" t="n"/>
       <c r="O128" s="46" t="n"/>
       <c r="P128" s="46" t="n"/>
-      <c r="Q128" s="47" t="n"/>
+      <c r="Q128" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R128" s="39" t="n">
         <v>3</v>
       </c>
@@ -15300,12 +15302,22 @@
       </c>
       <c r="U128" s="48" t="inlineStr">
         <is>
-          <t>• 🔴 Chaos test: timeout + reconnect produces exactly one order</t>
+          <t>WRITTEN 10 Sep 2026 BEFORE any code. The story carried ONE criterion ("chaos test: timeout + reconnect produces exactly one order") for two remaining tasks, and that criterion is an outcome of the design rather than a description of it — it cannot be satisfied incrementally, so it cannot guide the build.
+AC1 (RED) The intent is recorded BEFORE the broker is called: a row with status SUBMITTING and no broker_order_id. Nothing is persisted for an order that is never sent — an unapproved decision or a rate-limiter refusal leaves no row, because a SUBMITTING row for an order that never existed would send reconciliation looking for it forever.
+AC2 (RED) Submitting the SAME decision twice produces exactly ONE broker call. If the first attempt recorded a broker id, that id is returned. If it died between persist and submit, the BROKER is queried by client_order_id and its answer adopted.
+AC3 (RED) An ambiguous broker failure NEVER retries. The gateway queries by client_order_id; if the order is there it is adopted; if it is genuinely absent a distinct error says so and the gateway does NOT resubmit on its own initiative.
+AC4 After a successful submission the row carries the broker id and is no longer SUBMITTING. A failure to record that does NOT report the order as failed — the order is real, and telling the caller otherwise invites the duplicate this story exists to prevent.
+AC5 (CONTROL) An ordinary first submission persists exactly once, calls the broker exactly once, and attaches the broker id exactly once. Without this, a gateway that refused everything would satisfy AC1-AC3.</t>
         </is>
       </c>
       <c r="V128" s="48" t="inlineStr">
         <is>
-          <t>BOUNDARY CORRECTED 8 Sep 2026 while delivering E15-S01. Task 1 (the sha256 formula) moved to E15-S01 and is DONE. Two reasons: LOW_LEVEL 5.7 assigns 'generates the deterministic client_order_id' to the OrderGateway, and S01 structurally cannot build an OrderRequest without one - client_order_id is a required field with min_length=8. A story cannot depend on a later story for a field its own output requires. WHAT REMAINS HERE, and it is the part with the RED acceptance criterion: task 2 (persist the id BEFORE submission) and task 3 (on ambiguous failure, query by client_order_id and never retry), plus the chaos test that a timeout and reconnect produce exactly one order. THE BUILD CONCERN IS ANSWERED, and the answer is recorded in execution/gateway.py's docstring: the discriminator that prevents a deliberate re-entry being suppressed as a duplicate already exists - it is correlation_id, which is minted per SIGNAL, not per symbol-day. Two entries into one symbol on one day are two signals with two ids and do not collide; a retry of one decision reuses its id and does, which is the idempotency the key exists for. Asserted in tests/unit/test_gateway.py rather than assumed. RESIDUAL RISK, recorded where it would bite: if correlation ids are ever reused across signals, this key silently suppresses real orders.</t>
+          <t>DELIVERED 10 Sep 2026. execution/gateway.py.
+WHAT SHIPPED: the two-transaction submission rule and query-don't-retry. TX1 records the order as SUBMITTING with a null broker_order_id BEFORE the broker call; TX2 attaches the broker id after. An AmbiguousOrderError is resolved by querying the broker by client_order_id, never by resubmitting.
+THE DESIGN DECISION WORTH REVISITING LATER: when the recovery query says the order is genuinely ABSENT, the gateway raises OrderNeverLandedError rather than resubmitting. LOW_LEVEL 8.2 says such an order 'may be resubmitted' - permission, not obligation. Chosen deliberately: if the absence determination is ever wrong (a stale orderbook read, an eventually-consistent response), an automatic retry becomes a second real position, which 8.2 itself calls the most expensive bug possible here. The cost is that a crash between TX1 and the broker call leaves that signal unsendable until reconciliation or an operator acts. A lost signal is cheaper than a duplicate position. WHAT WOULD MAKE THIS WRONG: if reconciliation (E15-S09) turns out not to adopt these rows promptly, the lost-signal cost rises and this should be revisited then.
+STRUCTURE OVER DISCIPLINE: the store is a REQUIRED constructor argument. Optional would have meant None silently skips persistence - the shape of defect this codebase keeps finding, where an absent capability reads as a satisfied one. A gateway that cannot record an order cannot be built.
+CAPABILITY CHECK PASSED THIS TIME: OrderRepository already exposed exactly insert_submitting / attach_broker_id / find_by_client_order_id, and already documented the two-transaction rule. E15-S01's equivalent check found a gap (tick_size); this one did not, and it was still worth running - the integration test then proved the dict the gateway assembles is one the real Postgres schema accepts, which no double could show.
+53 unit + 14 integration (real Postgres) + 4 SIT + 2 security probes. Mutation: 12 injected, 12 killed.</t>
         </is>
       </c>
       <c r="W128" s="49" t="n"/>
@@ -21819,7 +21831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -26392,6 +26404,117 @@
           <t>tests/security/test_safety_invariants.py::test_the_hard_cap_keeps_this_system_out_of_the_registration_regime and ::test_the_import_guard_refuses_a_cap_at_or_above_the_threshold.
 MUTATION: 10 injected, 9 killed. The first run scored 7/8 with the guard-deletion mutation SURVIVING - with the cap at 5 the guard never executes, so its condition and message were entirely unverified and a swapped operator would have been found on the one day it mattered. Fixed by extracting the guard into _assert_below_registration_threshold(cap, threshold), which is reachable by a test; deleting its body and flipping its &gt;= to &gt; are now both killed.
 ONE SURVIVOR REMAINS AND IS VERIFIED BENIGN: removing the CALL at import time. With the cap at 5 the call is a no-op, and the state it guards against is already caught in CI by the invariant test above - confirmed by M6, which raises the cap and dies on that test alone. Killing it would require asserting on module text rather than behaviour. Recorded, not chased - same shape as QA-E15-03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="150" customHeight="1" s="59">
+      <c r="A124" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-04</t>
+        </is>
+      </c>
+      <c r="B124" s="76" t="inlineStr">
+        <is>
+          <t>E15-S02</t>
+        </is>
+      </c>
+      <c r="C124" s="76" t="inlineStr">
+        <is>
+          <t>A test asserted the duplicate this story exists to prevent</t>
+        </is>
+      </c>
+      <c r="D124" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E124" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::test_the_limiter_is_consulted_once_per_submission submitted the SAME decision three times - one correlation_id, therefore one client_order_id - and asserted that THREE orders reached the broker. It passed, because before E15-S02 the gateway had no idempotency at all.</t>
+        </is>
+      </c>
+      <c r="F124" s="76" t="inlineStr">
+        <is>
+          <t>This is the SDLC regression rule 'no test may depend on a defect existing', caught the only way it can be: the defect was fixed and the test went red. Worth recording because the test was not wrong about its INTENT - three submissions should consult the limiter three times - it was wrong that three submissions of ONE decision are three orders. Corrected to three distinct signals, each with its own correlation_id, and a second test added for the other half: a suppressed duplicate must NOT spend a rate-limiter token, because tokens are the scarce resource protecting a regulatory threshold.</t>
+        </is>
+      </c>
+      <c r="G124" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::TestAc3TheRateLimiter - test_the_limiter_is_consulted_once_per_submission (corrected) and test_a_suppressed_duplicate_does_not_spend_a_token (new).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="150" customHeight="1" s="59">
+      <c r="A125" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-05</t>
+        </is>
+      </c>
+      <c r="B125" s="76" t="inlineStr">
+        <is>
+          <t>E15-S02</t>
+        </is>
+      </c>
+      <c r="C125" s="76" t="inlineStr">
+        <is>
+          <t>The story shipped with one acceptance criterion for two tasks</t>
+        </is>
+      </c>
+      <c r="D125" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E125" s="76" t="inlineStr">
+        <is>
+          <t>E15-S02 carried a single criterion: 'chaos test: timeout + reconnect produces exactly one order'. That is falsifiable, but it is an OUTCOME of the whole design rather than a description of it - it cannot be satisfied incrementally, so it cannot guide a build or localise a failure.</t>
+        </is>
+      </c>
+      <c r="F125" s="76" t="inlineStr">
+        <is>
+          <t>Five criteria were written and recorded on the story BEFORE any code, per Phase 1's exit gate and the precedent set by QA-E15-01. Writing them first is what surfaced AC1's second half - that an order which is never sent must leave NO row. That behaviour appears in no task and in no design document, and without it a rate-limiter refusal would leave a SUBMITTING row that reconciliation would hunt every 30 seconds for the rest of the day.</t>
+        </is>
+      </c>
+      <c r="G125" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py, organised one class per AC; test_a_rate_limited_order_records_nothing is the one the criteria surfaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="150" customHeight="1" s="59">
+      <c r="A126" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-06</t>
+        </is>
+      </c>
+      <c r="B126" s="76" t="inlineStr">
+        <is>
+          <t>E15-S02</t>
+        </is>
+      </c>
+      <c r="C126" s="76" t="inlineStr">
+        <is>
+          <t>A test double could not express the state it was probing</t>
+        </is>
+      </c>
+      <c r="D126" s="76" t="inlineStr">
+        <is>
+          <t>PASS (noted)</t>
+        </is>
+      </c>
+      <c r="E126" s="76" t="inlineStr">
+        <is>
+          <t>The AC3 probe for a broker record carrying no order id called landed(request, None). The double treated None as 'use the default id', so the probe silently exercised the happy path and reported DID NOT RAISE.</t>
+        </is>
+      </c>
+      <c r="F126" s="76" t="inlineStr">
+        <is>
+          <t>Recorded rather than quietly fixed, because the failure mode generalises: a double whose default and whose meaningful value are the same sentinel makes a state INEXPRESSIBLE, and a probe that cannot express its state passes for the wrong reason. Here the test failed loudly, which is the lucky case. The fix is a distinct sentinel object, documented at the double so the next person adding a case does not reintroduce it.</t>
+        </is>
+      </c>
+      <c r="G126" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::RecordingPlacer._DEFAULT_ID, and test_a_half_answer_is_not_treated_as_either_answer which now genuinely fails when the guard is removed (mutation M7, killed).</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -28547,7 +28547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -28699,6 +28699,68 @@
       <c r="L5" s="76" t="inlineStr">
         <is>
           <t>None — fixed in the same session</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1" s="59">
+      <c r="A6" s="76" t="inlineStr">
+        <is>
+          <t>SIT-002</t>
+        </is>
+      </c>
+      <c r="B6" s="76" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C6" s="76" t="inlineStr">
+        <is>
+          <t>E15-S02</t>
+        </is>
+      </c>
+      <c r="D6" s="76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E6" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py (harness)</t>
+        </is>
+      </c>
+      <c r="F6" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G6" s="76" t="inlineStr">
+        <is>
+          <t>SIT-15's replay scenario - run the day, restart, run it again against the same store - asserted that the second pass reaches the broker zero times. It failed: the second pass submitted all 316 orders again. The SYSTEM was correct; the scenario was not replaying a day, it was trading a new one.</t>
+        </is>
+      </c>
+      <c r="H6" s="76" t="inlineStr">
+        <is>
+          <t>No component test can catch it. `_recommendation()` mints a fresh correlation_id on every call, and correlation_id is the first component of the idempotency key. A single-order test builds one recommendation and reuses the object, so the trap is invisible; only a scenario that rebuilds the day's signals per run steps on it. THE PROCESS FINDING, and the reason this is logged rather than quietly fixed: this is the SECOND time the same trap has fired - SIT-14's replay test hit it on 8 Sep 2026 and was corrected in place, in the caller. Fixing the caller left the helper just as sharp for the next one.</t>
+        </is>
+      </c>
+      <c r="I6" s="76" t="inlineStr">
+        <is>
+          <t>A test helper whose default behaviour (fresh identity per call) is correct for most callers and silently wrong for replay scenarios, with nothing at the helper saying so.</t>
+        </is>
+      </c>
+      <c r="J6" s="76" t="inlineStr">
+        <is>
+          <t>SIT-15 mints the day's signals ONCE via a `_signals(session)` helper and passes the list to both runs. The docstring on `_signals` states the trap and names SIT-14 as the prior occurrence, so the warning now lives where the next caller will read it rather than in the test that happened to trip over it.</t>
+        </is>
+      </c>
+      <c r="K6" s="76" t="inlineStr">
+        <is>
+          <t>tests/sit/test_e14_trading_session.py::TestSit15ASessionThatSurvivesATimeout::test_replaying_the_whole_day_sends_nothing_the_second_time - now genuinely asserts idempotency across a restart, and fails if the duplicate check is removed (mutation M12, killed).</t>
+        </is>
+      </c>
+      <c r="L6" s="76" t="inlineStr">
+        <is>
+          <t>None - fixed in the same session</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15350,7 +15350,7 @@
       </c>
       <c r="E129" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F129" s="41" t="inlineStr">
@@ -15386,16 +15386,40 @@
       <c r="N129" s="45" t="n"/>
       <c r="O129" s="46" t="n"/>
       <c r="P129" s="46" t="n"/>
-      <c r="Q129" s="47" t="n"/>
+      <c r="Q129" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R129" s="39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S129" s="48" t="n"/>
-      <c r="T129" s="48" t="n"/>
-      <c r="U129" s="48" t="n"/>
+      <c r="T129" s="48" t="inlineStr">
+        <is>
+          <t>1. The transition table: every legal move between OrderStatus members, exhaustive over the enum
+2. Reject illegal transitions, naming both states
+3. Cross-check the table's notion of 'terminal' against OrderStatus.is_terminal at import
+4. Wire the one path that changes status today - the gateway's SUBMITTING -&gt; SUBMITTED</t>
+        </is>
+      </c>
+      <c r="U129" s="48" t="inlineStr">
+        <is>
+          <t>WRITTEN 10 Sep 2026 BEFORE any code. The story arrived with no tasks and no acceptance criteria at all - the THIRD in E15 to do so (see QA-E15-01 and QA-E15-05). Its whole specification was one sentence: 'full lifecycle per LOW_LEVEL_ARCHITECTURE 8.2 with illegal transitions rejected'.
+AC1 (RED) Every transition drawn in 8.2 is legal, and any move not in the table is refused with an error naming BOTH states. A refusal that does not say what it refused is unusable in a 03:00 incident.
+AC2 (RED) A terminal status has NO outgoing transition. An order that reached FILLED, CANCELLED or REJECTED cannot be moved to any different state - a FILLED order becoming CANCELLED would erase a position that actually exists.
+AC3 (RED) The table is EXHAUSTIVE over OrderStatus, and its notion of terminal agrees with OrderStatus.is_terminal. Both are checked at IMPORT, so a new enum member or a stray edge out of a terminal state fails to load rather than being silently treated as having no legal moves.
+AC4 Re-observing the SAME status is not a transition and does not raise. Reconciliation polls every 30 seconds (8.3) and must not error on an order that has not moved.
+AC5 (CONTROL) The ordinary lifecycle of this system's actual entry order - PENDING_RISK, APPROVED, SUBMITTING, SUBMITTED, FILLED - is legal end to end. Without this a table that rejected everything would satisfy AC1-AC3.</t>
+        </is>
+      </c>
       <c r="V129" s="48" t="inlineStr">
         <is>
-          <t>Full lifecycle per LOW_LEVEL_ARCHITECTURE §8.2 with illegal transitions rejected.</t>
+          <t>DELIVERED 10 Sep 2026. execution/order_state.py.
+WHAT SHIPPED: one frozen, READ-ONLY transition table verified at import to be exhaustive over OrderStatus and to agree with OrderStatus.is_terminal - two independent definitions of 'this order is finished' that must not drift. assert_legal refuses anything outside the table and names both states. Terminal states have an EMPTY target set, so a FILLED order cannot become CANCELLED and erase a position that exists in the market.
+THE STORY ARRIVED WITH NOTHING: no tasks, no acceptance criteria, one sentence of specification. Third in E15 to do so - see QA-E15-01, QA-E15-05, and now QA-E15-10, which records the pattern rather than the instance.
+8.2's DIAGRAM TURNED OUT TO BE THE HAPPY PATH, NOT THE TABLE. Five groups of edge are real and undrawn, the most important being SUBMITTED -&gt; FILLED and OPEN -&gt; FILLED: this system's entry order is a MARKET order and reconciliation polls every 30s, so most fills are OBSERVED complete with no partial ever seen. Requiring PARTIAL would have made the normal case illegal. LOW_LEVEL 8.2 now documents all five with reasons.
+TWO EXCLUSIONS ARE DELIBERATE AND WILL LOOK LIKE BUGS: PARTIAL -&gt; OPEN is refused even though Kite reports OPEN for a partially-filled order, because going back discards the knowledge that a fill occurred; PARTIAL -&gt; REJECTED is refused because part of the order already happened.
+RESIDUAL UNCERTAINTY, recorded in the code where it bites: whether Kite ever reports a pre-open status AFTER an order has worked could not be established without a live account. The safest branch was taken - backwards moves into SUBMITTED are refused from every later state, because that is the direction that could re-enable submission.
+91 unit + 10 seam + 8 gateway-wiring tests. Mutation: 15 injected, 14 killed; the survivor is the verifier's CALL SITE, verified benign - its logic is fully covered by three mutations that all die, and with a correct table the call changes nothing observable. Same shape as the config threshold guard.</t>
         </is>
       </c>
       <c r="W129" s="49" t="n"/>
@@ -15888,7 +15912,11 @@
       <c r="W135" s="49" t="n"/>
       <c r="X135" s="75" t="inlineStr">
         <is>
-          <t>'Broker state wins' is right. The hazard is that the unknown-position path trips the kill switch, which halts ENTRIES — but an unknown position that is real and unprotected needs more than a halt. Make the P0 alert distinguish 'unknown position exists' from 'system halted': they need different human responses within different timeframes.</t>
+          <t>'Broker state wins' is right. The hazard is that the unknown-position path trips the kill switch, which halts ENTRIES — but an unknown position that is real and unprotected needs more than a halt. Make the P0 alert distinguish 'unknown position exists' from 'system halted': they need different human responses within different timeframes.
+CONSTRAINT INHERITED FROM E15-S03 (10 Sep 2026), recorded before this story starts rather than discovered as a crash in it.
+1. THE RECONCILER MUST NOT MAP BROKER STATUS TO OUR STATUS NAIVELY. Kite's OPEN covers working AND partially-filled orders (broker/kite/mapping.py says so in its own docstring), so a poll of a PARTIAL order reports OPEN, and PARTIAL -&gt; OPEN is ILLEGAL in the transition table. Consult filled_quantity, not status alone. The refusal is deliberate: going back discards the knowledge that a fill occurred.
+2. ON ANY REFUSED TRANSITION, RECORD RECONCILE_REQUIRED. It is legal from every non-terminal state and exists for exactly this. Retrying a refused transition every 30 seconds turns a fail-closed guard into a continuous alarm, and an alarm that is always on is not read.
+3. BACKWARDS MOVES INTO SUBMITTED ARE REFUSED from OPEN, PARTIAL and RECONCILE_REQUIRED. If a live account shows Kite genuinely reporting a pre-open status after an order has worked, that is new information and the table should be revisited - not worked around at the call site.</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -26515,6 +26543,154 @@
       <c r="G126" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_gateway.py::RecordingPlacer._DEFAULT_ID, and test_a_half_answer_is_not_treated_as_either_answer which now genuinely fails when the guard is removed (mutation M7, killed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="150" customHeight="1" s="59">
+      <c r="A127" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-07</t>
+        </is>
+      </c>
+      <c r="B127" s="76" t="inlineStr">
+        <is>
+          <t>E15-S03</t>
+        </is>
+      </c>
+      <c r="C127" s="76" t="inlineStr">
+        <is>
+          <t>The unit suite agreed with the table; the broker did not</t>
+        </is>
+      </c>
+      <c r="D127" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E127" s="76" t="inlineStr">
+        <is>
+          <t>The transition table passed 91 unit tests - exhaustive over the enum, agreeing with 8.2's diagram, terminal states terminal - and still refused four transitions the broker can actually produce: SUBMITTING -&gt; OPEN, FILLED, CANCELLED and REJECTED.</t>
+        </is>
+      </c>
+      <c r="F127" s="76" t="inlineStr">
+        <is>
+          <t>THE SEAM IS WHAT FOUND IT, and nothing in the unit suite could have. Those tests know what the diagram says; they do not know what Kite is capable of saying. The four are E15-S02's recovery path: an ambiguous submission is queried, the broker reports the order it already holds - possibly already COMPLETE - while our row still says SUBMITTING because the outcome was never recorded. Without them the result of a recovered timeout could not be written down at all, which is the exact case that story exists to handle. The test enumerates the full cross-product of (our live states) x (statuses status_in can produce) and requires every refused pair to carry a written reason, so a future gap cannot be added silently.</t>
+        </is>
+      </c>
+      <c r="G127" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_order_state_seam.py - test_every_broker_report_is_legal_or_documented, and test_the_recovery_path_of_e15_s02_can_be_recorded. Mutation M12 (remove SUBMITTING -&gt; FILLED) killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="150" customHeight="1" s="59">
+      <c r="A128" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-08</t>
+        </is>
+      </c>
+      <c r="B128" s="76" t="inlineStr">
+        <is>
+          <t>E15-S03</t>
+        </is>
+      </c>
+      <c r="C128" s="76" t="inlineStr">
+        <is>
+          <t>The entire safety property could be switched off with one assignment</t>
+        </is>
+      </c>
+      <c r="D128" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E128" s="76" t="inlineStr">
+        <is>
+          <t>ALLOWED_TRANSITIONS was annotated Final[Mapping[...]] and was a plain dict at runtime. Executing ALLOWED_TRANSITIONS[OrderStatus.FILLED] = frozenset({OrderStatus.OPEN}) made a filled order movable again - no exception, no log line, and every one of the 91 tests still green.</t>
+        </is>
+      </c>
+      <c r="F128" s="76" t="inlineStr">
+        <is>
+          <t>Found by asking the STRIDE tampering question against the diff rather than by reading the file, which is the point of Phase 7. Final is enforced by mypy and by nothing at runtime, and Mapping is a structural type, not a guarantee - together they read as immutability while providing none. Fixed with MappingProxyType, which raises on assignment; the values were already frozenset, so the structure is now immutable rather than merely annotated as such. This is the structure-over-discipline ladder: 'a type annotation says so' moved up to 'the assignment fails'.</t>
+        </is>
+      </c>
+      <c r="G128" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_order_state.py::TestTheTableCannotBeSwitchedOffAtRuntime - four tests covering replace, delete, in-place extend of a target set, and a control that ordinary reads still work. Mutation M13 killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="150" customHeight="1" s="59">
+      <c r="A129" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-09</t>
+        </is>
+      </c>
+      <c r="B129" s="76" t="inlineStr">
+        <is>
+          <t>E15-S03</t>
+        </is>
+      </c>
+      <c r="C129" s="76" t="inlineStr">
+        <is>
+          <t>An existing guard caught a new test gating itself on Docker</t>
+        </is>
+      </c>
+      <c r="D129" s="76" t="inlineStr">
+        <is>
+          <t>PASS (noted)</t>
+        </is>
+      </c>
+      <c r="E129" s="76" t="inlineStr">
+        <is>
+          <t>tests/integration/test_order_state_seam.py declared the container marker while using no container fixture. test_suite_integrity.py failed the full run.</t>
+        </is>
+      </c>
+      <c r="F129" s="76" t="inlineStr">
+        <is>
+          <t>The guard was right and the author was wrong: the marker means 'needs a container', not 'is an integration test'. Marking a pure-computation module would have gated it on whether Docker happened to be running - which is precisely how the only system-level test in this repository once spent a period silently skipped while the suite reported green. Recorded because it is the first time a guard added after that incident has caught a NEW instance of it, which is the evidence that the guard was worth writing. Its one weakness: it matches file TEXT, so it also fires on prose naming the marker - the docstring is phrased around the literal. Cheap to live with; noted so the next person does not think they are going mad.</t>
+        </is>
+      </c>
+      <c r="G129" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_suite_integrity.py::test_a_module_that_needs_no_container_does_not_declare_the_marker (existing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="150" customHeight="1" s="59">
+      <c r="A130" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-10</t>
+        </is>
+      </c>
+      <c r="B130" s="76" t="inlineStr">
+        <is>
+          <t>E15 (process)</t>
+        </is>
+      </c>
+      <c r="C130" s="76" t="inlineStr">
+        <is>
+          <t>Three consecutive stories arrived with no acceptance criteria</t>
+        </is>
+      </c>
+      <c r="D130" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Process finding</t>
+        </is>
+      </c>
+      <c r="E130" s="76" t="inlineStr">
+        <is>
+          <t>E15-S01 shipped with none (QA-E15-01). E15-S02 had one criterion for two tasks (QA-E15-05). E15-S03 had no tasks and no criteria at all - its entire specification was 'full lifecycle per LOW_LEVEL_ARCHITECTURE 8.2 with illegal transitions rejected'.</t>
+        </is>
+      </c>
+      <c r="F130" s="76" t="inlineStr">
+        <is>
+          <t>Recorded as a CLASS rather than a third instance, per the rule this repository already learned about log forgery: when a defect recurs a third time, fix the class. In all three cases writing the criteria first is what surfaced the behaviour no task mentioned - for S02 it was 'an order that is never sent must leave NO row'; for S03 it was that re-observing an unchanged state must not raise, without which reconciliation would alarm every 30 seconds. Neither appears in any design document. THE PATTERN: E15's stories were written as component names with a pointer to the architecture, which is enough to build from and not enough to know when you are done. Remaining E15 stories should have criteria written at the START of their session, before any code, and the /sdlc Phase 1 gate already requires exactly that.</t>
+        </is>
+      </c>
+      <c r="G130" s="76" t="inlineStr">
+        <is>
+          <t>No test - process. Criteria for E15-S03 were written to the tracker before the first line of order_state.py.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15419,7 +15419,8 @@
 8.2's DIAGRAM TURNED OUT TO BE THE HAPPY PATH, NOT THE TABLE. Five groups of edge are real and undrawn, the most important being SUBMITTED -&gt; FILLED and OPEN -&gt; FILLED: this system's entry order is a MARKET order and reconciliation polls every 30s, so most fills are OBSERVED complete with no partial ever seen. Requiring PARTIAL would have made the normal case illegal. LOW_LEVEL 8.2 now documents all five with reasons.
 TWO EXCLUSIONS ARE DELIBERATE AND WILL LOOK LIKE BUGS: PARTIAL -&gt; OPEN is refused even though Kite reports OPEN for a partially-filled order, because going back discards the knowledge that a fill occurred; PARTIAL -&gt; REJECTED is refused because part of the order already happened.
 RESIDUAL UNCERTAINTY, recorded in the code where it bites: whether Kite ever reports a pre-open status AFTER an order has worked could not be established without a live account. The safest branch was taken - backwards moves into SUBMITTED are refused from every later state, because that is the direction that could re-enable submission.
-91 unit + 10 seam + 8 gateway-wiring tests. Mutation: 15 injected, 14 killed; the survivor is the verifier's CALL SITE, verified benign - its logic is fully covered by three mutations that all die, and with a correct table the call changes nothing observable. Same shape as the config threshold guard.</t>
+91 unit + 10 seam + 8 gateway-wiring tests. Mutation: 15 injected, 14 killed; the survivor is the verifier's CALL SITE, verified benign - its logic is fully covered by three mutations that all die, and with a correct table the call changes nothing observable. Same shape as the config threshold guard.
+SIT RUN 10 Sep 2026 against promoted QA a2aac97 then f87fac7: 143 SIT + seam tests passed, NO SIT DEFECTS. SIT-16 added - a session that restarts onto a store it did not leave, which is the realistic restart rather than a fixture. Five scenarios across a full 316-order day, including the two that carry the weight: a clean store must still trade the WHOLE day (the control - without it a gateway that refused everything passes every other scenario), and a half-poisoned store must trade exactly the clean half, which is what would catch an off-by-one in the refusal.</t>
         </is>
       </c>
       <c r="W129" s="49" t="n"/>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15448,7 +15448,7 @@
       </c>
       <c r="E130" s="40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QA-Success</t>
         </is>
       </c>
       <c r="F130" s="41" t="inlineStr">
@@ -15484,7 +15484,9 @@
       <c r="N130" s="45" t="n"/>
       <c r="O130" s="46" t="n"/>
       <c r="P130" s="46" t="n"/>
-      <c r="Q130" s="47" t="n"/>
+      <c r="Q130" s="47" t="n">
+        <v>100</v>
+      </c>
       <c r="R130" s="39" t="n">
         <v>4</v>
       </c>
@@ -15503,10 +15505,31 @@
       </c>
       <c r="U130" s="48" t="inlineStr">
         <is>
-          <t>• 🔴 A position without a live stop cannot persist for more than one cycle</t>
-        </is>
-      </c>
-      <c r="V130" s="48" t="n"/>
+          <t>EXPANDED 11 Sep 2026 BEFORE any code. The story had ONE criterion - 'a position without a live stop cannot persist for more than one cycle' - which is the right property and is not buildable as stated: 'one cycle' belongs to the reconciliation loop, which is E15-S09 and does not exist. The criteria below split it into the part that binds NOW (the placement sequence and its failure response) and the part E15-S09 inherits (the predicate it must call).
+AC1 (RED) A filled entry gets a protective stop placed immediately: opposite side, full quantity, at the position's stop_price, as SL-M so it cannot fail to fill in a fast move.
+AC2 (RED) If the stop cannot be established - refused, ambiguous, or verified not-live - the position is closed at MARKET in the same call, before returning. The emergency close is attempted even when the stop's outcome is UNKNOWN, because an unknown stop is not a stop.
+AC3 (RED) The position is not reported established until the stop is verified LIVE at the broker. A stop the broker accepted and does not list counts as not live: acceptance is not liveness.
+AC4 (RED) If the emergency close ALSO fails, the session HALTS. A naked position that cannot be closed is not a trade-level problem, and the system must stop opening new ones rather than continue and hope.
+AC5 Every stop failure is logged at CRITICAL and counted, so a naked position is visible without querying a database.
+AC6 The predicate E15-S09 will call detects a position whose stop was accepted and LATER rejected or cancelled - the asynchronous case the build concern names, which no synchronous check can see.
+AC7 (CONTROL) A healthy entry produces exactly ONE stop order, no emergency close, no halt, and reports established. Without this, an implementation that closed every position immediately would satisfy AC2-AC5.</t>
+        </is>
+      </c>
+      <c r="V130" s="48" t="inlineStr">
+        <is>
+          <t>SCOPE BOUNDARY, written 11 Sep 2026 before starting.
+IN: build and submit the protective stop through the gateway (which 5.7 makes the only path to an order); verify it is live; on any failure close at market; on a failed close, halt; the predicate E15-S09 calls; CRITICAL log and metric.
+OUT, and each has a home: the FILL-CONFIRMATION TRIGGER that calls this belongs to E15-S05 (position manager); the RECONCILIATION CYCLE that calls the predicate every 30s is E15-S09; ALERT TRANSPORT is E14-S12, which needs credentials; TRAILING stops are E15-S08.
+CAPABILITY CHECK, run before designing rather than after: positions has stop_price NOT NULL (BR-1) but NO column for the stop ORDER's id - so nothing records WHICH order protects a position, and the async-rejection case the build concern names would have had nothing to look up. A migration is NOT needed: the stop order's client_order_id is DETERMINISTICALLY derivable from the position's correlation_id via 8.2's hash with intent=STOP, and find_by_client_order_id already exists on both the repository and the broker adapter. Verified by computing both ids and confirming they differ from the entry's.
+DELIVERED 11 Sep 2026. execution/protective_stop.py.
+THE SEQUENCE: place -&gt; verify -&gt; on any failure exit -&gt; on a failed exit halt. The only way to obtain an EstablishedPosition is to come out of the good end of it, so a caller cannot hold one for an unprotected position - 'is this position safe to keep?' stops being a question anyone has to remember to ask. A contained failure does NOT halt the day; one bad symbol must not stop trading. A failure to EXIT arms HaltReason.NAKED_POSITION, which is a new member rather than the nearest plausible neighbour (UNKNOWN_POSITION means the broker reports a position we have no record of - a different fact).
+NO MIGRATION WAS NEEDED, and the capability check is what established that: positions has no column naming the stop order, but the stop's client_order_id is derivable from the position's correlation_id via 8.2's hash with intent=STOP. Reconciliation can therefore find a stop it never saw placed.
+THE GATEWAY WAS REFACTORED rather than copied: submit_entry, submit_stop and submit_exit now share one submit(), so the stop inherits idempotency, TX1/TX2 and query-don't-retry. That matters more for a stop than for an entry - two stops on one position is two exits, and the second sells something that no longer exists.
+THE TICK RESOLVER BECAME LOAD-BEARING HERE. The entry is MARKET and needs no grid; the stop carries a trigger price, and the adapter refuses every priced order without a resolver. E15-S01 wired and tested it in isolation and nothing in the trading path used it until now. A deployment that forgot the wiring would have rejected every stop - which, before this story, meant a naked position per entry, silently. There is now an integration test for exactly that misconfiguration, and it ends in a closed position rather than a naked one.
+A PROPERTY WORTH KNOWING: round_to_tick was written for limit ENTRIES ('never pay more than intended') and happens to mean 'never risk more than budgeted' for stops - it tightens on both sides, never widens. A happy accident, therefore exactly the kind of thing someone later 'fixes', so it is locked down by test.
+48 unit + 10 integration (real Postgres). Mutation: 17 injected, 17 killed - after two survivors exposed test defects, both recorded.</t>
+        </is>
+      </c>
       <c r="W130" s="49" t="n"/>
       <c r="X130" s="75" t="inlineStr">
         <is>
@@ -15589,6 +15612,14 @@
       <c r="U131" s="48" t="n"/>
       <c r="V131" s="48" t="n"/>
       <c r="W131" s="49" t="n"/>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>CONSTRAINT INHERITED FROM E15-S04 (11 Sep 2026).
+1. THIS STORY OWNS THE FILL-CONFIRMATION TRIGGER that calls ProtectiveStop.attach. Until it exists, nothing calls the protective stop and an entry can still fill unprotected - the mechanism is built and unwired.
+2. ATTACH VERIFIES THE EXIT IS LIVE, NOT THAT IT FILLED. Confirming the fill of an emergency exit is this story's job; the strongest claim available without a fill feed is 'a live exit exists for the whole position'. Do not read the CRITICAL log line as proof of a flat book.
+3. A POSITION IS ONLY ESTABLISHED IF YOU HOLD AN EstablishedPosition. Do not reconstruct one from a database row: the row's stop_price is populated whether or not any order is protecting it.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="30" customHeight="1" s="59">
       <c r="A132" s="38" t="inlineStr">
@@ -15917,7 +15948,10 @@
 CONSTRAINT INHERITED FROM E15-S03 (10 Sep 2026), recorded before this story starts rather than discovered as a crash in it.
 1. THE RECONCILER MUST NOT MAP BROKER STATUS TO OUR STATUS NAIVELY. Kite's OPEN covers working AND partially-filled orders (broker/kite/mapping.py says so in its own docstring), so a poll of a PARTIAL order reports OPEN, and PARTIAL -&gt; OPEN is ILLEGAL in the transition table. Consult filled_quantity, not status alone. The refusal is deliberate: going back discards the knowledge that a fill occurred.
 2. ON ANY REFUSED TRANSITION, RECORD RECONCILE_REQUIRED. It is legal from every non-terminal state and exists for exactly this. Retrying a refused transition every 30 seconds turns a fail-closed guard into a continuous alarm, and an alarm that is always on is not read.
-3. BACKWARDS MOVES INTO SUBMITTED ARE REFUSED from OPEN, PARTIAL and RECONCILE_REQUIRED. If a live account shows Kite genuinely reporting a pre-open status after an order has worked, that is new information and the table should be revisited - not worked around at the call site.</t>
+3. BACKWARDS MOVES INTO SUBMITTED ARE REFUSED from OPEN, PARTIAL and RECONCILE_REQUIRED. If a live account shows Kite genuinely reporting a pre-open status after an order has worked, that is new information and the table should be revisited - not worked around at the call site.
+CONSTRAINT INHERITED FROM E15-S04 (11 Sep 2026), in addition to the E15-S03 constraints above.
+4. THE LOOP MUST CALL ProtectiveStop.is_protected FOR EVERY OPEN POSITION, every cycle. That predicate is the ONLY thing that catches a stop which was accepted, verified live at attach time, and rejected a second later - the asynchronous case E15-S04's build concern names, which no synchronous check can reach. E15-S04 delivers the predicate and deliberately does not deliver the loop; without this the story's acceptance criterion ('cannot persist for more than one cycle') is only half met.
+5. AN UNPROTECTED POSITION FOUND BY THE LOOP TAKES THE SAME PATH AS ONE FOUND AT ATTACH TIME: exit at market, and halt if the exit fails. Do not invent a second policy for it.</t>
         </is>
       </c>
     </row>
@@ -21860,7 +21894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -26692,6 +26726,117 @@
       <c r="G130" s="76" t="inlineStr">
         <is>
           <t>No test - process. Criteria for E15-S03 were written to the tracker before the first line of order_state.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="150" customHeight="1" s="59">
+      <c r="A131" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-11</t>
+        </is>
+      </c>
+      <c r="B131" s="76" t="inlineStr">
+        <is>
+          <t>E15-S04</t>
+        </is>
+      </c>
+      <c r="C131" s="76" t="inlineStr">
+        <is>
+          <t>The module trusted the emergency exit on acceptance - its own defect, one step along</t>
+        </is>
+      </c>
+      <c r="D131" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E131" s="76" t="inlineStr">
+        <is>
+          <t>protective_stop.py verifies that the STOP is live at the broker before calling a position protected, on the explicit principle that acceptance is not liveness. The emergency exit in the same file was then trusted on acceptance alone: submit_exit returning was treated as the position being closed, and the CRITICAL log line said 'closed at market' having verified nothing.</t>
+        </is>
+      </c>
+      <c r="F131" s="76" t="inlineStr">
+        <is>
+          <t>Found by running the STRIDE pass against this story's own diff rather than against the code it touched - Phase 7 asked 'can a value change between write and read', and the answer pointed at the exit. WHY IT MATTERS MORE THAN THE STOP: the exit is the only thing standing between a naked position and the square-off deadline; a stop that fails has the exit behind it, and an exit that fails has nothing. THE LESSON, which is the fourth variation of it in this codebase: applying a rule to the case you were thinking about does not apply it to the case one step further along. The exit is now verified through the same is_live() the stop uses, and a non-live exit halts.</t>
+        </is>
+      </c>
+      <c r="G131" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_protective_stop.py::test_an_exit_the_broker_will_not_list_also_halts and ::test_a_rejected_exit_halts. Mutation M7 (trust the exit on acceptance) killed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="150" customHeight="1" s="59">
+      <c r="A132" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-12</t>
+        </is>
+      </c>
+      <c r="B132" s="76" t="inlineStr">
+        <is>
+          <t>E15-S04</t>
+        </is>
+      </c>
+      <c r="C132" s="76" t="inlineStr">
+        <is>
+          <t>A test double that computed its answer with the function under test</t>
+        </is>
+      </c>
+      <c r="D132" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E132" s="76" t="inlineStr">
+        <is>
+          <t>Two mutations survived the first run. M12 flipped the side inside stop_client_order_id - which would place the stop on the SAME side as the position, doubling it instead of protecting it - and every unit test passed. M16 halved the exit quantity and every unit test passed.</t>
+        </is>
+      </c>
+      <c r="F132" s="76" t="inlineStr">
+        <is>
+          <t>ONE ROOT CAUSE FOR BOTH: the double answered using the code under test. FakeGateway listed the stop in its orderbook under stop_client_order_id(...), the same helper the attacher then looked it up with, so an error in it cancelled out perfectly. And the double recorded the POSITION handed to submit_exit rather than the ORDER built from it, so the builder was never observed at all. The integration tests did catch M12, because there the key is built by the real gateway and looked up through the real adapter - which is precisely the difference between the two tiers. FIXED at the double: it now derives both the key and the exit order through the real gateway builders, so production code is on the answering side. THE GENERAL FORM, and it is a new one for this repository's catalogue: a double that shares an implementation with the system under test is not an oracle - it agrees by construction, exactly like a component tested against its own fixtures.</t>
+        </is>
+      </c>
+      <c r="G132" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_protective_stop.py::FakeGateway (now uses _real_gateway().build_stop / build_exit) plus ::test_the_exit_closes_the_whole_position and ::test_the_exit_is_a_market_order_on_the_opposite_side. M12 and M16 both killed on re-run; final score 17/17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="150" customHeight="1" s="59">
+      <c r="A133" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-13</t>
+        </is>
+      </c>
+      <c r="B133" s="76" t="inlineStr">
+        <is>
+          <t>E15-S04</t>
+        </is>
+      </c>
+      <c r="C133" s="76" t="inlineStr">
+        <is>
+          <t>Two counters were read by name and existed nowhere</t>
+        </is>
+      </c>
+      <c r="D133" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E133" s="76" t="inlineStr">
+        <is>
+          <t>ProtectiveStop._count reads its counter with getattr and returns quietly when it is absent - deliberate, so a metrics outage cannot worsen a naked-position failure. Against the REAL Metrics class both stop_attach_failures_total and naked_positions_total were absent, so AC5's 'visible without querying a database' was satisfied by a double and by nothing else.</t>
+        </is>
+      </c>
+      <c r="F133" s="76" t="inlineStr">
+        <is>
+          <t>The same shape as the two exposure caps that sat in system.yaml binding on nothing, and as the special-sessions flag nothing read: the tolerant lookup that makes the code robust is the same lookup that makes the gap invisible. Caught by asking what the getattr would find in production, not by a failing test - there was no failing test to have. Both counters are now registered, with separate names on purpose: a contained stop failure is a bad trade, a naked position is an incident, and one counter would let the second hide in the first's noise.</t>
+        </is>
+      </c>
+      <c r="G133" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_protective_stop.py::TestTheCountersExistOnTheRealMetrics - asserts against the real registry's collected samples rather than a double.</t>
         </is>
       </c>
     </row>

--- a/Documents/BACKLOG_Tracker.xlsx
+++ b/Documents/BACKLOG_Tracker.xlsx
@@ -15527,7 +15527,9 @@
 THE GATEWAY WAS REFACTORED rather than copied: submit_entry, submit_stop and submit_exit now share one submit(), so the stop inherits idempotency, TX1/TX2 and query-don't-retry. That matters more for a stop than for an entry - two stops on one position is two exits, and the second sells something that no longer exists.
 THE TICK RESOLVER BECAME LOAD-BEARING HERE. The entry is MARKET and needs no grid; the stop carries a trigger price, and the adapter refuses every priced order without a resolver. E15-S01 wired and tested it in isolation and nothing in the trading path used it until now. A deployment that forgot the wiring would have rejected every stop - which, before this story, meant a naked position per entry, silently. There is now an integration test for exactly that misconfiguration, and it ends in a closed position rather than a naked one.
 A PROPERTY WORTH KNOWING: round_to_tick was written for limit ENTRIES ('never pay more than intended') and happens to mean 'never risk more than budgeted' for stops - it tightens on both sides, never widens. A happy accident, therefore exactly the kind of thing someone later 'fixes', so it is locked down by test.
-48 unit + 10 integration (real Postgres). Mutation: 17 injected, 17 killed - after two survivors exposed test defects, both recorded.</t>
+48 unit + 10 integration (real Postgres). Mutation: 17 injected, 17 killed - after two survivors exposed test defects, both recorded.
+SIT (SIT-17, 11 Sep 2026): 11 scenarios, all passing. A day of 316 fills yields 316 live stops and no exits; a day on which every stop is refused ends with nothing open, 316 market exits and the session STILL TRADING (a contained failure must not stop the day - a claim about 316 failures, which no component test makes); a day on which the exits fail too arms NAKED_POSITION and the next session approves nothing, which needs the real halt latch and the real risk engine in one test; a restart re-derives all 316 stop keys and places nothing. SIT-17 also walks is_protected across the book and finds EXACTLY the one stop that was rejected after being verified - the asynchronous case, and the predicate E15-S09 must call.
+SIT FOUND ONE DEFECT, SIT-003 (HIGH), fixed in the same session: an order the broker REFUSED was recorded, permanently, as in flight, and its reason code was discarded. Not E15-S04's code - the gateway's - but only reachable in volume through this story, because the protective stop is the first order the broker is ever asked to refuse en masse.</t>
         </is>
       </c>
       <c r="W130" s="49" t="n"/>
@@ -15951,7 +15953,10 @@
 3. BACKWARDS MOVES INTO SUBMITTED ARE REFUSED from OPEN, PARTIAL and RECONCILE_REQUIRED. If a live account shows Kite genuinely reporting a pre-open status after an order has worked, that is new information and the table should be revisited - not worked around at the call site.
 CONSTRAINT INHERITED FROM E15-S04 (11 Sep 2026), in addition to the E15-S03 constraints above.
 4. THE LOOP MUST CALL ProtectiveStop.is_protected FOR EVERY OPEN POSITION, every cycle. That predicate is the ONLY thing that catches a stop which was accepted, verified live at attach time, and rejected a second later - the asynchronous case E15-S04's build concern names, which no synchronous check can reach. E15-S04 delivers the predicate and deliberately does not deliver the loop; without this the story's acceptance criterion ('cannot persist for more than one cycle') is only half met.
-5. AN UNPROTECTED POSITION FOUND BY THE LOOP TAKES THE SAME PATH AS ONE FOUND AT ATTACH TIME: exit at market, and halt if the exit fails. Do not invent a second policy for it.</t>
+5. AN UNPROTECTED POSITION FOUND BY THE LOOP TAKES THE SAME PATH AS ONE FOUND AT ATTACH TIME: exit at market, and halt if the exit fails. Do not invent a second policy for it.
+CONSTRAINT INHERITED FROM SIT-003 (11 Sep 2026).
+6. SUBMIT_FAILED IS MODELLED AND NOTHING WRITES IT. order_state.py gives it a legal incoming edge from SUBMITTING and an outgoing edge to RECONCILE_REQUIRED, and no code path in src/ has ever produced it. It belongs to THIS story: a submission that failed in a way the broker did not refuse is exactly what reconciliation has to resolve. SIT-003 fixed the sibling case (an outright rejection now writes REJECTED); do not assume this one was fixed with it.
+7. A ROW IN SUBMITTING MEANS WE DO NOT KNOW, AND THAT IS NOW LOAD-BEARING. Since SIT-003 a refusal writes REJECTED, so a SUBMITTING row no longer conflates the refused case with the unknown one. Query it; do not treat it as failed.</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="59" min="1" max="1"/>
@@ -26837,6 +26842,43 @@
       <c r="G133" s="76" t="inlineStr">
         <is>
           <t>tests/unit/test_protective_stop.py::TestTheCountersExistOnTheRealMetrics - asserts against the real registry's collected samples rather than a double.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="150" customHeight="1" s="59">
+      <c r="A134" s="76" t="inlineStr">
+        <is>
+          <t>QA-E15-14</t>
+        </is>
+      </c>
+      <c r="B134" s="76" t="inlineStr">
+        <is>
+          <t>E15-S04</t>
+        </is>
+      </c>
+      <c r="C134" s="76" t="inlineStr">
+        <is>
+          <t>The order state machine modelled two states nothing could ever write</t>
+        </is>
+      </c>
+      <c r="D134" s="76" t="inlineStr">
+        <is>
+          <t>FAIL -&gt; Fixed</t>
+        </is>
+      </c>
+      <c r="E134" s="76" t="inlineStr">
+        <is>
+          <t>OrderStatus has REJECTED and SUBMIT_FAILED; order_state.py gives both legal incoming edges and E15-S03's _resume docstring reasons explicitly about 'a row recorded REJECTED or CANCELLED'. A grep of src/ for writes of either found none: the only mentions were the enum definition and the transition table.</t>
+        </is>
+      </c>
+      <c r="F134" s="76" t="inlineStr">
+        <is>
+          <t>Found while tracing SIT-003 rather than by a failing test - there was none to have. The state machine was verified for internal consistency (E15-S03's _verify_table checks exhaustiveness, self-edges and terminal states) and that verification cannot see whether any state is REACHABLE, because reachability is a property of the callers, not the table. THE GENERAL FORM, and it is the third variation in this repository: a structure can be complete and correct and still describe something the system never does. REJECTED is now written by the gateway; SUBMIT_FAILED remains unwritten and that is recorded on E15-S09, which owns the reconciliation path that would produce it.</t>
+        </is>
+      </c>
+      <c r="G134" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::TestARefusedOrderIsRecordedAsRefused::test_a_refused_order_is_terminal_and_is_never_resubmitted</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="59" min="1" max="1"/>
@@ -29081,6 +29123,68 @@
         </is>
       </c>
       <c r="L6" s="76" t="inlineStr">
+        <is>
+          <t>None - fixed in the same session</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="210" customHeight="1" s="59">
+      <c r="A7" s="76" t="inlineStr">
+        <is>
+          <t>SIT-003</t>
+        </is>
+      </c>
+      <c r="B7" s="76" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="inlineStr">
+        <is>
+          <t>E15-S04</t>
+        </is>
+      </c>
+      <c r="D7" s="76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E7" s="76" t="inlineStr">
+        <is>
+          <t>execution/gateway.py, common/db/repositories.py</t>
+        </is>
+      </c>
+      <c r="F7" s="76" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G7" s="76" t="inlineStr">
+        <is>
+          <t>SIT-17 ran a whole session in which the broker refused every protective stop. Every position was exited correctly, every exception was the right one, and no test failed. The store finished the day holding 316 rows with status SUBMITTING - 'this order is in flight' - for orders the broker had definitively REJECTED. The broker's reason code went into an exception message and nowhere durable, past an orders.rejection_reason column that has existed since the first migration and that nothing has ever written.</t>
+        </is>
+      </c>
+      <c r="H7" s="76" t="inlineStr">
+        <is>
+          <t>BECAUSE THE DEFECT IS IN WHAT THE DAY LEAVES BEHIND, NOT IN WHAT IT DOES. Every observable action was correct, so a test that asserts behaviour sees nothing wrong. There WAS a unit test for this exact input - test_an_outright_rejection_is_not_treated_as_ambiguous - and it asserted 'placer.find_calls == []': what must NOT happen. It never asked what DID happen to the row. That is the general shape: a test written to pin down a negative leaves the positive unobserved, and the state left behind is invisible until something later reads it. SIT reads it, because SIT is the only tier that runs a whole day and then looks at the record.</t>
+        </is>
+      </c>
+      <c r="I7" s="76" t="inlineStr">
+        <is>
+          <t>TX1 writes SUBMITTING before place_order, and submit() caught only AmbiguousOrderError. OrderRejectedError propagated with the row untouched. The consequence is not confined to a stale row: open_orders() is documented as 'the reconciliation working set', selecting everything not in (FILLED, CANCELLED, REJECTED) - so a refused order sits in that set for the rest of the day and reconciliation (S8.3, E15-S09) would query a broker that has never heard of it, every 30 seconds, forever. Underneath: OrderStatus models REJECTED and SUBMIT_FAILED, order_state.py gives both legal edges, and NO code path in src/ ever wrote either. The state machine had states that could be read and never reached - the same shape as the exposure caps that were configured and bound nothing.</t>
+        </is>
+      </c>
+      <c r="J7" s="76" t="inlineStr">
+        <is>
+          <t>submit() now catches OrderRejectedError, calls _reject(), and re-raises. _reject writes status=REJECTED plus the sanitised reason via a new OrderStore.mark_rejected, and NEVER raises: a persistence failure must not replace the broker's rejection with 'the database is down', and the row it leaves in SUBMITTING is exactly the prior behaviour. Deliberately NOT except Exception: SUBMITTING means 'we do not know whether it landed', which is the truth for an unmodelled error and the reason S8.2's query path exists. Only a documented refusal is a known outcome. No migration - the column was already there. A retry now meets a terminal REJECTED row and is refused by the state machine (IllegalTransitionError) rather than reported as OrderNeverLandedError, which had been saying 'it never landed' about an order that landed and was refused.</t>
+        </is>
+      </c>
+      <c r="K7" s="76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_gateway.py::TestARefusedOrderIsRecordedAsRefused (6, including two controls: an unmodelled failure still leaves SUBMITTING, and the ordinary path records no rejection); tests/integration/test_repositories.py::test_a_refused_order_is_recorded_with_the_brokers_reason and ::test_a_refused_order_leaves_the_reconciliation_working_set (real Postgres); tests/sit/...::test_a_day_of_refused_stops_leaves_no_row_claiming_to_be_in_flight. Mutation: 9 injected, 9 killed.</t>
+        </is>
+      </c>
+      <c r="L7" s="76" t="inlineStr">
         <is>
           <t>None - fixed in the same session</t>
         </is>
